--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD43C47-8A4E-45B5-8051-FB48F86493A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 普通场 
@@ -48,25 +42,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单位：分（换成元则除100)</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="2">
+    <comment ref="J1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -76,6 +72,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数
@@ -85,15 +82,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>扩大单线押分值100倍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>最大押分值*10000</t>
         </r>
       </text>
     </comment>
@@ -102,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -140,18 +151,15 @@
     <t>默认押分</t>
   </si>
   <si>
+    <t>初始化标准池</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
-    <t>gameId</t>
-  </si>
-  <si>
     <t>roomName</t>
   </si>
   <si>
@@ -179,26 +187,44 @@
     <t>defaultBet</t>
   </si>
   <si>
+    <t>initBasePool</t>
+  </si>
+  <si>
     <t>美元快递</t>
   </si>
   <si>
-    <t>20000:40000:60000:80000:100000:200000:1000000:2000000:4000000:6000000:10000000:20000000:40000000:60000000:100000000:120000000:150000000:200000000:300000000:400000000:600000000:1000000000:1200000000</t>
+    <t>100:200:300:400:500:1000:2000:3000:4000:5000</t>
   </si>
   <si>
     <t>40000:1</t>
+  </si>
+  <si>
+    <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
+  </si>
+  <si>
+    <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,168 +261,47 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,25 +310,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799340800195319"/>
+        <fgColor theme="7" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799340800195319"/>
+        <fgColor theme="9" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor theme="5" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,194 +338,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -643,258 +362,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -902,16 +379,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -932,63 +409,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1273,23 +727,25 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="5" max="5" width="21.75" customWidth="1"/>
     <col min="8" max="8" width="21.875" customWidth="1"/>
     <col min="9" max="9" width="13.125" customWidth="1"/>
     <col min="10" max="10" width="14.875" customWidth="1"/>
     <col min="11" max="11" width="17.375" customWidth="1"/>
     <col min="12" max="12" width="17.625" customWidth="1"/>
+    <col min="13" max="13" width="35.875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="17.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1326,26 +782,29 @@
       <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="15" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
-        <v>13</v>
+      <c r="D2" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>14</v>
@@ -1357,12 +816,14 @@
         <v>14</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="12"/>
+      <c r="M2" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
@@ -1376,42 +837,44 @@
       <c r="X2" s="12"/>
       <c r="Y2" s="12"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="3" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>15</v>
+      <c r="B3" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="K3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="L3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="M3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
@@ -1425,7 +888,7 @@
       <c r="X3" s="12"/>
       <c r="Y3" s="12"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="4" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -1438,7 +901,7 @@
       <c r="J4" s="10"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
+      <c r="M4" s="17"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
@@ -1452,7 +915,7 @@
       <c r="X4" s="12"/>
       <c r="Y4" s="12"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -1489,7 +952,9 @@
       <c r="L5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="12"/>
+      <c r="M5" s="17">
+        <v>50000000</v>
+      </c>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
@@ -1503,7 +968,7 @@
       <c r="X5" s="12"/>
       <c r="Y5" s="12"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -1526,7 +991,7 @@
         <v>500000</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I6" s="12">
         <v>1</v>
@@ -1540,7 +1005,9 @@
       <c r="L6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="12"/>
+      <c r="M6" s="17">
+        <v>5000000000</v>
+      </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
@@ -1554,7 +1021,7 @@
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:25">
+    <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -1577,7 +1044,7 @@
         <v>5000000</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I7" s="12">
         <v>1</v>
@@ -1591,7 +1058,9 @@
       <c r="L7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="12"/>
+      <c r="M7" s="18">
+        <v>500000000000</v>
+      </c>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
@@ -1605,9 +1074,12 @@
       <c r="X7" s="12"/>
       <c r="Y7" s="12"/>
     </row>
+    <row r="8" spans="1:25" ht="16.5">
+      <c r="M8" s="17"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD43C47-8A4E-45B5-8051-FB48F86493A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AC29E6-B26B-400C-B01E-3F39EA93B73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,8 @@
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
     <author/>
+    <author>Microsoft Office User</author>
+    <author>vidisJW</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -108,12 +110,78 @@
         </r>
       </text>
     </comment>
+    <comment ref="P1" authorId="3" shapeId="0" xr:uid="{52892340-87D9-43E2-8D79-C15E5ADE7FD7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Microsoft Office User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+适用房间外部的总累计奖池计算
+当 (总假奖池金额 - 总真奖池金额)  &gt; 当前大于X 时，押注抽水进入假奖池比例为Y，反之进入假奖池比例为Z
+格式 { X , Y , Z}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{17FCAE84-13E8-4B12-8303-E0517118BE4D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>vidisJW:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值需要除以1万
+每次押注，将万分比的金额存入不同奖池
+每X秒同步一次奖池变化，客户端每秒改变一次金额Y，变化值为金额Y/X</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -200,9 +268,6 @@
   </si>
   <si>
     <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
-  </si>
-  <si>
-    <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
   </si>
   <si>
     <t>long</t>
@@ -214,6 +279,52 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000:1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000000:1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>押注进入标准池万分比</t>
+  </si>
+  <si>
+    <t>假总奖池金额</t>
+  </si>
+  <si>
+    <t>假累计奖池部分进入比率</t>
+  </si>
+  <si>
+    <t>实际押注抽水入奖池万分比</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{,}</t>
+  </si>
+  <si>
+    <t>initBasePoolProportion</t>
+  </si>
+  <si>
+    <t>fakePool</t>
+  </si>
+  <si>
+    <t>fakeCommissionProp</t>
+  </si>
+  <si>
+    <t>commissionProp</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>long</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -221,10 +332,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,29 +347,34 @@
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -300,8 +417,74 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,8 +521,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -362,16 +551,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -415,23 +622,53 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="百分比" xfId="2" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
@@ -733,19 +970,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="5" max="5" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="21.875" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.25" customWidth="1"/>
     <col min="9" max="9" width="13.125" customWidth="1"/>
     <col min="10" max="10" width="14.875" customWidth="1"/>
-    <col min="11" max="11" width="17.375" customWidth="1"/>
-    <col min="12" max="12" width="17.625" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="14" style="23" customWidth="1"/>
     <col min="13" max="13" width="35.875" style="19" customWidth="1"/>
+    <col min="14" max="14" width="21.25" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="20.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="17.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -779,11 +1022,23 @@
       <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="21" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="15" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="2" customFormat="1" ht="16.5">
@@ -795,7 +1050,7 @@
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>14</v>
@@ -818,16 +1073,24 @@
       <c r="K2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="R2" s="12"/>
       <c r="S2" s="10"/>
       <c r="T2" s="10"/>
@@ -842,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
@@ -869,16 +1132,24 @@
       <c r="K3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="22" t="s">
         <v>23</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="R3" s="12"/>
       <c r="S3" s="10"/>
       <c r="T3" s="10"/>
@@ -900,12 +1171,10 @@
       <c r="I4" s="12"/>
       <c r="J4" s="10"/>
       <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="L4" s="22"/>
       <c r="M4" s="17"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="10"/>
       <c r="T4" s="10"/>
@@ -916,8 +1185,8 @@
       <c r="Y4" s="12"/>
     </row>
     <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A5" s="7">
-        <v>1</v>
+      <c r="A5">
+        <v>10010001</v>
       </c>
       <c r="B5" s="8">
         <v>100100</v>
@@ -949,16 +1218,24 @@
       <c r="K5" s="12">
         <v>100</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>27</v>
+      <c r="L5" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="M5" s="17">
         <v>50000000</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
+      <c r="N5" s="12">
+        <v>9600</v>
+      </c>
+      <c r="O5" s="12">
+        <v>500000</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="28">
+        <v>100</v>
+      </c>
       <c r="R5" s="12"/>
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
@@ -969,8 +1246,8 @@
       <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A6" s="7">
-        <v>2</v>
+      <c r="A6">
+        <v>10010002</v>
       </c>
       <c r="B6" s="8">
         <v>100100</v>
@@ -1002,16 +1279,24 @@
       <c r="K6" s="12">
         <v>100</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="22" t="s">
         <v>27</v>
       </c>
       <c r="M6" s="17">
         <v>5000000000</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
+      <c r="N6" s="12">
+        <v>9600</v>
+      </c>
+      <c r="O6" s="12">
+        <v>50000000</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="28">
+        <v>100</v>
+      </c>
       <c r="R6" s="12"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
@@ -1022,8 +1307,8 @@
       <c r="Y6" s="12"/>
     </row>
     <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A7" s="7">
-        <v>3</v>
+      <c r="A7">
+        <v>10010003</v>
       </c>
       <c r="B7" s="8">
         <v>100100</v>
@@ -1043,8 +1328,8 @@
       <c r="G7" s="8">
         <v>5000000</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>29</v>
+      <c r="H7" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="I7" s="12">
         <v>1</v>
@@ -1055,16 +1340,24 @@
       <c r="K7" s="12">
         <v>100</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>27</v>
+      <c r="L7" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="M7" s="18">
         <v>500000000000</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
+      <c r="N7" s="12">
+        <v>9600</v>
+      </c>
+      <c r="O7" s="12">
+        <v>5000000000</v>
+      </c>
+      <c r="P7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="28">
+        <v>100</v>
+      </c>
       <c r="R7" s="12"/>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
@@ -1076,10 +1369,25 @@
     </row>
     <row r="8" spans="1:25" ht="16.5">
       <c r="M8" s="17"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="P11" s="29"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="P12" s="29"/>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="P13" s="29"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="P14" s="29"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AC29E6-B26B-400C-B01E-3F39EA93B73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E10BF6-086F-4289-ABFB-DA3A81E2C652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="30390" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E10BF6-086F-4289-ABFB-DA3A81E2C652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9F910C-F3F7-4EC5-B029-A9A2A00B9A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30390" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30165" yWindow="2025" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -578,7 +578,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -666,6 +666,9 @@
     </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="百分比" xfId="2" builtinId="5"/>
@@ -1185,8 +1188,8 @@
       <c r="Y4" s="12"/>
     </row>
     <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A5">
-        <v>10010001</v>
+      <c r="A5" s="31">
+        <v>1001001</v>
       </c>
       <c r="B5" s="8">
         <v>100100</v>
@@ -1246,8 +1249,8 @@
       <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A6">
-        <v>10010002</v>
+      <c r="A6" s="31">
+        <v>1001002</v>
       </c>
       <c r="B6" s="8">
         <v>100100</v>
@@ -1307,8 +1310,8 @@
       <c r="Y6" s="12"/>
     </row>
     <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A7">
-        <v>10010003</v>
+      <c r="A7" s="31">
+        <v>1001003</v>
       </c>
       <c r="B7" s="8">
         <v>100100</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9F910C-F3F7-4EC5-B029-A9A2A00B9A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E5D37A-F2AD-409A-8C7A-BA289EDAC2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30165" yWindow="2025" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -84,20 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>扩大单线押分值100倍</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -110,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="3" shapeId="0" xr:uid="{52892340-87D9-43E2-8D79-C15E5ADE7FD7}">
+    <comment ref="O1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{17FCAE84-13E8-4B12-8303-E0517118BE4D}">
+    <comment ref="P1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -181,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -213,21 +200,39 @@
     <t>线注倍数</t>
   </si>
   <si>
-    <t>押分系数</t>
-  </si>
-  <si>
     <t>默认押分</t>
   </si>
   <si>
     <t>初始化标准池</t>
   </si>
   <si>
+    <t>押注进入标准池万分比</t>
+  </si>
+  <si>
+    <t>假总奖池金额</t>
+  </si>
+  <si>
+    <t>假累计奖池部分进入比率</t>
+  </si>
+  <si>
+    <t>实际押注抽水入奖池万分比</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{,}</t>
+  </si>
+  <si>
+    <t>gameType</t>
+  </si>
+  <si>
     <t>roomName</t>
   </si>
   <si>
@@ -249,83 +254,46 @@
     <t>lineMultiple</t>
   </si>
   <si>
-    <t>betCoefficient</t>
-  </si>
-  <si>
     <t>defaultBet</t>
   </si>
   <si>
     <t>initBasePool</t>
   </si>
   <si>
+    <t>initBasePoolProportion</t>
+  </si>
+  <si>
+    <t>fakePool</t>
+  </si>
+  <si>
+    <t>fakeCommissionProp</t>
+  </si>
+  <si>
+    <t>commissionProp</t>
+  </si>
+  <si>
     <t>美元快递</t>
   </si>
   <si>
     <t>100:200:300:400:500:1000:2000:3000:4000:5000</t>
   </si>
   <si>
+    <t>4000:1</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
+  </si>
+  <si>
     <t>40000:1</t>
   </si>
   <si>
-    <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>gameType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>4000:1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>1000000:1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>押注进入标准池万分比</t>
-  </si>
-  <si>
-    <t>假总奖池金额</t>
-  </si>
-  <si>
-    <t>假累计奖池部分进入比率</t>
-  </si>
-  <si>
-    <t>实际押注抽水入奖池万分比</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;{,}</t>
-  </si>
-  <si>
-    <t>initBasePoolProportion</t>
-  </si>
-  <si>
-    <t>fakePool</t>
-  </si>
-  <si>
-    <t>fakeCommissionProp</t>
-  </si>
-  <si>
-    <t>commissionProp</t>
-  </si>
-  <si>
-    <t>0,5000,10000</t>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -333,10 +301,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,68 +344,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -448,6 +354,33 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC Regular"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -456,17 +389,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -477,11 +411,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -571,14 +511,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -586,16 +526,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -613,67 +559,42 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="百分比" xfId="2" builtinId="5"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -686,13 +607,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -973,424 +887,404 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="5" max="5" width="21.75" customWidth="1"/>
-    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="9.5" customWidth="1"/>
     <col min="8" max="8" width="43.25" customWidth="1"/>
     <col min="9" max="9" width="13.125" customWidth="1"/>
     <col min="10" max="10" width="14.875" customWidth="1"/>
-    <col min="11" max="11" width="14.625" customWidth="1"/>
-    <col min="12" max="12" width="14" style="23" customWidth="1"/>
-    <col min="13" max="13" width="35.875" style="19" customWidth="1"/>
-    <col min="14" max="14" width="21.25" customWidth="1"/>
-    <col min="15" max="15" width="14.25" customWidth="1"/>
-    <col min="16" max="16" width="20.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="20.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14" style="3" customWidth="1"/>
+    <col min="12" max="12" width="35.875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="20.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="2" customFormat="1" ht="16.5">
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+    </row>
+    <row r="3" spans="1:24" s="2" customFormat="1" ht="16.5" hidden="1">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="16.5" hidden="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+    </row>
+    <row r="5" spans="1:24" s="2" customFormat="1" ht="16.5">
+      <c r="A5" s="10">
+        <v>1001001</v>
+      </c>
+      <c r="B5" s="10">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="I5" s="19">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12">
+        <v>1</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="L5" s="16">
+        <v>50000000</v>
+      </c>
+      <c r="M5" s="19">
+        <v>9600</v>
+      </c>
+      <c r="N5" s="19">
+        <v>500000</v>
+      </c>
+      <c r="O5" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="P5" s="22">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+    </row>
+    <row r="6" spans="1:24" s="2" customFormat="1" ht="16.5">
+      <c r="A6" s="10">
+        <v>1001002</v>
+      </c>
+      <c r="B6" s="10">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="11">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>50</v>
+      </c>
+      <c r="G6" s="10">
+        <v>500000</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="I6" s="19">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12">
+        <v>1</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="16">
+        <v>5000000000</v>
+      </c>
+      <c r="M6" s="19">
+        <v>9600</v>
+      </c>
+      <c r="N6" s="19">
+        <v>50000000</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="22">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="12"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
+    <row r="7" spans="1:24" s="2" customFormat="1" ht="16.5">
+      <c r="A7" s="10">
+        <v>1001003</v>
+      </c>
+      <c r="B7" s="10">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>100</v>
+      </c>
+      <c r="G7" s="10">
+        <v>5000000</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="19">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="23">
+        <v>500000000000</v>
+      </c>
+      <c r="M7" s="19">
+        <v>9600</v>
+      </c>
+      <c r="N7" s="19">
+        <v>5000000000</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="22">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
     </row>
-    <row r="3" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="12"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
+    <row r="8" spans="1:24" ht="16.5">
+      <c r="L8" s="16"/>
+      <c r="O8"/>
+      <c r="P8"/>
     </row>
-    <row r="4" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
+    <row r="11" spans="1:24">
+      <c r="O11" s="24"/>
     </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A5" s="31">
-        <v>1001001</v>
-      </c>
-      <c r="B5" s="8">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="12">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12">
-        <v>100</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="17">
-        <v>50000000</v>
-      </c>
-      <c r="N5" s="12">
-        <v>9600</v>
-      </c>
-      <c r="O5" s="12">
-        <v>500000</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="28">
-        <v>100</v>
-      </c>
-      <c r="R5" s="12"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
+    <row r="12" spans="1:24">
+      <c r="O12" s="24"/>
     </row>
-    <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A6" s="31">
-        <v>1001002</v>
-      </c>
-      <c r="B6" s="8">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>50</v>
-      </c>
-      <c r="G6" s="8">
-        <v>500000</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="12">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12">
-        <v>100</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="17">
-        <v>5000000000</v>
-      </c>
-      <c r="N6" s="12">
-        <v>9600</v>
-      </c>
-      <c r="O6" s="12">
-        <v>50000000</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="28">
-        <v>100</v>
-      </c>
-      <c r="R6" s="12"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
+    <row r="13" spans="1:24">
+      <c r="O13" s="24"/>
     </row>
-    <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A7" s="31">
-        <v>1001003</v>
-      </c>
-      <c r="B7" s="8">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="9">
-        <v>3</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
-        <v>100</v>
-      </c>
-      <c r="G7" s="8">
-        <v>5000000</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="12">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12">
-        <v>100</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="18">
-        <v>500000000000</v>
-      </c>
-      <c r="N7" s="12">
-        <v>9600</v>
-      </c>
-      <c r="O7" s="12">
-        <v>5000000000</v>
-      </c>
-      <c r="P7" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="28">
-        <v>100</v>
-      </c>
-      <c r="R7" s="12"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-    </row>
-    <row r="8" spans="1:25" ht="16.5">
-      <c r="M8" s="17"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="P11" s="29"/>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="P12" s="29"/>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="P13" s="29"/>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="P14" s="29"/>
+    <row r="14" spans="1:24">
+      <c r="O14" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E5D37A-F2AD-409A-8C7A-BA289EDAC2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF11B51-E5AC-4F1B-9E36-54566256ACB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <author>vidisJW</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -44,7 +44,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="P1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -163,12 +163,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+单局游戏获得金额大于此值时，添加至跑马灯列表播放
+当值小于等于0时，不播</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -218,6 +243,9 @@
     <t>实际押注抽水入奖池万分比</t>
   </si>
   <si>
+    <t>跑马触发金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -272,6 +300,9 @@
     <t>commissionProp</t>
   </si>
   <si>
+    <t>marqueeTrigger</t>
+  </si>
+  <si>
     <t>美元快递</t>
   </si>
   <si>
@@ -294,6 +325,28 @@
   </si>
   <si>
     <t>1000000:1</t>
+  </si>
+  <si>
+    <t>500000,17001</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000000,17001</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000000000,17001</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;long&gt;{,}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>多语言表ID</t>
+  </si>
+  <si>
+    <t>nameid</t>
   </si>
 </sst>
 </file>
@@ -304,7 +357,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,34 +368,29 @@
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -350,14 +398,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -368,14 +414,29 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -389,21 +450,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -422,6 +468,20 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="8">
@@ -518,7 +578,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -590,6 +650,19 @@
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
@@ -887,24 +960,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="7" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="8" width="43.25" customWidth="1"/>
-    <col min="9" max="9" width="13.125" customWidth="1"/>
-    <col min="10" max="10" width="14.875" customWidth="1"/>
-    <col min="11" max="11" width="14" style="3" customWidth="1"/>
-    <col min="12" max="12" width="35.875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="20.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="43.25" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="14" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="21.25" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="20.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="14.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -914,114 +989,125 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="Q1" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="R1" s="25" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" s="2" customFormat="1" ht="16.5">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="11"/>
-      <c r="D2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="29" t="s">
         <v>17</v>
       </c>
+      <c r="E2" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F2" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="H2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>17</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>18</v>
       </c>
       <c r="O2" s="19" t="s">
         <v>19</v>
       </c>
       <c r="P2" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>47</v>
+      </c>
       <c r="S2" s="12"/>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
-      <c r="W2" s="19"/>
+      <c r="W2" s="12"/>
       <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
     </row>
-    <row r="3" spans="1:24" s="2" customFormat="1" ht="16.5" hidden="1">
+    <row r="3" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="11"/>
-      <c r="D3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1030,22 +1116,22 @@
       <c r="G3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="16" t="s">
         <v>30</v>
       </c>
       <c r="N3" s="19" t="s">
@@ -1057,40 +1143,46 @@
       <c r="P3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="12"/>
+      <c r="Q3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>35</v>
+      </c>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
-      <c r="W3" s="19"/>
+      <c r="W3" s="12"/>
       <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
     </row>
-    <row r="4" spans="1:24" s="2" customFormat="1" ht="16.5" hidden="1">
+    <row r="4" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="10"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="19"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="16"/>
       <c r="N4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="12"/>
+      <c r="O4" s="19"/>
+      <c r="R4" s="20"/>
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
       <c r="V4" s="12"/>
-      <c r="W4" s="19"/>
+      <c r="W4" s="12"/>
       <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
     </row>
-    <row r="5" spans="1:24" s="2" customFormat="1" ht="16.5">
+    <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A5" s="10">
         <v>1001001</v>
       </c>
@@ -1098,57 +1190,62 @@
         <v>100100</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="11">
+        <v>100100026</v>
+      </c>
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="10">
+      <c r="F5" s="10">
         <v>1</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="19">
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="19">
         <v>1</v>
       </c>
-      <c r="J5" s="12">
+      <c r="K5" s="12">
         <v>1</v>
       </c>
-      <c r="K5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="16">
+      <c r="L5" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="16">
         <v>50000000</v>
       </c>
-      <c r="M5" s="19">
+      <c r="N5" s="19">
         <v>9600</v>
       </c>
-      <c r="N5" s="19">
+      <c r="O5" s="19">
         <v>500000</v>
       </c>
-      <c r="O5" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="22">
+      <c r="P5" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="22">
         <v>100</v>
       </c>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="12"/>
+      <c r="R5" s="26" t="s">
+        <v>44</v>
+      </c>
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
-      <c r="W5" s="19"/>
+      <c r="W5" s="12"/>
       <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
     </row>
-    <row r="6" spans="1:24" s="2" customFormat="1" ht="16.5">
+    <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A6" s="10">
         <v>1001002</v>
       </c>
@@ -1156,57 +1253,62 @@
         <v>100100</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="11">
+        <v>100100026</v>
+      </c>
+      <c r="E6" s="11">
         <v>2</v>
       </c>
-      <c r="E6" s="10">
+      <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="10">
         <v>50</v>
       </c>
-      <c r="G6" s="10">
+      <c r="H6" s="10">
         <v>500000</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="19">
+      <c r="I6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="19">
         <v>1</v>
       </c>
-      <c r="J6" s="12">
+      <c r="K6" s="12">
         <v>1</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="L6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="16">
+        <v>5000000000</v>
+      </c>
+      <c r="N6" s="19">
+        <v>9600</v>
+      </c>
+      <c r="O6" s="19">
+        <v>50000000</v>
+      </c>
+      <c r="P6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="16">
-        <v>5000000000</v>
-      </c>
-      <c r="M6" s="19">
-        <v>9600</v>
-      </c>
-      <c r="N6" s="19">
-        <v>50000000</v>
-      </c>
-      <c r="O6" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" s="22">
+      <c r="Q6" s="22">
         <v>100</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="12"/>
+      <c r="R6" s="26" t="s">
+        <v>45</v>
+      </c>
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
-      <c r="W6" s="19"/>
+      <c r="W6" s="12"/>
       <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
     </row>
-    <row r="7" spans="1:24" s="2" customFormat="1" ht="16.5">
+    <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
       <c r="A7" s="10">
         <v>1001003</v>
       </c>
@@ -1214,72 +1316,77 @@
         <v>100100</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="11">
+        <v>100100026</v>
+      </c>
+      <c r="E7" s="11">
         <v>3</v>
       </c>
-      <c r="E7" s="10">
+      <c r="F7" s="10">
         <v>1</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="10">
         <v>100</v>
       </c>
-      <c r="G7" s="10">
+      <c r="H7" s="10">
         <v>5000000</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="19">
+      <c r="I7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="19">
         <v>1</v>
       </c>
-      <c r="J7" s="12">
+      <c r="K7" s="12">
         <v>1</v>
       </c>
-      <c r="K7" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="23">
+      <c r="L7" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="23">
         <v>500000000000</v>
       </c>
-      <c r="M7" s="19">
+      <c r="N7" s="19">
         <v>9600</v>
       </c>
-      <c r="N7" s="19">
+      <c r="O7" s="19">
         <v>5000000000</v>
       </c>
-      <c r="O7" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="22">
+      <c r="P7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="22">
         <v>100</v>
       </c>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="12"/>
+      <c r="R7" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
-      <c r="W7" s="19"/>
+      <c r="W7" s="12"/>
       <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
     </row>
-    <row r="8" spans="1:24" ht="16.5">
-      <c r="L8" s="16"/>
-      <c r="O8"/>
+    <row r="8" spans="1:25" ht="16.5">
+      <c r="M8" s="16"/>
       <c r="P8"/>
+      <c r="Q8"/>
     </row>
-    <row r="11" spans="1:24">
-      <c r="O11" s="24"/>
+    <row r="11" spans="1:25">
+      <c r="P11" s="24"/>
     </row>
-    <row r="12" spans="1:24">
-      <c r="O12" s="24"/>
+    <row r="12" spans="1:25">
+      <c r="P12" s="24"/>
     </row>
-    <row r="13" spans="1:24">
-      <c r="O13" s="24"/>
+    <row r="13" spans="1:25">
+      <c r="P13" s="24"/>
     </row>
-    <row r="14" spans="1:24">
-      <c r="O14" s="24"/>
+    <row r="14" spans="1:25">
+      <c r="P14" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF11B51-E5AC-4F1B-9E36-54566256ACB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
@@ -29,13 +36,12 @@
     <author>vidisJW</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 普通场 
@@ -44,27 +50,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单位：分（换成元则除100)</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -74,7 +78,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数
@@ -84,20 +87,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="P1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -105,7 +107,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>Microsoft Office User:</t>
@@ -115,7 +116,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,7 +126,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 适用房间外部的总累计奖池计算
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="Q1" authorId="4">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -153,7 +152,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -163,14 +161,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -179,12 +176,34 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+触发金额_多语言ID
 单局游戏获得金额大于此值时，添加至跑马灯列表播放
 当值小于等于0时，不播</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+道具ID_数量</t>
         </r>
       </text>
     </comment>
@@ -193,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -204,6 +223,9 @@
     <t>游戏名称</t>
   </si>
   <si>
+    <t>多语言表ID</t>
+  </si>
+  <si>
     <t>倍场名称</t>
   </si>
   <si>
@@ -246,6 +268,9 @@
     <t>跑马触发金额</t>
   </si>
   <si>
+    <t>上庄最低金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -258,9 +283,18 @@
     <t>List&lt;int&gt;{,}</t>
   </si>
   <si>
+    <t>List&lt;long&gt;{_}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>gameType</t>
   </si>
   <si>
+    <t>nameid</t>
+  </si>
+  <si>
     <t>roomName</t>
   </si>
   <si>
@@ -303,6 +337,9 @@
     <t>marqueeTrigger</t>
   </si>
   <si>
+    <t>minBankerAmount</t>
+  </si>
+  <si>
     <t>美元快递</t>
   </si>
   <si>
@@ -315,49 +352,40 @@
     <t>0,5000,10000</t>
   </si>
   <si>
+    <t>500000_17001</t>
+  </si>
+  <si>
     <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
   </si>
   <si>
     <t>40000:1</t>
   </si>
   <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
     <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
   </si>
   <si>
     <t>1000000:1</t>
   </si>
   <si>
-    <t>500000,17001</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>50000000,17001</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>5000000000,17001</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;long&gt;{,}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>多语言表ID</t>
-  </si>
-  <si>
-    <t>nameid</t>
+    <t>5000000000_17001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,6 +416,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -401,29 +435,153 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -431,14 +589,23 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -446,45 +613,22 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,25 +637,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,12 +673,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -566,19 +896,258 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -589,19 +1158,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -613,70 +1185,113 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -954,17 +1569,17 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="43.25" customWidth="1"/>
@@ -976,10 +1591,11 @@
     <col min="15" max="15" width="14.25" customWidth="1"/>
     <col min="16" max="16" width="20.25" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="14.625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="17.4916666666667" customWidth="1"/>
+    <col min="19" max="19" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="18" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -989,409 +1605,422 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A5" s="11">
+        <v>1001001</v>
+      </c>
+      <c r="B5" s="11">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="14">
+        <v>100100026</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="21">
+        <v>1</v>
+      </c>
+      <c r="K5" s="20">
+        <v>1</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="18">
+        <v>50000000</v>
+      </c>
+      <c r="N5" s="21">
+        <v>9600</v>
+      </c>
+      <c r="O5" s="21">
+        <v>500000</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q5" s="30">
+        <v>100</v>
+      </c>
+      <c r="R5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" s="20">
+        <v>0</v>
+      </c>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A6" s="11">
+        <v>1001002</v>
+      </c>
+      <c r="B6" s="11">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="14">
+        <v>100100026</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11">
+        <v>50</v>
+      </c>
+      <c r="H6" s="11">
+        <v>500000</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1</v>
+      </c>
+      <c r="K6" s="20">
+        <v>1</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="M6" s="18">
+        <v>5000000000</v>
+      </c>
+      <c r="N6" s="21">
+        <v>9600</v>
+      </c>
+      <c r="O6" s="21">
+        <v>50000000</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" s="30">
+        <v>100</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0</v>
+      </c>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:25">
+      <c r="A7" s="11">
+        <v>1001003</v>
+      </c>
+      <c r="B7" s="11">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="14">
+        <v>100100026</v>
+      </c>
+      <c r="E7" s="12">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="25" t="s">
-        <v>16</v>
-      </c>
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11">
+        <v>100</v>
+      </c>
+      <c r="H7" s="11">
+        <v>5000000</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20">
+        <v>1</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="24">
+        <v>500000000000</v>
+      </c>
+      <c r="N7" s="21">
+        <v>9600</v>
+      </c>
+      <c r="O7" s="21">
+        <v>5000000000</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="30">
+        <v>100</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="20">
+        <v>0</v>
+      </c>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
-    </row>
-    <row r="3" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-    </row>
-    <row r="4" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-    </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A5" s="10">
-        <v>1001001</v>
-      </c>
-      <c r="B5" s="10">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="11">
-        <v>100100026</v>
-      </c>
-      <c r="E5" s="11">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="19">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12">
-        <v>1</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="16">
-        <v>50000000</v>
-      </c>
-      <c r="N5" s="19">
-        <v>9600</v>
-      </c>
-      <c r="O5" s="19">
-        <v>500000</v>
-      </c>
-      <c r="P5" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q5" s="22">
-        <v>100</v>
-      </c>
-      <c r="R5" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
-    </row>
-    <row r="6" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A6" s="10">
-        <v>1001002</v>
-      </c>
-      <c r="B6" s="10">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="11">
-        <v>100100026</v>
-      </c>
-      <c r="E6" s="11">
-        <v>2</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>50</v>
-      </c>
-      <c r="H6" s="10">
-        <v>500000</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="19">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12">
-        <v>1</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="16">
-        <v>5000000000</v>
-      </c>
-      <c r="N6" s="19">
-        <v>9600</v>
-      </c>
-      <c r="O6" s="19">
-        <v>50000000</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q6" s="22">
-        <v>100</v>
-      </c>
-      <c r="R6" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-    </row>
-    <row r="7" spans="1:25" s="2" customFormat="1" ht="16.5">
-      <c r="A7" s="10">
-        <v>1001003</v>
-      </c>
-      <c r="B7" s="10">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="11">
-        <v>100100026</v>
-      </c>
-      <c r="E7" s="11">
-        <v>3</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>100</v>
-      </c>
-      <c r="H7" s="10">
-        <v>5000000</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="19">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12">
-        <v>1</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="23">
-        <v>500000000000</v>
-      </c>
-      <c r="N7" s="19">
-        <v>9600</v>
-      </c>
-      <c r="O7" s="19">
-        <v>5000000000</v>
-      </c>
-      <c r="P7" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q7" s="22">
-        <v>100</v>
-      </c>
-      <c r="R7" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-    </row>
-    <row r="8" spans="1:25" ht="16.5">
-      <c r="M8" s="16"/>
+    <row r="8" ht="16.5" spans="13:17">
+      <c r="M8" s="18"/>
       <c r="P8"/>
       <c r="Q8"/>
     </row>
-    <row r="11" spans="1:25">
-      <c r="P11" s="24"/>
+    <row r="11" spans="16:16">
+      <c r="P11" s="25"/>
     </row>
-    <row r="12" spans="1:25">
-      <c r="P12" s="24"/>
+    <row r="12" spans="16:16">
+      <c r="P12" s="25"/>
     </row>
-    <row r="13" spans="1:25">
-      <c r="P13" s="24"/>
+    <row r="13" spans="16:16">
+      <c r="P13" s="25"/>
     </row>
-    <row r="14" spans="1:25">
-      <c r="P14" s="24"/>
+    <row r="14" spans="16:16">
+      <c r="P14" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -31,7 +31,6 @@
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
-    <author/>
     <author>Microsoft Office User</author>
     <author>vidisJW</author>
   </authors>
@@ -62,32 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数
-如中式厨房，选1/2/3
-格式：[1,2,3,5,10,50,100,500,1000]
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="3">
+    <comment ref="O1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -135,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="4">
+    <comment ref="P1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -161,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -185,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -241,10 +215,7 @@
     <t>单线押分值</t>
   </si>
   <si>
-    <t>押分倍数</t>
-  </si>
-  <si>
-    <t>线注倍数</t>
+    <t>被动小游戏</t>
   </si>
   <si>
     <t>默认押分</t>
@@ -277,6 +248,9 @@
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
+    <t>List&lt;int&gt;{|}</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -310,10 +284,7 @@
     <t>lineBetScore</t>
   </si>
   <si>
-    <t>betMultiple</t>
-  </si>
-  <si>
-    <t>lineMultiple</t>
+    <t>AutomaticallyGames</t>
   </si>
   <si>
     <t>defaultBet</t>
@@ -340,37 +311,46 @@
     <t>minBankerAmount</t>
   </si>
   <si>
-    <t>美元快递</t>
-  </si>
-  <si>
-    <t>100:200:300:400:500:1000:2000:3000:4000:5000</t>
+    <t>金矿大亨</t>
+  </si>
+  <si>
+    <t>2:4:6:8:10:20:40:60:80:100</t>
+  </si>
+  <si>
+    <t>3001001|3001002</t>
+  </si>
+  <si>
+    <t>40:1</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>500000_17001</t>
+  </si>
+  <si>
+    <t>200:400:600:800:1000:2000:4000:6000:8000:10000</t>
   </si>
   <si>
     <t>4000:1</t>
   </si>
   <si>
-    <t>0,5000,10000</t>
-  </si>
-  <si>
-    <t>500000_17001</t>
-  </si>
-  <si>
-    <t>10000:20000:30000:40000:50000:100000:200000:300000:400000:500000</t>
-  </si>
-  <si>
-    <t>40000:1</t>
-  </si>
-  <si>
     <t>50000000_17001</t>
   </si>
   <si>
-    <t>1000000:2000000:3000000:4000000:5000000:10000000:20000000:30000000:40000000:50000000</t>
-  </si>
-  <si>
-    <t>1000000:1</t>
+    <t>20000:40000:60000:80000:100000:200000:400000:600000:800000:1000000</t>
+  </si>
+  <si>
+    <t>100000:1</t>
   </si>
   <si>
     <t>5000000000_17001</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
   </si>
 </sst>
 </file>
@@ -585,6 +565,30 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -592,43 +596,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,6 +617,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -667,7 +653,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1020,7 +1018,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1044,16 +1042,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1062,60 +1060,48 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1125,29 +1111,41 @@
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1155,25 +1153,31 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1188,13 +1192,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1203,37 +1210,46 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1575,447 +1591,774 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="15.5" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="43.25" customWidth="1"/>
-    <col min="10" max="10" width="13.125" customWidth="1"/>
-    <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="35.875" style="4" customWidth="1"/>
-    <col min="14" max="14" width="21.25" customWidth="1"/>
-    <col min="15" max="15" width="14.25" customWidth="1"/>
-    <col min="16" max="16" width="20.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="20.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="17.4916666666667" customWidth="1"/>
-    <col min="19" max="19" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="45.75" customWidth="1"/>
+    <col min="10" max="10" width="18.375" customWidth="1"/>
+    <col min="11" max="11" width="14" style="4" customWidth="1"/>
+    <col min="12" max="12" width="16.375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="14" max="14" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="20.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="17.4916666666667" customWidth="1"/>
+    <col min="18" max="18" width="19.125" customWidth="1"/>
+    <col min="19" max="19" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:18">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="Q1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="28" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A2" s="12" t="s">
         <v>18</v>
       </c>
+      <c r="B2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A3" s="10" t="s">
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A5" s="13">
+        <v>1001001</v>
+      </c>
+      <c r="B5" s="13">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="13">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="28" t="s">
+      <c r="H5" s="13">
+        <v>0</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="21">
+        <v>50000000</v>
+      </c>
+      <c r="M5" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N5" s="28">
+        <v>500000</v>
+      </c>
+      <c r="O5" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" s="25">
+        <v>0</v>
+      </c>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A6" s="13">
+        <v>1001002</v>
+      </c>
+      <c r="B6" s="13">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
+      <c r="D6" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E6" s="14">
+        <v>2</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13">
+        <v>50</v>
+      </c>
+      <c r="H6" s="13">
+        <v>500000</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="21">
+        <v>5000000000</v>
+      </c>
+      <c r="M6" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N6" s="28">
+        <v>50000000</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="25">
+        <v>0</v>
+      </c>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A7" s="13">
+        <v>1001003</v>
+      </c>
+      <c r="B7" s="13">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E7" s="14">
+        <v>3</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13">
+        <v>100</v>
+      </c>
+      <c r="H7" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="32">
+        <v>500000000000</v>
+      </c>
+      <c r="M7" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N7" s="28">
+        <v>5000000000</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="25">
+        <v>0</v>
+      </c>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A5" s="11">
-        <v>1001001</v>
-      </c>
-      <c r="B5" s="11">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="12" t="s">
+    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A8" s="13">
+        <v>1007001</v>
+      </c>
+      <c r="B8" s="13">
+        <v>100700</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="14">
+      <c r="J8" s="25"/>
+      <c r="K8" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="21">
+        <v>50000000</v>
+      </c>
+      <c r="M8" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N8" s="28">
+        <v>500000</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="R8" s="25">
+        <v>0</v>
+      </c>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A9" s="13">
+        <v>1007002</v>
+      </c>
+      <c r="B9" s="13">
+        <v>100700</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="17">
         <v>100100026</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E9" s="14">
+        <v>2</v>
+      </c>
+      <c r="F9" s="16">
         <v>1</v>
       </c>
-      <c r="F5" s="11">
+      <c r="G9" s="13">
+        <v>50</v>
+      </c>
+      <c r="H9" s="13">
+        <v>500000</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="21">
+        <v>5000000000</v>
+      </c>
+      <c r="M9" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N9" s="28">
+        <v>50000000</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="25">
+        <v>0</v>
+      </c>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A10" s="13">
+        <v>1007003</v>
+      </c>
+      <c r="B10" s="13">
+        <v>100700</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E10" s="14">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16">
         <v>1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G10" s="13">
+        <v>100</v>
+      </c>
+      <c r="H10" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="32">
+        <v>500000000000</v>
+      </c>
+      <c r="M10" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N10" s="28">
+        <v>5000000000</v>
+      </c>
+      <c r="O10" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="25">
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A11" s="13">
+        <v>1014001</v>
+      </c>
+      <c r="B11" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="21">
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="25"/>
+      <c r="K11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="21">
+        <v>50000000</v>
+      </c>
+      <c r="M11" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N11" s="28">
+        <v>500000</v>
+      </c>
+      <c r="O11" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P11" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" s="25">
+        <v>0</v>
+      </c>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A12" s="13">
+        <v>1014002</v>
+      </c>
+      <c r="B12" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E12" s="14">
+        <v>2</v>
+      </c>
+      <c r="F12" s="16">
         <v>1</v>
       </c>
-      <c r="K5" s="20">
+      <c r="G12" s="13">
+        <v>50</v>
+      </c>
+      <c r="H12" s="13">
+        <v>500000</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="25"/>
+      <c r="K12" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="21">
+        <v>5000000000</v>
+      </c>
+      <c r="M12" s="28">
+        <v>9600</v>
+      </c>
+      <c r="N12" s="28">
+        <v>50000000</v>
+      </c>
+      <c r="O12" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" s="31">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="R12" s="25">
+        <v>0</v>
+      </c>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:24">
+      <c r="A13" s="13">
+        <v>1014003</v>
+      </c>
+      <c r="B13" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16">
         <v>1</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="18">
-        <v>50000000</v>
-      </c>
-      <c r="N5" s="21">
+      <c r="G13" s="13">
+        <v>100</v>
+      </c>
+      <c r="H13" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="25"/>
+      <c r="K13" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="32">
+        <v>500000000000</v>
+      </c>
+      <c r="M13" s="28">
         <v>9600</v>
       </c>
-      <c r="O5" s="21">
-        <v>500000</v>
-      </c>
-      <c r="P5" s="23" t="s">
+      <c r="N13" s="28">
+        <v>5000000000</v>
+      </c>
+      <c r="O13" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="P13" s="31">
         <v>100</v>
       </c>
-      <c r="R5" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" s="20">
+      <c r="Q13" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="R13" s="25">
         <v>0</v>
       </c>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A6" s="11">
-        <v>1001002</v>
-      </c>
-      <c r="B6" s="11">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="14">
-        <v>100100026</v>
-      </c>
-      <c r="E6" s="12">
-        <v>2</v>
-      </c>
-      <c r="F6" s="11">
-        <v>1</v>
-      </c>
-      <c r="G6" s="11">
-        <v>50</v>
-      </c>
-      <c r="H6" s="11">
-        <v>500000</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="21">
-        <v>1</v>
-      </c>
-      <c r="K6" s="20">
-        <v>1</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="18">
-        <v>5000000000</v>
-      </c>
-      <c r="N6" s="21">
-        <v>9600</v>
-      </c>
-      <c r="O6" s="21">
-        <v>50000000</v>
-      </c>
-      <c r="P6" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="30">
-        <v>100</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="S6" s="20">
-        <v>0</v>
-      </c>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A7" s="11">
-        <v>1001003</v>
-      </c>
-      <c r="B7" s="11">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="14">
-        <v>100100026</v>
-      </c>
-      <c r="E7" s="12">
-        <v>3</v>
-      </c>
-      <c r="F7" s="11">
-        <v>1</v>
-      </c>
-      <c r="G7" s="11">
-        <v>100</v>
-      </c>
-      <c r="H7" s="11">
-        <v>5000000</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="21">
-        <v>1</v>
-      </c>
-      <c r="K7" s="20">
-        <v>1</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="24">
-        <v>500000000000</v>
-      </c>
-      <c r="N7" s="21">
-        <v>9600</v>
-      </c>
-      <c r="O7" s="21">
-        <v>5000000000</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="30">
-        <v>100</v>
-      </c>
-      <c r="R7" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="20">
-        <v>0</v>
-      </c>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-    </row>
-    <row r="8" ht="16.5" spans="13:17">
-      <c r="M8" s="18"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-    </row>
-    <row r="11" spans="16:16">
-      <c r="P11" s="25"/>
-    </row>
-    <row r="12" spans="16:16">
-      <c r="P12" s="25"/>
-    </row>
-    <row r="13" spans="16:16">
-      <c r="P13" s="25"/>
-    </row>
-    <row r="14" spans="16:16">
-      <c r="P14" s="25"/>
+    <row r="14" spans="15:15">
+      <c r="O14" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="N1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="3">
+    <comment ref="O1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -215,9 +215,6 @@
     <t>单线押分值</t>
   </si>
   <si>
-    <t>被动小游戏</t>
-  </si>
-  <si>
     <t>默认押分</t>
   </si>
   <si>
@@ -248,9 +245,6 @@
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
-    <t>List&lt;int&gt;{|}</t>
-  </si>
-  <si>
     <t>long</t>
   </si>
   <si>
@@ -284,9 +278,6 @@
     <t>lineBetScore</t>
   </si>
   <si>
-    <t>AutomaticallyGames</t>
-  </si>
-  <si>
     <t>defaultBet</t>
   </si>
   <si>
@@ -317,9 +308,6 @@
     <t>2:4:6:8:10:20:40:60:80:100</t>
   </si>
   <si>
-    <t>3001001|3001002</t>
-  </si>
-  <si>
     <t>40:1</t>
   </si>
   <si>
@@ -347,7 +335,13 @@
     <t>5000000000_17001</t>
   </si>
   <si>
+    <t>超级明星</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>财神</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -565,12 +559,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -583,12 +571,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -596,6 +578,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -608,7 +602,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -653,19 +647,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1018,7 +1000,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1042,16 +1024,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1060,92 +1042,92 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1198,10 +1180,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1210,46 +1189,40 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1591,7 +1564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1599,19 +1572,18 @@
     <col min="6" max="6" width="15.5" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="45.75" customWidth="1"/>
-    <col min="10" max="10" width="18.375" customWidth="1"/>
-    <col min="11" max="11" width="14" style="4" customWidth="1"/>
-    <col min="12" max="12" width="16.375" style="5" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="20.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="17.4916666666667" customWidth="1"/>
-    <col min="18" max="18" width="19.125" customWidth="1"/>
-    <col min="19" max="19" width="9.375"/>
+    <col min="10" max="10" width="14" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="21.25" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="14" width="20.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="20.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="17.4916666666667" customWidth="1"/>
+    <col min="17" max="17" width="19.125" customWidth="1"/>
+    <col min="18" max="18" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1660,134 +1632,125 @@
       <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="35" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A2" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:24">
-      <c r="A2" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="B2" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="J2" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="25" t="s">
+      <c r="L2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="N2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="21" t="s">
+      <c r="O2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="28" t="s">
+      <c r="Q2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="R2" s="25"/>
       <c r="S2" s="25"/>
       <c r="T2" s="25"/>
       <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="H3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="I3" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="J3" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="K3" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="L3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="M3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="N3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="O3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="28" t="s">
+      <c r="P3" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="28" t="s">
+      <c r="Q3" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>40</v>
-      </c>
+      <c r="R3" s="25"/>
       <c r="S3" s="25"/>
       <c r="T3" s="25"/>
       <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A4" s="12"/>
       <c r="B4" s="13"/>
       <c r="C4" s="14"/>
@@ -1797,21 +1760,20 @@
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="25"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="Q4" s="28"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="25"/>
       <c r="R4" s="25"/>
       <c r="S4" s="25"/>
       <c r="T4" s="25"/>
       <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A5" s="13">
         <v>1001001</v>
       </c>
@@ -1819,7 +1781,7 @@
         <v>100100</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" s="17">
         <v>100100026</v>
@@ -1837,43 +1799,40 @@
         <v>0</v>
       </c>
       <c r="I5" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="L5" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M5" s="27">
+        <v>500000</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="30">
+        <v>100</v>
+      </c>
+      <c r="P5" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="21">
-        <v>50000000</v>
-      </c>
-      <c r="M5" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N5" s="28">
-        <v>500000</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="R5" s="25">
+      <c r="Q5" s="25">
         <v>0</v>
       </c>
+      <c r="R5" s="25"/>
       <c r="S5" s="25"/>
       <c r="T5" s="25"/>
       <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A6" s="13">
         <v>1001002</v>
       </c>
@@ -1881,7 +1840,7 @@
         <v>100100</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="17">
         <v>100100026</v>
@@ -1899,43 +1858,40 @@
         <v>500000</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="21">
+      <c r="J6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="20">
         <v>5000000000</v>
       </c>
-      <c r="M6" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="L6" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M6" s="27">
         <v>50000000</v>
       </c>
-      <c r="O6" s="30" t="s">
+      <c r="N6" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="30">
+        <v>100</v>
+      </c>
+      <c r="P6" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="25">
+      <c r="Q6" s="25">
         <v>0</v>
       </c>
+      <c r="R6" s="25"/>
       <c r="S6" s="25"/>
       <c r="T6" s="25"/>
       <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A7" s="13">
         <v>1001003</v>
       </c>
@@ -1943,7 +1899,7 @@
         <v>100100</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D7" s="17">
         <v>100100026</v>
@@ -1961,51 +1917,48 @@
         <v>5000000</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="32">
+        <v>46</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="31">
         <v>500000000000</v>
       </c>
-      <c r="M7" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="L7" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M7" s="27">
         <v>5000000000</v>
       </c>
-      <c r="O7" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="31">
+      <c r="N7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="30">
         <v>100</v>
       </c>
-      <c r="Q7" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="R7" s="25">
+      <c r="P7" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="25">
         <v>0</v>
       </c>
+      <c r="R7" s="25"/>
       <c r="S7" s="25"/>
       <c r="T7" s="25"/>
       <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A8" s="13">
-        <v>1007001</v>
+        <v>1003001</v>
       </c>
       <c r="B8" s="13">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D8" s="17">
         <v>100100026</v>
@@ -2023,49 +1976,48 @@
         <v>0</v>
       </c>
       <c r="I8" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="L8" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M8" s="27">
+        <v>500000</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="30">
+        <v>100</v>
+      </c>
+      <c r="P8" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="21">
-        <v>50000000</v>
-      </c>
-      <c r="M8" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N8" s="28">
-        <v>500000</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="R8" s="25">
+      <c r="Q8" s="25">
         <v>0</v>
       </c>
+      <c r="R8" s="25"/>
       <c r="S8" s="25"/>
       <c r="T8" s="25"/>
       <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A9" s="13">
-        <v>1007002</v>
+        <v>1003002</v>
       </c>
       <c r="B9" s="13">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" s="17">
         <v>100100026</v>
@@ -2083,49 +2035,48 @@
         <v>500000</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="21">
+        <v>43</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="20">
         <v>5000000000</v>
       </c>
-      <c r="M9" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="L9" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M9" s="27">
         <v>50000000</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="N9" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="30">
+        <v>100</v>
+      </c>
+      <c r="P9" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="R9" s="25">
+      <c r="Q9" s="25">
         <v>0</v>
       </c>
+      <c r="R9" s="25"/>
       <c r="S9" s="25"/>
       <c r="T9" s="25"/>
       <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A10" s="13">
-        <v>1007003</v>
+        <v>1003003</v>
       </c>
       <c r="B10" s="13">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D10" s="17">
         <v>100100026</v>
@@ -2143,49 +2094,48 @@
         <v>5000000</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="32">
+        <v>46</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="31">
         <v>500000000000</v>
       </c>
-      <c r="M10" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N10" s="28">
+      <c r="L10" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M10" s="27">
         <v>5000000000</v>
       </c>
-      <c r="O10" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P10" s="31">
+      <c r="N10" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="30">
         <v>100</v>
       </c>
-      <c r="Q10" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="R10" s="25">
+      <c r="P10" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="25">
         <v>0</v>
       </c>
+      <c r="R10" s="25"/>
       <c r="S10" s="25"/>
       <c r="T10" s="25"/>
       <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A11" s="13">
-        <v>1014001</v>
+        <v>1007001</v>
       </c>
       <c r="B11" s="13">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D11" s="17">
         <v>100100026</v>
@@ -2203,49 +2153,48 @@
         <v>0</v>
       </c>
       <c r="I11" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="L11" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M11" s="27">
+        <v>500000</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="30">
+        <v>100</v>
+      </c>
+      <c r="P11" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="21">
-        <v>50000000</v>
-      </c>
-      <c r="M11" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N11" s="28">
-        <v>500000</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" s="25">
+      <c r="Q11" s="25">
         <v>0</v>
       </c>
+      <c r="R11" s="25"/>
       <c r="S11" s="25"/>
       <c r="T11" s="25"/>
       <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="28"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
     </row>
-    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A12" s="13">
-        <v>1014002</v>
+        <v>1007002</v>
       </c>
       <c r="B12" s="13">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D12" s="17">
         <v>100100026</v>
@@ -2263,49 +2212,48 @@
         <v>500000</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="21">
+        <v>43</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="20">
         <v>5000000000</v>
       </c>
-      <c r="M12" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N12" s="28">
+      <c r="L12" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M12" s="27">
         <v>50000000</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="N12" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="30">
+        <v>100</v>
+      </c>
+      <c r="P12" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="P12" s="31">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="R12" s="25">
+      <c r="Q12" s="25">
         <v>0</v>
       </c>
+      <c r="R12" s="25"/>
       <c r="S12" s="25"/>
       <c r="T12" s="25"/>
       <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="28"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="27"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:24">
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:23">
       <c r="A13" s="13">
-        <v>1014003</v>
+        <v>1007003</v>
       </c>
       <c r="B13" s="13">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" s="17">
         <v>100100026</v>
@@ -2323,42 +2271,395 @@
         <v>5000000</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="32">
+        <v>46</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="31">
         <v>500000000000</v>
       </c>
-      <c r="M13" s="28">
-        <v>9600</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="L13" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M13" s="27">
         <v>5000000000</v>
       </c>
-      <c r="O13" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" s="31">
+      <c r="N13" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="30">
         <v>100</v>
       </c>
-      <c r="Q13" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="R13" s="25">
+      <c r="P13" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="25">
         <v>0</v>
       </c>
+      <c r="R13" s="25"/>
       <c r="S13" s="25"/>
       <c r="T13" s="25"/>
       <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
     </row>
-    <row r="14" spans="15:15">
-      <c r="O14" s="33"/>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A14" s="13">
+        <v>1012001</v>
+      </c>
+      <c r="B14" s="13">
+        <v>101200</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E14" s="14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="L14" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M14" s="27">
+        <v>500000</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O14" s="30">
+        <v>100</v>
+      </c>
+      <c r="P14" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>0</v>
+      </c>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A15" s="13">
+        <v>1012002</v>
+      </c>
+      <c r="B15" s="13">
+        <v>101200</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E15" s="14">
+        <v>2</v>
+      </c>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13">
+        <v>50</v>
+      </c>
+      <c r="H15" s="13">
+        <v>500000</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="L15" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M15" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="30">
+        <v>100</v>
+      </c>
+      <c r="P15" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>0</v>
+      </c>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A16" s="13">
+        <v>1012003</v>
+      </c>
+      <c r="B16" s="13">
+        <v>101200</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3</v>
+      </c>
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13">
+        <v>100</v>
+      </c>
+      <c r="H16" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="31">
+        <v>500000000000</v>
+      </c>
+      <c r="L16" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M16" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="30">
+        <v>100</v>
+      </c>
+      <c r="P16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>0</v>
+      </c>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A17" s="13">
+        <v>1014001</v>
+      </c>
+      <c r="B17" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="L17" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M17" s="27">
+        <v>500000</v>
+      </c>
+      <c r="N17" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="30">
+        <v>100</v>
+      </c>
+      <c r="P17" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>0</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A18" s="13">
+        <v>1014002</v>
+      </c>
+      <c r="B18" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E18" s="14">
+        <v>2</v>
+      </c>
+      <c r="F18" s="16">
+        <v>1</v>
+      </c>
+      <c r="G18" s="13">
+        <v>50</v>
+      </c>
+      <c r="H18" s="13">
+        <v>500000</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="L18" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M18" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="N18" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O18" s="30">
+        <v>100</v>
+      </c>
+      <c r="P18" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>0</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A19" s="13">
+        <v>1014003</v>
+      </c>
+      <c r="B19" s="13">
+        <v>101400</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="17">
+        <v>100100026</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3</v>
+      </c>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="G19" s="13">
+        <v>100</v>
+      </c>
+      <c r="H19" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" s="31">
+        <v>500000000000</v>
+      </c>
+      <c r="L19" s="27">
+        <v>9700</v>
+      </c>
+      <c r="M19" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="N19" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="30">
+        <v>100</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+    </row>
+    <row r="20" spans="14:14">
+      <c r="N20" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -351,13 +351,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -559,11 +560,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -571,6 +567,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -590,19 +591,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -648,6 +649,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,7 +1007,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1024,16 +1031,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1042,92 +1049,92 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1211,16 +1218,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1564,7 +1577,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1632,7 +1645,7 @@
       <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="35" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1740,7 +1753,7 @@
       <c r="P3" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="33" t="s">
+      <c r="Q3" s="35" t="s">
         <v>37</v>
       </c>
       <c r="R3" s="25"/>
@@ -1807,16 +1820,16 @@
       <c r="K5" s="20">
         <v>50000000</v>
       </c>
-      <c r="L5" s="27">
-        <v>9700</v>
+      <c r="L5" s="29">
+        <v>9600</v>
       </c>
       <c r="M5" s="27">
         <v>500000</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="N5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="30">
+      <c r="O5" s="31">
         <v>100</v>
       </c>
       <c r="P5" s="27" t="s">
@@ -1866,16 +1879,16 @@
       <c r="K6" s="20">
         <v>5000000000</v>
       </c>
-      <c r="L6" s="27">
-        <v>9700</v>
+      <c r="L6" s="29">
+        <v>9600</v>
       </c>
       <c r="M6" s="27">
         <v>50000000</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O6" s="30">
+      <c r="O6" s="31">
         <v>100</v>
       </c>
       <c r="P6" s="27" t="s">
@@ -1922,19 +1935,19 @@
       <c r="J7" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="32">
         <v>500000000000</v>
       </c>
-      <c r="L7" s="27">
-        <v>9700</v>
+      <c r="L7" s="29">
+        <v>9600</v>
       </c>
       <c r="M7" s="27">
         <v>5000000000</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="30">
+      <c r="O7" s="31">
         <v>100</v>
       </c>
       <c r="P7" s="27" t="s">
@@ -1984,16 +1997,16 @@
       <c r="K8" s="20">
         <v>50000000</v>
       </c>
-      <c r="L8" s="27">
-        <v>9700</v>
+      <c r="L8" s="29">
+        <v>9600</v>
       </c>
       <c r="M8" s="27">
         <v>500000</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O8" s="30">
+      <c r="O8" s="31">
         <v>100</v>
       </c>
       <c r="P8" s="27" t="s">
@@ -2043,16 +2056,16 @@
       <c r="K9" s="20">
         <v>5000000000</v>
       </c>
-      <c r="L9" s="27">
-        <v>9700</v>
+      <c r="L9" s="29">
+        <v>9600</v>
       </c>
       <c r="M9" s="27">
         <v>50000000</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="N9" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="30">
+      <c r="O9" s="31">
         <v>100</v>
       </c>
       <c r="P9" s="27" t="s">
@@ -2099,19 +2112,19 @@
       <c r="J10" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="32">
         <v>500000000000</v>
       </c>
-      <c r="L10" s="27">
-        <v>9700</v>
+      <c r="L10" s="29">
+        <v>9600</v>
       </c>
       <c r="M10" s="27">
         <v>5000000000</v>
       </c>
-      <c r="N10" s="29" t="s">
+      <c r="N10" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10" s="31">
         <v>100</v>
       </c>
       <c r="P10" s="27" t="s">
@@ -2167,10 +2180,10 @@
       <c r="M11" s="27">
         <v>500000</v>
       </c>
-      <c r="N11" s="29" t="s">
+      <c r="N11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O11" s="30">
+      <c r="O11" s="31">
         <v>100</v>
       </c>
       <c r="P11" s="27" t="s">
@@ -2226,10 +2239,10 @@
       <c r="M12" s="27">
         <v>50000000</v>
       </c>
-      <c r="N12" s="29" t="s">
+      <c r="N12" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O12" s="30">
+      <c r="O12" s="31">
         <v>100</v>
       </c>
       <c r="P12" s="27" t="s">
@@ -2276,7 +2289,7 @@
       <c r="J13" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="32">
         <v>500000000000</v>
       </c>
       <c r="L13" s="27">
@@ -2285,10 +2298,10 @@
       <c r="M13" s="27">
         <v>5000000000</v>
       </c>
-      <c r="N13" s="29" t="s">
+      <c r="N13" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O13" s="30">
+      <c r="O13" s="31">
         <v>100</v>
       </c>
       <c r="P13" s="27" t="s">
@@ -2338,16 +2351,16 @@
       <c r="K14" s="20">
         <v>50000000</v>
       </c>
-      <c r="L14" s="27">
-        <v>9700</v>
+      <c r="L14" s="29">
+        <v>9600</v>
       </c>
       <c r="M14" s="27">
         <v>500000</v>
       </c>
-      <c r="N14" s="29" t="s">
+      <c r="N14" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O14" s="30">
+      <c r="O14" s="31">
         <v>100</v>
       </c>
       <c r="P14" s="27" t="s">
@@ -2397,16 +2410,16 @@
       <c r="K15" s="20">
         <v>5000000000</v>
       </c>
-      <c r="L15" s="27">
-        <v>9700</v>
+      <c r="L15" s="29">
+        <v>9600</v>
       </c>
       <c r="M15" s="27">
         <v>50000000</v>
       </c>
-      <c r="N15" s="29" t="s">
+      <c r="N15" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O15" s="30">
+      <c r="O15" s="31">
         <v>100</v>
       </c>
       <c r="P15" s="27" t="s">
@@ -2453,19 +2466,19 @@
       <c r="J16" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="32">
         <v>500000000000</v>
       </c>
-      <c r="L16" s="27">
-        <v>9700</v>
+      <c r="L16" s="29">
+        <v>9600</v>
       </c>
       <c r="M16" s="27">
         <v>5000000000</v>
       </c>
-      <c r="N16" s="29" t="s">
+      <c r="N16" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O16" s="30">
+      <c r="O16" s="31">
         <v>100</v>
       </c>
       <c r="P16" s="27" t="s">
@@ -2515,16 +2528,16 @@
       <c r="K17" s="20">
         <v>50000000</v>
       </c>
-      <c r="L17" s="27">
-        <v>9700</v>
+      <c r="L17" s="29">
+        <v>9600</v>
       </c>
       <c r="M17" s="27">
         <v>500000</v>
       </c>
-      <c r="N17" s="29" t="s">
+      <c r="N17" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O17" s="30">
+      <c r="O17" s="31">
         <v>100</v>
       </c>
       <c r="P17" s="27" t="s">
@@ -2574,16 +2587,16 @@
       <c r="K18" s="20">
         <v>5000000000</v>
       </c>
-      <c r="L18" s="27">
-        <v>9700</v>
+      <c r="L18" s="29">
+        <v>9600</v>
       </c>
       <c r="M18" s="27">
         <v>50000000</v>
       </c>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O18" s="30">
+      <c r="O18" s="31">
         <v>100</v>
       </c>
       <c r="P18" s="27" t="s">
@@ -2630,19 +2643,19 @@
       <c r="J19" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="32">
         <v>500000000000</v>
       </c>
-      <c r="L19" s="27">
-        <v>9700</v>
+      <c r="L19" s="29">
+        <v>9600</v>
       </c>
       <c r="M19" s="27">
         <v>5000000000</v>
       </c>
-      <c r="N19" s="29" t="s">
+      <c r="N19" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="O19" s="30">
+      <c r="O19" s="31">
         <v>100</v>
       </c>
       <c r="P19" s="27" t="s">
@@ -2659,7 +2672,10 @@
       <c r="W19" s="27"/>
     </row>
     <row r="20" spans="14:14">
-      <c r="N20" s="32"/>
+      <c r="N20" s="33"/>
+    </row>
+    <row r="31" spans="9:9">
+      <c r="I31" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -561,39 +561,39 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2355,7 +2355,7 @@
         <v>9600</v>
       </c>
       <c r="M14" s="27">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N14" s="30" t="s">
         <v>41</v>
@@ -2414,7 +2414,7 @@
         <v>9600</v>
       </c>
       <c r="M15" s="27">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="N15" s="30" t="s">
         <v>41</v>
@@ -2473,7 +2473,7 @@
         <v>9600</v>
       </c>
       <c r="M16" s="27">
-        <v>5000000000</v>
+        <v>0</v>
       </c>
       <c r="N16" s="30" t="s">
         <v>41</v>
@@ -2532,7 +2532,7 @@
         <v>9600</v>
       </c>
       <c r="M17" s="27">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N17" s="30" t="s">
         <v>41</v>
@@ -2591,7 +2591,7 @@
         <v>9600</v>
       </c>
       <c r="M18" s="27">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="N18" s="30" t="s">
         <v>41</v>
@@ -2650,7 +2650,7 @@
         <v>9600</v>
       </c>
       <c r="M19" s="27">
-        <v>5000000000</v>
+        <v>0</v>
       </c>
       <c r="N19" s="30" t="s">
         <v>41</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -49,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="2">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="3">
+    <comment ref="L1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -203,15 +203,6 @@
     <t>倍场名称</t>
   </si>
   <si>
-    <t>房间列表</t>
-  </si>
-  <si>
-    <t>VIP等级限制</t>
-  </si>
-  <si>
-    <t>最小准入</t>
-  </si>
-  <si>
     <t>单线押分值</t>
   </si>
   <si>
@@ -264,15 +255,6 @@
   </si>
   <si>
     <t>roomName</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t>vipLvLimit</t>
-  </si>
-  <si>
-    <t>enterLimit</t>
   </si>
   <si>
     <t>lineBetScore</t>
@@ -357,8 +339,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="177" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -391,13 +373,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -560,50 +542,50 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,12 +594,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -636,19 +612,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +977,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1031,16 +1001,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1049,92 +1019,92 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1142,32 +1112,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1181,62 +1148,53 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1577,1105 +1535,938 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="45.75" customWidth="1"/>
-    <col min="10" max="10" width="14" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="21.25" customWidth="1"/>
-    <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="14" width="20.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="20.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.4916666666667" customWidth="1"/>
-    <col min="17" max="17" width="19.125" customWidth="1"/>
-    <col min="18" max="18" width="9.375"/>
+    <col min="6" max="6" width="45.75" customWidth="1"/>
+    <col min="7" max="7" width="14" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.4916666666667" customWidth="1"/>
+    <col min="14" max="14" width="19.125" customWidth="1"/>
+    <col min="15" max="15" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:14">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="23" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="B2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="G2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>16</v>
       </c>
+      <c r="I2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="27" t="s">
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="28" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="E3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
+      <c r="F3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A3" s="12" t="s">
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A5" s="12">
+        <v>1001001</v>
+      </c>
+      <c r="B5" s="12">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="I5" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J5" s="26">
+        <v>500000</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="30">
+        <v>100</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="15">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="27" t="s">
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A6" s="12">
+        <v>1001002</v>
+      </c>
+      <c r="B6" s="12">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="D6" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E6" s="13">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="17">
+        <v>5000000000</v>
+      </c>
+      <c r="I6" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J6" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="30">
+        <v>100</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A7" s="12">
+        <v>1001003</v>
+      </c>
+      <c r="B7" s="12">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E7" s="13">
+        <v>3</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I7" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J7" s="26">
+        <v>5000000000</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="30">
+        <v>100</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A8" s="12">
+        <v>1003001</v>
+      </c>
+      <c r="B8" s="12">
+        <v>100300</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="G8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="H8" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="I8" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J8" s="26">
+        <v>500000</v>
+      </c>
+      <c r="K8" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="L8" s="30">
+        <v>100</v>
+      </c>
+      <c r="M8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="N8" s="15">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A9" s="12">
+        <v>1003002</v>
+      </c>
+      <c r="B9" s="12">
+        <v>100300</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E9" s="13">
+        <v>2</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
+      <c r="G9" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="17">
+        <v>5000000000</v>
+      </c>
+      <c r="I9" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J9" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="30">
+        <v>100</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A10" s="12">
+        <v>1003003</v>
+      </c>
+      <c r="B10" s="12">
+        <v>100300</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E10" s="13">
+        <v>3</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I10" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J10" s="26">
+        <v>5000000000</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="30">
+        <v>100</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A5" s="13">
-        <v>1001001</v>
-      </c>
-      <c r="B5" s="13">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="14" t="s">
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A11" s="12">
+        <v>1007001</v>
+      </c>
+      <c r="B11" s="12">
+        <v>100700</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="I11" s="26">
+        <v>9700</v>
+      </c>
+      <c r="J11" s="26">
+        <v>500000</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="30">
+        <v>100</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A12" s="12">
+        <v>1007002</v>
+      </c>
+      <c r="B12" s="12">
+        <v>100700</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="17">
+      <c r="H12" s="17">
+        <v>5000000000</v>
+      </c>
+      <c r="I12" s="26">
+        <v>9700</v>
+      </c>
+      <c r="J12" s="26">
+        <v>50000000</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="30">
+        <v>100</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="15">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A13" s="12">
+        <v>1007003</v>
+      </c>
+      <c r="B13" s="12">
+        <v>100700</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="18">
         <v>100100026</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E13" s="13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I13" s="26">
+        <v>9700</v>
+      </c>
+      <c r="J13" s="26">
+        <v>5000000000</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="30">
+        <v>100</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="15">
+        <v>0</v>
+      </c>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A14" s="12">
+        <v>1012001</v>
+      </c>
+      <c r="B14" s="12">
+        <v>101200</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E14" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F14" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="I14" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J14" s="26">
+        <v>0</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="30">
+        <v>100</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0</v>
+      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A15" s="12">
+        <v>1012002</v>
+      </c>
+      <c r="B15" s="12">
+        <v>101200</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E15" s="13">
+        <v>2</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="17">
+        <v>5000000000</v>
+      </c>
+      <c r="I15" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J15" s="26">
+        <v>0</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="30">
+        <v>100</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="N15" s="15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A16" s="12">
+        <v>1012003</v>
+      </c>
+      <c r="B16" s="12">
+        <v>101200</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E16" s="13">
+        <v>3</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I16" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J16" s="26">
+        <v>0</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="30">
+        <v>100</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A17" s="12">
+        <v>1014001</v>
+      </c>
+      <c r="B17" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E17" s="13">
         <v>1</v>
       </c>
-      <c r="G5" s="13">
+      <c r="F17" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="I17" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J17" s="26">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
+      <c r="K17" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="30">
+        <v>100</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" s="15">
         <v>0</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A18" s="12">
+        <v>1014002</v>
+      </c>
+      <c r="B18" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E18" s="13">
+        <v>2</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="17">
+        <v>5000000000</v>
+      </c>
+      <c r="I18" s="28">
+        <v>9600</v>
+      </c>
+      <c r="J18" s="26">
+        <v>0</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="30">
+        <v>100</v>
+      </c>
+      <c r="M18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="N18" s="15">
+        <v>0</v>
+      </c>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A19" s="12">
+        <v>1014003</v>
+      </c>
+      <c r="B19" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="E19" s="13">
+        <v>3</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="L5" s="29">
+      <c r="G19" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I19" s="28">
         <v>9600</v>
       </c>
-      <c r="M5" s="27">
-        <v>500000</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="31">
+      <c r="J19" s="26">
+        <v>0</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="30">
         <v>100</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="M19" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="N19" s="15">
         <v>0</v>
       </c>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A6" s="13">
-        <v>1001002</v>
-      </c>
-      <c r="B6" s="13">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E6" s="14">
-        <v>2</v>
-      </c>
-      <c r="F6" s="16">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13">
-        <v>50</v>
-      </c>
-      <c r="H6" s="13">
-        <v>500000</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="L6" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M6" s="27">
-        <v>50000000</v>
-      </c>
-      <c r="N6" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="31">
-        <v>100</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="25">
-        <v>0</v>
-      </c>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
+    <row r="20" spans="11:11">
+      <c r="K20" s="31"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A7" s="13">
-        <v>1001003</v>
-      </c>
-      <c r="B7" s="13">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E7" s="14">
-        <v>3</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13">
-        <v>100</v>
-      </c>
-      <c r="H7" s="13">
-        <v>5000000</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" s="32">
-        <v>500000000000</v>
-      </c>
-      <c r="L7" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M7" s="27">
-        <v>5000000000</v>
-      </c>
-      <c r="N7" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="31">
-        <v>100</v>
-      </c>
-      <c r="P7" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="25">
-        <v>0</v>
-      </c>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A8" s="13">
-        <v>1003001</v>
-      </c>
-      <c r="B8" s="13">
-        <v>100300</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E8" s="14">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="L8" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M8" s="27">
-        <v>500000</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="31">
-        <v>100</v>
-      </c>
-      <c r="P8" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="25">
-        <v>0</v>
-      </c>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A9" s="13">
-        <v>1003002</v>
-      </c>
-      <c r="B9" s="13">
-        <v>100300</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E9" s="14">
-        <v>2</v>
-      </c>
-      <c r="F9" s="16">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13">
-        <v>50</v>
-      </c>
-      <c r="H9" s="13">
-        <v>500000</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="L9" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M9" s="27">
-        <v>50000000</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="31">
-        <v>100</v>
-      </c>
-      <c r="P9" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="25">
-        <v>0</v>
-      </c>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A10" s="13">
-        <v>1003003</v>
-      </c>
-      <c r="B10" s="13">
-        <v>100300</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E10" s="14">
-        <v>3</v>
-      </c>
-      <c r="F10" s="16">
-        <v>1</v>
-      </c>
-      <c r="G10" s="13">
-        <v>100</v>
-      </c>
-      <c r="H10" s="13">
-        <v>5000000</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="32">
-        <v>500000000000</v>
-      </c>
-      <c r="L10" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M10" s="27">
-        <v>5000000000</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="31">
-        <v>100</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="25">
-        <v>0</v>
-      </c>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A11" s="13">
-        <v>1007001</v>
-      </c>
-      <c r="B11" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E11" s="14">
-        <v>1</v>
-      </c>
-      <c r="F11" s="16">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="L11" s="27">
-        <v>9700</v>
-      </c>
-      <c r="M11" s="27">
-        <v>500000</v>
-      </c>
-      <c r="N11" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="31">
-        <v>100</v>
-      </c>
-      <c r="P11" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q11" s="25">
-        <v>0</v>
-      </c>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A12" s="13">
-        <v>1007002</v>
-      </c>
-      <c r="B12" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E12" s="14">
-        <v>2</v>
-      </c>
-      <c r="F12" s="16">
-        <v>1</v>
-      </c>
-      <c r="G12" s="13">
-        <v>50</v>
-      </c>
-      <c r="H12" s="13">
-        <v>500000</v>
-      </c>
-      <c r="I12" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="L12" s="27">
-        <v>9700</v>
-      </c>
-      <c r="M12" s="27">
-        <v>50000000</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="31">
-        <v>100</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="25">
-        <v>0</v>
-      </c>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A13" s="13">
-        <v>1007003</v>
-      </c>
-      <c r="B13" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E13" s="14">
-        <v>3</v>
-      </c>
-      <c r="F13" s="16">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13">
-        <v>100</v>
-      </c>
-      <c r="H13" s="13">
-        <v>5000000</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="32">
-        <v>500000000000</v>
-      </c>
-      <c r="L13" s="27">
-        <v>9700</v>
-      </c>
-      <c r="M13" s="27">
-        <v>5000000000</v>
-      </c>
-      <c r="N13" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O13" s="31">
-        <v>100</v>
-      </c>
-      <c r="P13" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="25">
-        <v>0</v>
-      </c>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A14" s="13">
-        <v>1012001</v>
-      </c>
-      <c r="B14" s="13">
-        <v>101200</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E14" s="14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="16">
-        <v>1</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="L14" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M14" s="27">
-        <v>0</v>
-      </c>
-      <c r="N14" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O14" s="31">
-        <v>100</v>
-      </c>
-      <c r="P14" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q14" s="25">
-        <v>0</v>
-      </c>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A15" s="13">
-        <v>1012002</v>
-      </c>
-      <c r="B15" s="13">
-        <v>101200</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E15" s="14">
-        <v>2</v>
-      </c>
-      <c r="F15" s="16">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13">
-        <v>50</v>
-      </c>
-      <c r="H15" s="13">
-        <v>500000</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="L15" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M15" s="27">
-        <v>0</v>
-      </c>
-      <c r="N15" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" s="31">
-        <v>100</v>
-      </c>
-      <c r="P15" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>0</v>
-      </c>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A16" s="13">
-        <v>1012003</v>
-      </c>
-      <c r="B16" s="13">
-        <v>101200</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E16" s="14">
-        <v>3</v>
-      </c>
-      <c r="F16" s="16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13">
-        <v>100</v>
-      </c>
-      <c r="H16" s="13">
-        <v>5000000</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="32">
-        <v>500000000000</v>
-      </c>
-      <c r="L16" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M16" s="27">
-        <v>0</v>
-      </c>
-      <c r="N16" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O16" s="31">
-        <v>100</v>
-      </c>
-      <c r="P16" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q16" s="25">
-        <v>0</v>
-      </c>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A17" s="13">
-        <v>1014001</v>
-      </c>
-      <c r="B17" s="13">
-        <v>101400</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E17" s="14">
-        <v>1</v>
-      </c>
-      <c r="F17" s="16">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="L17" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M17" s="27">
-        <v>0</v>
-      </c>
-      <c r="N17" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O17" s="31">
-        <v>100</v>
-      </c>
-      <c r="P17" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q17" s="25">
-        <v>0</v>
-      </c>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A18" s="13">
-        <v>1014002</v>
-      </c>
-      <c r="B18" s="13">
-        <v>101400</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E18" s="14">
-        <v>2</v>
-      </c>
-      <c r="F18" s="16">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13">
-        <v>50</v>
-      </c>
-      <c r="H18" s="13">
-        <v>500000</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="L18" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M18" s="27">
-        <v>0</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O18" s="31">
-        <v>100</v>
-      </c>
-      <c r="P18" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q18" s="25">
-        <v>0</v>
-      </c>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:23">
-      <c r="A19" s="13">
-        <v>1014003</v>
-      </c>
-      <c r="B19" s="13">
-        <v>101400</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="17">
-        <v>100100026</v>
-      </c>
-      <c r="E19" s="14">
-        <v>3</v>
-      </c>
-      <c r="F19" s="16">
-        <v>1</v>
-      </c>
-      <c r="G19" s="13">
-        <v>100</v>
-      </c>
-      <c r="H19" s="13">
-        <v>5000000</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="32">
-        <v>500000000000</v>
-      </c>
-      <c r="L19" s="29">
-        <v>9600</v>
-      </c>
-      <c r="M19" s="27">
-        <v>0</v>
-      </c>
-      <c r="N19" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="O19" s="31">
-        <v>100</v>
-      </c>
-      <c r="P19" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q19" s="25">
-        <v>0</v>
-      </c>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-    </row>
-    <row r="20" spans="14:14">
-      <c r="N20" s="33"/>
-    </row>
-    <row r="31" spans="9:9">
-      <c r="I31" s="34"/>
+    <row r="31" spans="6:6">
+      <c r="F31" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -544,6 +544,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
@@ -562,13 +568,8 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -580,7 +581,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2191,7 +2191,7 @@
         <v>9600</v>
       </c>
       <c r="J14" s="26">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="K14" s="29" t="s">
         <v>35</v>
@@ -2241,7 +2241,7 @@
         <v>9600</v>
       </c>
       <c r="J15" s="26">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="K15" s="29" t="s">
         <v>35</v>
@@ -2291,7 +2291,7 @@
         <v>9600</v>
       </c>
       <c r="J16" s="26">
-        <v>0</v>
+        <v>5000000000</v>
       </c>
       <c r="K16" s="29" t="s">
         <v>35</v>
@@ -2341,7 +2341,7 @@
         <v>9600</v>
       </c>
       <c r="J17" s="26">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="K17" s="29" t="s">
         <v>35</v>
@@ -2391,7 +2391,7 @@
         <v>9600</v>
       </c>
       <c r="J18" s="26">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>35</v>
@@ -2441,7 +2441,7 @@
         <v>9600</v>
       </c>
       <c r="J19" s="26">
-        <v>0</v>
+        <v>5000000000</v>
       </c>
       <c r="K19" s="29" t="s">
         <v>35</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -542,20 +542,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -566,10 +567,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2047,7 +2047,7 @@
         <v>35</v>
       </c>
       <c r="L11" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" s="26" t="s">
         <v>36</v>
@@ -2097,7 +2097,7 @@
         <v>35</v>
       </c>
       <c r="L12" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12" s="26" t="s">
         <v>39</v>
@@ -2147,7 +2147,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" s="26" t="s">
         <v>42</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E20E213-085A-45E8-9DC4-CFA45E7CA627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
@@ -35,12 +41,13 @@
     <author>vidisJW</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 普通场 
@@ -49,31 +56,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单位：分（换成元则除100)</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2">
+    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -81,6 +90,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
+            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>Microsoft Office User:</t>
@@ -90,6 +100,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
+            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -100,7 +111,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 适用房间外部的总累计奖池计算
@@ -109,7 +120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="3">
+    <comment ref="L1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -117,6 +128,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -126,6 +138,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -135,13 +148,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -150,6 +164,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -159,13 +174,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -174,6 +190,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -186,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
   <si>
     <t>id</t>
   </si>
@@ -287,10 +304,10 @@
     <t>金矿大亨</t>
   </si>
   <si>
-    <t>2:4:6:8:10:20:40:60:80:100</t>
-  </si>
-  <si>
-    <t>40:1</t>
+    <t>1_2_5_10_20_50</t>
+  </si>
+  <si>
+    <t>10:1</t>
   </si>
   <si>
     <t>0,5000,10000</t>
@@ -299,16 +316,16 @@
     <t>500000_17001</t>
   </si>
   <si>
-    <t>200:400:600:800:1000:2000:4000:6000:8000:10000</t>
-  </si>
-  <si>
-    <t>4000:1</t>
+    <t>100_200_500_1000_2000_5000</t>
+  </si>
+  <si>
+    <t>1000:1</t>
   </si>
   <si>
     <t>50000000_17001</t>
   </si>
   <si>
-    <t>20000:40000:60000:80000:100000:200000:400000:600000:800000:1000000</t>
+    <t>10000_20000_50000_100000_200000_500000</t>
   </si>
   <si>
     <t>100000:1</t>
@@ -320,29 +337,88 @@
     <t>超级明星</t>
   </si>
   <si>
+    <t>1000000_2000000_5000000_10000000_20000000_50000000</t>
+  </si>
+  <si>
+    <t>10000000:1</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
   </si>
   <si>
+    <t>5_10_25_50_100_250</t>
+  </si>
+  <si>
+    <t>50:1</t>
+  </si>
+  <si>
+    <t>500_1000_2500_5000_10000_25000</t>
+  </si>
+  <si>
+    <t>5000:1</t>
+  </si>
+  <si>
+    <t>50000_100000_250000_500000_1000000_2500000</t>
+  </si>
+  <si>
+    <t>500000:1</t>
+  </si>
+  <si>
     <t>财神</t>
   </si>
   <si>
+    <t>6_12_32_66_132_332</t>
+  </si>
+  <si>
+    <t>66:1</t>
+  </si>
+  <si>
+    <t>600_1200_3200_6600_13200_33200</t>
+  </si>
+  <si>
+    <t>6600:1</t>
+  </si>
+  <si>
+    <t>60000_120000_320000_660000_1320000_3320000</t>
+  </si>
+  <si>
+    <t>660000:1</t>
+  </si>
+  <si>
     <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>10_20_50_100_200_500</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>1000_2000_5000_10000_20000_50000</t>
+  </si>
+  <si>
+    <t>10000:1</t>
+  </si>
+  <si>
+    <t>100000_200000_500000_1000000_2000000_5000000</t>
+  </si>
+  <si>
+    <t>1000000:1</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{_}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,163 +463,62 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -551,41 +526,31 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,19 +559,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799340800195319"/>
+        <fgColor theme="7" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799340800195319"/>
+        <fgColor theme="9" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,204 +583,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -853,258 +638,19 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1115,25 +661,25 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1145,113 +691,66 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="3">
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1529,13 +1028,13 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:T31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1547,12 +1046,12 @@
     <col min="10" max="10" width="14.25" customWidth="1"/>
     <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="20.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.4916666666667" customWidth="1"/>
+    <col min="13" max="13" width="17.5" customWidth="1"/>
     <col min="14" max="14" width="19.125" customWidth="1"/>
     <col min="15" max="15" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1076,7 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="21" t="s">
@@ -1589,14 +1088,14 @@
       <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:20">
+    <row r="2" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -1604,47 +1103,47 @@
         <v>14</v>
       </c>
       <c r="C2" s="13"/>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="12" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
@@ -1658,61 +1157,61 @@
       <c r="E3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+    </row>
+    <row r="4" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+    </row>
+    <row r="5" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A5" s="12">
         <v>1001001</v>
       </c>
@@ -1722,47 +1221,47 @@
       <c r="C5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>100100026</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>50000000</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="25">
         <v>9600</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="24">
         <v>500000</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="30">
+      <c r="L5" s="27">
         <v>100</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="14">
         <v>0</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+    </row>
+    <row r="6" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A6" s="12">
         <v>1001002</v>
       </c>
@@ -1772,47 +1271,47 @@
       <c r="C6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>100100026</v>
       </c>
       <c r="E6" s="13">
         <v>2</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="25">
         <v>9600</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="24">
         <v>50000000</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="27">
         <v>100</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <v>0</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+    </row>
+    <row r="7" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A7" s="12">
         <v>1001003</v>
       </c>
@@ -1822,47 +1321,47 @@
       <c r="C7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>100100026</v>
       </c>
       <c r="E7" s="13">
         <v>3</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <v>500000000000</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="25">
         <v>9600</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="24">
         <v>5000000000</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="27">
         <v>100</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="14">
         <v>0</v>
       </c>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+    </row>
+    <row r="8" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A8" s="12">
         <v>1003001</v>
       </c>
@@ -1872,47 +1371,47 @@
       <c r="C8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>100100026</v>
       </c>
       <c r="E8" s="13">
         <v>1</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="17">
+      <c r="F8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="16">
         <v>50000000</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="25">
         <v>9600</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="24">
         <v>500000</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="27">
         <v>100</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <v>0</v>
       </c>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+    </row>
+    <row r="9" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A9" s="12">
         <v>1003002</v>
       </c>
@@ -1922,47 +1421,47 @@
       <c r="C9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>100100026</v>
       </c>
       <c r="E9" s="13">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="17">
+      <c r="F9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="25">
         <v>9600</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="24">
         <v>50000000</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="27">
         <v>100</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="14">
         <v>0</v>
       </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+    </row>
+    <row r="10" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A10" s="12">
         <v>1003003</v>
       </c>
@@ -1972,47 +1471,47 @@
       <c r="C10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>100100026</v>
       </c>
       <c r="E10" s="13">
         <v>3</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="19">
+      <c r="F10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="18">
         <v>500000000000</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="25">
         <v>9600</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="24">
         <v>5000000000</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="27">
         <v>100</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="14">
         <v>0</v>
       </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+    </row>
+    <row r="11" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A11" s="12">
         <v>1007001</v>
       </c>
@@ -2020,49 +1519,49 @@
         <v>100700</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="18">
+        <v>46</v>
+      </c>
+      <c r="D11" s="17">
         <v>100100026</v>
       </c>
       <c r="E11" s="13">
         <v>1</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="17">
+      <c r="F11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="16">
         <v>50000000</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="24">
         <v>9700</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="24">
         <v>500000</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="27">
         <v>0</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <v>0</v>
       </c>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+    </row>
+    <row r="12" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A12" s="12">
         <v>1007002</v>
       </c>
@@ -2070,49 +1569,49 @@
         <v>100700</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="18">
+        <v>46</v>
+      </c>
+      <c r="D12" s="17">
         <v>100100026</v>
       </c>
       <c r="E12" s="13">
         <v>2</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="17">
+      <c r="F12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="24">
         <v>9700</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="24">
         <v>50000000</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="27">
         <v>0</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="14">
         <v>0</v>
       </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+    </row>
+    <row r="13" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A13" s="12">
         <v>1007003</v>
       </c>
@@ -2120,49 +1619,49 @@
         <v>100700</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="18">
+        <v>46</v>
+      </c>
+      <c r="D13" s="17">
         <v>100100026</v>
       </c>
       <c r="E13" s="13">
         <v>3</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="19">
+      <c r="F13" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="18">
         <v>500000000000</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="24">
         <v>9700</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="24">
         <v>5000000000</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="27">
         <v>0</v>
       </c>
-      <c r="M13" s="26" t="s">
+      <c r="M13" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="14">
         <v>0</v>
       </c>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+    </row>
+    <row r="14" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A14" s="12">
         <v>1012001</v>
       </c>
@@ -2170,49 +1669,49 @@
         <v>101200</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="18">
+        <v>53</v>
+      </c>
+      <c r="D14" s="17">
         <v>100100026</v>
       </c>
       <c r="E14" s="13">
         <v>1</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="17">
+      <c r="F14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="16">
         <v>50000000</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="25">
         <v>9600</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="24">
         <v>500000</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K14" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="27">
         <v>100</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="14">
         <v>0</v>
       </c>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+    </row>
+    <row r="15" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A15" s="12">
         <v>1012002</v>
       </c>
@@ -2220,49 +1719,49 @@
         <v>101200</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="18">
+        <v>53</v>
+      </c>
+      <c r="D15" s="17">
         <v>100100026</v>
       </c>
       <c r="E15" s="13">
         <v>2</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="17">
+      <c r="F15" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="25">
         <v>9600</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="24">
         <v>50000000</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="27">
         <v>100</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="14">
         <v>0</v>
       </c>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+    </row>
+    <row r="16" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A16" s="12">
         <v>1012003</v>
       </c>
@@ -2270,49 +1769,49 @@
         <v>101200</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="18">
+        <v>53</v>
+      </c>
+      <c r="D16" s="17">
         <v>100100026</v>
       </c>
       <c r="E16" s="13">
         <v>3</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="19">
+      <c r="F16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="18">
         <v>500000000000</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="25">
         <v>9600</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="24">
         <v>5000000000</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="27">
         <v>100</v>
       </c>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="14">
         <v>0</v>
       </c>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+    </row>
+    <row r="17" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A17" s="12">
         <v>1014001</v>
       </c>
@@ -2320,49 +1819,49 @@
         <v>101400</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="18">
+        <v>60</v>
+      </c>
+      <c r="D17" s="17">
         <v>100100026</v>
       </c>
       <c r="E17" s="13">
         <v>1</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="17">
+      <c r="F17" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="16">
         <v>50000000</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="25">
         <v>9600</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="24">
         <v>500000</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="27">
         <v>100</v>
       </c>
-      <c r="M17" s="26" t="s">
+      <c r="M17" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="14">
         <v>0</v>
       </c>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+    </row>
+    <row r="18" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A18" s="12">
         <v>1014002</v>
       </c>
@@ -2370,49 +1869,49 @@
         <v>101400</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="18">
+        <v>60</v>
+      </c>
+      <c r="D18" s="17">
         <v>100100026</v>
       </c>
       <c r="E18" s="13">
         <v>2</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="17">
+      <c r="F18" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>9600</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="24">
         <v>50000000</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="27">
         <v>100</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="M18" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="14">
         <v>0</v>
       </c>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+    </row>
+    <row r="19" spans="1:20" s="2" customFormat="1" ht="16.5">
       <c r="A19" s="12">
         <v>1014003</v>
       </c>
@@ -2420,58 +1919,210 @@
         <v>101400</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="18">
+        <v>60</v>
+      </c>
+      <c r="D19" s="17">
         <v>100100026</v>
       </c>
       <c r="E19" s="13">
         <v>3</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="19">
+      <c r="F19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="18">
         <v>500000000000</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="25">
         <v>9600</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="24">
         <v>5000000000</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="27">
         <v>100</v>
       </c>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="14">
         <v>0</v>
       </c>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-    </row>
-    <row r="20" spans="11:11">
-      <c r="K20" s="31"/>
-    </row>
-    <row r="31" spans="6:6">
-      <c r="F31" s="20"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="K20" s="28"/>
+    </row>
+    <row r="34" spans="6:14" ht="16.5">
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+    </row>
+    <row r="35" spans="6:14" ht="16.5">
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+    </row>
+    <row r="37" spans="6:14">
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="6:14">
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="6:14" ht="16.5">
+      <c r="F39" s="20"/>
+      <c r="G39" s="13"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="6:14" ht="16.5">
+      <c r="F40" s="20"/>
+      <c r="G40" s="13"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="6:14" ht="16.5">
+      <c r="F41" s="20"/>
+      <c r="G41" s="13"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="6:14" ht="16.5">
+      <c r="G42" s="13"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="6:14" ht="16.5">
+      <c r="G43" s="13"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="6:14" ht="16.5">
+      <c r="G44" s="13"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="6:14" ht="16.5">
+      <c r="G45" s="13"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="6:14" ht="16.5">
+      <c r="G46" s="13"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="6:14" ht="16.5">
+      <c r="G47" s="13"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="6:14" ht="16.5">
+      <c r="G48" s="13"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="7:13" ht="16.5">
+      <c r="G49" s="13"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="7:13" ht="16.5">
+      <c r="G50" s="13"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="7:13" ht="16.5">
+      <c r="G51" s="13"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="7:13" ht="16.5">
+      <c r="G52" s="13"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="7:13" ht="16.5">
+      <c r="G53" s="13"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E20E213-085A-45E8-9DC4-CFA45E7CA627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
@@ -41,13 +35,12 @@
     <author>vidisJW</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 普通场 
@@ -56,33 +49,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单位：分（换成元则除100)</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -90,7 +81,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>Microsoft Office User:</t>
@@ -100,7 +90,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Microsoft YaHei UI"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -111,7 +100,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 适用房间外部的总累计奖池计算
@@ -120,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="L1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -128,7 +117,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>vidisJW:</t>
@@ -138,7 +126,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -148,14 +135,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -164,7 +150,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -174,14 +159,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -190,7 +174,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -203,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="68">
   <si>
     <t>id</t>
   </si>
@@ -250,6 +233,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>List&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
@@ -404,21 +390,21 @@
   </si>
   <si>
     <t>1000000:1</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;{_}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,6 +436,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -475,29 +466,158 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -505,20 +625,30 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -526,31 +656,10 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,19 +668,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,24 +692,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -638,19 +933,258 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -661,25 +1195,25 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -691,66 +1225,108 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1028,12 +1604,12 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:T53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -1051,7 +1627,7 @@
     <col min="15" max="15" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="18" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:14">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1079,13 +1655,13 @@
       <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -1095,7 +1671,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="2" customFormat="1" ht="16.5">
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -1109,109 +1685,109 @@
       <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="29" t="s">
-        <v>67</v>
+      <c r="F2" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="24" t="s">
+      <c r="J2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="K2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" s="2" customFormat="1" ht="16.5">
+        <v>20</v>
+      </c>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="14" t="s">
         <v>23</v>
       </c>
+      <c r="F3" s="17" t="s">
+        <v>24</v>
+      </c>
       <c r="G3" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="I3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="J3" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="K3" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="L3" s="25" t="s">
+        <v>30</v>
+      </c>
       <c r="M3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-    </row>
-    <row r="4" spans="1:20" s="2" customFormat="1" ht="16.5">
+        <v>32</v>
+      </c>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="15"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-    </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A5" s="12">
         <v>1001001</v>
       </c>
@@ -1219,49 +1795,49 @@
         <v>100100</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="17">
+        <v>33</v>
+      </c>
+      <c r="D5" s="18">
         <v>100100026</v>
       </c>
       <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>33</v>
+      <c r="F5" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" s="16">
         <v>50000000</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="26">
         <v>9600</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="25">
         <v>500000</v>
       </c>
-      <c r="K5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="27">
+      <c r="K5" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="28">
         <v>100</v>
       </c>
-      <c r="M5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="14">
+      <c r="M5" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="17">
         <v>0</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-    </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A6" s="12">
         <v>1001002</v>
       </c>
@@ -1269,49 +1845,49 @@
         <v>100100</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="17">
+        <v>33</v>
+      </c>
+      <c r="D6" s="18">
         <v>100100026</v>
       </c>
       <c r="E6" s="13">
         <v>2</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>37</v>
+      <c r="F6" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="26">
         <v>9600</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="25">
         <v>50000000</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="27">
+      <c r="K6" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="28">
         <v>100</v>
       </c>
-      <c r="M6" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="14">
+      <c r="M6" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="17">
         <v>0</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-    </row>
-    <row r="7" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A7" s="12">
         <v>1001003</v>
       </c>
@@ -1319,49 +1895,49 @@
         <v>100100</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="17">
+        <v>33</v>
+      </c>
+      <c r="D7" s="18">
         <v>100100026</v>
       </c>
       <c r="E7" s="13">
         <v>3</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>40</v>
+      <c r="F7" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="18">
+        <v>42</v>
+      </c>
+      <c r="H7" s="19">
         <v>500000000000</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="26">
         <v>9600</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <v>5000000000</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="27">
+      <c r="K7" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="28">
         <v>100</v>
       </c>
-      <c r="M7" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="14">
+      <c r="M7" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="17">
         <v>0</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-    </row>
-    <row r="8" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A8" s="12">
         <v>1003001</v>
       </c>
@@ -1369,49 +1945,49 @@
         <v>100300</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="17">
+        <v>44</v>
+      </c>
+      <c r="D8" s="18">
         <v>100100026</v>
       </c>
       <c r="E8" s="13">
         <v>1</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>37</v>
+      <c r="F8" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="16">
         <v>50000000</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <v>9600</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <v>500000</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="27">
+      <c r="K8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="28">
         <v>100</v>
       </c>
-      <c r="M8" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="14">
+      <c r="M8" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="17">
         <v>0</v>
       </c>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-    </row>
-    <row r="9" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A9" s="12">
         <v>1003002</v>
       </c>
@@ -1419,49 +1995,49 @@
         <v>100300</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="17">
+        <v>44</v>
+      </c>
+      <c r="D9" s="18">
         <v>100100026</v>
       </c>
       <c r="E9" s="13">
         <v>2</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>40</v>
+      <c r="F9" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <v>9600</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="25">
         <v>50000000</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="27">
+      <c r="K9" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="28">
         <v>100</v>
       </c>
-      <c r="M9" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="14">
+      <c r="M9" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="17">
         <v>0</v>
       </c>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-    </row>
-    <row r="10" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A10" s="12">
         <v>1003003</v>
       </c>
@@ -1469,49 +2045,49 @@
         <v>100300</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="17">
+        <v>44</v>
+      </c>
+      <c r="D10" s="18">
         <v>100100026</v>
       </c>
       <c r="E10" s="13">
         <v>3</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>44</v>
+      <c r="F10" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="18">
+        <v>46</v>
+      </c>
+      <c r="H10" s="19">
         <v>500000000000</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="26">
         <v>9600</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="25">
         <v>5000000000</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="27">
+      <c r="K10" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="28">
         <v>100</v>
       </c>
-      <c r="M10" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10" s="14">
+      <c r="M10" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="17">
         <v>0</v>
       </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-    </row>
-    <row r="11" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A11" s="12">
         <v>1007001</v>
       </c>
@@ -1519,49 +2095,49 @@
         <v>100700</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="17">
+        <v>47</v>
+      </c>
+      <c r="D11" s="18">
         <v>100100026</v>
       </c>
       <c r="E11" s="13">
         <v>1</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>47</v>
+      <c r="F11" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="16">
         <v>50000000</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="25">
         <v>9700</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="25">
         <v>500000</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="27">
+      <c r="K11" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="28">
         <v>0</v>
       </c>
-      <c r="M11" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="14">
+      <c r="M11" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" s="17">
         <v>0</v>
       </c>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-    </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A12" s="12">
         <v>1007002</v>
       </c>
@@ -1569,49 +2145,49 @@
         <v>100700</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="17">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18">
         <v>100100026</v>
       </c>
       <c r="E12" s="13">
         <v>2</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>49</v>
+      <c r="F12" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="25">
         <v>9700</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="25">
         <v>50000000</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="27">
+      <c r="K12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="28">
         <v>0</v>
       </c>
-      <c r="M12" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="14">
+      <c r="M12" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12" s="17">
         <v>0</v>
       </c>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-    </row>
-    <row r="13" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A13" s="12">
         <v>1007003</v>
       </c>
@@ -1619,49 +2195,49 @@
         <v>100700</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="17">
+        <v>47</v>
+      </c>
+      <c r="D13" s="18">
         <v>100100026</v>
       </c>
       <c r="E13" s="13">
         <v>3</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>51</v>
+      <c r="F13" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="18">
+        <v>53</v>
+      </c>
+      <c r="H13" s="19">
         <v>500000000000</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="25">
         <v>9700</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="25">
         <v>5000000000</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="27">
+      <c r="K13" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="28">
         <v>0</v>
       </c>
-      <c r="M13" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13" s="14">
+      <c r="M13" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="17">
         <v>0</v>
       </c>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-    </row>
-    <row r="14" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A14" s="12">
         <v>1012001</v>
       </c>
@@ -1669,49 +2245,49 @@
         <v>101200</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="17">
+        <v>54</v>
+      </c>
+      <c r="D14" s="18">
         <v>100100026</v>
       </c>
       <c r="E14" s="13">
         <v>1</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>54</v>
+      <c r="F14" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14" s="16">
         <v>50000000</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="26">
         <v>9600</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="25">
         <v>500000</v>
       </c>
-      <c r="K14" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="27">
+      <c r="K14" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="28">
         <v>100</v>
       </c>
-      <c r="M14" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" s="14">
+      <c r="M14" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="17">
         <v>0</v>
       </c>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-    </row>
-    <row r="15" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A15" s="12">
         <v>1012002</v>
       </c>
@@ -1719,49 +2295,49 @@
         <v>101200</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="17">
+        <v>54</v>
+      </c>
+      <c r="D15" s="18">
         <v>100100026</v>
       </c>
       <c r="E15" s="13">
         <v>2</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>56</v>
+      <c r="F15" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="26">
         <v>9600</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="25">
         <v>50000000</v>
       </c>
-      <c r="K15" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="27">
+      <c r="K15" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="28">
         <v>100</v>
       </c>
-      <c r="M15" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N15" s="14">
+      <c r="M15" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="17">
         <v>0</v>
       </c>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A16" s="12">
         <v>1012003</v>
       </c>
@@ -1769,49 +2345,49 @@
         <v>101200</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="17">
+        <v>54</v>
+      </c>
+      <c r="D16" s="18">
         <v>100100026</v>
       </c>
       <c r="E16" s="13">
         <v>3</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>58</v>
+      <c r="F16" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="18">
+        <v>60</v>
+      </c>
+      <c r="H16" s="19">
         <v>500000000000</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="26">
         <v>9600</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="25">
         <v>5000000000</v>
       </c>
-      <c r="K16" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="27">
+      <c r="K16" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="28">
         <v>100</v>
       </c>
-      <c r="M16" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="N16" s="14">
+      <c r="M16" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="17">
         <v>0</v>
       </c>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A17" s="12">
         <v>1014001</v>
       </c>
@@ -1819,49 +2395,49 @@
         <v>101400</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="17">
+        <v>61</v>
+      </c>
+      <c r="D17" s="18">
         <v>100100026</v>
       </c>
       <c r="E17" s="13">
         <v>1</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>61</v>
+      <c r="F17" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" s="16">
         <v>50000000</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <v>9600</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="25">
         <v>500000</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="27">
+      <c r="K17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="28">
         <v>100</v>
       </c>
-      <c r="M17" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N17" s="14">
+      <c r="M17" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="17">
         <v>0</v>
       </c>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A18" s="12">
         <v>1014002</v>
       </c>
@@ -1869,49 +2445,49 @@
         <v>101400</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="17">
+        <v>61</v>
+      </c>
+      <c r="D18" s="18">
         <v>100100026</v>
       </c>
       <c r="E18" s="13">
         <v>2</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>63</v>
+      <c r="F18" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="16">
         <v>5000000000</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="26">
         <v>9600</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="25">
         <v>50000000</v>
       </c>
-      <c r="K18" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" s="27">
+      <c r="K18" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="28">
         <v>100</v>
       </c>
-      <c r="M18" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" s="14">
+      <c r="M18" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="17">
         <v>0</v>
       </c>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-    </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" ht="16.5">
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A19" s="12">
         <v>1014003</v>
       </c>
@@ -1919,85 +2495,232 @@
         <v>101400</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="17">
+        <v>61</v>
+      </c>
+      <c r="D19" s="18">
         <v>100100026</v>
       </c>
       <c r="E19" s="13">
         <v>3</v>
       </c>
-      <c r="F19" s="14" t="s">
-        <v>65</v>
+      <c r="F19" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="18">
+        <v>67</v>
+      </c>
+      <c r="H19" s="19">
         <v>500000000000</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="26">
         <v>9600</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="25">
         <v>5000000000</v>
       </c>
-      <c r="K19" s="26" t="s">
+      <c r="K19" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="28">
+        <v>100</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N19" s="17">
+        <v>0</v>
+      </c>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A20" s="12">
+        <v>1024001</v>
+      </c>
+      <c r="B20" s="12">
+        <v>102400</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="E20" s="13">
+        <v>1</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="L19" s="27">
+      <c r="H20" s="16">
+        <v>50000000</v>
+      </c>
+      <c r="I20" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J20" s="25">
+        <v>500000</v>
+      </c>
+      <c r="K20" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="28">
         <v>100</v>
       </c>
-      <c r="M19" s="24" t="s">
+      <c r="M20" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="17">
+        <v>0</v>
+      </c>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A21" s="12">
+        <v>1024002</v>
+      </c>
+      <c r="B21" s="12">
+        <v>102400</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="E21" s="13">
+        <v>2</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="16">
+        <v>5000000000</v>
+      </c>
+      <c r="I21" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J21" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="28">
+        <v>100</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="17">
+        <v>0</v>
+      </c>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A22" s="12">
+        <v>1024003</v>
+      </c>
+      <c r="B22" s="12">
+        <v>102400</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="E22" s="13">
+        <v>3</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="N19" s="14">
+      <c r="H22" s="19">
+        <v>500000000000</v>
+      </c>
+      <c r="I22" s="26">
+        <v>9600</v>
+      </c>
+      <c r="J22" s="25">
+        <v>5000000000</v>
+      </c>
+      <c r="K22" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="28">
+        <v>100</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="17">
         <v>0</v>
       </c>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="K20" s="28"/>
-    </row>
-    <row r="34" spans="6:14" ht="16.5">
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-    </row>
-    <row r="35" spans="6:14" ht="16.5">
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-    </row>
-    <row r="37" spans="6:14">
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+    </row>
+    <row r="34" ht="16.5" spans="8:14">
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
+    </row>
+    <row r="35" ht="16.5" spans="8:14">
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+    </row>
+    <row r="37" spans="9:13">
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" spans="6:14">
+    <row r="38" spans="9:13">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" spans="6:14" ht="16.5">
-      <c r="F39" s="20"/>
+    <row r="39" ht="16.5" spans="6:13">
+      <c r="F39" s="21"/>
       <c r="G39" s="13"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2005,8 +2728,8 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="6:14" ht="16.5">
-      <c r="F40" s="20"/>
+    <row r="40" ht="16.5" spans="6:13">
+      <c r="F40" s="21"/>
       <c r="G40" s="13"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2014,8 +2737,8 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" spans="6:14" ht="16.5">
-      <c r="F41" s="20"/>
+    <row r="41" ht="16.5" spans="6:13">
+      <c r="F41" s="21"/>
       <c r="G41" s="13"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2023,7 +2746,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" spans="6:14" ht="16.5">
+    <row r="42" ht="16.5" spans="7:13">
       <c r="G42" s="13"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2031,7 +2754,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" spans="6:14" ht="16.5">
+    <row r="43" ht="16.5" spans="7:13">
       <c r="G43" s="13"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2039,7 +2762,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="6:14" ht="16.5">
+    <row r="44" ht="16.5" spans="7:13">
       <c r="G44" s="13"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2047,7 +2770,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="6:14" ht="16.5">
+    <row r="45" ht="16.5" spans="7:13">
       <c r="G45" s="13"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2055,7 +2778,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="6:14" ht="16.5">
+    <row r="46" ht="16.5" spans="7:13">
       <c r="G46" s="13"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2063,7 +2786,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="6:14" ht="16.5">
+    <row r="47" ht="16.5" spans="7:13">
       <c r="G47" s="13"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2071,7 +2794,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="6:14" ht="16.5">
+    <row r="48" ht="16.5" spans="7:13">
       <c r="G48" s="13"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2079,7 +2802,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="7:13" ht="16.5">
+    <row r="49" ht="16.5" spans="7:13">
       <c r="G49" s="13"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2087,7 +2810,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="7:13" ht="16.5">
+    <row r="50" ht="16.5" spans="7:13">
       <c r="G50" s="13"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2095,7 +2818,7 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="7:13" ht="16.5">
+    <row r="51" ht="16.5" spans="7:13">
       <c r="G51" s="13"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2103,7 +2826,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="7:13" ht="16.5">
+    <row r="52" ht="16.5" spans="7:13">
       <c r="G52" s="13"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2111,7 +2834,7 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="7:13" ht="16.5">
+    <row r="53" ht="16.5" spans="7:13">
       <c r="G53" s="13"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2120,9 +2843,9 @@
       <c r="M53" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>1000000:1</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>雷神</t>
   </si>
 </sst>
 </file>
@@ -404,7 +410,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,18 +436,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -455,13 +463,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -617,6 +618,31 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -630,36 +656,11 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,18 +783,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -831,12 +820,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1051,82 +1034,88 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1135,56 +1124,50 @@
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1216,59 +1199,56 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1627,7 +1607,7 @@
     <col min="15" max="15" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:20">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1652,16 +1632,16 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -1672,86 +1652,86 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="20" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -1760,1042 +1740,1342 @@
       <c r="N3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A5" s="12">
+      <c r="A5" s="16">
         <v>1001001</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="16">
         <v>100100</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="21">
         <v>100100026</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="17">
         <v>1</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="11">
         <v>50000000</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="22">
         <v>9600</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="20">
         <v>500000</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="24">
         <v>100</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <v>0</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A6" s="12">
+      <c r="A6" s="16">
         <v>1001002</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="16">
         <v>100100</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="21">
         <v>100100026</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="17">
         <v>2</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="22">
         <v>9600</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="20">
         <v>50000000</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="24">
         <v>100</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <v>0</v>
       </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A7" s="12">
+      <c r="A7" s="16">
         <v>1001003</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="16">
         <v>100100</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="21">
         <v>100100026</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="17">
         <v>3</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="22">
         <v>9600</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="24">
         <v>100</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <v>0</v>
       </c>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A8" s="12">
+      <c r="A8" s="16">
         <v>1003001</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="16">
         <v>100300</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="21">
         <v>100100026</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="17">
         <v>1</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="11">
         <v>50000000</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="22">
         <v>9600</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="20">
         <v>500000</v>
       </c>
-      <c r="K8" s="27" t="s">
+      <c r="K8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="24">
         <v>100</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <v>0</v>
       </c>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A9" s="12">
+      <c r="A9" s="16">
         <v>1003002</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="16">
         <v>100300</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <v>100100026</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="17">
         <v>2</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="22">
         <v>9600</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="20">
         <v>50000000</v>
       </c>
-      <c r="K9" s="27" t="s">
+      <c r="K9" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="24">
         <v>100</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="18">
         <v>0</v>
       </c>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A10" s="12">
+      <c r="A10" s="16">
         <v>1003003</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="16">
         <v>100300</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="21">
         <v>100100026</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="17">
         <v>3</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="22">
         <v>9600</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="24">
         <v>100</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="18">
         <v>0</v>
       </c>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A11" s="12">
+      <c r="A11" s="16">
         <v>1007001</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="16">
         <v>100700</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="21">
         <v>100100026</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="17">
         <v>1</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="11">
         <v>50000000</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="20">
         <v>9700</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="20">
         <v>500000</v>
       </c>
-      <c r="K11" s="27" t="s">
+      <c r="K11" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="24">
         <v>0</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <v>0</v>
       </c>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A12" s="12">
+      <c r="A12" s="16">
         <v>1007002</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="16">
         <v>100700</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="21">
         <v>100100026</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="17">
         <v>2</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="20">
         <v>9700</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="20">
         <v>50000000</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="24">
         <v>0</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="M12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="18">
         <v>0</v>
       </c>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A13" s="12">
+      <c r="A13" s="16">
         <v>1007003</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="16">
         <v>100700</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="21">
         <v>100100026</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="17">
         <v>3</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="20">
         <v>9700</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="24">
         <v>0</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="18">
         <v>0</v>
       </c>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A14" s="12">
+      <c r="A14" s="16">
         <v>1012001</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="16">
         <v>101200</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="21">
         <v>100100026</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="17">
         <v>1</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="11">
         <v>50000000</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="22">
         <v>9600</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="20">
         <v>500000</v>
       </c>
-      <c r="K14" s="27" t="s">
+      <c r="K14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="24">
         <v>100</v>
       </c>
-      <c r="M14" s="25" t="s">
+      <c r="M14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="18">
         <v>0</v>
       </c>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A15" s="12">
+      <c r="A15" s="16">
         <v>1012002</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="16">
         <v>101200</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="21">
         <v>100100026</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="17">
         <v>2</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="22">
         <v>9600</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="20">
         <v>50000000</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K15" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="24">
         <v>100</v>
       </c>
-      <c r="M15" s="25" t="s">
+      <c r="M15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <v>0</v>
       </c>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A16" s="12">
+      <c r="A16" s="16">
         <v>1012003</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="16">
         <v>101200</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <v>100100026</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="17">
         <v>3</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="22">
         <v>9600</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K16" s="27" t="s">
+      <c r="K16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="24">
         <v>100</v>
       </c>
-      <c r="M16" s="25" t="s">
+      <c r="M16" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <v>0</v>
       </c>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A17" s="12">
+      <c r="A17" s="16">
         <v>1014001</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="16">
         <v>101400</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="21">
         <v>100100026</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="17">
         <v>1</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="11">
         <v>50000000</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="22">
         <v>9600</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="20">
         <v>500000</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="24">
         <v>100</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="18">
         <v>0</v>
       </c>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A18" s="12">
+      <c r="A18" s="16">
         <v>1014002</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="16">
         <v>101400</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="21">
         <v>100100026</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="17">
         <v>2</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="22">
         <v>9600</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="20">
         <v>50000000</v>
       </c>
-      <c r="K18" s="27" t="s">
+      <c r="K18" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="24">
         <v>100</v>
       </c>
-      <c r="M18" s="25" t="s">
+      <c r="M18" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N18" s="17">
+      <c r="N18" s="18">
         <v>0</v>
       </c>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A19" s="12">
+      <c r="A19" s="16">
         <v>1014003</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="16">
         <v>101400</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="21">
         <v>100100026</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="17">
         <v>3</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="22">
         <v>9600</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K19" s="27" t="s">
+      <c r="K19" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="24">
         <v>100</v>
       </c>
-      <c r="M19" s="25" t="s">
+      <c r="M19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="18">
         <v>0</v>
       </c>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A20" s="12">
+      <c r="A20" s="16">
         <v>1024001</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="16">
         <v>102400</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="21">
         <v>102400026</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="17">
         <v>1</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="11">
         <v>50000000</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="22">
         <v>9600</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="20">
         <v>500000</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="24">
         <v>100</v>
       </c>
-      <c r="M20" s="25" t="s">
+      <c r="M20" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <v>0</v>
       </c>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A21" s="12">
+      <c r="A21" s="16">
         <v>1024002</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="16">
         <v>102400</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="21">
         <v>102400026</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="17">
         <v>2</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="11">
         <v>5000000000</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="22">
         <v>9600</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="20">
         <v>50000000</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="24">
         <v>100</v>
       </c>
-      <c r="M21" s="25" t="s">
+      <c r="M21" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>0</v>
       </c>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A22" s="12">
+      <c r="A22" s="16">
         <v>1024003</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="16">
         <v>102400</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="21">
         <v>102400026</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="17">
         <v>3</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="25">
         <v>500000000000</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="22">
         <v>9600</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="20">
         <v>5000000000</v>
       </c>
-      <c r="K22" s="27" t="s">
+      <c r="K22" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="24">
         <v>100</v>
       </c>
-      <c r="M22" s="25" t="s">
+      <c r="M22" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="18">
         <v>0</v>
       </c>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-    </row>
-    <row r="34" ht="16.5" spans="8:14">
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-    </row>
-    <row r="35" ht="16.5" spans="8:14">
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-    </row>
-    <row r="37" spans="9:13">
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A23" s="16">
+        <v>1017001</v>
+      </c>
+      <c r="B23" s="16">
+        <v>101700</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="21">
+        <v>101700001</v>
+      </c>
+      <c r="E23" s="17">
+        <v>1</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="11">
+        <v>50000000</v>
+      </c>
+      <c r="I23" s="20">
+        <v>9700</v>
+      </c>
+      <c r="J23" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="24">
+        <v>100</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="18">
+        <v>0</v>
+      </c>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A24" s="16">
+        <v>1017002</v>
+      </c>
+      <c r="B24" s="16">
+        <v>101700</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="21">
+        <v>101700001</v>
+      </c>
+      <c r="E24" s="17">
+        <v>2</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="11">
+        <v>5000000000</v>
+      </c>
+      <c r="I24" s="20">
+        <v>9700</v>
+      </c>
+      <c r="J24" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="24">
+        <v>100</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="18">
+        <v>0</v>
+      </c>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A25" s="16">
+        <v>1017003</v>
+      </c>
+      <c r="B25" s="16">
+        <v>101700</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="21">
+        <v>101700001</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="25">
+        <v>500000000000</v>
+      </c>
+      <c r="I25" s="20">
+        <v>9700</v>
+      </c>
+      <c r="J25" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="24">
+        <v>100</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" s="18">
+        <v>0</v>
+      </c>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A26" s="16">
+        <v>1022001</v>
+      </c>
+      <c r="B26" s="16">
+        <v>102200</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="21">
+        <v>102200001</v>
+      </c>
+      <c r="E26" s="17">
+        <v>1</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="I26" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J26" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="24">
+        <v>100</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="18">
+        <v>0</v>
+      </c>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A27" s="16">
+        <v>1022002</v>
+      </c>
+      <c r="B27" s="16">
+        <v>102200</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="21">
+        <v>102200001</v>
+      </c>
+      <c r="E27" s="17">
+        <v>2</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="25">
+        <v>5000000000</v>
+      </c>
+      <c r="I27" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J27" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="24">
+        <v>100</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27" s="18">
+        <v>0</v>
+      </c>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A28" s="16">
+        <v>1022003</v>
+      </c>
+      <c r="B28" s="16">
+        <v>102200</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="21">
+        <v>102200001</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="25">
+        <v>500000000000</v>
+      </c>
+      <c r="I28" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J28" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="24">
+        <v>100</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" s="18">
+        <v>0</v>
+      </c>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+    </row>
+    <row r="34" ht="16.5" spans="6:14">
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+    </row>
+    <row r="35" ht="16.5" spans="6:14">
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+    </row>
+    <row r="37" spans="6:14">
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" spans="9:13">
+    <row r="38" spans="6:14">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" ht="16.5" spans="6:13">
-      <c r="F39" s="21"/>
-      <c r="G39" s="13"/>
+    <row r="39" ht="16.5" spans="6:14">
+      <c r="F39" s="27"/>
+      <c r="G39" s="17"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" ht="16.5" spans="6:13">
-      <c r="F40" s="21"/>
-      <c r="G40" s="13"/>
+    <row r="40" ht="16.5" spans="6:14">
+      <c r="F40" s="27"/>
+      <c r="G40" s="17"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" ht="16.5" spans="6:13">
-      <c r="F41" s="21"/>
-      <c r="G41" s="13"/>
+    <row r="41" ht="16.5" spans="6:14">
+      <c r="F41" s="27"/>
+      <c r="G41" s="17"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" ht="16.5" spans="7:13">
-      <c r="G42" s="13"/>
+    <row r="42" ht="16.5" spans="6:14">
+      <c r="G42" s="17"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" ht="16.5" spans="7:13">
-      <c r="G43" s="13"/>
+    <row r="43" ht="16.5" spans="6:14">
+      <c r="G43" s="17"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" ht="16.5" spans="7:13">
-      <c r="G44" s="13"/>
+    <row r="44" ht="16.5" spans="6:14">
+      <c r="G44" s="17"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" ht="16.5" spans="7:13">
-      <c r="G45" s="13"/>
+    <row r="45" ht="16.5" spans="6:14">
+      <c r="G45" s="17"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" ht="16.5" spans="7:13">
-      <c r="G46" s="13"/>
+    <row r="46" ht="16.5" spans="6:14">
+      <c r="G46" s="17"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" ht="16.5" spans="7:13">
-      <c r="G47" s="13"/>
+    <row r="47" ht="16.5" spans="6:14">
+      <c r="G47" s="17"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" ht="16.5" spans="7:13">
-      <c r="G48" s="13"/>
+    <row r="48" ht="16.5" spans="6:14">
+      <c r="G48" s="17"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
@@ -2803,7 +3083,7 @@
       <c r="M48" s="4"/>
     </row>
     <row r="49" ht="16.5" spans="7:13">
-      <c r="G49" s="13"/>
+      <c r="G49" s="17"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
@@ -2811,7 +3091,7 @@
       <c r="M49" s="4"/>
     </row>
     <row r="50" ht="16.5" spans="7:13">
-      <c r="G50" s="13"/>
+      <c r="G50" s="17"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -2819,7 +3099,7 @@
       <c r="M50" s="4"/>
     </row>
     <row r="51" ht="16.5" spans="7:13">
-      <c r="G51" s="13"/>
+      <c r="G51" s="17"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
@@ -2827,7 +3107,7 @@
       <c r="M51" s="4"/>
     </row>
     <row r="52" ht="16.5" spans="7:13">
-      <c r="G52" s="13"/>
+      <c r="G52" s="17"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
@@ -2835,7 +3115,7 @@
       <c r="M52" s="4"/>
     </row>
     <row r="53" ht="16.5" spans="7:13">
-      <c r="G53" s="13"/>
+      <c r="G53" s="17"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>雷神</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
   </si>
 </sst>
 </file>
@@ -623,26 +626,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -656,7 +640,26 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2967,6 +2970,156 @@
       <c r="S28" s="20"/>
       <c r="T28" s="20"/>
     </row>
+    <row r="29" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A29" s="16">
+        <v>1021001</v>
+      </c>
+      <c r="B29" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="21">
+        <v>102100001</v>
+      </c>
+      <c r="E29" s="17">
+        <v>1</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="25">
+        <v>50000000</v>
+      </c>
+      <c r="I29" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J29" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" s="24">
+        <v>100</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" s="18">
+        <v>0</v>
+      </c>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A30" s="16">
+        <v>1021002</v>
+      </c>
+      <c r="B30" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="21">
+        <v>102100001</v>
+      </c>
+      <c r="E30" s="17">
+        <v>2</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="25">
+        <v>5000000000</v>
+      </c>
+      <c r="I30" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J30" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" s="24">
+        <v>100</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30" s="18">
+        <v>0</v>
+      </c>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A31" s="16">
+        <v>1021003</v>
+      </c>
+      <c r="B31" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="21">
+        <v>102100001</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="25">
+        <v>500000000000</v>
+      </c>
+      <c r="I31" s="20">
+        <v>9600</v>
+      </c>
+      <c r="J31" s="20">
+        <v>5000000000</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" s="24">
+        <v>100</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" s="18">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+    </row>
     <row r="34" ht="16.5" spans="6:14">
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -227,7 +227,7 @@
     <t>跑马触发金额</t>
   </si>
   <si>
-    <t>上庄最低金额</t>
+    <t>准备金最低金额</t>
   </si>
   <si>
     <t>int</t>
@@ -395,10 +395,73 @@
     <t>圣诞狂欢夜</t>
   </si>
   <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
     <t>雷神</t>
   </si>
   <si>
-    <t>杰克船长</t>
+    <t>财富银行</t>
+  </si>
+  <si>
+    <t>1_2_5</t>
+  </si>
+  <si>
+    <t>2:1</t>
+  </si>
+  <si>
+    <t>1980000_10000</t>
+  </si>
+  <si>
+    <t>10_20_50</t>
+  </si>
+  <si>
+    <t>20:1</t>
+  </si>
+  <si>
+    <t>1980000_100000</t>
+  </si>
+  <si>
+    <t>100_200_500</t>
+  </si>
+  <si>
+    <t>200:1</t>
+  </si>
+  <si>
+    <t>1980000_1000000</t>
+  </si>
+  <si>
+    <t>1000_2000_5000</t>
+  </si>
+  <si>
+    <t>2000:1</t>
+  </si>
+  <si>
+    <t>5_10_25</t>
+  </si>
+  <si>
+    <t>50_100_250</t>
+  </si>
+  <si>
+    <t>500_1000_2500</t>
+  </si>
+  <si>
+    <t>6_12_32</t>
+  </si>
+  <si>
+    <t>12:1</t>
+  </si>
+  <si>
+    <t>60_120_320</t>
+  </si>
+  <si>
+    <t>120:1</t>
+  </si>
+  <si>
+    <t>600_1200_3200</t>
+  </si>
+  <si>
+    <t>1200:1</t>
   </si>
 </sst>
 </file>
@@ -413,7 +476,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,13 +521,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -620,9 +676,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -638,37 +706,37 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1037,70 +1105,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1109,22 +1171,22 @@
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,22 +1195,22 @@
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1157,20 +1219,26 @@
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1178,25 +1246,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1205,13 +1275,13 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1232,26 +1302,71 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1593,14 +1708,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
     <col min="6" max="6" width="45.75" customWidth="1"/>
-    <col min="7" max="7" width="14" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.375" style="6" customWidth="1"/>
     <col min="9" max="9" width="21.25" customWidth="1"/>
     <col min="10" max="10" width="14.25" customWidth="1"/>
     <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
@@ -1611,40 +1726,40 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:20">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -1655,86 +1770,86 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="22" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -1743,1537 +1858,2740 @@
       <c r="N3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A5" s="16">
+      <c r="A5" s="18">
         <v>1001001</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="18">
         <v>100100</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="23">
         <v>100100026</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="13">
         <v>50000000</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="24">
         <v>9600</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="22">
         <v>500000</v>
       </c>
-      <c r="K5" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="24">
+      <c r="K5" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="26">
         <v>100</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
+      <c r="N5" s="20">
+        <v>0</v>
+      </c>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A6" s="16">
+      <c r="A6" s="18">
         <v>1001002</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="18">
         <v>100100</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="23">
         <v>100100026</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <v>2</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="13">
         <v>5000000000</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="24">
         <v>9600</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="22">
         <v>50000000</v>
       </c>
-      <c r="K6" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="24">
+      <c r="K6" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="26">
         <v>100</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="18">
-        <v>0</v>
-      </c>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
+      <c r="N6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A7" s="16">
+      <c r="A7" s="18">
         <v>1001003</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="18">
         <v>100100</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="23">
         <v>100100026</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <v>3</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="27">
         <v>500000000000</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="24">
         <v>9600</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="22">
         <v>5000000000</v>
       </c>
-      <c r="K7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="24">
+      <c r="K7" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="26">
         <v>100</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
+      <c r="N7" s="20">
+        <v>0</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A8" s="16">
+      <c r="A8" s="18">
         <v>1003001</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="18">
         <v>100300</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="23">
         <v>100100026</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <v>1</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="13">
         <v>50000000</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="24">
         <v>9600</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="22">
         <v>500000</v>
       </c>
-      <c r="K8" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="24">
+      <c r="K8" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="26">
         <v>100</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
+      <c r="N8" s="20">
+        <v>0</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A9" s="16">
+      <c r="A9" s="18">
         <v>1003002</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="18">
         <v>100300</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="23">
         <v>100100026</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="19">
         <v>2</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="13">
         <v>5000000000</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="24">
         <v>9600</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="22">
         <v>50000000</v>
       </c>
-      <c r="K9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="24">
+      <c r="K9" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="26">
         <v>100</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="M9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
+      <c r="N9" s="20">
+        <v>0</v>
+      </c>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A10" s="16">
+      <c r="A10" s="18">
         <v>1003003</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="18">
         <v>100300</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="23">
         <v>100100026</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="19">
         <v>3</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="27">
         <v>500000000000</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="24">
         <v>9600</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="22">
         <v>5000000000</v>
       </c>
-      <c r="K10" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="24">
+      <c r="K10" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="26">
         <v>100</v>
       </c>
-      <c r="M10" s="20" t="s">
+      <c r="M10" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="18">
-        <v>0</v>
-      </c>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
+      <c r="N10" s="20">
+        <v>0</v>
+      </c>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A11" s="16">
+      <c r="A11" s="18">
         <v>1007001</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="18">
         <v>100700</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="23">
         <v>100100026</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="19">
         <v>1</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="13">
         <v>50000000</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="22">
         <v>9700</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="22">
         <v>500000</v>
       </c>
-      <c r="K11" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="24">
-        <v>0</v>
-      </c>
-      <c r="M11" s="20" t="s">
+      <c r="K11" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="26">
+        <v>0</v>
+      </c>
+      <c r="M11" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="18">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
+      <c r="N11" s="20">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A12" s="16">
+      <c r="A12" s="18">
         <v>1007002</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="18">
         <v>100700</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="23">
         <v>100100026</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <v>2</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="13">
         <v>5000000000</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="22">
         <v>9700</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="22">
         <v>50000000</v>
       </c>
-      <c r="K12" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="24">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20" t="s">
+      <c r="K12" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="26">
+        <v>0</v>
+      </c>
+      <c r="M12" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
+      <c r="N12" s="20">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A13" s="16">
+      <c r="A13" s="18">
         <v>1007003</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="18">
         <v>100700</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="23">
         <v>100100026</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <v>3</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="27">
         <v>500000000000</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="22">
         <v>9700</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="22">
         <v>5000000000</v>
       </c>
-      <c r="K13" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="24">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20" t="s">
+      <c r="K13" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="26">
+        <v>0</v>
+      </c>
+      <c r="M13" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N13" s="18">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
+      <c r="N13" s="20">
+        <v>0</v>
+      </c>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A14" s="16">
+      <c r="A14" s="18">
         <v>1012001</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="18">
         <v>101200</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="23">
         <v>100100026</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="19">
         <v>1</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="13">
         <v>50000000</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="24">
         <v>9600</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="22">
         <v>500000</v>
       </c>
-      <c r="K14" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L14" s="24">
+      <c r="K14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="26">
         <v>100</v>
       </c>
-      <c r="M14" s="20" t="s">
+      <c r="M14" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
+      <c r="N14" s="20">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A15" s="16">
+      <c r="A15" s="18">
         <v>1012002</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="18">
         <v>101200</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="23">
         <v>100100026</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="19">
         <v>2</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="13">
         <v>5000000000</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="24">
         <v>9600</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="22">
         <v>50000000</v>
       </c>
-      <c r="K15" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="24">
+      <c r="K15" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="26">
         <v>100</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N15" s="18">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
+      <c r="N15" s="20">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A16" s="16">
+      <c r="A16" s="18">
         <v>1012003</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="18">
         <v>101200</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="23">
         <v>100100026</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <v>3</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="27">
         <v>500000000000</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="24">
         <v>9600</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="22">
         <v>5000000000</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="24">
+      <c r="K16" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="26">
         <v>100</v>
       </c>
-      <c r="M16" s="20" t="s">
+      <c r="M16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N16" s="18">
-        <v>0</v>
-      </c>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A17" s="16">
+      <c r="A17" s="18">
         <v>1014001</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="18">
         <v>101400</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="23">
         <v>100100026</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="19">
         <v>1</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="13">
         <v>50000000</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="24">
         <v>9600</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="22">
         <v>500000</v>
       </c>
-      <c r="K17" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" s="24">
+      <c r="K17" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="26">
         <v>100</v>
       </c>
-      <c r="M17" s="20" t="s">
+      <c r="M17" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="18">
-        <v>0</v>
-      </c>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
+      <c r="N17" s="20">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A18" s="16">
+      <c r="A18" s="18">
         <v>1014002</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="18">
         <v>101400</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="23">
         <v>100100026</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="19">
         <v>2</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="13">
         <v>5000000000</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="24">
         <v>9600</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="22">
         <v>50000000</v>
       </c>
-      <c r="K18" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="24">
+      <c r="K18" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="26">
         <v>100</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N18" s="18">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A19" s="16">
+      <c r="A19" s="18">
         <v>1014003</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="18">
         <v>101400</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="23">
         <v>100100026</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="19">
         <v>3</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="27">
         <v>500000000000</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="24">
         <v>9600</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="22">
         <v>5000000000</v>
       </c>
-      <c r="K19" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="24">
+      <c r="K19" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="26">
         <v>100</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M19" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="18">
-        <v>0</v>
-      </c>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
+      <c r="N19" s="20">
+        <v>0</v>
+      </c>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A20" s="16">
+      <c r="A20" s="18">
+        <v>1017001</v>
+      </c>
+      <c r="B20" s="18">
+        <v>101700</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="23">
+        <v>101700001</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="13">
+        <v>50000000</v>
+      </c>
+      <c r="I20" s="22">
+        <v>9700</v>
+      </c>
+      <c r="J20" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="26">
+        <v>100</v>
+      </c>
+      <c r="M20" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A21" s="18">
+        <v>1017002</v>
+      </c>
+      <c r="B21" s="18">
+        <v>101700</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="23">
+        <v>101700001</v>
+      </c>
+      <c r="E21" s="19">
+        <v>2</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="I21" s="22">
+        <v>9700</v>
+      </c>
+      <c r="J21" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="26">
+        <v>100</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="20">
+        <v>0</v>
+      </c>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A22" s="18">
+        <v>1017003</v>
+      </c>
+      <c r="B22" s="18">
+        <v>101700</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="23">
+        <v>101700001</v>
+      </c>
+      <c r="E22" s="19">
+        <v>3</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I22" s="22">
+        <v>9700</v>
+      </c>
+      <c r="J22" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="26">
+        <v>100</v>
+      </c>
+      <c r="M22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="20">
+        <v>0</v>
+      </c>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A23" s="18">
+        <v>1021001</v>
+      </c>
+      <c r="B23" s="18">
+        <v>102100</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="23">
+        <v>102100001</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="I23" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J23" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="26">
+        <v>100</v>
+      </c>
+      <c r="M23" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="20">
+        <v>0</v>
+      </c>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A24" s="18">
+        <v>1021002</v>
+      </c>
+      <c r="B24" s="18">
+        <v>102100</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="23">
+        <v>102100001</v>
+      </c>
+      <c r="E24" s="19">
+        <v>2</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="I24" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J24" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="26">
+        <v>100</v>
+      </c>
+      <c r="M24" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="20">
+        <v>0</v>
+      </c>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A25" s="18">
+        <v>1021003</v>
+      </c>
+      <c r="B25" s="18">
+        <v>102100</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="23">
+        <v>102100001</v>
+      </c>
+      <c r="E25" s="19">
+        <v>3</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I25" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J25" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="26">
+        <v>100</v>
+      </c>
+      <c r="M25" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" s="20">
+        <v>0</v>
+      </c>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A26" s="18">
+        <v>1022001</v>
+      </c>
+      <c r="B26" s="18">
+        <v>102200</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="23">
+        <v>102200001</v>
+      </c>
+      <c r="E26" s="19">
+        <v>1</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="I26" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J26" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="26">
+        <v>100</v>
+      </c>
+      <c r="M26" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="20">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A27" s="18">
+        <v>1022002</v>
+      </c>
+      <c r="B27" s="18">
+        <v>102200</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="23">
+        <v>102200001</v>
+      </c>
+      <c r="E27" s="19">
+        <v>2</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="I27" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J27" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="26">
+        <v>100</v>
+      </c>
+      <c r="M27" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27" s="20">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A28" s="18">
+        <v>1022003</v>
+      </c>
+      <c r="B28" s="18">
+        <v>102200</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="23">
+        <v>102200001</v>
+      </c>
+      <c r="E28" s="19">
+        <v>3</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I28" s="22">
+        <v>9600</v>
+      </c>
+      <c r="J28" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="26">
+        <v>100</v>
+      </c>
+      <c r="M28" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" s="20">
+        <v>0</v>
+      </c>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A29" s="18">
         <v>1024001</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B29" s="18">
         <v>102400</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C29" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="23">
+        <v>102400026</v>
+      </c>
+      <c r="E29" s="19">
+        <v>1</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="13">
+        <v>50000000</v>
+      </c>
+      <c r="I29" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J29" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" s="26">
+        <v>100</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" s="20">
+        <v>0</v>
+      </c>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A30" s="18">
+        <v>1024002</v>
+      </c>
+      <c r="B30" s="18">
+        <v>102400</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="23">
+        <v>102400026</v>
+      </c>
+      <c r="E30" s="19">
+        <v>2</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="I30" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J30" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" s="26">
+        <v>100</v>
+      </c>
+      <c r="M30" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30" s="20">
+        <v>0</v>
+      </c>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A31" s="18">
+        <v>1024003</v>
+      </c>
+      <c r="B31" s="18">
+        <v>102400</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="23">
+        <v>102400026</v>
+      </c>
+      <c r="E31" s="19">
+        <v>3</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I31" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J31" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" s="26">
+        <v>100</v>
+      </c>
+      <c r="M31" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0</v>
+      </c>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+    </row>
+    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A32" s="28">
+        <v>10010010</v>
+      </c>
+      <c r="B32" s="29">
+        <v>100100</v>
+      </c>
+      <c r="C32" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D32" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E32" s="32">
+        <v>10</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="35">
+        <v>0</v>
+      </c>
+      <c r="I32" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J32" s="37">
+        <v>0</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="38">
+        <v>0</v>
+      </c>
+      <c r="M32" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+    </row>
+    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A33" s="28">
+        <v>10010011</v>
+      </c>
+      <c r="B33" s="29">
+        <v>100100</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E33" s="32">
+        <v>11</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="35">
+        <v>0</v>
+      </c>
+      <c r="I33" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J33" s="37">
+        <v>0</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="38">
+        <v>0</v>
+      </c>
+      <c r="M33" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+    </row>
+    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A34" s="28">
+        <v>10010012</v>
+      </c>
+      <c r="B34" s="29">
+        <v>100100</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E34" s="32">
+        <v>12</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H34" s="40">
+        <v>0</v>
+      </c>
+      <c r="I34" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J34" s="37">
+        <v>0</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="38">
+        <v>0</v>
+      </c>
+      <c r="M34" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N34" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+    </row>
+    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A35" s="28">
+        <v>10030010</v>
+      </c>
+      <c r="B35" s="29">
+        <v>100300</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E35" s="32">
+        <v>10</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J35" s="37">
+        <v>0</v>
+      </c>
+      <c r="K35" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="41">
+        <v>0</v>
+      </c>
+      <c r="M35" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+    </row>
+    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A36" s="28">
+        <v>10030011</v>
+      </c>
+      <c r="B36" s="29">
+        <v>100300</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E36" s="32">
+        <v>11</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="35">
+        <v>0</v>
+      </c>
+      <c r="I36" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J36" s="37">
+        <v>0</v>
+      </c>
+      <c r="K36" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" s="41">
+        <v>0</v>
+      </c>
+      <c r="M36" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+    </row>
+    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A37" s="28">
+        <v>10030012</v>
+      </c>
+      <c r="B37" s="29">
+        <v>100300</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E37" s="32">
+        <v>12</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" s="40">
+        <v>0</v>
+      </c>
+      <c r="I37" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J37" s="37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="41">
+        <v>0</v>
+      </c>
+      <c r="M37" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+    </row>
+    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A38" s="28">
+        <v>10070010</v>
+      </c>
+      <c r="B38" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E38" s="32">
+        <v>10</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="35">
+        <v>0</v>
+      </c>
+      <c r="I38" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J38" s="37">
+        <v>0</v>
+      </c>
+      <c r="K38" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A39" s="28">
+        <v>10070011</v>
+      </c>
+      <c r="B39" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E39" s="32">
+        <v>11</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="35">
+        <v>0</v>
+      </c>
+      <c r="I39" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J39" s="37">
+        <v>0</v>
+      </c>
+      <c r="K39" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" s="38">
+        <v>0</v>
+      </c>
+      <c r="M39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A40" s="28">
+        <v>10070012</v>
+      </c>
+      <c r="B40" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E40" s="32">
+        <v>12</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" s="40">
+        <v>0</v>
+      </c>
+      <c r="I40" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J40" s="37">
+        <v>0</v>
+      </c>
+      <c r="K40" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="38">
+        <v>0</v>
+      </c>
+      <c r="M40" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N40" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A41" s="28">
+        <v>10120010</v>
+      </c>
+      <c r="B41" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="43">
+        <v>101200026</v>
+      </c>
+      <c r="E41" s="32">
+        <v>10</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="35">
+        <v>0</v>
+      </c>
+      <c r="I41" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J41" s="37">
+        <v>0</v>
+      </c>
+      <c r="K41" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="41">
+        <v>0</v>
+      </c>
+      <c r="M41" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="37"/>
+      <c r="T41" s="37"/>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A42" s="28">
+        <v>10120011</v>
+      </c>
+      <c r="B42" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="43">
+        <v>101200026</v>
+      </c>
+      <c r="E42" s="32">
+        <v>11</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" s="35">
+        <v>0</v>
+      </c>
+      <c r="I42" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J42" s="37">
+        <v>0</v>
+      </c>
+      <c r="K42" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="41">
+        <v>0</v>
+      </c>
+      <c r="M42" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
+      <c r="S42" s="37"/>
+      <c r="T42" s="37"/>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A43" s="28">
+        <v>10120012</v>
+      </c>
+      <c r="B43" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="43">
+        <v>101200026</v>
+      </c>
+      <c r="E43" s="32">
+        <v>12</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="40">
+        <v>0</v>
+      </c>
+      <c r="I43" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J43" s="37">
+        <v>0</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="41">
+        <v>0</v>
+      </c>
+      <c r="M43" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="N43" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O43" s="39"/>
+      <c r="P43" s="39"/>
+      <c r="Q43" s="39"/>
+      <c r="R43" s="39"/>
+      <c r="S43" s="37"/>
+      <c r="T43" s="37"/>
+    </row>
+    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A44" s="28">
+        <v>10140010</v>
+      </c>
+      <c r="B44" s="29">
+        <v>101400</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E44" s="32">
+        <v>10</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="35">
+        <v>0</v>
+      </c>
+      <c r="I44" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J44" s="37">
+        <v>0</v>
+      </c>
+      <c r="K44" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="38">
+        <v>0</v>
+      </c>
+      <c r="M44" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A45" s="28">
+        <v>10140011</v>
+      </c>
+      <c r="B45" s="29">
+        <v>101400</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E45" s="32">
+        <v>11</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="35">
+        <v>0</v>
+      </c>
+      <c r="I45" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J45" s="37">
+        <v>0</v>
+      </c>
+      <c r="K45" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="38">
+        <v>0</v>
+      </c>
+      <c r="M45" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N45" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A46" s="28">
+        <v>10140012</v>
+      </c>
+      <c r="B46" s="29">
+        <v>101400</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="31">
+        <v>100100026</v>
+      </c>
+      <c r="E46" s="32">
+        <v>12</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" s="40">
+        <v>0</v>
+      </c>
+      <c r="I46" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J46" s="37">
+        <v>0</v>
+      </c>
+      <c r="K46" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="38">
+        <v>0</v>
+      </c>
+      <c r="M46" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N46" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+    </row>
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A47" s="28">
+        <v>10170010</v>
+      </c>
+      <c r="B47" s="29">
+        <v>101700</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="31">
+        <v>101700001</v>
+      </c>
+      <c r="E47" s="32">
+        <v>10</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G47" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="35">
+        <v>0</v>
+      </c>
+      <c r="I47" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J47" s="37">
+        <v>0</v>
+      </c>
+      <c r="K47" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="38">
+        <v>0</v>
+      </c>
+      <c r="M47" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+    </row>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A48" s="28">
+        <v>10170011</v>
+      </c>
+      <c r="B48" s="29">
+        <v>101700</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="31">
+        <v>101700001</v>
+      </c>
+      <c r="E48" s="32">
+        <v>11</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="35">
+        <v>0</v>
+      </c>
+      <c r="I48" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J48" s="37">
+        <v>0</v>
+      </c>
+      <c r="K48" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="38">
+        <v>0</v>
+      </c>
+      <c r="M48" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N48" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A49" s="28">
+        <v>10170012</v>
+      </c>
+      <c r="B49" s="29">
+        <v>101700</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="31">
+        <v>101700001</v>
+      </c>
+      <c r="E49" s="32">
+        <v>12</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="40">
+        <v>0</v>
+      </c>
+      <c r="I49" s="36">
+        <v>9700</v>
+      </c>
+      <c r="J49" s="37">
+        <v>0</v>
+      </c>
+      <c r="K49" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="38">
+        <v>0</v>
+      </c>
+      <c r="M49" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N49" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A50" s="28">
+        <v>10210010</v>
+      </c>
+      <c r="B50" s="29">
+        <v>102100</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="31">
+        <v>102100001</v>
+      </c>
+      <c r="E50" s="32">
+        <v>10</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G50" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50" s="35">
+        <v>0</v>
+      </c>
+      <c r="I50" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J50" s="37">
+        <v>0</v>
+      </c>
+      <c r="K50" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="41">
+        <v>0</v>
+      </c>
+      <c r="M50" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+    </row>
+    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A51" s="28">
+        <v>10210011</v>
+      </c>
+      <c r="B51" s="29">
+        <v>102100</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="31">
+        <v>102100001</v>
+      </c>
+      <c r="E51" s="32">
+        <v>11</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="35">
+        <v>0</v>
+      </c>
+      <c r="I51" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J51" s="37">
+        <v>0</v>
+      </c>
+      <c r="K51" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="41">
+        <v>0</v>
+      </c>
+      <c r="M51" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+    </row>
+    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A52" s="28">
+        <v>10210012</v>
+      </c>
+      <c r="B52" s="29">
+        <v>102100</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="31">
+        <v>102100001</v>
+      </c>
+      <c r="E52" s="32">
+        <v>12</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" s="40">
+        <v>0</v>
+      </c>
+      <c r="I52" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J52" s="37">
+        <v>0</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="41">
+        <v>0</v>
+      </c>
+      <c r="M52" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N52" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
+    </row>
+    <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A53" s="28">
+        <v>10220010</v>
+      </c>
+      <c r="B53" s="29">
+        <v>102200</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="31">
+        <v>102200001</v>
+      </c>
+      <c r="E53" s="32">
+        <v>10</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="35">
+        <v>0</v>
+      </c>
+      <c r="I53" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J53" s="37">
+        <v>0</v>
+      </c>
+      <c r="K53" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="41">
+        <v>0</v>
+      </c>
+      <c r="M53" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="36"/>
+    </row>
+    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A54" s="28">
+        <v>10220011</v>
+      </c>
+      <c r="B54" s="29">
+        <v>102200</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="31">
+        <v>102200001</v>
+      </c>
+      <c r="E54" s="32">
+        <v>11</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H54" s="35">
+        <v>0</v>
+      </c>
+      <c r="I54" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J54" s="37">
+        <v>0</v>
+      </c>
+      <c r="K54" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="41">
+        <v>0</v>
+      </c>
+      <c r="M54" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36"/>
+    </row>
+    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A55" s="28">
+        <v>10220012</v>
+      </c>
+      <c r="B55" s="29">
+        <v>102200</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="31">
+        <v>102200001</v>
+      </c>
+      <c r="E55" s="32">
+        <v>12</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="40">
+        <v>0</v>
+      </c>
+      <c r="I55" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J55" s="37">
+        <v>0</v>
+      </c>
+      <c r="K55" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="41">
+        <v>0</v>
+      </c>
+      <c r="M55" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N55" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O55" s="33"/>
+      <c r="P55" s="33"/>
+      <c r="Q55" s="33"/>
+      <c r="R55" s="33"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+    </row>
+    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A56" s="28">
+        <v>10240010</v>
+      </c>
+      <c r="B56" s="29">
+        <v>102400</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="31">
         <v>102400026</v>
       </c>
-      <c r="E20" s="17">
-        <v>1</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="11">
-        <v>50000000</v>
-      </c>
-      <c r="I20" s="22">
+      <c r="E56" s="32">
+        <v>10</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H56" s="35">
+        <v>0</v>
+      </c>
+      <c r="I56" s="36">
         <v>9600</v>
       </c>
-      <c r="J20" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" s="24">
-        <v>100</v>
-      </c>
-      <c r="M20" s="20" t="s">
+      <c r="J56" s="37">
+        <v>0</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="41">
+        <v>0</v>
+      </c>
+      <c r="M56" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="N20" s="18">
-        <v>0</v>
-      </c>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A21" s="16">
-        <v>1024002</v>
-      </c>
-      <c r="B21" s="16">
+      <c r="N56" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="36"/>
+    </row>
+    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A57" s="28">
+        <v>10240011</v>
+      </c>
+      <c r="B57" s="29">
         <v>102400</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C57" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" s="31">
         <v>102400026</v>
       </c>
-      <c r="E21" s="17">
-        <v>2</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21" s="11">
-        <v>5000000000</v>
-      </c>
-      <c r="I21" s="22">
+      <c r="E57" s="32">
+        <v>11</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" s="35">
+        <v>0</v>
+      </c>
+      <c r="I57" s="36">
         <v>9600</v>
       </c>
-      <c r="J21" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="24">
-        <v>100</v>
-      </c>
-      <c r="M21" s="20" t="s">
+      <c r="J57" s="37">
+        <v>0</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="41">
+        <v>0</v>
+      </c>
+      <c r="M57" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="18">
-        <v>0</v>
-      </c>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A22" s="16">
-        <v>1024003</v>
-      </c>
-      <c r="B22" s="16">
+      <c r="N57" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="O57" s="33"/>
+      <c r="P57" s="33"/>
+      <c r="Q57" s="33"/>
+      <c r="R57" s="33"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+    </row>
+    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A58" s="28">
+        <v>10240012</v>
+      </c>
+      <c r="B58" s="29">
         <v>102400</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="21">
+      <c r="C58" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" s="31">
         <v>102400026</v>
       </c>
-      <c r="E22" s="17">
-        <v>3</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="25">
-        <v>500000000000</v>
-      </c>
-      <c r="I22" s="22">
+      <c r="E58" s="32">
+        <v>12</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G58" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H58" s="40">
+        <v>0</v>
+      </c>
+      <c r="I58" s="36">
         <v>9600</v>
       </c>
-      <c r="J22" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L22" s="24">
-        <v>100</v>
-      </c>
-      <c r="M22" s="20" t="s">
+      <c r="J58" s="37">
+        <v>0</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="41">
+        <v>0</v>
+      </c>
+      <c r="M58" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="18">
-        <v>0</v>
-      </c>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A23" s="16">
-        <v>1017001</v>
-      </c>
-      <c r="B23" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="21">
-        <v>101700001</v>
-      </c>
-      <c r="E23" s="17">
-        <v>1</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="11">
-        <v>50000000</v>
-      </c>
-      <c r="I23" s="20">
-        <v>9700</v>
-      </c>
-      <c r="J23" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K23" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L23" s="24">
-        <v>100</v>
-      </c>
-      <c r="M23" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" s="18">
-        <v>0</v>
-      </c>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A24" s="16">
-        <v>1017002</v>
-      </c>
-      <c r="B24" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="21">
-        <v>101700001</v>
-      </c>
-      <c r="E24" s="17">
-        <v>2</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" s="11">
-        <v>5000000000</v>
-      </c>
-      <c r="I24" s="20">
-        <v>9700</v>
-      </c>
-      <c r="J24" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="K24" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L24" s="24">
-        <v>100</v>
-      </c>
-      <c r="M24" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" s="18">
-        <v>0</v>
-      </c>
-      <c r="O24" s="18"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="18"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A25" s="16">
-        <v>1017003</v>
-      </c>
-      <c r="B25" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="21">
-        <v>101700001</v>
-      </c>
-      <c r="E25" s="17">
-        <v>3</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="25">
-        <v>500000000000</v>
-      </c>
-      <c r="I25" s="20">
-        <v>9700</v>
-      </c>
-      <c r="J25" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" s="24">
-        <v>100</v>
-      </c>
-      <c r="M25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" s="18">
-        <v>0</v>
-      </c>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A26" s="16">
-        <v>1022001</v>
-      </c>
-      <c r="B26" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="21">
-        <v>102200001</v>
-      </c>
-      <c r="E26" s="17">
-        <v>1</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" s="25">
-        <v>50000000</v>
-      </c>
-      <c r="I26" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J26" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K26" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L26" s="24">
-        <v>100</v>
-      </c>
-      <c r="M26" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A27" s="16">
-        <v>1022002</v>
-      </c>
-      <c r="B27" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="21">
-        <v>102200001</v>
-      </c>
-      <c r="E27" s="17">
-        <v>2</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H27" s="25">
-        <v>5000000000</v>
-      </c>
-      <c r="I27" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J27" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L27" s="24">
-        <v>100</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A28" s="16">
-        <v>1022003</v>
-      </c>
-      <c r="B28" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="21">
-        <v>102200001</v>
-      </c>
-      <c r="E28" s="17">
-        <v>3</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="25">
-        <v>500000000000</v>
-      </c>
-      <c r="I28" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J28" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L28" s="24">
-        <v>100</v>
-      </c>
-      <c r="M28" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-    </row>
-    <row r="29" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A29" s="16">
-        <v>1021001</v>
-      </c>
-      <c r="B29" s="16">
-        <v>102100</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="21">
-        <v>102100001</v>
-      </c>
-      <c r="E29" s="17">
-        <v>1</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="25">
-        <v>50000000</v>
-      </c>
-      <c r="I29" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J29" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L29" s="24">
-        <v>100</v>
-      </c>
-      <c r="M29" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N29" s="18">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A30" s="16">
-        <v>1021002</v>
-      </c>
-      <c r="B30" s="16">
-        <v>102100</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="21">
-        <v>102100001</v>
-      </c>
-      <c r="E30" s="17">
-        <v>2</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="25">
-        <v>5000000000</v>
-      </c>
-      <c r="I30" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J30" s="20">
-        <v>50000000</v>
-      </c>
-      <c r="K30" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L30" s="24">
-        <v>100</v>
-      </c>
-      <c r="M30" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A31" s="16">
-        <v>1021003</v>
-      </c>
-      <c r="B31" s="16">
-        <v>102100</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="21">
-        <v>102100001</v>
-      </c>
-      <c r="E31" s="17">
-        <v>3</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H31" s="25">
-        <v>500000000000</v>
-      </c>
-      <c r="I31" s="20">
-        <v>9600</v>
-      </c>
-      <c r="J31" s="20">
-        <v>5000000000</v>
-      </c>
-      <c r="K31" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L31" s="24">
-        <v>100</v>
-      </c>
-      <c r="M31" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-    </row>
-    <row r="34" ht="16.5" spans="6:14">
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-    </row>
-    <row r="35" ht="16.5" spans="6:14">
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-    </row>
-    <row r="37" spans="6:14">
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" spans="6:14">
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" ht="16.5" spans="6:14">
-      <c r="F39" s="27"/>
-      <c r="G39" s="17"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" ht="16.5" spans="6:14">
-      <c r="F40" s="27"/>
-      <c r="G40" s="17"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" ht="16.5" spans="6:14">
-      <c r="F41" s="27"/>
-      <c r="G41" s="17"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" ht="16.5" spans="6:14">
-      <c r="G42" s="17"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" ht="16.5" spans="6:14">
-      <c r="G43" s="17"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" ht="16.5" spans="6:14">
-      <c r="G44" s="17"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" ht="16.5" spans="6:14">
-      <c r="G45" s="17"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" ht="16.5" spans="6:14">
-      <c r="G46" s="17"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" ht="16.5" spans="6:14">
-      <c r="G47" s="17"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" ht="16.5" spans="6:14">
-      <c r="G48" s="17"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" ht="16.5" spans="7:13">
-      <c r="G49" s="17"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" ht="16.5" spans="7:13">
-      <c r="G50" s="17"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" ht="16.5" spans="7:13">
-      <c r="G51" s="17"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" ht="16.5" spans="7:13">
-      <c r="G52" s="17"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" ht="16.5" spans="7:13">
-      <c r="G53" s="17"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
+      <c r="N58" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="O58" s="33"/>
+      <c r="P58" s="33"/>
+      <c r="Q58" s="33"/>
+      <c r="R58" s="33"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:20">
+      <c r="G59" s="19"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -404,6 +404,27 @@
     <t>财富银行</t>
   </si>
   <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>2_4_8_20_40</t>
+  </si>
+  <si>
+    <t>8:1</t>
+  </si>
+  <si>
+    <t>200_400_800_2000_4000</t>
+  </si>
+  <si>
+    <t>800:1</t>
+  </si>
+  <si>
+    <t>20000_40000_80000_200000_400000</t>
+  </si>
+  <si>
+    <t>80000:1</t>
+  </si>
+  <si>
     <t>1_2_5</t>
   </si>
   <si>
@@ -462,6 +483,24 @@
   </si>
   <si>
     <t>1200:1</t>
+  </si>
+  <si>
+    <t>2_4_8</t>
+  </si>
+  <si>
+    <t>4:1</t>
+  </si>
+  <si>
+    <t>20_40_80</t>
+  </si>
+  <si>
+    <t>40:1</t>
+  </si>
+  <si>
+    <t>200_400_800</t>
+  </si>
+  <si>
+    <t>400:1</t>
   </si>
 </sst>
 </file>
@@ -678,6 +717,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -688,6 +733,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -695,11 +741,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -708,13 +754,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1708,7 +1747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T59"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3235,165 +3274,165 @@
       <c r="S31" s="22"/>
       <c r="T31" s="22"/>
     </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A32" s="28">
-        <v>10010010</v>
-      </c>
-      <c r="B32" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E32" s="32">
-        <v>10</v>
-      </c>
-      <c r="F32" s="33" t="s">
+    <row r="32" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A32" s="18">
+        <v>1018001</v>
+      </c>
+      <c r="B32" s="18">
+        <v>101800</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="D32" s="23">
+        <v>101800001</v>
+      </c>
+      <c r="E32" s="19">
+        <v>1</v>
+      </c>
+      <c r="F32" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H32" s="35">
-        <v>0</v>
-      </c>
-      <c r="I32" s="36">
+      <c r="G32" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="13">
+        <v>50000000</v>
+      </c>
+      <c r="I32" s="24">
         <v>9600</v>
       </c>
-      <c r="J32" s="37">
-        <v>0</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L32" s="38">
-        <v>0</v>
-      </c>
-      <c r="M32" s="36" t="s">
+      <c r="J32" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K32" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="26">
+        <v>100</v>
+      </c>
+      <c r="M32" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N32" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-    </row>
-    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A33" s="28">
-        <v>10010011</v>
-      </c>
-      <c r="B33" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E33" s="32">
-        <v>11</v>
-      </c>
-      <c r="F33" s="33" t="s">
+      <c r="N32" s="20">
+        <v>0</v>
+      </c>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A33" s="18">
+        <v>1018002</v>
+      </c>
+      <c r="B33" s="18">
+        <v>101800</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="23">
+        <v>101800001</v>
+      </c>
+      <c r="E33" s="19">
+        <v>2</v>
+      </c>
+      <c r="F33" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G33" s="34" t="s">
+      <c r="G33" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="35">
-        <v>0</v>
-      </c>
-      <c r="I33" s="36">
+      <c r="H33" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="I33" s="24">
         <v>9600</v>
       </c>
-      <c r="J33" s="37">
-        <v>0</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L33" s="38">
-        <v>0</v>
-      </c>
-      <c r="M33" s="36" t="s">
+      <c r="J33" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="26">
+        <v>100</v>
+      </c>
+      <c r="M33" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N33" s="39" t="s">
+      <c r="N33" s="20">
+        <v>0</v>
+      </c>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A34" s="18">
+        <v>1018003</v>
+      </c>
+      <c r="B34" s="18">
+        <v>101800</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="23">
+        <v>101800001</v>
+      </c>
+      <c r="E34" s="19">
+        <v>3</v>
+      </c>
+      <c r="F34" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-    </row>
-    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A34" s="28">
-        <v>10010012</v>
-      </c>
-      <c r="B34" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E34" s="32">
-        <v>12</v>
-      </c>
-      <c r="F34" s="33" t="s">
+      <c r="G34" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="G34" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="H34" s="40">
-        <v>0</v>
-      </c>
-      <c r="I34" s="36">
+      <c r="H34" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I34" s="24">
         <v>9600</v>
       </c>
-      <c r="J34" s="37">
-        <v>0</v>
-      </c>
-      <c r="K34" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L34" s="38">
-        <v>0</v>
-      </c>
-      <c r="M34" s="36" t="s">
+      <c r="J34" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="26">
+        <v>100</v>
+      </c>
+      <c r="M34" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N34" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
+      <c r="N34" s="20">
+        <v>0</v>
+      </c>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A35" s="28">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B35" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D35" s="31">
         <v>100100026</v>
@@ -3402,10 +3441,10 @@
         <v>10</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H35" s="35">
         <v>0</v>
@@ -3419,14 +3458,14 @@
       <c r="K35" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L35" s="41">
+      <c r="L35" s="38">
         <v>0</v>
       </c>
       <c r="M35" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N35" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O35" s="33"/>
       <c r="P35" s="33"/>
@@ -3437,13 +3476,13 @@
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A36" s="28">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B36" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D36" s="31">
         <v>100100026</v>
@@ -3452,10 +3491,10 @@
         <v>11</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H36" s="35">
         <v>0</v>
@@ -3469,14 +3508,14 @@
       <c r="K36" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L36" s="41">
+      <c r="L36" s="38">
         <v>0</v>
       </c>
       <c r="M36" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N36" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O36" s="33"/>
       <c r="P36" s="33"/>
@@ -3487,13 +3526,13 @@
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A37" s="28">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B37" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D37" s="31">
         <v>100100026</v>
@@ -3502,10 +3541,10 @@
         <v>12</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H37" s="40">
         <v>0</v>
@@ -3519,14 +3558,14 @@
       <c r="K37" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="41">
+      <c r="L37" s="38">
         <v>0</v>
       </c>
       <c r="M37" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N37" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O37" s="33"/>
       <c r="P37" s="33"/>
@@ -3537,13 +3576,13 @@
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A38" s="28">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B38" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D38" s="31">
         <v>100100026</v>
@@ -3552,16 +3591,16 @@
         <v>10</v>
       </c>
       <c r="F38" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="34" t="s">
-        <v>35</v>
-      </c>
       <c r="H38" s="35">
         <v>0</v>
       </c>
       <c r="I38" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J38" s="37">
         <v>0</v>
@@ -3569,14 +3608,14 @@
       <c r="K38" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L38" s="38">
+      <c r="L38" s="41">
         <v>0</v>
       </c>
       <c r="M38" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N38" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O38" s="33"/>
       <c r="P38" s="33"/>
@@ -3587,13 +3626,13 @@
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A39" s="28">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B39" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D39" s="31">
         <v>100100026</v>
@@ -3602,16 +3641,16 @@
         <v>11</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="H39" s="35">
         <v>0</v>
       </c>
       <c r="I39" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J39" s="37">
         <v>0</v>
@@ -3619,14 +3658,14 @@
       <c r="K39" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L39" s="38">
+      <c r="L39" s="41">
         <v>0</v>
       </c>
       <c r="M39" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N39" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O39" s="33"/>
       <c r="P39" s="33"/>
@@ -3637,13 +3676,13 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A40" s="28">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B40" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D40" s="31">
         <v>100100026</v>
@@ -3652,16 +3691,16 @@
         <v>12</v>
       </c>
       <c r="F40" s="33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H40" s="40">
         <v>0</v>
       </c>
       <c r="I40" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J40" s="37">
         <v>0</v>
@@ -3669,14 +3708,14 @@
       <c r="K40" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L40" s="38">
+      <c r="L40" s="41">
         <v>0</v>
       </c>
       <c r="M40" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O40" s="33"/>
       <c r="P40" s="33"/>
@@ -3685,333 +3724,333 @@
       <c r="S40" s="36"/>
       <c r="T40" s="36"/>
     </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A41" s="28">
-        <v>10120010</v>
-      </c>
-      <c r="B41" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="43">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B41" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="31">
+        <v>100100026</v>
       </c>
       <c r="E41" s="32">
         <v>10</v>
       </c>
-      <c r="F41" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="G41" s="44" t="s">
-        <v>87</v>
+      <c r="F41" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H41" s="35">
         <v>0</v>
       </c>
-      <c r="I41" s="37">
-        <v>9500</v>
+      <c r="I41" s="36">
+        <v>9700</v>
       </c>
       <c r="J41" s="37">
         <v>0</v>
       </c>
-      <c r="K41" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L41" s="41">
-        <v>0</v>
-      </c>
-      <c r="M41" s="37" t="s">
+      <c r="K41" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="38">
+        <v>0</v>
+      </c>
+      <c r="M41" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N41" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>81</v>
+      </c>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A42" s="28">
-        <v>10120011</v>
-      </c>
-      <c r="B42" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="43">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B42" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="31">
+        <v>100100026</v>
       </c>
       <c r="E42" s="32">
         <v>11</v>
       </c>
-      <c r="F42" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="G42" s="44" t="s">
-        <v>89</v>
+      <c r="F42" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="H42" s="35">
         <v>0</v>
       </c>
-      <c r="I42" s="37">
-        <v>9500</v>
+      <c r="I42" s="36">
+        <v>9700</v>
       </c>
       <c r="J42" s="37">
         <v>0</v>
       </c>
-      <c r="K42" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L42" s="41">
-        <v>0</v>
-      </c>
-      <c r="M42" s="37" t="s">
+      <c r="K42" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="38">
+        <v>0</v>
+      </c>
+      <c r="M42" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="O42" s="39"/>
-      <c r="P42" s="39"/>
-      <c r="Q42" s="39"/>
-      <c r="R42" s="39"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-    </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>84</v>
+      </c>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+    </row>
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A43" s="28">
-        <v>10120012</v>
-      </c>
-      <c r="B43" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="43">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B43" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="31">
+        <v>100100026</v>
       </c>
       <c r="E43" s="32">
         <v>12</v>
       </c>
-      <c r="F43" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" s="44" t="s">
-        <v>91</v>
+      <c r="F43" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="H43" s="40">
         <v>0</v>
       </c>
-      <c r="I43" s="37">
-        <v>9500</v>
+      <c r="I43" s="36">
+        <v>9700</v>
       </c>
       <c r="J43" s="37">
         <v>0</v>
       </c>
-      <c r="K43" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L43" s="41">
-        <v>0</v>
-      </c>
-      <c r="M43" s="37" t="s">
+      <c r="K43" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="38">
+        <v>0</v>
+      </c>
+      <c r="M43" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N43" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="39"/>
-      <c r="R43" s="39"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-    </row>
-    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>87</v>
+      </c>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+    </row>
+    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A44" s="28">
-        <v>10140010</v>
-      </c>
-      <c r="B44" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="31">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B44" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="43">
+        <v>101200026</v>
       </c>
       <c r="E44" s="32">
         <v>10</v>
       </c>
-      <c r="F44" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="G44" s="34" t="s">
-        <v>76</v>
+      <c r="F44" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>94</v>
       </c>
       <c r="H44" s="35">
         <v>0</v>
       </c>
-      <c r="I44" s="36">
-        <v>9600</v>
+      <c r="I44" s="37">
+        <v>9500</v>
       </c>
       <c r="J44" s="37">
         <v>0</v>
       </c>
-      <c r="K44" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" s="38">
-        <v>0</v>
-      </c>
-      <c r="M44" s="36" t="s">
+      <c r="K44" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="41">
+        <v>0</v>
+      </c>
+      <c r="M44" s="37" t="s">
         <v>37</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>81</v>
+      </c>
+      <c r="O44" s="39"/>
+      <c r="P44" s="39"/>
+      <c r="Q44" s="39"/>
+      <c r="R44" s="39"/>
+      <c r="S44" s="37"/>
+      <c r="T44" s="37"/>
+    </row>
+    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A45" s="28">
-        <v>10140011</v>
-      </c>
-      <c r="B45" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="31">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B45" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="43">
+        <v>101200026</v>
       </c>
       <c r="E45" s="32">
         <v>11</v>
       </c>
-      <c r="F45" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="G45" s="34" t="s">
-        <v>79</v>
+      <c r="F45" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>96</v>
       </c>
       <c r="H45" s="35">
         <v>0</v>
       </c>
-      <c r="I45" s="36">
-        <v>9600</v>
+      <c r="I45" s="37">
+        <v>9500</v>
       </c>
       <c r="J45" s="37">
         <v>0</v>
       </c>
-      <c r="K45" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L45" s="38">
-        <v>0</v>
-      </c>
-      <c r="M45" s="36" t="s">
+      <c r="K45" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="41">
+        <v>0</v>
+      </c>
+      <c r="M45" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="36"/>
-      <c r="T45" s="36"/>
-    </row>
-    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>84</v>
+      </c>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="39"/>
+      <c r="S45" s="37"/>
+      <c r="T45" s="37"/>
+    </row>
+    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A46" s="28">
-        <v>10140012</v>
-      </c>
-      <c r="B46" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" s="31">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B46" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="43">
+        <v>101200026</v>
       </c>
       <c r="E46" s="32">
         <v>12</v>
       </c>
-      <c r="F46" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="G46" s="34" t="s">
-        <v>82</v>
+      <c r="F46" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>98</v>
       </c>
       <c r="H46" s="40">
         <v>0</v>
       </c>
-      <c r="I46" s="36">
-        <v>9600</v>
+      <c r="I46" s="37">
+        <v>9500</v>
       </c>
       <c r="J46" s="37">
         <v>0</v>
       </c>
-      <c r="K46" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L46" s="38">
-        <v>0</v>
-      </c>
-      <c r="M46" s="36" t="s">
+      <c r="K46" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="41">
+        <v>0</v>
+      </c>
+      <c r="M46" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="36"/>
-      <c r="T46" s="36"/>
+        <v>87</v>
+      </c>
+      <c r="O46" s="39"/>
+      <c r="P46" s="39"/>
+      <c r="Q46" s="39"/>
+      <c r="R46" s="39"/>
+      <c r="S46" s="37"/>
+      <c r="T46" s="37"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A47" s="28">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B47" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D47" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E47" s="32">
         <v>10</v>
       </c>
       <c r="F47" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="G47" s="34" t="s">
-        <v>35</v>
-      </c>
       <c r="H47" s="35">
         <v>0</v>
       </c>
       <c r="I47" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J47" s="37">
         <v>0</v>
@@ -4026,7 +4065,7 @@
         <v>37</v>
       </c>
       <c r="N47" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O47" s="33"/>
       <c r="P47" s="33"/>
@@ -4037,31 +4076,31 @@
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A48" s="28">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B48" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D48" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E48" s="32">
         <v>11</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="H48" s="35">
         <v>0</v>
       </c>
       <c r="I48" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J48" s="37">
         <v>0</v>
@@ -4076,7 +4115,7 @@
         <v>40</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
@@ -4087,31 +4126,31 @@
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A49" s="28">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B49" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D49" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E49" s="32">
         <v>12</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H49" s="40">
         <v>0</v>
       </c>
       <c r="I49" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J49" s="37">
         <v>0</v>
@@ -4126,7 +4165,7 @@
         <v>43</v>
       </c>
       <c r="N49" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O49" s="33"/>
       <c r="P49" s="33"/>
@@ -4137,22 +4176,22 @@
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A50" s="28">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B50" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E50" s="32">
         <v>10</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G50" s="34" t="s">
         <v>35</v>
@@ -4161,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J50" s="37">
         <v>0</v>
@@ -4169,14 +4208,14 @@
       <c r="K50" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L50" s="41">
+      <c r="L50" s="38">
         <v>0</v>
       </c>
       <c r="M50" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O50" s="33"/>
       <c r="P50" s="33"/>
@@ -4187,22 +4226,22 @@
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A51" s="28">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B51" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D51" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E51" s="32">
         <v>11</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G51" s="34" t="s">
         <v>63</v>
@@ -4211,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J51" s="37">
         <v>0</v>
@@ -4219,14 +4258,14 @@
       <c r="K51" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L51" s="41">
+      <c r="L51" s="38">
         <v>0</v>
       </c>
       <c r="M51" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O51" s="33"/>
       <c r="P51" s="33"/>
@@ -4237,22 +4276,22 @@
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A52" s="28">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B52" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D52" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E52" s="32">
         <v>12</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G52" s="34" t="s">
         <v>39</v>
@@ -4261,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J52" s="37">
         <v>0</v>
@@ -4269,14 +4308,14 @@
       <c r="K52" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L52" s="41">
+      <c r="L52" s="38">
         <v>0</v>
       </c>
       <c r="M52" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O52" s="33"/>
       <c r="P52" s="33"/>
@@ -4287,22 +4326,22 @@
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="28">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B53" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D53" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E53" s="32">
         <v>10</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G53" s="34" t="s">
         <v>35</v>
@@ -4326,7 +4365,7 @@
         <v>37</v>
       </c>
       <c r="N53" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
@@ -4337,22 +4376,22 @@
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="28">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B54" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D54" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E54" s="32">
         <v>11</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G54" s="34" t="s">
         <v>63</v>
@@ -4376,7 +4415,7 @@
         <v>40</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O54" s="33"/>
       <c r="P54" s="33"/>
@@ -4387,22 +4426,22 @@
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="28">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B55" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E55" s="32">
         <v>12</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G55" s="34" t="s">
         <v>39</v>
@@ -4426,7 +4465,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O55" s="33"/>
       <c r="P55" s="33"/>
@@ -4437,25 +4476,25 @@
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="28">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B56" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D56" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E56" s="32">
         <v>10</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="H56" s="35">
         <v>0</v>
@@ -4476,7 +4515,7 @@
         <v>37</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -4487,25 +4526,25 @@
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="28">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B57" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E57" s="32">
         <v>11</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H57" s="35">
         <v>0</v>
@@ -4526,7 +4565,7 @@
         <v>40</v>
       </c>
       <c r="N57" s="39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O57" s="33"/>
       <c r="P57" s="33"/>
@@ -4537,25 +4576,25 @@
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="28">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B58" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D58" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E58" s="32">
         <v>12</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H58" s="40">
         <v>0</v>
@@ -4576,7 +4615,7 @@
         <v>43</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O58" s="33"/>
       <c r="P58" s="33"/>
@@ -4585,13 +4624,305 @@
       <c r="S58" s="36"/>
       <c r="T58" s="36"/>
     </row>
-    <row r="59" ht="16.5" spans="1:20">
-      <c r="G59" s="19"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
+    <row r="59" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A59" s="28">
+        <v>10240010</v>
+      </c>
+      <c r="B59" s="29">
+        <v>102400</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" s="31">
+        <v>102400026</v>
+      </c>
+      <c r="E59" s="32">
+        <v>10</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="G59" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="H59" s="35">
+        <v>0</v>
+      </c>
+      <c r="I59" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J59" s="37">
+        <v>0</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="41">
+        <v>0</v>
+      </c>
+      <c r="M59" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+    </row>
+    <row r="60" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A60" s="28">
+        <v>10240011</v>
+      </c>
+      <c r="B60" s="29">
+        <v>102400</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="31">
+        <v>102400026</v>
+      </c>
+      <c r="E60" s="32">
+        <v>11</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="35">
+        <v>0</v>
+      </c>
+      <c r="I60" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J60" s="37">
+        <v>0</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="41">
+        <v>0</v>
+      </c>
+      <c r="M60" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N60" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36"/>
+    </row>
+    <row r="61" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A61" s="28">
+        <v>10240012</v>
+      </c>
+      <c r="B61" s="29">
+        <v>102400</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="31">
+        <v>102400026</v>
+      </c>
+      <c r="E61" s="32">
+        <v>12</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H61" s="40">
+        <v>0</v>
+      </c>
+      <c r="I61" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J61" s="37">
+        <v>0</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="41">
+        <v>0</v>
+      </c>
+      <c r="M61" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N61" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O61" s="33"/>
+      <c r="P61" s="33"/>
+      <c r="Q61" s="33"/>
+      <c r="R61" s="33"/>
+      <c r="S61" s="36"/>
+      <c r="T61" s="36"/>
+    </row>
+    <row r="62" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A62" s="28">
+        <v>10180010</v>
+      </c>
+      <c r="B62" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E62" s="32">
+        <v>10</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="H62" s="40">
+        <v>0</v>
+      </c>
+      <c r="I62" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J62" s="37">
+        <v>0</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="41">
+        <v>0</v>
+      </c>
+      <c r="M62" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33"/>
+      <c r="Q62" s="33"/>
+      <c r="R62" s="33"/>
+      <c r="S62" s="36"/>
+      <c r="T62" s="36"/>
+    </row>
+    <row r="63" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A63" s="28">
+        <v>10180011</v>
+      </c>
+      <c r="B63" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E63" s="32">
+        <v>11</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="G63" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H63" s="40">
+        <v>0</v>
+      </c>
+      <c r="I63" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J63" s="37">
+        <v>0</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="41">
+        <v>0</v>
+      </c>
+      <c r="M63" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N63" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+    </row>
+    <row r="64" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A64" s="28">
+        <v>10180012</v>
+      </c>
+      <c r="B64" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E64" s="32">
+        <v>12</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="G64" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="H64" s="40">
+        <v>0</v>
+      </c>
+      <c r="I64" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J64" s="37">
+        <v>0</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="41">
+        <v>0</v>
+      </c>
+      <c r="M64" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N64" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O64" s="33"/>
+      <c r="P64" s="33"/>
+      <c r="Q64" s="33"/>
+      <c r="R64" s="33"/>
+      <c r="S64" s="36"/>
+      <c r="T64" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -715,21 +715,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -741,6 +729,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -748,7 +748,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>80000:1</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
   </si>
   <si>
     <t>1_2_5</t>
@@ -715,26 +718,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -746,15 +736,28 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1747,7 +1750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T64"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3424,165 +3427,165 @@
       <c r="S34" s="22"/>
       <c r="T34" s="22"/>
     </row>
-    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A35" s="28">
-        <v>10010010</v>
-      </c>
-      <c r="B35" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E35" s="32">
-        <v>10</v>
-      </c>
-      <c r="F35" s="33" t="s">
+    <row r="35" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A35" s="18">
+        <v>1025001</v>
+      </c>
+      <c r="B35" s="18">
+        <v>102500</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="G35" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="H35" s="35">
-        <v>0</v>
-      </c>
-      <c r="I35" s="36">
+      <c r="D35" s="23">
+        <v>102500001</v>
+      </c>
+      <c r="E35" s="19">
+        <v>1</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" s="13">
+        <v>50000000</v>
+      </c>
+      <c r="I35" s="24">
         <v>9600</v>
       </c>
-      <c r="J35" s="37">
-        <v>0</v>
-      </c>
-      <c r="K35" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="38">
-        <v>0</v>
-      </c>
-      <c r="M35" s="36" t="s">
+      <c r="J35" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K35" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="26">
+        <v>100</v>
+      </c>
+      <c r="M35" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N35" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-    </row>
-    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A36" s="28">
-        <v>10010011</v>
-      </c>
-      <c r="B36" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E36" s="32">
-        <v>11</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="35">
-        <v>0</v>
-      </c>
-      <c r="I36" s="36">
+      <c r="N35" s="20">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+    </row>
+    <row r="36" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A36" s="18">
+        <v>1025002</v>
+      </c>
+      <c r="B36" s="18">
+        <v>102500</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="23">
+        <v>102500001</v>
+      </c>
+      <c r="E36" s="19">
+        <v>2</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="13">
+        <v>5000000000</v>
+      </c>
+      <c r="I36" s="24">
         <v>9600</v>
       </c>
-      <c r="J36" s="37">
-        <v>0</v>
-      </c>
-      <c r="K36" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L36" s="38">
-        <v>0</v>
-      </c>
-      <c r="M36" s="36" t="s">
+      <c r="J36" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K36" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" s="26">
+        <v>100</v>
+      </c>
+      <c r="M36" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N36" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-    </row>
-    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A37" s="28">
-        <v>10010012</v>
-      </c>
-      <c r="B37" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E37" s="32">
-        <v>12</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H37" s="40">
-        <v>0</v>
-      </c>
-      <c r="I37" s="36">
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A37" s="18">
+        <v>1025003</v>
+      </c>
+      <c r="B37" s="18">
+        <v>102500</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="23">
+        <v>102500001</v>
+      </c>
+      <c r="E37" s="19">
+        <v>3</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I37" s="24">
         <v>9600</v>
       </c>
-      <c r="J37" s="37">
-        <v>0</v>
-      </c>
-      <c r="K37" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L37" s="38">
-        <v>0</v>
-      </c>
-      <c r="M37" s="36" t="s">
+      <c r="J37" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="26">
+        <v>100</v>
+      </c>
+      <c r="M37" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N37" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A38" s="28">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B38" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D38" s="31">
         <v>100100026</v>
@@ -3591,10 +3594,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H38" s="35">
         <v>0</v>
@@ -3608,14 +3611,14 @@
       <c r="K38" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="38">
         <v>0</v>
       </c>
       <c r="M38" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N38" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O38" s="33"/>
       <c r="P38" s="33"/>
@@ -3626,13 +3629,13 @@
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A39" s="28">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B39" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D39" s="31">
         <v>100100026</v>
@@ -3641,10 +3644,10 @@
         <v>11</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H39" s="35">
         <v>0</v>
@@ -3658,14 +3661,14 @@
       <c r="K39" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L39" s="41">
+      <c r="L39" s="38">
         <v>0</v>
       </c>
       <c r="M39" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N39" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O39" s="33"/>
       <c r="P39" s="33"/>
@@ -3676,13 +3679,13 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A40" s="28">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B40" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D40" s="31">
         <v>100100026</v>
@@ -3691,10 +3694,10 @@
         <v>12</v>
       </c>
       <c r="F40" s="33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H40" s="40">
         <v>0</v>
@@ -3708,14 +3711,14 @@
       <c r="K40" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L40" s="41">
+      <c r="L40" s="38">
         <v>0</v>
       </c>
       <c r="M40" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O40" s="33"/>
       <c r="P40" s="33"/>
@@ -3726,13 +3729,13 @@
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A41" s="28">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B41" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D41" s="31">
         <v>100100026</v>
@@ -3741,16 +3744,16 @@
         <v>10</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H41" s="35">
         <v>0</v>
       </c>
       <c r="I41" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J41" s="37">
         <v>0</v>
@@ -3758,14 +3761,14 @@
       <c r="K41" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L41" s="38">
+      <c r="L41" s="41">
         <v>0</v>
       </c>
       <c r="M41" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N41" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O41" s="33"/>
       <c r="P41" s="33"/>
@@ -3776,13 +3779,13 @@
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A42" s="28">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B42" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D42" s="31">
         <v>100100026</v>
@@ -3791,16 +3794,16 @@
         <v>11</v>
       </c>
       <c r="F42" s="33" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="H42" s="35">
         <v>0</v>
       </c>
       <c r="I42" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J42" s="37">
         <v>0</v>
@@ -3808,14 +3811,14 @@
       <c r="K42" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L42" s="38">
+      <c r="L42" s="41">
         <v>0</v>
       </c>
       <c r="M42" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
@@ -3826,13 +3829,13 @@
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A43" s="28">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B43" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D43" s="31">
         <v>100100026</v>
@@ -3841,16 +3844,16 @@
         <v>12</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H43" s="40">
         <v>0</v>
       </c>
       <c r="I43" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J43" s="37">
         <v>0</v>
@@ -3858,14 +3861,14 @@
       <c r="K43" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L43" s="38">
+      <c r="L43" s="41">
         <v>0</v>
       </c>
       <c r="M43" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N43" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O43" s="33"/>
       <c r="P43" s="33"/>
@@ -3874,333 +3877,333 @@
       <c r="S43" s="36"/>
       <c r="T43" s="36"/>
     </row>
-    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A44" s="28">
-        <v>10120010</v>
-      </c>
-      <c r="B44" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="43">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B44" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="31">
+        <v>100100026</v>
       </c>
       <c r="E44" s="32">
         <v>10</v>
       </c>
-      <c r="F44" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G44" s="44" t="s">
-        <v>94</v>
+      <c r="F44" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H44" s="35">
         <v>0</v>
       </c>
-      <c r="I44" s="37">
-        <v>9500</v>
+      <c r="I44" s="36">
+        <v>9700</v>
       </c>
       <c r="J44" s="37">
         <v>0</v>
       </c>
-      <c r="K44" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" s="41">
-        <v>0</v>
-      </c>
-      <c r="M44" s="37" t="s">
+      <c r="K44" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="38">
+        <v>0</v>
+      </c>
+      <c r="M44" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="37"/>
-      <c r="T44" s="37"/>
-    </row>
-    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A45" s="28">
-        <v>10120011</v>
-      </c>
-      <c r="B45" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="43">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B45" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="31">
+        <v>100100026</v>
       </c>
       <c r="E45" s="32">
         <v>11</v>
       </c>
-      <c r="F45" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="G45" s="44" t="s">
-        <v>96</v>
+      <c r="F45" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="H45" s="35">
         <v>0</v>
       </c>
-      <c r="I45" s="37">
-        <v>9500</v>
+      <c r="I45" s="36">
+        <v>9700</v>
       </c>
       <c r="J45" s="37">
         <v>0</v>
       </c>
-      <c r="K45" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L45" s="41">
-        <v>0</v>
-      </c>
-      <c r="M45" s="37" t="s">
+      <c r="K45" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="38">
+        <v>0</v>
+      </c>
+      <c r="M45" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="O45" s="39"/>
-      <c r="P45" s="39"/>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="39"/>
-      <c r="S45" s="37"/>
-      <c r="T45" s="37"/>
-    </row>
-    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>85</v>
+      </c>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A46" s="28">
-        <v>10120012</v>
-      </c>
-      <c r="B46" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="43">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B46" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="31">
+        <v>100100026</v>
       </c>
       <c r="E46" s="32">
         <v>12</v>
       </c>
-      <c r="F46" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46" s="44" t="s">
-        <v>98</v>
+      <c r="F46" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="H46" s="40">
         <v>0</v>
       </c>
-      <c r="I46" s="37">
-        <v>9500</v>
+      <c r="I46" s="36">
+        <v>9700</v>
       </c>
       <c r="J46" s="37">
         <v>0</v>
       </c>
-      <c r="K46" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L46" s="41">
-        <v>0</v>
-      </c>
-      <c r="M46" s="37" t="s">
+      <c r="K46" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="38">
+        <v>0</v>
+      </c>
+      <c r="M46" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O46" s="39"/>
-      <c r="P46" s="39"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="39"/>
-      <c r="S46" s="37"/>
-      <c r="T46" s="37"/>
-    </row>
-    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>88</v>
+      </c>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+    </row>
+    <row r="47" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A47" s="28">
-        <v>10140010</v>
-      </c>
-      <c r="B47" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="31">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B47" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="43">
+        <v>101200026</v>
       </c>
       <c r="E47" s="32">
         <v>10</v>
       </c>
-      <c r="F47" s="33" t="s">
+      <c r="F47" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="35">
+        <v>0</v>
+      </c>
+      <c r="I47" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J47" s="37">
+        <v>0</v>
+      </c>
+      <c r="K47" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="41">
+        <v>0</v>
+      </c>
+      <c r="M47" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="G47" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="35">
-        <v>0</v>
-      </c>
-      <c r="I47" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J47" s="37">
-        <v>0</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L47" s="38">
-        <v>0</v>
-      </c>
-      <c r="M47" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="N47" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="36"/>
-      <c r="T47" s="36"/>
-    </row>
-    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O47" s="39"/>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
+      <c r="R47" s="39"/>
+      <c r="S47" s="37"/>
+      <c r="T47" s="37"/>
+    </row>
+    <row r="48" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A48" s="28">
-        <v>10140011</v>
-      </c>
-      <c r="B48" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" s="31">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B48" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="43">
+        <v>101200026</v>
       </c>
       <c r="E48" s="32">
         <v>11</v>
       </c>
-      <c r="F48" s="33" t="s">
+      <c r="F48" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="H48" s="35">
+        <v>0</v>
+      </c>
+      <c r="I48" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J48" s="37">
+        <v>0</v>
+      </c>
+      <c r="K48" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="41">
+        <v>0</v>
+      </c>
+      <c r="M48" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N48" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="G48" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H48" s="35">
-        <v>0</v>
-      </c>
-      <c r="I48" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J48" s="37">
-        <v>0</v>
-      </c>
-      <c r="K48" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L48" s="38">
-        <v>0</v>
-      </c>
-      <c r="M48" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="N48" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="36"/>
-      <c r="T48" s="36"/>
-    </row>
-    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+      <c r="Q48" s="39"/>
+      <c r="R48" s="39"/>
+      <c r="S48" s="37"/>
+      <c r="T48" s="37"/>
+    </row>
+    <row r="49" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A49" s="28">
-        <v>10140012</v>
-      </c>
-      <c r="B49" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="31">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B49" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="43">
+        <v>101200026</v>
       </c>
       <c r="E49" s="32">
         <v>12</v>
       </c>
-      <c r="F49" s="33" t="s">
+      <c r="F49" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H49" s="40">
+        <v>0</v>
+      </c>
+      <c r="I49" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J49" s="37">
+        <v>0</v>
+      </c>
+      <c r="K49" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="41">
+        <v>0</v>
+      </c>
+      <c r="M49" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="N49" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="G49" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="H49" s="40">
-        <v>0</v>
-      </c>
-      <c r="I49" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J49" s="37">
-        <v>0</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L49" s="38">
-        <v>0</v>
-      </c>
-      <c r="M49" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="N49" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="36"/>
-      <c r="T49" s="36"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="39"/>
+      <c r="S49" s="37"/>
+      <c r="T49" s="37"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A50" s="28">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B50" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D50" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E50" s="32">
         <v>10</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H50" s="35">
         <v>0</v>
       </c>
       <c r="I50" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J50" s="37">
         <v>0</v>
@@ -4215,7 +4218,7 @@
         <v>37</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O50" s="33"/>
       <c r="P50" s="33"/>
@@ -4226,31 +4229,31 @@
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A51" s="28">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B51" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D51" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E51" s="32">
         <v>11</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="H51" s="35">
         <v>0</v>
       </c>
       <c r="I51" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J51" s="37">
         <v>0</v>
@@ -4265,7 +4268,7 @@
         <v>40</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O51" s="33"/>
       <c r="P51" s="33"/>
@@ -4276,31 +4279,31 @@
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A52" s="28">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B52" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D52" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E52" s="32">
         <v>12</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="H52" s="40">
         <v>0</v>
       </c>
       <c r="I52" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J52" s="37">
         <v>0</v>
@@ -4315,7 +4318,7 @@
         <v>43</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O52" s="33"/>
       <c r="P52" s="33"/>
@@ -4326,22 +4329,22 @@
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="28">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B53" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D53" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E53" s="32">
         <v>10</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G53" s="34" t="s">
         <v>35</v>
@@ -4350,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J53" s="37">
         <v>0</v>
@@ -4358,14 +4361,14 @@
       <c r="K53" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L53" s="41">
+      <c r="L53" s="38">
         <v>0</v>
       </c>
       <c r="M53" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N53" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
@@ -4376,22 +4379,22 @@
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="28">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B54" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D54" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E54" s="32">
         <v>11</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G54" s="34" t="s">
         <v>63</v>
@@ -4400,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J54" s="37">
         <v>0</v>
@@ -4408,14 +4411,14 @@
       <c r="K54" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L54" s="41">
+      <c r="L54" s="38">
         <v>0</v>
       </c>
       <c r="M54" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O54" s="33"/>
       <c r="P54" s="33"/>
@@ -4426,22 +4429,22 @@
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="28">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B55" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E55" s="32">
         <v>12</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G55" s="34" t="s">
         <v>39</v>
@@ -4450,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J55" s="37">
         <v>0</v>
@@ -4458,14 +4461,14 @@
       <c r="K55" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L55" s="41">
+      <c r="L55" s="38">
         <v>0</v>
       </c>
       <c r="M55" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N55" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O55" s="33"/>
       <c r="P55" s="33"/>
@@ -4476,22 +4479,22 @@
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="28">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B56" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E56" s="32">
         <v>10</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>35</v>
@@ -4515,7 +4518,7 @@
         <v>37</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -4526,22 +4529,22 @@
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="28">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B57" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E57" s="32">
         <v>11</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G57" s="34" t="s">
         <v>63</v>
@@ -4565,7 +4568,7 @@
         <v>40</v>
       </c>
       <c r="N57" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O57" s="33"/>
       <c r="P57" s="33"/>
@@ -4576,22 +4579,22 @@
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="28">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B58" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E58" s="32">
         <v>12</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>39</v>
@@ -4615,7 +4618,7 @@
         <v>43</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O58" s="33"/>
       <c r="P58" s="33"/>
@@ -4626,25 +4629,25 @@
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A59" s="28">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B59" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E59" s="32">
         <v>10</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="H59" s="35">
         <v>0</v>
@@ -4665,7 +4668,7 @@
         <v>37</v>
       </c>
       <c r="N59" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O59" s="33"/>
       <c r="P59" s="33"/>
@@ -4676,25 +4679,25 @@
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A60" s="28">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B60" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D60" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E60" s="32">
         <v>11</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H60" s="35">
         <v>0</v>
@@ -4715,7 +4718,7 @@
         <v>40</v>
       </c>
       <c r="N60" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O60" s="33"/>
       <c r="P60" s="33"/>
@@ -4726,25 +4729,25 @@
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A61" s="28">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B61" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E61" s="32">
         <v>12</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G61" s="34" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="H61" s="40">
         <v>0</v>
@@ -4765,7 +4768,7 @@
         <v>43</v>
       </c>
       <c r="N61" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O61" s="33"/>
       <c r="P61" s="33"/>
@@ -4776,27 +4779,27 @@
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A62" s="28">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B62" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D62" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E62" s="32">
         <v>10</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="H62" s="40">
+        <v>81</v>
+      </c>
+      <c r="H62" s="35">
         <v>0</v>
       </c>
       <c r="I62" s="36">
@@ -4815,7 +4818,7 @@
         <v>37</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O62" s="33"/>
       <c r="P62" s="33"/>
@@ -4826,27 +4829,27 @@
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="28">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B63" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D63" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E63" s="32">
         <v>11</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="H63" s="40">
+        <v>84</v>
+      </c>
+      <c r="H63" s="35">
         <v>0</v>
       </c>
       <c r="I63" s="36">
@@ -4865,7 +4868,7 @@
         <v>40</v>
       </c>
       <c r="N63" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O63" s="33"/>
       <c r="P63" s="33"/>
@@ -4876,25 +4879,25 @@
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="28">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B64" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D64" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E64" s="32">
         <v>12</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H64" s="40">
         <v>0</v>
@@ -4915,7 +4918,7 @@
         <v>43</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O64" s="33"/>
       <c r="P64" s="33"/>
@@ -4923,6 +4926,309 @@
       <c r="R64" s="33"/>
       <c r="S64" s="36"/>
       <c r="T64" s="36"/>
+    </row>
+    <row r="65" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A65" s="28">
+        <v>10180010</v>
+      </c>
+      <c r="B65" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E65" s="32">
+        <v>10</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G65" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H65" s="40">
+        <v>0</v>
+      </c>
+      <c r="I65" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J65" s="37">
+        <v>0</v>
+      </c>
+      <c r="K65" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="41">
+        <v>0</v>
+      </c>
+      <c r="M65" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="33"/>
+      <c r="R65" s="33"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+    </row>
+    <row r="66" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A66" s="28">
+        <v>10180011</v>
+      </c>
+      <c r="B66" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E66" s="32">
+        <v>11</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G66" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="H66" s="40">
+        <v>0</v>
+      </c>
+      <c r="I66" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J66" s="37">
+        <v>0</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="41">
+        <v>0</v>
+      </c>
+      <c r="M66" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N66" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="33"/>
+      <c r="R66" s="33"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+    </row>
+    <row r="67" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A67" s="28">
+        <v>10180012</v>
+      </c>
+      <c r="B67" s="29">
+        <v>101800</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="31">
+        <v>101800001</v>
+      </c>
+      <c r="E67" s="32">
+        <v>12</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="G67" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="H67" s="40">
+        <v>0</v>
+      </c>
+      <c r="I67" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J67" s="37">
+        <v>0</v>
+      </c>
+      <c r="K67" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="41">
+        <v>0</v>
+      </c>
+      <c r="M67" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N67" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="O67" s="33"/>
+      <c r="P67" s="33"/>
+      <c r="Q67" s="33"/>
+      <c r="R67" s="33"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="36"/>
+    </row>
+    <row r="68" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A68" s="28">
+        <f>(B68*100)+E68</f>
+        <v>10250010</v>
+      </c>
+      <c r="B68" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E68" s="32">
+        <v>10</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H68" s="40">
+        <v>0</v>
+      </c>
+      <c r="I68" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J68" s="37">
+        <v>0</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="41">
+        <v>0</v>
+      </c>
+      <c r="M68" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="33"/>
+      <c r="R68" s="33"/>
+      <c r="S68" s="36"/>
+      <c r="T68" s="36"/>
+    </row>
+    <row r="69" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A69" s="28">
+        <f>(B69*100)+E69</f>
+        <v>10250011</v>
+      </c>
+      <c r="B69" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E69" s="32">
+        <v>11</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="40">
+        <v>0</v>
+      </c>
+      <c r="I69" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J69" s="37">
+        <v>0</v>
+      </c>
+      <c r="K69" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="41">
+        <v>0</v>
+      </c>
+      <c r="M69" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N69" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="33"/>
+      <c r="R69" s="33"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36"/>
+    </row>
+    <row r="70" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A70" s="28">
+        <f>(B70*100)+E70</f>
+        <v>10250012</v>
+      </c>
+      <c r="B70" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E70" s="32">
+        <v>12</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="H70" s="40">
+        <v>0</v>
+      </c>
+      <c r="I70" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J70" s="37">
+        <v>0</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="41">
+        <v>0</v>
+      </c>
+      <c r="M70" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N70" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="O70" s="33"/>
+      <c r="P70" s="33"/>
+      <c r="Q70" s="33"/>
+      <c r="R70" s="33"/>
+      <c r="S70" s="36"/>
+      <c r="T70" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="116">
   <si>
     <t>id</t>
   </si>
@@ -428,6 +428,27 @@
     <t>寒冰王座</t>
   </si>
   <si>
+    <t>5:1</t>
+  </si>
+  <si>
+    <t>500:1</t>
+  </si>
+  <si>
+    <t>50000:1</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>2_4_10_20_40</t>
+  </si>
+  <si>
+    <t>200_400_1000_2000_4000</t>
+  </si>
+  <si>
+    <t>20000_40000_100000_200000_400000</t>
+  </si>
+  <si>
     <t>1_2_5</t>
   </si>
   <si>
@@ -504,6 +525,15 @@
   </si>
   <si>
     <t>400:1</t>
+  </si>
+  <si>
+    <t>2_4_10</t>
+  </si>
+  <si>
+    <t>20_40_100</t>
+  </si>
+  <si>
+    <t>200_400_1000</t>
   </si>
 </sst>
 </file>
@@ -718,20 +748,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -749,15 +766,28 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1750,7 +1780,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3447,7 +3477,7 @@
         <v>34</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H35" s="13">
         <v>50000000</v>
@@ -3497,7 +3527,7 @@
         <v>38</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="H36" s="13">
         <v>5000000000</v>
@@ -3547,7 +3577,7 @@
         <v>41</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="H37" s="27">
         <v>500000000000</v>
@@ -3577,165 +3607,165 @@
       <c r="S37" s="22"/>
       <c r="T37" s="22"/>
     </row>
-    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A38" s="28">
-        <v>10010010</v>
-      </c>
-      <c r="B38" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E38" s="32">
-        <v>10</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="H38" s="35">
-        <v>0</v>
-      </c>
-      <c r="I38" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J38" s="37">
-        <v>0</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L38" s="38">
-        <v>0</v>
-      </c>
-      <c r="M38" s="36" t="s">
+    <row r="38" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A38" s="18">
+        <v>1023001</v>
+      </c>
+      <c r="B38" s="18">
+        <v>102300</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="23">
+        <v>102300001</v>
+      </c>
+      <c r="E38" s="19">
+        <v>1</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="I38" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J38" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="26">
+        <v>100</v>
+      </c>
+      <c r="M38" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N38" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="36"/>
-      <c r="T38" s="36"/>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A39" s="28">
-        <v>10010011</v>
-      </c>
-      <c r="B39" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D39" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E39" s="32">
-        <v>11</v>
-      </c>
-      <c r="F39" s="33" t="s">
+      <c r="N38" s="20">
+        <v>0</v>
+      </c>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A39" s="18">
+        <v>1023002</v>
+      </c>
+      <c r="B39" s="18">
+        <v>102300</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="G39" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H39" s="35">
-        <v>0</v>
-      </c>
-      <c r="I39" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J39" s="37">
-        <v>0</v>
-      </c>
-      <c r="K39" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L39" s="38">
-        <v>0</v>
-      </c>
-      <c r="M39" s="36" t="s">
+      <c r="D39" s="23">
+        <v>102300001</v>
+      </c>
+      <c r="E39" s="19">
+        <v>2</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="I39" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J39" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" s="26">
+        <v>100</v>
+      </c>
+      <c r="M39" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N39" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
-    </row>
-    <row r="40" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A40" s="28">
-        <v>10010012</v>
-      </c>
-      <c r="B40" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E40" s="32">
-        <v>12</v>
-      </c>
-      <c r="F40" s="33" t="s">
+      <c r="N39" s="20">
+        <v>0</v>
+      </c>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="22"/>
+      <c r="T39" s="22"/>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A40" s="18">
+        <v>1023003</v>
+      </c>
+      <c r="B40" s="18">
+        <v>102300</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="23">
+        <v>102300001</v>
+      </c>
+      <c r="E40" s="19">
+        <v>3</v>
+      </c>
+      <c r="F40" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G40" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="40">
-        <v>0</v>
-      </c>
-      <c r="I40" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J40" s="37">
-        <v>0</v>
-      </c>
-      <c r="K40" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L40" s="38">
-        <v>0</v>
-      </c>
-      <c r="M40" s="36" t="s">
+      <c r="G40" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I40" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J40" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K40" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="26">
+        <v>100</v>
+      </c>
+      <c r="M40" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N40" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="36"/>
-      <c r="T40" s="36"/>
+      <c r="N40" s="20">
+        <v>0</v>
+      </c>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="22"/>
+      <c r="T40" s="22"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A41" s="28">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B41" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D41" s="31">
         <v>100100026</v>
@@ -3744,10 +3774,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H41" s="35">
         <v>0</v>
@@ -3761,14 +3791,14 @@
       <c r="K41" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L41" s="41">
+      <c r="L41" s="38">
         <v>0</v>
       </c>
       <c r="M41" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N41" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O41" s="33"/>
       <c r="P41" s="33"/>
@@ -3779,13 +3809,13 @@
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A42" s="28">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B42" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D42" s="31">
         <v>100100026</v>
@@ -3794,10 +3824,10 @@
         <v>11</v>
       </c>
       <c r="F42" s="33" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H42" s="35">
         <v>0</v>
@@ -3811,14 +3841,14 @@
       <c r="K42" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L42" s="41">
+      <c r="L42" s="38">
         <v>0</v>
       </c>
       <c r="M42" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
@@ -3829,13 +3859,13 @@
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A43" s="28">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B43" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D43" s="31">
         <v>100100026</v>
@@ -3844,10 +3874,10 @@
         <v>12</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H43" s="40">
         <v>0</v>
@@ -3861,14 +3891,14 @@
       <c r="K43" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L43" s="41">
+      <c r="L43" s="38">
         <v>0</v>
       </c>
       <c r="M43" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N43" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O43" s="33"/>
       <c r="P43" s="33"/>
@@ -3879,13 +3909,13 @@
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A44" s="28">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B44" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D44" s="31">
         <v>100100026</v>
@@ -3894,16 +3924,16 @@
         <v>10</v>
       </c>
       <c r="F44" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G44" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="34" t="s">
-        <v>35</v>
-      </c>
       <c r="H44" s="35">
         <v>0</v>
       </c>
       <c r="I44" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J44" s="37">
         <v>0</v>
@@ -3911,14 +3941,14 @@
       <c r="K44" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="38">
+      <c r="L44" s="41">
         <v>0</v>
       </c>
       <c r="M44" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O44" s="33"/>
       <c r="P44" s="33"/>
@@ -3929,13 +3959,13 @@
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A45" s="28">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B45" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D45" s="31">
         <v>100100026</v>
@@ -3944,16 +3974,16 @@
         <v>11</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="H45" s="35">
         <v>0</v>
       </c>
       <c r="I45" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J45" s="37">
         <v>0</v>
@@ -3961,14 +3991,14 @@
       <c r="K45" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L45" s="38">
+      <c r="L45" s="41">
         <v>0</v>
       </c>
       <c r="M45" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O45" s="33"/>
       <c r="P45" s="33"/>
@@ -3979,13 +4009,13 @@
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A46" s="28">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B46" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D46" s="31">
         <v>100100026</v>
@@ -3994,16 +4024,16 @@
         <v>12</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H46" s="40">
         <v>0</v>
       </c>
       <c r="I46" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J46" s="37">
         <v>0</v>
@@ -4011,14 +4041,14 @@
       <c r="K46" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L46" s="38">
+      <c r="L46" s="41">
         <v>0</v>
       </c>
       <c r="M46" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O46" s="33"/>
       <c r="P46" s="33"/>
@@ -4027,333 +4057,333 @@
       <c r="S46" s="36"/>
       <c r="T46" s="36"/>
     </row>
-    <row r="47" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A47" s="28">
-        <v>10120010</v>
-      </c>
-      <c r="B47" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C47" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" s="43">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B47" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="31">
+        <v>100100026</v>
       </c>
       <c r="E47" s="32">
         <v>10</v>
       </c>
-      <c r="F47" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" s="44" t="s">
-        <v>95</v>
+      <c r="F47" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H47" s="35">
         <v>0</v>
       </c>
-      <c r="I47" s="37">
-        <v>9500</v>
+      <c r="I47" s="36">
+        <v>9700</v>
       </c>
       <c r="J47" s="37">
         <v>0</v>
       </c>
-      <c r="K47" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L47" s="41">
-        <v>0</v>
-      </c>
-      <c r="M47" s="37" t="s">
+      <c r="K47" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="38">
+        <v>0</v>
+      </c>
+      <c r="M47" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N47" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="O47" s="39"/>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="39"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-    </row>
-    <row r="48" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>89</v>
+      </c>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+    </row>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A48" s="28">
-        <v>10120011</v>
-      </c>
-      <c r="B48" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" s="43">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B48" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="31">
+        <v>100100026</v>
       </c>
       <c r="E48" s="32">
         <v>11</v>
       </c>
-      <c r="F48" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G48" s="44" t="s">
-        <v>97</v>
+      <c r="F48" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="H48" s="35">
         <v>0</v>
       </c>
-      <c r="I48" s="37">
-        <v>9500</v>
+      <c r="I48" s="36">
+        <v>9700</v>
       </c>
       <c r="J48" s="37">
         <v>0</v>
       </c>
-      <c r="K48" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L48" s="41">
-        <v>0</v>
-      </c>
-      <c r="M48" s="37" t="s">
+      <c r="K48" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="38">
+        <v>0</v>
+      </c>
+      <c r="M48" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="O48" s="39"/>
-      <c r="P48" s="39"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="39"/>
-      <c r="S48" s="37"/>
-      <c r="T48" s="37"/>
-    </row>
-    <row r="49" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A49" s="28">
-        <v>10120012</v>
-      </c>
-      <c r="B49" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" s="43">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B49" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="31">
+        <v>100100026</v>
       </c>
       <c r="E49" s="32">
         <v>12</v>
       </c>
-      <c r="F49" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>99</v>
+      <c r="F49" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G49" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="H49" s="40">
         <v>0</v>
       </c>
-      <c r="I49" s="37">
-        <v>9500</v>
+      <c r="I49" s="36">
+        <v>9700</v>
       </c>
       <c r="J49" s="37">
         <v>0</v>
       </c>
-      <c r="K49" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L49" s="41">
-        <v>0</v>
-      </c>
-      <c r="M49" s="37" t="s">
+      <c r="K49" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="38">
+        <v>0</v>
+      </c>
+      <c r="M49" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N49" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O49" s="39"/>
-      <c r="P49" s="39"/>
-      <c r="Q49" s="39"/>
-      <c r="R49" s="39"/>
-      <c r="S49" s="37"/>
-      <c r="T49" s="37"/>
-    </row>
-    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>95</v>
+      </c>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+    </row>
+    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A50" s="28">
-        <v>10140010</v>
-      </c>
-      <c r="B50" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="31">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B50" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="43">
+        <v>101200026</v>
       </c>
       <c r="E50" s="32">
         <v>10</v>
       </c>
-      <c r="F50" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" s="34" t="s">
-        <v>84</v>
+      <c r="F50" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>102</v>
       </c>
       <c r="H50" s="35">
         <v>0</v>
       </c>
-      <c r="I50" s="36">
-        <v>9600</v>
+      <c r="I50" s="37">
+        <v>9500</v>
       </c>
       <c r="J50" s="37">
         <v>0</v>
       </c>
-      <c r="K50" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="38">
-        <v>0</v>
-      </c>
-      <c r="M50" s="36" t="s">
+      <c r="K50" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="41">
+        <v>0</v>
+      </c>
+      <c r="M50" s="37" t="s">
         <v>37</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33"/>
-      <c r="S50" s="36"/>
-      <c r="T50" s="36"/>
-    </row>
-    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>89</v>
+      </c>
+      <c r="O50" s="39"/>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39"/>
+      <c r="S50" s="37"/>
+      <c r="T50" s="37"/>
+    </row>
+    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A51" s="28">
-        <v>10140011</v>
-      </c>
-      <c r="B51" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="31">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B51" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="43">
+        <v>101200026</v>
       </c>
       <c r="E51" s="32">
         <v>11</v>
       </c>
-      <c r="F51" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="G51" s="34" t="s">
-        <v>87</v>
+      <c r="F51" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>104</v>
       </c>
       <c r="H51" s="35">
         <v>0</v>
       </c>
-      <c r="I51" s="36">
-        <v>9600</v>
+      <c r="I51" s="37">
+        <v>9500</v>
       </c>
       <c r="J51" s="37">
         <v>0</v>
       </c>
-      <c r="K51" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="38">
-        <v>0</v>
-      </c>
-      <c r="M51" s="36" t="s">
+      <c r="K51" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="41">
+        <v>0</v>
+      </c>
+      <c r="M51" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="33"/>
-      <c r="S51" s="36"/>
-      <c r="T51" s="36"/>
-    </row>
-    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O51" s="39"/>
+      <c r="P51" s="39"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="39"/>
+      <c r="S51" s="37"/>
+      <c r="T51" s="37"/>
+    </row>
+    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A52" s="28">
-        <v>10140012</v>
-      </c>
-      <c r="B52" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" s="31">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B52" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="43">
+        <v>101200026</v>
       </c>
       <c r="E52" s="32">
         <v>12</v>
       </c>
-      <c r="F52" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="G52" s="34" t="s">
-        <v>90</v>
+      <c r="F52" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>106</v>
       </c>
       <c r="H52" s="40">
         <v>0</v>
       </c>
-      <c r="I52" s="36">
-        <v>9600</v>
+      <c r="I52" s="37">
+        <v>9500</v>
       </c>
       <c r="J52" s="37">
         <v>0</v>
       </c>
-      <c r="K52" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="38">
-        <v>0</v>
-      </c>
-      <c r="M52" s="36" t="s">
+      <c r="K52" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="41">
+        <v>0</v>
+      </c>
+      <c r="M52" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="36"/>
-      <c r="T52" s="36"/>
+        <v>95</v>
+      </c>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="37"/>
+      <c r="T52" s="37"/>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="28">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B53" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D53" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E53" s="32">
         <v>10</v>
       </c>
       <c r="F53" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="34" t="s">
-        <v>35</v>
-      </c>
       <c r="H53" s="35">
         <v>0</v>
       </c>
       <c r="I53" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J53" s="37">
         <v>0</v>
@@ -4368,7 +4398,7 @@
         <v>37</v>
       </c>
       <c r="N53" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
@@ -4379,31 +4409,31 @@
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="28">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B54" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D54" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E54" s="32">
         <v>11</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="H54" s="35">
         <v>0</v>
       </c>
       <c r="I54" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J54" s="37">
         <v>0</v>
@@ -4418,7 +4448,7 @@
         <v>40</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O54" s="33"/>
       <c r="P54" s="33"/>
@@ -4429,31 +4459,31 @@
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="28">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B55" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D55" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E55" s="32">
         <v>12</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H55" s="40">
         <v>0</v>
       </c>
       <c r="I55" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J55" s="37">
         <v>0</v>
@@ -4468,7 +4498,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O55" s="33"/>
       <c r="P55" s="33"/>
@@ -4479,22 +4509,22 @@
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="28">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B56" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D56" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E56" s="32">
         <v>10</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>35</v>
@@ -4503,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J56" s="37">
         <v>0</v>
@@ -4511,14 +4541,14 @@
       <c r="K56" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L56" s="41">
+      <c r="L56" s="38">
         <v>0</v>
       </c>
       <c r="M56" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -4529,22 +4559,22 @@
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="28">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B57" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E57" s="32">
         <v>11</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G57" s="34" t="s">
         <v>63</v>
@@ -4553,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J57" s="37">
         <v>0</v>
@@ -4561,14 +4591,14 @@
       <c r="K57" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L57" s="41">
+      <c r="L57" s="38">
         <v>0</v>
       </c>
       <c r="M57" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N57" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O57" s="33"/>
       <c r="P57" s="33"/>
@@ -4579,22 +4609,22 @@
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="28">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B58" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D58" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E58" s="32">
         <v>12</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>39</v>
@@ -4603,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J58" s="37">
         <v>0</v>
@@ -4611,14 +4641,14 @@
       <c r="K58" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L58" s="41">
+      <c r="L58" s="38">
         <v>0</v>
       </c>
       <c r="M58" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O58" s="33"/>
       <c r="P58" s="33"/>
@@ -4629,22 +4659,22 @@
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A59" s="28">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B59" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D59" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E59" s="32">
         <v>10</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G59" s="34" t="s">
         <v>35</v>
@@ -4668,7 +4698,7 @@
         <v>37</v>
       </c>
       <c r="N59" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O59" s="33"/>
       <c r="P59" s="33"/>
@@ -4679,22 +4709,22 @@
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A60" s="28">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B60" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D60" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E60" s="32">
         <v>11</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G60" s="34" t="s">
         <v>63</v>
@@ -4718,7 +4748,7 @@
         <v>40</v>
       </c>
       <c r="N60" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O60" s="33"/>
       <c r="P60" s="33"/>
@@ -4729,22 +4759,22 @@
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A61" s="28">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B61" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D61" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E61" s="32">
         <v>12</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>39</v>
@@ -4768,7 +4798,7 @@
         <v>43</v>
       </c>
       <c r="N61" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O61" s="33"/>
       <c r="P61" s="33"/>
@@ -4779,25 +4809,25 @@
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A62" s="28">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B62" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E62" s="32">
         <v>10</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H62" s="35">
         <v>0</v>
@@ -4818,7 +4848,7 @@
         <v>37</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O62" s="33"/>
       <c r="P62" s="33"/>
@@ -4829,25 +4859,25 @@
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="28">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B63" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D63" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E63" s="32">
         <v>11</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H63" s="35">
         <v>0</v>
@@ -4868,7 +4898,7 @@
         <v>40</v>
       </c>
       <c r="N63" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O63" s="33"/>
       <c r="P63" s="33"/>
@@ -4879,25 +4909,25 @@
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="28">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B64" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D64" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E64" s="32">
         <v>12</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="H64" s="40">
         <v>0</v>
@@ -4918,7 +4948,7 @@
         <v>43</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O64" s="33"/>
       <c r="P64" s="33"/>
@@ -4929,27 +4959,27 @@
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="28">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B65" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D65" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E65" s="32">
         <v>10</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="H65" s="40">
+        <v>88</v>
+      </c>
+      <c r="H65" s="35">
         <v>0</v>
       </c>
       <c r="I65" s="36">
@@ -4968,7 +4998,7 @@
         <v>37</v>
       </c>
       <c r="N65" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O65" s="33"/>
       <c r="P65" s="33"/>
@@ -4979,27 +5009,27 @@
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="28">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B66" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D66" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E66" s="32">
         <v>11</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H66" s="40">
+        <v>91</v>
+      </c>
+      <c r="H66" s="35">
         <v>0</v>
       </c>
       <c r="I66" s="36">
@@ -5018,7 +5048,7 @@
         <v>40</v>
       </c>
       <c r="N66" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O66" s="33"/>
       <c r="P66" s="33"/>
@@ -5029,25 +5059,25 @@
     </row>
     <row r="67" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="28">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B67" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D67" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E67" s="32">
         <v>12</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G67" s="34" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H67" s="40">
         <v>0</v>
@@ -5068,7 +5098,7 @@
         <v>43</v>
       </c>
       <c r="N67" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O67" s="33"/>
       <c r="P67" s="33"/>
@@ -5079,26 +5109,25 @@
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="28">
-        <f>(B68*100)+E68</f>
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B68" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D68" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E68" s="32">
         <v>10</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="H68" s="40">
         <v>0</v>
@@ -5119,7 +5148,7 @@
         <v>37</v>
       </c>
       <c r="N68" s="39" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O68" s="33"/>
       <c r="P68" s="33"/>
@@ -5130,26 +5159,25 @@
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="28">
-        <f>(B69*100)+E69</f>
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B69" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D69" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E69" s="32">
         <v>11</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="H69" s="40">
         <v>0</v>
@@ -5170,7 +5198,7 @@
         <v>40</v>
       </c>
       <c r="N69" s="39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O69" s="33"/>
       <c r="P69" s="33"/>
@@ -5181,26 +5209,25 @@
     </row>
     <row r="70" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="28">
-        <f>(B70*100)+E70</f>
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B70" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D70" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E70" s="32">
         <v>12</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="H70" s="40">
         <v>0</v>
@@ -5221,7 +5248,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O70" s="33"/>
       <c r="P70" s="33"/>
@@ -5229,6 +5256,312 @@
       <c r="R70" s="33"/>
       <c r="S70" s="36"/>
       <c r="T70" s="36"/>
+    </row>
+    <row r="71" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A71" s="28">
+        <f>(B71*100)+E71</f>
+        <v>10250010</v>
+      </c>
+      <c r="B71" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E71" s="32">
+        <v>10</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="G71" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="H71" s="40">
+        <v>0</v>
+      </c>
+      <c r="I71" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J71" s="37">
+        <v>0</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="41">
+        <v>0</v>
+      </c>
+      <c r="M71" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="O71" s="33"/>
+      <c r="P71" s="33"/>
+      <c r="Q71" s="33"/>
+      <c r="R71" s="33"/>
+      <c r="S71" s="36"/>
+      <c r="T71" s="36"/>
+    </row>
+    <row r="72" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A72" s="28">
+        <f>(B72*100)+E72</f>
+        <v>10250011</v>
+      </c>
+      <c r="B72" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E72" s="32">
+        <v>11</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G72" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72" s="40">
+        <v>0</v>
+      </c>
+      <c r="I72" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J72" s="37">
+        <v>0</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="41">
+        <v>0</v>
+      </c>
+      <c r="M72" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N72" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33"/>
+      <c r="Q72" s="33"/>
+      <c r="R72" s="33"/>
+      <c r="S72" s="36"/>
+      <c r="T72" s="36"/>
+    </row>
+    <row r="73" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A73" s="28">
+        <f>(B73*100)+E73</f>
+        <v>10250012</v>
+      </c>
+      <c r="B73" s="29">
+        <v>102500</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="31">
+        <v>102500001</v>
+      </c>
+      <c r="E73" s="32">
+        <v>12</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G73" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H73" s="40">
+        <v>0</v>
+      </c>
+      <c r="I73" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J73" s="37">
+        <v>0</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="41">
+        <v>0</v>
+      </c>
+      <c r="M73" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N73" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="O73" s="33"/>
+      <c r="P73" s="33"/>
+      <c r="Q73" s="33"/>
+      <c r="R73" s="33"/>
+      <c r="S73" s="36"/>
+      <c r="T73" s="36"/>
+    </row>
+    <row r="74" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A74" s="28">
+        <f>(B74*100)+E74</f>
+        <v>10230010</v>
+      </c>
+      <c r="B74" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D74" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E74" s="32">
+        <v>10</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G74" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="H74" s="40">
+        <v>0</v>
+      </c>
+      <c r="I74" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J74" s="37">
+        <v>0</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="41">
+        <v>0</v>
+      </c>
+      <c r="M74" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="O74" s="33"/>
+      <c r="P74" s="33"/>
+      <c r="Q74" s="33"/>
+      <c r="R74" s="33"/>
+      <c r="S74" s="36"/>
+      <c r="T74" s="36"/>
+    </row>
+    <row r="75" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A75" s="28">
+        <f>(B75*100)+E75</f>
+        <v>10230011</v>
+      </c>
+      <c r="B75" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D75" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E75" s="32">
+        <v>11</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G75" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="H75" s="40">
+        <v>0</v>
+      </c>
+      <c r="I75" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J75" s="37">
+        <v>0</v>
+      </c>
+      <c r="K75" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="41">
+        <v>0</v>
+      </c>
+      <c r="M75" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N75" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="O75" s="33"/>
+      <c r="P75" s="33"/>
+      <c r="Q75" s="33"/>
+      <c r="R75" s="33"/>
+      <c r="S75" s="36"/>
+      <c r="T75" s="36"/>
+    </row>
+    <row r="76" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A76" s="28">
+        <f>(B76*100)+E76</f>
+        <v>10230012</v>
+      </c>
+      <c r="B76" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E76" s="32">
+        <v>12</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G76" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="H76" s="40">
+        <v>0</v>
+      </c>
+      <c r="I76" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J76" s="37">
+        <v>0</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="41">
+        <v>0</v>
+      </c>
+      <c r="M76" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N76" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="O76" s="33"/>
+      <c r="P76" s="33"/>
+      <c r="Q76" s="33"/>
+      <c r="R76" s="33"/>
+      <c r="S76" s="36"/>
+      <c r="T76" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="117">
   <si>
     <t>id</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>20000_40000_100000_200000_400000</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
   </si>
   <si>
     <t>1_2_5</t>
@@ -749,6 +752,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -781,12 +790,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1780,7 +1783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T76"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3757,165 +3760,165 @@
       <c r="S40" s="22"/>
       <c r="T40" s="22"/>
     </row>
-    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A41" s="28">
-        <v>10010010</v>
-      </c>
-      <c r="B41" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E41" s="32">
-        <v>10</v>
-      </c>
-      <c r="F41" s="33" t="s">
+    <row r="41" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A41" s="18">
+        <v>1034001</v>
+      </c>
+      <c r="B41" s="18">
+        <v>103400</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="H41" s="35">
-        <v>0</v>
-      </c>
-      <c r="I41" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J41" s="37">
-        <v>0</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L41" s="38">
-        <v>0</v>
-      </c>
-      <c r="M41" s="36" t="s">
+      <c r="D41" s="23">
+        <v>103400001</v>
+      </c>
+      <c r="E41" s="19">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" s="27">
+        <v>50000000</v>
+      </c>
+      <c r="I41" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J41" s="22">
+        <v>500000</v>
+      </c>
+      <c r="K41" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="26">
+        <v>100</v>
+      </c>
+      <c r="M41" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="N41" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
-    </row>
-    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A42" s="28">
-        <v>10010011</v>
-      </c>
-      <c r="B42" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E42" s="32">
-        <v>11</v>
-      </c>
-      <c r="F42" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="G42" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="H42" s="35">
-        <v>0</v>
-      </c>
-      <c r="I42" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J42" s="37">
-        <v>0</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L42" s="38">
-        <v>0</v>
-      </c>
-      <c r="M42" s="36" t="s">
+      <c r="N41" s="20">
+        <v>0</v>
+      </c>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+    </row>
+    <row r="42" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A42" s="18">
+        <v>1034002</v>
+      </c>
+      <c r="B42" s="18">
+        <v>103401</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="23">
+        <v>103400001</v>
+      </c>
+      <c r="E42" s="19">
+        <v>2</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42" s="27">
+        <v>5000000000</v>
+      </c>
+      <c r="I42" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J42" s="22">
+        <v>50000000</v>
+      </c>
+      <c r="K42" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="26">
+        <v>100</v>
+      </c>
+      <c r="M42" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N42" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="36"/>
-      <c r="T42" s="36"/>
-    </row>
-    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A43" s="28">
-        <v>10010012</v>
-      </c>
-      <c r="B43" s="29">
-        <v>100100</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="31">
-        <v>100100026</v>
-      </c>
-      <c r="E43" s="32">
-        <v>12</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H43" s="40">
-        <v>0</v>
-      </c>
-      <c r="I43" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J43" s="37">
-        <v>0</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L43" s="38">
-        <v>0</v>
-      </c>
-      <c r="M43" s="36" t="s">
+      <c r="N42" s="20">
+        <v>0</v>
+      </c>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A43" s="18">
+        <v>1034003</v>
+      </c>
+      <c r="B43" s="18">
+        <v>103402</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="23">
+        <v>103400001</v>
+      </c>
+      <c r="E43" s="19">
+        <v>3</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="27">
+        <v>500000000000</v>
+      </c>
+      <c r="I43" s="24">
+        <v>9600</v>
+      </c>
+      <c r="J43" s="22">
+        <v>5000000000</v>
+      </c>
+      <c r="K43" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="26">
+        <v>100</v>
+      </c>
+      <c r="M43" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N43" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
+      <c r="N43" s="20">
+        <v>0</v>
+      </c>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="22"/>
+      <c r="T43" s="22"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A44" s="28">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B44" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D44" s="31">
         <v>100100026</v>
@@ -3924,10 +3927,10 @@
         <v>10</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H44" s="35">
         <v>0</v>
@@ -3941,14 +3944,14 @@
       <c r="K44" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="41">
+      <c r="L44" s="38">
         <v>0</v>
       </c>
       <c r="M44" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O44" s="33"/>
       <c r="P44" s="33"/>
@@ -3959,13 +3962,13 @@
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A45" s="28">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B45" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D45" s="31">
         <v>100100026</v>
@@ -3974,10 +3977,10 @@
         <v>11</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H45" s="35">
         <v>0</v>
@@ -3991,14 +3994,14 @@
       <c r="K45" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L45" s="41">
+      <c r="L45" s="38">
         <v>0</v>
       </c>
       <c r="M45" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O45" s="33"/>
       <c r="P45" s="33"/>
@@ -4009,13 +4012,13 @@
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A46" s="28">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B46" s="29">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D46" s="31">
         <v>100100026</v>
@@ -4024,10 +4027,10 @@
         <v>12</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H46" s="40">
         <v>0</v>
@@ -4041,14 +4044,14 @@
       <c r="K46" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L46" s="41">
+      <c r="L46" s="38">
         <v>0</v>
       </c>
       <c r="M46" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O46" s="33"/>
       <c r="P46" s="33"/>
@@ -4059,13 +4062,13 @@
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A47" s="28">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B47" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D47" s="31">
         <v>100100026</v>
@@ -4074,16 +4077,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="H47" s="35">
         <v>0</v>
       </c>
       <c r="I47" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J47" s="37">
         <v>0</v>
@@ -4091,14 +4094,14 @@
       <c r="K47" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L47" s="38">
+      <c r="L47" s="41">
         <v>0</v>
       </c>
       <c r="M47" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N47" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O47" s="33"/>
       <c r="P47" s="33"/>
@@ -4109,13 +4112,13 @@
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A48" s="28">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B48" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D48" s="31">
         <v>100100026</v>
@@ -4124,16 +4127,16 @@
         <v>11</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="H48" s="35">
         <v>0</v>
       </c>
       <c r="I48" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J48" s="37">
         <v>0</v>
@@ -4141,14 +4144,14 @@
       <c r="K48" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L48" s="38">
+      <c r="L48" s="41">
         <v>0</v>
       </c>
       <c r="M48" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
@@ -4159,13 +4162,13 @@
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A49" s="28">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B49" s="29">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D49" s="31">
         <v>100100026</v>
@@ -4174,16 +4177,16 @@
         <v>12</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="H49" s="40">
         <v>0</v>
       </c>
       <c r="I49" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J49" s="37">
         <v>0</v>
@@ -4191,14 +4194,14 @@
       <c r="K49" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L49" s="38">
+      <c r="L49" s="41">
         <v>0</v>
       </c>
       <c r="M49" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N49" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O49" s="33"/>
       <c r="P49" s="33"/>
@@ -4207,333 +4210,333 @@
       <c r="S49" s="36"/>
       <c r="T49" s="36"/>
     </row>
-    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A50" s="28">
-        <v>10120010</v>
-      </c>
-      <c r="B50" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="43">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B50" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="31">
+        <v>100100026</v>
       </c>
       <c r="E50" s="32">
         <v>10</v>
       </c>
-      <c r="F50" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="G50" s="44" t="s">
-        <v>102</v>
+      <c r="F50" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="H50" s="35">
         <v>0</v>
       </c>
-      <c r="I50" s="37">
-        <v>9500</v>
+      <c r="I50" s="36">
+        <v>9700</v>
       </c>
       <c r="J50" s="37">
         <v>0</v>
       </c>
-      <c r="K50" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="41">
-        <v>0</v>
-      </c>
-      <c r="M50" s="37" t="s">
+      <c r="K50" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="38">
+        <v>0</v>
+      </c>
+      <c r="M50" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="O50" s="39"/>
-      <c r="P50" s="39"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="39"/>
-      <c r="S50" s="37"/>
-      <c r="T50" s="37"/>
-    </row>
-    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+    </row>
+    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A51" s="28">
-        <v>10120011</v>
-      </c>
-      <c r="B51" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C51" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" s="43">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B51" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="31">
+        <v>100100026</v>
       </c>
       <c r="E51" s="32">
         <v>11</v>
       </c>
-      <c r="F51" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="G51" s="44" t="s">
-        <v>104</v>
+      <c r="F51" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G51" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="H51" s="35">
         <v>0</v>
       </c>
-      <c r="I51" s="37">
-        <v>9500</v>
+      <c r="I51" s="36">
+        <v>9700</v>
       </c>
       <c r="J51" s="37">
         <v>0</v>
       </c>
-      <c r="K51" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="41">
-        <v>0</v>
-      </c>
-      <c r="M51" s="37" t="s">
+      <c r="K51" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="38">
+        <v>0</v>
+      </c>
+      <c r="M51" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="O51" s="39"/>
-      <c r="P51" s="39"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="39"/>
-      <c r="S51" s="37"/>
-      <c r="T51" s="37"/>
-    </row>
-    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>93</v>
+      </c>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+    </row>
+    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A52" s="28">
-        <v>10120012</v>
-      </c>
-      <c r="B52" s="42">
-        <v>101200</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" s="43">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B52" s="29">
+        <v>100700</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="31">
+        <v>100100026</v>
       </c>
       <c r="E52" s="32">
         <v>12</v>
       </c>
-      <c r="F52" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="G52" s="44" t="s">
-        <v>106</v>
+      <c r="F52" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="H52" s="40">
         <v>0</v>
       </c>
-      <c r="I52" s="37">
-        <v>9500</v>
+      <c r="I52" s="36">
+        <v>9700</v>
       </c>
       <c r="J52" s="37">
         <v>0</v>
       </c>
-      <c r="K52" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="41">
-        <v>0</v>
-      </c>
-      <c r="M52" s="37" t="s">
+      <c r="K52" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="38">
+        <v>0</v>
+      </c>
+      <c r="M52" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="37"/>
-      <c r="T52" s="37"/>
-    </row>
-    <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
+        <v>96</v>
+      </c>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
+    </row>
+    <row r="53" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="28">
-        <v>10140010</v>
-      </c>
-      <c r="B53" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="31">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B53" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="43">
+        <v>101200026</v>
       </c>
       <c r="E53" s="32">
         <v>10</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F53" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" s="35">
+        <v>0</v>
+      </c>
+      <c r="I53" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J53" s="37">
+        <v>0</v>
+      </c>
+      <c r="K53" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="41">
+        <v>0</v>
+      </c>
+      <c r="M53" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="G53" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="H53" s="35">
-        <v>0</v>
-      </c>
-      <c r="I53" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J53" s="37">
-        <v>0</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L53" s="38">
-        <v>0</v>
-      </c>
-      <c r="M53" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="N53" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="36"/>
-      <c r="T53" s="36"/>
-    </row>
-    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="37"/>
+      <c r="T53" s="37"/>
+    </row>
+    <row r="54" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="28">
-        <v>10140011</v>
-      </c>
-      <c r="B54" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D54" s="31">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B54" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="43">
+        <v>101200026</v>
       </c>
       <c r="E54" s="32">
         <v>11</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="35">
+        <v>0</v>
+      </c>
+      <c r="I54" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J54" s="37">
+        <v>0</v>
+      </c>
+      <c r="K54" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="41">
+        <v>0</v>
+      </c>
+      <c r="M54" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="G54" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H54" s="35">
-        <v>0</v>
-      </c>
-      <c r="I54" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J54" s="37">
-        <v>0</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L54" s="38">
-        <v>0</v>
-      </c>
-      <c r="M54" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33"/>
-      <c r="Q54" s="33"/>
-      <c r="R54" s="33"/>
-      <c r="S54" s="36"/>
-      <c r="T54" s="36"/>
-    </row>
-    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+      <c r="S54" s="37"/>
+      <c r="T54" s="37"/>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="28">
-        <v>10140012</v>
-      </c>
-      <c r="B55" s="29">
-        <v>101400</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="31">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B55" s="42">
+        <v>101200</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="43">
+        <v>101200026</v>
       </c>
       <c r="E55" s="32">
         <v>12</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="F55" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H55" s="40">
+        <v>0</v>
+      </c>
+      <c r="I55" s="37">
+        <v>9500</v>
+      </c>
+      <c r="J55" s="37">
+        <v>0</v>
+      </c>
+      <c r="K55" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="41">
+        <v>0</v>
+      </c>
+      <c r="M55" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="N55" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="G55" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="H55" s="40">
-        <v>0</v>
-      </c>
-      <c r="I55" s="36">
-        <v>9600</v>
-      </c>
-      <c r="J55" s="37">
-        <v>0</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="38">
-        <v>0</v>
-      </c>
-      <c r="M55" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="N55" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="O55" s="33"/>
-      <c r="P55" s="33"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="33"/>
-      <c r="S55" s="36"/>
-      <c r="T55" s="36"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="39"/>
+      <c r="Q55" s="39"/>
+      <c r="R55" s="39"/>
+      <c r="S55" s="37"/>
+      <c r="T55" s="37"/>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="28">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B56" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D56" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E56" s="32">
         <v>10</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="H56" s="35">
         <v>0</v>
       </c>
       <c r="I56" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J56" s="37">
         <v>0</v>
@@ -4548,7 +4551,7 @@
         <v>37</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -4559,31 +4562,31 @@
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="28">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B57" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D57" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E57" s="32">
         <v>11</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="H57" s="35">
         <v>0</v>
       </c>
       <c r="I57" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J57" s="37">
         <v>0</v>
@@ -4598,7 +4601,7 @@
         <v>40</v>
       </c>
       <c r="N57" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O57" s="33"/>
       <c r="P57" s="33"/>
@@ -4609,31 +4612,31 @@
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="28">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B58" s="29">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D58" s="31">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E58" s="32">
         <v>12</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="H58" s="40">
         <v>0</v>
       </c>
       <c r="I58" s="36">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="J58" s="37">
         <v>0</v>
@@ -4648,7 +4651,7 @@
         <v>43</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O58" s="33"/>
       <c r="P58" s="33"/>
@@ -4659,22 +4662,22 @@
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A59" s="28">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B59" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D59" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E59" s="32">
         <v>10</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G59" s="34" t="s">
         <v>35</v>
@@ -4683,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J59" s="37">
         <v>0</v>
@@ -4691,14 +4694,14 @@
       <c r="K59" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L59" s="41">
+      <c r="L59" s="38">
         <v>0</v>
       </c>
       <c r="M59" s="36" t="s">
         <v>37</v>
       </c>
       <c r="N59" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O59" s="33"/>
       <c r="P59" s="33"/>
@@ -4709,22 +4712,22 @@
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A60" s="28">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B60" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D60" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E60" s="32">
         <v>11</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G60" s="34" t="s">
         <v>63</v>
@@ -4733,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J60" s="37">
         <v>0</v>
@@ -4741,14 +4744,14 @@
       <c r="K60" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L60" s="41">
+      <c r="L60" s="38">
         <v>0</v>
       </c>
       <c r="M60" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N60" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O60" s="33"/>
       <c r="P60" s="33"/>
@@ -4759,22 +4762,22 @@
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A61" s="28">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B61" s="29">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="31">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E61" s="32">
         <v>12</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>39</v>
@@ -4783,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="36">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="J61" s="37">
         <v>0</v>
@@ -4791,14 +4794,14 @@
       <c r="K61" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L61" s="41">
+      <c r="L61" s="38">
         <v>0</v>
       </c>
       <c r="M61" s="36" t="s">
         <v>43</v>
       </c>
       <c r="N61" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O61" s="33"/>
       <c r="P61" s="33"/>
@@ -4809,22 +4812,22 @@
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A62" s="28">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B62" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D62" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E62" s="32">
         <v>10</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G62" s="34" t="s">
         <v>35</v>
@@ -4848,7 +4851,7 @@
         <v>37</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O62" s="33"/>
       <c r="P62" s="33"/>
@@ -4859,22 +4862,22 @@
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="28">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B63" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D63" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E63" s="32">
         <v>11</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G63" s="34" t="s">
         <v>63</v>
@@ -4898,7 +4901,7 @@
         <v>40</v>
       </c>
       <c r="N63" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O63" s="33"/>
       <c r="P63" s="33"/>
@@ -4909,22 +4912,22 @@
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="28">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B64" s="29">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D64" s="31">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E64" s="32">
         <v>12</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G64" s="34" t="s">
         <v>39</v>
@@ -4948,7 +4951,7 @@
         <v>43</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O64" s="33"/>
       <c r="P64" s="33"/>
@@ -4959,25 +4962,25 @@
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="28">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B65" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D65" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E65" s="32">
         <v>10</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="H65" s="35">
         <v>0</v>
@@ -4998,7 +5001,7 @@
         <v>37</v>
       </c>
       <c r="N65" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O65" s="33"/>
       <c r="P65" s="33"/>
@@ -5009,25 +5012,25 @@
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="28">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B66" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D66" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E66" s="32">
         <v>11</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H66" s="35">
         <v>0</v>
@@ -5048,7 +5051,7 @@
         <v>40</v>
       </c>
       <c r="N66" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O66" s="33"/>
       <c r="P66" s="33"/>
@@ -5059,25 +5062,25 @@
     </row>
     <row r="67" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="28">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B67" s="29">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D67" s="31">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E67" s="32">
         <v>12</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G67" s="34" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="H67" s="40">
         <v>0</v>
@@ -5098,7 +5101,7 @@
         <v>43</v>
       </c>
       <c r="N67" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O67" s="33"/>
       <c r="P67" s="33"/>
@@ -5109,27 +5112,27 @@
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="28">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B68" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D68" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E68" s="32">
         <v>10</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="H68" s="40">
+        <v>89</v>
+      </c>
+      <c r="H68" s="35">
         <v>0</v>
       </c>
       <c r="I68" s="36">
@@ -5148,7 +5151,7 @@
         <v>37</v>
       </c>
       <c r="N68" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O68" s="33"/>
       <c r="P68" s="33"/>
@@ -5159,27 +5162,27 @@
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="28">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B69" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D69" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E69" s="32">
         <v>11</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H69" s="40">
+        <v>92</v>
+      </c>
+      <c r="H69" s="35">
         <v>0</v>
       </c>
       <c r="I69" s="36">
@@ -5198,7 +5201,7 @@
         <v>40</v>
       </c>
       <c r="N69" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O69" s="33"/>
       <c r="P69" s="33"/>
@@ -5209,25 +5212,25 @@
     </row>
     <row r="70" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="28">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B70" s="29">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D70" s="31">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E70" s="32">
         <v>12</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H70" s="40">
         <v>0</v>
@@ -5248,7 +5251,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O70" s="33"/>
       <c r="P70" s="33"/>
@@ -5259,26 +5262,25 @@
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="28">
-        <f>(B71*100)+E71</f>
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B71" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D71" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E71" s="32">
         <v>10</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G71" s="34" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="H71" s="40">
         <v>0</v>
@@ -5299,7 +5301,7 @@
         <v>37</v>
       </c>
       <c r="N71" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O71" s="33"/>
       <c r="P71" s="33"/>
@@ -5310,26 +5312,25 @@
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="28">
-        <f>(B72*100)+E72</f>
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B72" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D72" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E72" s="32">
         <v>11</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="H72" s="40">
         <v>0</v>
@@ -5350,7 +5351,7 @@
         <v>40</v>
       </c>
       <c r="N72" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O72" s="33"/>
       <c r="P72" s="33"/>
@@ -5361,26 +5362,25 @@
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="28">
-        <f>(B73*100)+E73</f>
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B73" s="29">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D73" s="31">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E73" s="32">
         <v>12</v>
       </c>
       <c r="F73" s="33" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H73" s="40">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O73" s="33"/>
       <c r="P73" s="33"/>
@@ -5412,26 +5412,26 @@
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="28">
-        <f>(B74*100)+E74</f>
-        <v>10230010</v>
+        <f t="shared" ref="A74:A79" si="0">(B74*100)+E74</f>
+        <v>10250010</v>
       </c>
       <c r="B74" s="29">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D74" s="31">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E74" s="32">
         <v>10</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="G74" s="34" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H74" s="40">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>37</v>
       </c>
       <c r="N74" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O74" s="33"/>
       <c r="P74" s="33"/>
@@ -5463,26 +5463,26 @@
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="28">
-        <f>(B75*100)+E75</f>
-        <v>10230011</v>
+        <f t="shared" si="0"/>
+        <v>10250011</v>
       </c>
       <c r="B75" s="29">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D75" s="31">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E75" s="32">
         <v>11</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="G75" s="34" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="H75" s="40">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>40</v>
       </c>
       <c r="N75" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O75" s="33"/>
       <c r="P75" s="33"/>
@@ -5514,26 +5514,26 @@
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="28">
-        <f>(B76*100)+E76</f>
-        <v>10230012</v>
+        <f t="shared" si="0"/>
+        <v>10250012</v>
       </c>
       <c r="B76" s="29">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D76" s="31">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E76" s="32">
         <v>12</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G76" s="34" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H76" s="40">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>43</v>
       </c>
       <c r="N76" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O76" s="33"/>
       <c r="P76" s="33"/>
@@ -5562,6 +5562,309 @@
       <c r="R76" s="33"/>
       <c r="S76" s="36"/>
       <c r="T76" s="36"/>
+    </row>
+    <row r="77" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A77" s="28">
+        <f t="shared" si="0"/>
+        <v>10230010</v>
+      </c>
+      <c r="B77" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E77" s="32">
+        <v>10</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G77" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="H77" s="40">
+        <v>0</v>
+      </c>
+      <c r="I77" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J77" s="37">
+        <v>0</v>
+      </c>
+      <c r="K77" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="41">
+        <v>0</v>
+      </c>
+      <c r="M77" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="O77" s="33"/>
+      <c r="P77" s="33"/>
+      <c r="Q77" s="33"/>
+      <c r="R77" s="33"/>
+      <c r="S77" s="36"/>
+      <c r="T77" s="36"/>
+    </row>
+    <row r="78" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A78" s="28">
+        <f t="shared" si="0"/>
+        <v>10230011</v>
+      </c>
+      <c r="B78" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E78" s="32">
+        <v>11</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G78" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="H78" s="40">
+        <v>0</v>
+      </c>
+      <c r="I78" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J78" s="37">
+        <v>0</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="41">
+        <v>0</v>
+      </c>
+      <c r="M78" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N78" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="O78" s="33"/>
+      <c r="P78" s="33"/>
+      <c r="Q78" s="33"/>
+      <c r="R78" s="33"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="36"/>
+    </row>
+    <row r="79" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A79" s="28">
+        <f t="shared" si="0"/>
+        <v>10230012</v>
+      </c>
+      <c r="B79" s="29">
+        <v>102300</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" s="31">
+        <v>102300001</v>
+      </c>
+      <c r="E79" s="32">
+        <v>12</v>
+      </c>
+      <c r="F79" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G79" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="H79" s="40">
+        <v>0</v>
+      </c>
+      <c r="I79" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J79" s="37">
+        <v>0</v>
+      </c>
+      <c r="K79" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="41">
+        <v>0</v>
+      </c>
+      <c r="M79" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N79" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="O79" s="33"/>
+      <c r="P79" s="33"/>
+      <c r="Q79" s="33"/>
+      <c r="R79" s="33"/>
+      <c r="S79" s="36"/>
+      <c r="T79" s="36"/>
+    </row>
+    <row r="80" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A80" s="28">
+        <v>10340010</v>
+      </c>
+      <c r="B80" s="29">
+        <v>103400</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" s="31">
+        <v>103400001</v>
+      </c>
+      <c r="E80" s="32">
+        <v>10</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G80" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="H80" s="40">
+        <v>0</v>
+      </c>
+      <c r="I80" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J80" s="37">
+        <v>0</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="41">
+        <v>0</v>
+      </c>
+      <c r="M80" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="O80" s="33"/>
+      <c r="P80" s="33"/>
+      <c r="Q80" s="33"/>
+      <c r="R80" s="33"/>
+      <c r="S80" s="36"/>
+      <c r="T80" s="36"/>
+    </row>
+    <row r="81" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A81" s="28">
+        <v>10340011</v>
+      </c>
+      <c r="B81" s="29">
+        <v>103400</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="31">
+        <v>103400001</v>
+      </c>
+      <c r="E81" s="32">
+        <v>11</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G81" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="H81" s="40">
+        <v>0</v>
+      </c>
+      <c r="I81" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J81" s="37">
+        <v>0</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="41">
+        <v>0</v>
+      </c>
+      <c r="M81" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N81" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="O81" s="33"/>
+      <c r="P81" s="33"/>
+      <c r="Q81" s="33"/>
+      <c r="R81" s="33"/>
+      <c r="S81" s="36"/>
+      <c r="T81" s="36"/>
+    </row>
+    <row r="82" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A82" s="28">
+        <v>10340012</v>
+      </c>
+      <c r="B82" s="29">
+        <v>103400</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="31">
+        <v>103400001</v>
+      </c>
+      <c r="E82" s="32">
+        <v>12</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G82" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="H82" s="40">
+        <v>0</v>
+      </c>
+      <c r="I82" s="36">
+        <v>9600</v>
+      </c>
+      <c r="J82" s="37">
+        <v>0</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="41">
+        <v>0</v>
+      </c>
+      <c r="M82" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N82" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="O82" s="33"/>
+      <c r="P82" s="33"/>
+      <c r="Q82" s="33"/>
+      <c r="R82" s="33"/>
+      <c r="S82" s="36"/>
+      <c r="T82" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -290,250 +290,124 @@
     <t>金矿大亨</t>
   </si>
   <si>
-    <t>1_2_5_10_20_50</t>
-  </si>
-  <si>
-    <t>10:1</t>
+    <t>10_20_50_100_200_500_1000</t>
+  </si>
+  <si>
+    <t>50:1</t>
   </si>
   <si>
     <t>0,5000,10000</t>
   </si>
   <si>
-    <t>500000_17001</t>
-  </si>
-  <si>
-    <t>100_200_500_1000_2000_5000</t>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>100_200_500_1000_2000_5000_10000</t>
+  </si>
+  <si>
+    <t>500:1</t>
+  </si>
+  <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
+  </si>
+  <si>
+    <t>5000:1</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+  </si>
+  <si>
+    <t>50000:1</t>
+  </si>
+  <si>
+    <t>100000_200000_500000_1000000_2000000_500000_100000000</t>
+  </si>
+  <si>
+    <t>500000:1</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>50_100_250_500_1000_2500_5000</t>
+  </si>
+  <si>
+    <t>250:1</t>
+  </si>
+  <si>
+    <t>500_1000_2500_5000_10000_25000_50000</t>
+  </si>
+  <si>
+    <t>2500:1</t>
+  </si>
+  <si>
+    <t>5000_10000_25000_50000_100000_250000_500000</t>
+  </si>
+  <si>
+    <t>25000:1</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>财富银行</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>20_40_100_200_400_1000_2000</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>200_400_1000_2000_4000_10000_20000</t>
   </si>
   <si>
     <t>1000:1</t>
   </si>
   <si>
-    <t>50000000_17001</t>
-  </si>
-  <si>
-    <t>10000_20000_50000_100000_200000_500000</t>
-  </si>
-  <si>
-    <t>100000:1</t>
-  </si>
-  <si>
-    <t>5000000000_17001</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>1000000_2000000_5000000_10000000_20000000_50000000</t>
-  </si>
-  <si>
-    <t>10000000:1</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>5_10_25_50_100_250</t>
-  </si>
-  <si>
-    <t>50:1</t>
-  </si>
-  <si>
-    <t>500_1000_2500_5000_10000_25000</t>
-  </si>
-  <si>
-    <t>5000:1</t>
-  </si>
-  <si>
-    <t>50000_100000_250000_500000_1000000_2500000</t>
-  </si>
-  <si>
-    <t>500000:1</t>
-  </si>
-  <si>
-    <t>财神</t>
-  </si>
-  <si>
-    <t>6_12_32_66_132_332</t>
-  </si>
-  <si>
-    <t>66:1</t>
-  </si>
-  <si>
-    <t>600_1200_3200_6600_13200_33200</t>
-  </si>
-  <si>
-    <t>6600:1</t>
-  </si>
-  <si>
-    <t>60000_120000_320000_660000_1320000_3320000</t>
-  </si>
-  <si>
-    <t>660000:1</t>
-  </si>
-  <si>
-    <t>埃及艳后</t>
-  </si>
-  <si>
-    <t>10_20_50_100_200_500</t>
-  </si>
-  <si>
-    <t>100:1</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000_50000</t>
+    <t>2000_4000_10000_20000_40000_100000_200000</t>
   </si>
   <si>
     <t>10000:1</t>
   </si>
   <si>
-    <t>100000_200000_500000_1000000_2000000_5000000</t>
-  </si>
-  <si>
-    <t>1000000:1</t>
-  </si>
-  <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
-  </si>
-  <si>
-    <t>雷神</t>
-  </si>
-  <si>
-    <t>财富银行</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>2_4_8_20_40</t>
-  </si>
-  <si>
-    <t>8:1</t>
-  </si>
-  <si>
-    <t>200_400_800_2000_4000</t>
-  </si>
-  <si>
-    <t>800:1</t>
-  </si>
-  <si>
-    <t>20000_40000_80000_200000_400000</t>
-  </si>
-  <si>
-    <t>80000:1</t>
-  </si>
-  <si>
-    <t>寒冰王座</t>
-  </si>
-  <si>
-    <t>5:1</t>
-  </si>
-  <si>
-    <t>500:1</t>
-  </si>
-  <si>
-    <t>50000:1</t>
-  </si>
-  <si>
     <t>蒸汽时代</t>
   </si>
   <si>
-    <t>2_4_10_20_40</t>
-  </si>
-  <si>
-    <t>200_400_1000_2000_4000</t>
-  </si>
-  <si>
-    <t>20000_40000_100000_200000_400000</t>
-  </si>
-  <si>
-    <t>1_2_5</t>
-  </si>
-  <si>
-    <t>2:1</t>
-  </si>
-  <si>
-    <t>1980000_10000</t>
-  </si>
-  <si>
-    <t>10_20_50</t>
-  </si>
-  <si>
-    <t>20:1</t>
-  </si>
-  <si>
-    <t>1980000_100000</t>
-  </si>
-  <si>
-    <t>100_200_500</t>
-  </si>
-  <si>
-    <t>200:1</t>
-  </si>
-  <si>
-    <t>1980000_1000000</t>
-  </si>
-  <si>
-    <t>1000_2000_5000</t>
-  </si>
-  <si>
-    <t>2000:1</t>
-  </si>
-  <si>
-    <t>5_10_25</t>
-  </si>
-  <si>
-    <t>50_100_250</t>
-  </si>
-  <si>
-    <t>500_1000_2500</t>
-  </si>
-  <si>
-    <t>6_12_32</t>
-  </si>
-  <si>
-    <t>12:1</t>
-  </si>
-  <si>
-    <t>60_120_320</t>
-  </si>
-  <si>
-    <t>120:1</t>
-  </si>
-  <si>
-    <t>600_1200_3200</t>
-  </si>
-  <si>
-    <t>1200:1</t>
-  </si>
-  <si>
-    <t>2_4_8</t>
-  </si>
-  <si>
-    <t>4:1</t>
-  </si>
-  <si>
-    <t>20_40_80</t>
-  </si>
-  <si>
-    <t>40:1</t>
-  </si>
-  <si>
-    <t>200_400_800</t>
-  </si>
-  <si>
-    <t>400:1</t>
-  </si>
-  <si>
-    <t>2_4_10</t>
-  </si>
-  <si>
-    <t>20_40_100</t>
-  </si>
-  <si>
-    <t>200_400_1000</t>
+    <t>1980000_500000</t>
+  </si>
+  <si>
+    <t>1980000_5000000</t>
+  </si>
+  <si>
+    <t>1980000_50000000</t>
   </si>
 </sst>
 </file>
@@ -748,8 +622,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -760,19 +646,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -781,12 +661,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1980,13 +1854,13 @@
         <v>35</v>
       </c>
       <c r="H5" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I5" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J5" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K5" s="25" t="s">
         <v>36</v>
@@ -2033,7 +1907,7 @@
         <v>5000000000</v>
       </c>
       <c r="I6" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J6" s="22">
         <v>50000000</v>
@@ -2080,13 +1954,13 @@
         <v>42</v>
       </c>
       <c r="H7" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I7" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J7" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K7" s="25" t="s">
         <v>36</v>
@@ -2124,19 +1998,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H8" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I8" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J8" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K8" s="25" t="s">
         <v>36</v>
@@ -2174,16 +2048,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H9" s="13">
         <v>5000000000</v>
       </c>
       <c r="I9" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J9" s="22">
         <v>50000000</v>
@@ -2224,19 +2098,19 @@
         <v>3</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H10" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I10" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J10" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K10" s="25" t="s">
         <v>36</v>
@@ -2265,7 +2139,7 @@
         <v>100700</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" s="23">
         <v>100100026</v>
@@ -2274,19 +2148,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I11" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J11" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K11" s="25" t="s">
         <v>36</v>
@@ -2315,7 +2189,7 @@
         <v>100700</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="23">
         <v>100100026</v>
@@ -2324,16 +2198,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H12" s="13">
         <v>5000000000</v>
       </c>
       <c r="I12" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J12" s="22">
         <v>50000000</v>
@@ -2365,7 +2239,7 @@
         <v>100700</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="23">
         <v>100100026</v>
@@ -2374,19 +2248,19 @@
         <v>3</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I13" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J13" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K13" s="25" t="s">
         <v>36</v>
@@ -2415,7 +2289,7 @@
         <v>101200</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="23">
         <v>100100026</v>
@@ -2424,19 +2298,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H14" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I14" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J14" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K14" s="25" t="s">
         <v>36</v>
@@ -2465,7 +2339,7 @@
         <v>101200</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="23">
         <v>100100026</v>
@@ -2474,16 +2348,16 @@
         <v>2</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H15" s="13">
         <v>5000000000</v>
       </c>
       <c r="I15" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J15" s="22">
         <v>50000000</v>
@@ -2515,7 +2389,7 @@
         <v>101200</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="23">
         <v>100100026</v>
@@ -2524,19 +2398,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H16" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I16" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J16" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K16" s="25" t="s">
         <v>36</v>
@@ -2565,7 +2439,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="23">
         <v>100100026</v>
@@ -2574,19 +2448,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H17" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I17" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J17" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>36</v>
@@ -2615,7 +2489,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18" s="23">
         <v>100100026</v>
@@ -2624,16 +2498,16 @@
         <v>2</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H18" s="13">
         <v>5000000000</v>
       </c>
       <c r="I18" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J18" s="22">
         <v>50000000</v>
@@ -2665,7 +2539,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D19" s="23">
         <v>100100026</v>
@@ -2674,19 +2548,19 @@
         <v>3</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H19" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I19" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J19" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K19" s="25" t="s">
         <v>36</v>
@@ -2715,7 +2589,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D20" s="23">
         <v>101700001</v>
@@ -2724,19 +2598,19 @@
         <v>1</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H20" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I20" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J20" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K20" s="25" t="s">
         <v>36</v>
@@ -2765,7 +2639,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D21" s="23">
         <v>101700001</v>
@@ -2774,16 +2648,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H21" s="13">
         <v>5000000000</v>
       </c>
       <c r="I21" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J21" s="22">
         <v>50000000</v>
@@ -2815,7 +2689,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D22" s="23">
         <v>101700001</v>
@@ -2824,19 +2698,19 @@
         <v>3</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H22" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I22" s="22">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J22" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K22" s="25" t="s">
         <v>36</v>
@@ -2865,7 +2739,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D23" s="23">
         <v>102100001</v>
@@ -2874,19 +2748,19 @@
         <v>1</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H23" s="27">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I23" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J23" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K23" s="25" t="s">
         <v>36</v>
@@ -2915,7 +2789,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D24" s="23">
         <v>102100001</v>
@@ -2924,16 +2798,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H24" s="27">
         <v>5000000000</v>
       </c>
       <c r="I24" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J24" s="22">
         <v>50000000</v>
@@ -2965,7 +2839,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D25" s="23">
         <v>102100001</v>
@@ -2974,19 +2848,19 @@
         <v>3</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H25" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I25" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J25" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K25" s="25" t="s">
         <v>36</v>
@@ -3015,7 +2889,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D26" s="23">
         <v>102200001</v>
@@ -3024,19 +2898,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H26" s="27">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I26" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J26" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K26" s="25" t="s">
         <v>36</v>
@@ -3065,7 +2939,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D27" s="23">
         <v>102200001</v>
@@ -3074,16 +2948,16 @@
         <v>2</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H27" s="27">
         <v>5000000000</v>
       </c>
       <c r="I27" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J27" s="22">
         <v>50000000</v>
@@ -3115,7 +2989,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D28" s="23">
         <v>102200001</v>
@@ -3124,19 +2998,19 @@
         <v>3</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H28" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I28" s="22">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J28" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K28" s="25" t="s">
         <v>36</v>
@@ -3165,7 +3039,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D29" s="23">
         <v>102400026</v>
@@ -3180,13 +3054,13 @@
         <v>35</v>
       </c>
       <c r="H29" s="13">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I29" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J29" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K29" s="25" t="s">
         <v>36</v>
@@ -3215,7 +3089,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D30" s="23">
         <v>102400026</v>
@@ -3233,7 +3107,7 @@
         <v>5000000000</v>
       </c>
       <c r="I30" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J30" s="22">
         <v>50000000</v>
@@ -3265,7 +3139,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D31" s="23">
         <v>102400026</v>
@@ -3280,13 +3154,13 @@
         <v>42</v>
       </c>
       <c r="H31" s="27">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I31" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J31" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K31" s="25" t="s">
         <v>36</v>
@@ -3315,7 +3189,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D32" s="23">
         <v>101800001</v>
@@ -3324,16 +3198,16 @@
         <v>1</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H32" s="13">
         <v>50000000</v>
       </c>
       <c r="I32" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J32" s="22">
         <v>500000</v>
@@ -3365,7 +3239,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D33" s="23">
         <v>101800001</v>
@@ -3374,16 +3248,16 @@
         <v>2</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H33" s="13">
         <v>5000000000</v>
       </c>
       <c r="I33" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J33" s="22">
         <v>50000000</v>
@@ -3415,7 +3289,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D34" s="23">
         <v>101800001</v>
@@ -3424,16 +3298,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H34" s="27">
         <v>500000000000</v>
       </c>
       <c r="I34" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J34" s="22">
         <v>5000000000</v>
@@ -3465,7 +3339,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D35" s="23">
         <v>102500001</v>
@@ -3474,16 +3348,16 @@
         <v>1</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H35" s="13">
         <v>50000000</v>
       </c>
       <c r="I35" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J35" s="22">
         <v>500000</v>
@@ -3515,7 +3389,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D36" s="23">
         <v>102500001</v>
@@ -3524,16 +3398,16 @@
         <v>2</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H36" s="13">
         <v>5000000000</v>
       </c>
       <c r="I36" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J36" s="22">
         <v>50000000</v>
@@ -3565,7 +3439,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D37" s="23">
         <v>102500001</v>
@@ -3574,16 +3448,16 @@
         <v>3</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H37" s="27">
         <v>500000000000</v>
       </c>
       <c r="I37" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J37" s="22">
         <v>5000000000</v>
@@ -3615,7 +3489,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D38" s="23">
         <v>102300001</v>
@@ -3624,16 +3498,16 @@
         <v>1</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H38" s="27">
         <v>50000000</v>
       </c>
       <c r="I38" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J38" s="22">
         <v>500000</v>
@@ -3665,7 +3539,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D39" s="23">
         <v>102300001</v>
@@ -3674,16 +3548,16 @@
         <v>2</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H39" s="27">
         <v>5000000000</v>
       </c>
       <c r="I39" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J39" s="22">
         <v>50000000</v>
@@ -3715,7 +3589,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D40" s="23">
         <v>102300001</v>
@@ -3724,16 +3598,16 @@
         <v>3</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H40" s="27">
         <v>500000000000</v>
       </c>
       <c r="I40" s="24">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J40" s="22">
         <v>5000000000</v>
@@ -3774,16 +3648,16 @@
         <v>10</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="H41" s="35">
         <v>0</v>
       </c>
       <c r="I41" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J41" s="37">
         <v>0</v>
@@ -3798,7 +3672,7 @@
         <v>37</v>
       </c>
       <c r="N41" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O41" s="33"/>
       <c r="P41" s="33"/>
@@ -3824,16 +3698,16 @@
         <v>11</v>
       </c>
       <c r="F42" s="33" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="H42" s="35">
         <v>0</v>
       </c>
       <c r="I42" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J42" s="37">
         <v>0</v>
@@ -3848,7 +3722,7 @@
         <v>40</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
@@ -3874,16 +3748,16 @@
         <v>12</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="H43" s="40">
         <v>0</v>
       </c>
       <c r="I43" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J43" s="37">
         <v>0</v>
@@ -3898,7 +3772,7 @@
         <v>43</v>
       </c>
       <c r="N43" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O43" s="33"/>
       <c r="P43" s="33"/>
@@ -3924,16 +3798,16 @@
         <v>10</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="H44" s="35">
         <v>0</v>
       </c>
       <c r="I44" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J44" s="37">
         <v>0</v>
@@ -3948,7 +3822,7 @@
         <v>37</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O44" s="33"/>
       <c r="P44" s="33"/>
@@ -3974,16 +3848,16 @@
         <v>11</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="H45" s="35">
         <v>0</v>
       </c>
       <c r="I45" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J45" s="37">
         <v>0</v>
@@ -3998,7 +3872,7 @@
         <v>40</v>
       </c>
       <c r="N45" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O45" s="33"/>
       <c r="P45" s="33"/>
@@ -4024,16 +3898,16 @@
         <v>12</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="H46" s="40">
         <v>0</v>
       </c>
       <c r="I46" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J46" s="37">
         <v>0</v>
@@ -4048,7 +3922,7 @@
         <v>43</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O46" s="33"/>
       <c r="P46" s="33"/>
@@ -4065,7 +3939,7 @@
         <v>100700</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D47" s="31">
         <v>100100026</v>
@@ -4074,16 +3948,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H47" s="35">
         <v>0</v>
       </c>
       <c r="I47" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J47" s="37">
         <v>0</v>
@@ -4098,7 +3972,7 @@
         <v>37</v>
       </c>
       <c r="N47" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O47" s="33"/>
       <c r="P47" s="33"/>
@@ -4115,7 +3989,7 @@
         <v>100700</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D48" s="31">
         <v>100100026</v>
@@ -4124,16 +3998,16 @@
         <v>11</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H48" s="35">
         <v>0</v>
       </c>
       <c r="I48" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J48" s="37">
         <v>0</v>
@@ -4148,7 +4022,7 @@
         <v>40</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O48" s="33"/>
       <c r="P48" s="33"/>
@@ -4165,7 +4039,7 @@
         <v>100700</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D49" s="31">
         <v>100100026</v>
@@ -4174,16 +4048,16 @@
         <v>12</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H49" s="40">
         <v>0</v>
       </c>
       <c r="I49" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J49" s="37">
         <v>0</v>
@@ -4198,7 +4072,7 @@
         <v>43</v>
       </c>
       <c r="N49" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O49" s="33"/>
       <c r="P49" s="33"/>
@@ -4215,7 +4089,7 @@
         <v>101200</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D50" s="43">
         <v>101200026</v>
@@ -4224,10 +4098,10 @@
         <v>10</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H50" s="35">
         <v>0</v>
@@ -4248,7 +4122,7 @@
         <v>37</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O50" s="39"/>
       <c r="P50" s="39"/>
@@ -4265,7 +4139,7 @@
         <v>101200</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D51" s="43">
         <v>101200026</v>
@@ -4274,10 +4148,10 @@
         <v>11</v>
       </c>
       <c r="F51" s="39" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="H51" s="35">
         <v>0</v>
@@ -4298,7 +4172,7 @@
         <v>40</v>
       </c>
       <c r="N51" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O51" s="39"/>
       <c r="P51" s="39"/>
@@ -4315,7 +4189,7 @@
         <v>101200</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D52" s="43">
         <v>101200026</v>
@@ -4324,10 +4198,10 @@
         <v>12</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="H52" s="40">
         <v>0</v>
@@ -4348,7 +4222,7 @@
         <v>43</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O52" s="39"/>
       <c r="P52" s="39"/>
@@ -4365,7 +4239,7 @@
         <v>101400</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D53" s="31">
         <v>100100026</v>
@@ -4374,16 +4248,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="H53" s="35">
         <v>0</v>
       </c>
       <c r="I53" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J53" s="37">
         <v>0</v>
@@ -4398,7 +4272,7 @@
         <v>37</v>
       </c>
       <c r="N53" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O53" s="33"/>
       <c r="P53" s="33"/>
@@ -4415,7 +4289,7 @@
         <v>101400</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D54" s="31">
         <v>100100026</v>
@@ -4424,16 +4298,16 @@
         <v>11</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="H54" s="35">
         <v>0</v>
       </c>
       <c r="I54" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J54" s="37">
         <v>0</v>
@@ -4448,7 +4322,7 @@
         <v>40</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O54" s="33"/>
       <c r="P54" s="33"/>
@@ -4465,7 +4339,7 @@
         <v>101400</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D55" s="31">
         <v>100100026</v>
@@ -4474,16 +4348,16 @@
         <v>12</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="H55" s="40">
         <v>0</v>
       </c>
       <c r="I55" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J55" s="37">
         <v>0</v>
@@ -4498,7 +4372,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O55" s="33"/>
       <c r="P55" s="33"/>
@@ -4515,7 +4389,7 @@
         <v>101700</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D56" s="31">
         <v>101700001</v>
@@ -4524,16 +4398,16 @@
         <v>10</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H56" s="35">
         <v>0</v>
       </c>
       <c r="I56" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J56" s="37">
         <v>0</v>
@@ -4548,7 +4422,7 @@
         <v>37</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
@@ -4565,7 +4439,7 @@
         <v>101700</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D57" s="31">
         <v>101700001</v>
@@ -4574,16 +4448,16 @@
         <v>11</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H57" s="35">
         <v>0</v>
       </c>
       <c r="I57" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J57" s="37">
         <v>0</v>
@@ -4598,7 +4472,7 @@
         <v>40</v>
       </c>
       <c r="N57" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O57" s="33"/>
       <c r="P57" s="33"/>
@@ -4615,7 +4489,7 @@
         <v>101700</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D58" s="31">
         <v>101700001</v>
@@ -4624,16 +4498,16 @@
         <v>12</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H58" s="40">
         <v>0</v>
       </c>
       <c r="I58" s="36">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J58" s="37">
         <v>0</v>
@@ -4648,7 +4522,7 @@
         <v>43</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O58" s="33"/>
       <c r="P58" s="33"/>
@@ -4665,7 +4539,7 @@
         <v>102100</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D59" s="31">
         <v>102100001</v>
@@ -4674,16 +4548,16 @@
         <v>10</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H59" s="35">
         <v>0</v>
       </c>
       <c r="I59" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J59" s="37">
         <v>0</v>
@@ -4698,7 +4572,7 @@
         <v>37</v>
       </c>
       <c r="N59" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O59" s="33"/>
       <c r="P59" s="33"/>
@@ -4715,7 +4589,7 @@
         <v>102100</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D60" s="31">
         <v>102100001</v>
@@ -4724,16 +4598,16 @@
         <v>11</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H60" s="35">
         <v>0</v>
       </c>
       <c r="I60" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J60" s="37">
         <v>0</v>
@@ -4748,7 +4622,7 @@
         <v>40</v>
       </c>
       <c r="N60" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O60" s="33"/>
       <c r="P60" s="33"/>
@@ -4765,7 +4639,7 @@
         <v>102100</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D61" s="31">
         <v>102100001</v>
@@ -4774,16 +4648,16 @@
         <v>12</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G61" s="34" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H61" s="40">
         <v>0</v>
       </c>
       <c r="I61" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J61" s="37">
         <v>0</v>
@@ -4798,7 +4672,7 @@
         <v>43</v>
       </c>
       <c r="N61" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O61" s="33"/>
       <c r="P61" s="33"/>
@@ -4815,7 +4689,7 @@
         <v>102200</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D62" s="31">
         <v>102200001</v>
@@ -4824,16 +4698,16 @@
         <v>10</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H62" s="35">
         <v>0</v>
       </c>
       <c r="I62" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J62" s="37">
         <v>0</v>
@@ -4848,7 +4722,7 @@
         <v>37</v>
       </c>
       <c r="N62" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O62" s="33"/>
       <c r="P62" s="33"/>
@@ -4865,7 +4739,7 @@
         <v>102200</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D63" s="31">
         <v>102200001</v>
@@ -4874,16 +4748,16 @@
         <v>11</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H63" s="35">
         <v>0</v>
       </c>
       <c r="I63" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J63" s="37">
         <v>0</v>
@@ -4898,7 +4772,7 @@
         <v>40</v>
       </c>
       <c r="N63" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O63" s="33"/>
       <c r="P63" s="33"/>
@@ -4915,7 +4789,7 @@
         <v>102200</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D64" s="31">
         <v>102200001</v>
@@ -4924,16 +4798,16 @@
         <v>12</v>
       </c>
       <c r="F64" s="33" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H64" s="40">
         <v>0</v>
       </c>
       <c r="I64" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J64" s="37">
         <v>0</v>
@@ -4948,7 +4822,7 @@
         <v>43</v>
       </c>
       <c r="N64" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O64" s="33"/>
       <c r="P64" s="33"/>
@@ -4965,7 +4839,7 @@
         <v>102400</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D65" s="31">
         <v>102400026</v>
@@ -4974,16 +4848,16 @@
         <v>10</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="H65" s="35">
         <v>0</v>
       </c>
       <c r="I65" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J65" s="37">
         <v>0</v>
@@ -4998,7 +4872,7 @@
         <v>37</v>
       </c>
       <c r="N65" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O65" s="33"/>
       <c r="P65" s="33"/>
@@ -5015,7 +4889,7 @@
         <v>102400</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D66" s="31">
         <v>102400026</v>
@@ -5024,16 +4898,16 @@
         <v>11</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="H66" s="35">
         <v>0</v>
       </c>
       <c r="I66" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J66" s="37">
         <v>0</v>
@@ -5048,7 +4922,7 @@
         <v>40</v>
       </c>
       <c r="N66" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O66" s="33"/>
       <c r="P66" s="33"/>
@@ -5065,7 +4939,7 @@
         <v>102400</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D67" s="31">
         <v>102400026</v>
@@ -5074,16 +4948,16 @@
         <v>12</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G67" s="34" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="H67" s="40">
         <v>0</v>
       </c>
       <c r="I67" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J67" s="37">
         <v>0</v>
@@ -5098,7 +4972,7 @@
         <v>43</v>
       </c>
       <c r="N67" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O67" s="33"/>
       <c r="P67" s="33"/>
@@ -5115,7 +4989,7 @@
         <v>101800</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D68" s="31">
         <v>101800001</v>
@@ -5123,17 +4997,17 @@
       <c r="E68" s="32">
         <v>10</v>
       </c>
-      <c r="F68" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="G68" s="34" t="s">
-        <v>108</v>
+      <c r="F68" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="H68" s="40">
         <v>0</v>
       </c>
       <c r="I68" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J68" s="37">
         <v>0</v>
@@ -5148,7 +5022,7 @@
         <v>37</v>
       </c>
       <c r="N68" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O68" s="33"/>
       <c r="P68" s="33"/>
@@ -5165,7 +5039,7 @@
         <v>101800</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D69" s="31">
         <v>101800001</v>
@@ -5173,17 +5047,17 @@
       <c r="E69" s="32">
         <v>11</v>
       </c>
-      <c r="F69" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="G69" s="34" t="s">
-        <v>110</v>
+      <c r="F69" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="H69" s="40">
         <v>0</v>
       </c>
       <c r="I69" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J69" s="37">
         <v>0</v>
@@ -5198,7 +5072,7 @@
         <v>40</v>
       </c>
       <c r="N69" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O69" s="33"/>
       <c r="P69" s="33"/>
@@ -5215,7 +5089,7 @@
         <v>101800</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D70" s="31">
         <v>101800001</v>
@@ -5223,17 +5097,17 @@
       <c r="E70" s="32">
         <v>12</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="G70" s="34" t="s">
-        <v>112</v>
+      <c r="F70" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="H70" s="40">
         <v>0</v>
       </c>
       <c r="I70" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J70" s="37">
         <v>0</v>
@@ -5248,7 +5122,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O70" s="33"/>
       <c r="P70" s="33"/>
@@ -5259,14 +5133,14 @@
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="28">
-        <f>(B71*100)+E71</f>
+        <f t="shared" ref="A71:A76" si="0">(B71*100)+E71</f>
         <v>10250010</v>
       </c>
       <c r="B71" s="29">
         <v>102500</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D71" s="31">
         <v>102500001</v>
@@ -5274,17 +5148,17 @@
       <c r="E71" s="32">
         <v>10</v>
       </c>
-      <c r="F71" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G71" s="34" t="s">
-        <v>88</v>
+      <c r="F71" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>65</v>
       </c>
       <c r="H71" s="40">
         <v>0</v>
       </c>
       <c r="I71" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J71" s="37">
         <v>0</v>
@@ -5299,7 +5173,7 @@
         <v>37</v>
       </c>
       <c r="N71" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O71" s="33"/>
       <c r="P71" s="33"/>
@@ -5310,14 +5184,14 @@
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="28">
-        <f>(B72*100)+E72</f>
+        <f t="shared" si="0"/>
         <v>10250011</v>
       </c>
       <c r="B72" s="29">
         <v>102500</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D72" s="31">
         <v>102500001</v>
@@ -5325,17 +5199,17 @@
       <c r="E72" s="32">
         <v>11</v>
       </c>
-      <c r="F72" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="G72" s="34" t="s">
-        <v>91</v>
+      <c r="F72" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G72" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="H72" s="40">
         <v>0</v>
       </c>
       <c r="I72" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J72" s="37">
         <v>0</v>
@@ -5350,7 +5224,7 @@
         <v>40</v>
       </c>
       <c r="N72" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O72" s="33"/>
       <c r="P72" s="33"/>
@@ -5361,14 +5235,14 @@
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="28">
-        <f>(B73*100)+E73</f>
+        <f t="shared" si="0"/>
         <v>10250012</v>
       </c>
       <c r="B73" s="29">
         <v>102500</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D73" s="31">
         <v>102500001</v>
@@ -5376,17 +5250,17 @@
       <c r="E73" s="32">
         <v>12</v>
       </c>
-      <c r="F73" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G73" s="34" t="s">
-        <v>94</v>
+      <c r="F73" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="H73" s="40">
         <v>0</v>
       </c>
       <c r="I73" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J73" s="37">
         <v>0</v>
@@ -5401,7 +5275,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O73" s="33"/>
       <c r="P73" s="33"/>
@@ -5412,14 +5286,14 @@
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="28">
-        <f>(B74*100)+E74</f>
+        <f t="shared" si="0"/>
         <v>10230010</v>
       </c>
       <c r="B74" s="29">
         <v>102300</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D74" s="31">
         <v>102300001</v>
@@ -5427,17 +5301,17 @@
       <c r="E74" s="32">
         <v>10</v>
       </c>
-      <c r="F74" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="G74" s="34" t="s">
-        <v>108</v>
+      <c r="F74" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="H74" s="40">
         <v>0</v>
       </c>
       <c r="I74" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J74" s="37">
         <v>0</v>
@@ -5452,7 +5326,7 @@
         <v>37</v>
       </c>
       <c r="N74" s="39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O74" s="33"/>
       <c r="P74" s="33"/>
@@ -5463,14 +5337,14 @@
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="28">
-        <f>(B75*100)+E75</f>
+        <f t="shared" si="0"/>
         <v>10230011</v>
       </c>
       <c r="B75" s="29">
         <v>102300</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D75" s="31">
         <v>102300001</v>
@@ -5478,17 +5352,17 @@
       <c r="E75" s="32">
         <v>11</v>
       </c>
-      <c r="F75" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="G75" s="34" t="s">
-        <v>110</v>
+      <c r="F75" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="H75" s="40">
         <v>0</v>
       </c>
       <c r="I75" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J75" s="37">
         <v>0</v>
@@ -5503,7 +5377,7 @@
         <v>40</v>
       </c>
       <c r="N75" s="39" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="O75" s="33"/>
       <c r="P75" s="33"/>
@@ -5514,14 +5388,14 @@
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="28">
-        <f>(B76*100)+E76</f>
+        <f t="shared" si="0"/>
         <v>10230012</v>
       </c>
       <c r="B76" s="29">
         <v>102300</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D76" s="31">
         <v>102300001</v>
@@ -5529,17 +5403,17 @@
       <c r="E76" s="32">
         <v>12</v>
       </c>
-      <c r="F76" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="G76" s="34" t="s">
-        <v>112</v>
+      <c r="F76" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="H76" s="40">
         <v>0</v>
       </c>
       <c r="I76" s="36">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J76" s="37">
         <v>0</v>
@@ -5554,7 +5428,7 @@
         <v>43</v>
       </c>
       <c r="N76" s="39" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O76" s="33"/>
       <c r="P76" s="33"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -290,28 +290,133 @@
     <t>金矿大亨</t>
   </si>
   <si>
-    <t>1_2_5_10_20_50</t>
+    <t>10_20_50_100_200_500_1000</t>
+  </si>
+  <si>
+    <t>50:1</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>100_200_500_1000_2000_5000_10000</t>
+  </si>
+  <si>
+    <t>500:1</t>
+  </si>
+  <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
+  </si>
+  <si>
+    <t>5000:1</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+  </si>
+  <si>
+    <t>50000:1</t>
+  </si>
+  <si>
+    <t>100000_200000_500000_1000000_2000000_500000_100000000</t>
+  </si>
+  <si>
+    <t>500000:1</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>50_100_250_500_1000_2500_5000</t>
+  </si>
+  <si>
+    <t>250:1</t>
+  </si>
+  <si>
+    <t>500_1000_2500_5000_10000_25000_50000</t>
+  </si>
+  <si>
+    <t>2500:1</t>
+  </si>
+  <si>
+    <t>5000_10000_25000_50000_100000_250000_500000</t>
+  </si>
+  <si>
+    <t>25000:1</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>财富银行</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>20_40_100_200_400_1000_2000</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>200_400_1000_2000_4000_10000_20000</t>
+  </si>
+  <si>
+    <t>1000:1</t>
+  </si>
+  <si>
+    <t>2000_4000_10000_20000_40000_100000_200000</t>
+  </si>
+  <si>
+    <t>10000:1</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>2_4_10_20_40</t>
   </si>
   <si>
     <t>10:1</t>
   </si>
   <si>
-    <t>0,5000,10000</t>
-  </si>
-  <si>
     <t>500000_17001</t>
   </si>
   <si>
-    <t>100_200_500_1000_2000_5000</t>
-  </si>
-  <si>
-    <t>1000:1</t>
-  </si>
-  <si>
-    <t>50000000_17001</t>
-  </si>
-  <si>
-    <t>10000_20000_50000_100000_200000_500000</t>
+    <t>200_400_1000_2000_4000</t>
+  </si>
+  <si>
+    <t>20000_40000_100000_200000_400000</t>
   </si>
   <si>
     <t>100000:1</t>
@@ -320,229 +425,37 @@
     <t>5000000000_17001</t>
   </si>
   <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>1000000_2000000_5000000_10000000_20000000_50000000</t>
-  </si>
-  <si>
-    <t>10000000:1</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>5_10_25_50_100_250</t>
-  </si>
-  <si>
-    <t>50:1</t>
-  </si>
-  <si>
-    <t>500_1000_2500_5000_10000_25000</t>
-  </si>
-  <si>
-    <t>5000:1</t>
-  </si>
-  <si>
-    <t>50000_100000_250000_500000_1000000_2500000</t>
-  </si>
-  <si>
-    <t>500000:1</t>
-  </si>
-  <si>
-    <t>财神</t>
-  </si>
-  <si>
-    <t>6_12_32_66_132_332</t>
-  </si>
-  <si>
-    <t>66:1</t>
-  </si>
-  <si>
-    <t>600_1200_3200_6600_13200_33200</t>
-  </si>
-  <si>
-    <t>6600:1</t>
-  </si>
-  <si>
-    <t>60000_120000_320000_660000_1320000_3320000</t>
-  </si>
-  <si>
-    <t>660000:1</t>
-  </si>
-  <si>
-    <t>埃及艳后</t>
-  </si>
-  <si>
-    <t>10_20_50_100_200_500</t>
-  </si>
-  <si>
-    <t>100:1</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000_50000</t>
-  </si>
-  <si>
-    <t>10000:1</t>
-  </si>
-  <si>
-    <t>100000_200000_500000_1000000_2000000_5000000</t>
-  </si>
-  <si>
-    <t>1000000:1</t>
-  </si>
-  <si>
-    <t>圣诞狂欢夜</t>
-  </si>
-  <si>
-    <t>杰克船长</t>
-  </si>
-  <si>
-    <t>雷神</t>
-  </si>
-  <si>
-    <t>财富银行</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>2_4_8_20_40</t>
-  </si>
-  <si>
-    <t>8:1</t>
-  </si>
-  <si>
-    <t>200_400_800_2000_4000</t>
-  </si>
-  <si>
-    <t>800:1</t>
-  </si>
-  <si>
-    <t>20000_40000_80000_200000_400000</t>
-  </si>
-  <si>
-    <t>80000:1</t>
-  </si>
-  <si>
-    <t>寒冰王座</t>
-  </si>
-  <si>
-    <t>5:1</t>
-  </si>
-  <si>
-    <t>500:1</t>
-  </si>
-  <si>
-    <t>50000:1</t>
-  </si>
-  <si>
-    <t>蒸汽时代</t>
-  </si>
-  <si>
-    <t>2_4_10_20_40</t>
-  </si>
-  <si>
-    <t>200_400_1000_2000_4000</t>
-  </si>
-  <si>
-    <t>20000_40000_100000_200000_400000</t>
-  </si>
-  <si>
-    <t>神马飞扬</t>
-  </si>
-  <si>
     <t>金蛇招财</t>
   </si>
   <si>
     <t>金钱兔</t>
   </si>
   <si>
-    <t>1_2_5</t>
-  </si>
-  <si>
-    <t>2:1</t>
-  </si>
-  <si>
-    <t>1980000_10000</t>
-  </si>
-  <si>
-    <t>10_20_50</t>
-  </si>
-  <si>
-    <t>20:1</t>
-  </si>
-  <si>
-    <t>1980000_100000</t>
-  </si>
-  <si>
-    <t>100_200_500</t>
-  </si>
-  <si>
-    <t>200:1</t>
-  </si>
-  <si>
-    <t>1980000_1000000</t>
-  </si>
-  <si>
-    <t>1000_2000_5000</t>
-  </si>
-  <si>
-    <t>2000:1</t>
-  </si>
-  <si>
-    <t>5_10_25</t>
-  </si>
-  <si>
-    <t>50_100_250</t>
-  </si>
-  <si>
-    <t>500_1000_2500</t>
-  </si>
-  <si>
-    <t>6_12_32</t>
-  </si>
-  <si>
-    <t>12:1</t>
-  </si>
-  <si>
-    <t>60_120_320</t>
-  </si>
-  <si>
-    <t>120:1</t>
-  </si>
-  <si>
-    <t>600_1200_3200</t>
-  </si>
-  <si>
-    <t>1200:1</t>
-  </si>
-  <si>
-    <t>2_4_8</t>
+    <t>1980000_500000</t>
+  </si>
+  <si>
+    <t>1980000_5000000</t>
+  </si>
+  <si>
+    <t>1980000_50000000</t>
+  </si>
+  <si>
+    <t>2_4_10</t>
   </si>
   <si>
     <t>4:1</t>
   </si>
   <si>
-    <t>20_40_80</t>
+    <t>20_40_100</t>
   </si>
   <si>
     <t>40:1</t>
   </si>
   <si>
-    <t>200_400_800</t>
+    <t>200_400_1000</t>
   </si>
   <si>
     <t>400:1</t>
-  </si>
-  <si>
-    <t>2_4_10</t>
-  </si>
-  <si>
-    <t>20_40_100</t>
-  </si>
-  <si>
-    <t>200_400_1000</t>
   </si>
 </sst>
 </file>
@@ -757,14 +670,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -778,12 +691,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
@@ -791,6 +698,12 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2017,13 +1930,13 @@
         <v>35</v>
       </c>
       <c r="H5" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I5" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J5" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K5" s="26" t="s">
         <v>36</v>
@@ -2070,7 +1983,7 @@
         <v>5000000000</v>
       </c>
       <c r="I6" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J6" s="23">
         <v>50000000</v>
@@ -2117,13 +2030,13 @@
         <v>42</v>
       </c>
       <c r="H7" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I7" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J7" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>36</v>
@@ -2161,19 +2074,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H8" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I8" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J8" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K8" s="26" t="s">
         <v>36</v>
@@ -2211,16 +2124,16 @@
         <v>2</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H9" s="14">
         <v>5000000000</v>
       </c>
       <c r="I9" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J9" s="23">
         <v>50000000</v>
@@ -2261,19 +2174,19 @@
         <v>3</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H10" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I10" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J10" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K10" s="26" t="s">
         <v>36</v>
@@ -2302,7 +2215,7 @@
         <v>100700</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" s="24">
         <v>100100026</v>
@@ -2311,19 +2224,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I11" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J11" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K11" s="26" t="s">
         <v>36</v>
@@ -2352,7 +2265,7 @@
         <v>100700</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="24">
         <v>100100026</v>
@@ -2361,16 +2274,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H12" s="14">
         <v>5000000000</v>
       </c>
       <c r="I12" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J12" s="23">
         <v>50000000</v>
@@ -2402,7 +2315,7 @@
         <v>100700</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="24">
         <v>100100026</v>
@@ -2411,19 +2324,19 @@
         <v>3</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I13" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J13" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K13" s="26" t="s">
         <v>36</v>
@@ -2452,7 +2365,7 @@
         <v>101200</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="24">
         <v>100100026</v>
@@ -2461,19 +2374,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H14" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I14" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J14" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K14" s="26" t="s">
         <v>36</v>
@@ -2502,7 +2415,7 @@
         <v>101200</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="24">
         <v>100100026</v>
@@ -2511,16 +2424,16 @@
         <v>2</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H15" s="14">
         <v>5000000000</v>
       </c>
       <c r="I15" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J15" s="23">
         <v>50000000</v>
@@ -2552,7 +2465,7 @@
         <v>101200</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="24">
         <v>100100026</v>
@@ -2561,19 +2474,19 @@
         <v>3</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H16" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I16" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J16" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K16" s="26" t="s">
         <v>36</v>
@@ -2602,7 +2515,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="24">
         <v>100100026</v>
@@ -2611,19 +2524,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H17" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I17" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J17" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>36</v>
@@ -2652,7 +2565,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18" s="24">
         <v>100100026</v>
@@ -2661,16 +2574,16 @@
         <v>2</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H18" s="14">
         <v>5000000000</v>
       </c>
       <c r="I18" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J18" s="23">
         <v>50000000</v>
@@ -2702,7 +2615,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D19" s="24">
         <v>100100026</v>
@@ -2711,19 +2624,19 @@
         <v>3</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H19" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I19" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J19" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K19" s="26" t="s">
         <v>36</v>
@@ -2752,7 +2665,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D20" s="24">
         <v>101700001</v>
@@ -2761,19 +2674,19 @@
         <v>1</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H20" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I20" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J20" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K20" s="26" t="s">
         <v>36</v>
@@ -2802,7 +2715,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D21" s="24">
         <v>101700001</v>
@@ -2811,16 +2724,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H21" s="14">
         <v>5000000000</v>
       </c>
       <c r="I21" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J21" s="23">
         <v>50000000</v>
@@ -2852,7 +2765,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D22" s="24">
         <v>101700001</v>
@@ -2861,19 +2774,19 @@
         <v>3</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H22" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I22" s="23">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J22" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K22" s="26" t="s">
         <v>36</v>
@@ -2902,7 +2815,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D23" s="24">
         <v>102100001</v>
@@ -2911,19 +2824,19 @@
         <v>1</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H23" s="28">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I23" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J23" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K23" s="26" t="s">
         <v>36</v>
@@ -2952,7 +2865,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D24" s="24">
         <v>102100001</v>
@@ -2961,16 +2874,16 @@
         <v>2</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H24" s="28">
         <v>5000000000</v>
       </c>
       <c r="I24" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J24" s="23">
         <v>50000000</v>
@@ -3002,7 +2915,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D25" s="24">
         <v>102100001</v>
@@ -3011,19 +2924,19 @@
         <v>3</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H25" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I25" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J25" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K25" s="26" t="s">
         <v>36</v>
@@ -3052,7 +2965,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D26" s="24">
         <v>102200001</v>
@@ -3061,19 +2974,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H26" s="28">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I26" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J26" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K26" s="26" t="s">
         <v>36</v>
@@ -3102,7 +3015,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D27" s="24">
         <v>102200001</v>
@@ -3111,16 +3024,16 @@
         <v>2</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H27" s="28">
         <v>5000000000</v>
       </c>
       <c r="I27" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J27" s="23">
         <v>50000000</v>
@@ -3152,7 +3065,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D28" s="24">
         <v>102200001</v>
@@ -3161,19 +3074,19 @@
         <v>3</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H28" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I28" s="23">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J28" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K28" s="26" t="s">
         <v>36</v>
@@ -3202,7 +3115,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D29" s="24">
         <v>102400026</v>
@@ -3217,13 +3130,13 @@
         <v>35</v>
       </c>
       <c r="H29" s="14">
-        <v>50000000</v>
+        <v>500000000</v>
       </c>
       <c r="I29" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J29" s="23">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K29" s="26" t="s">
         <v>36</v>
@@ -3252,7 +3165,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D30" s="24">
         <v>102400026</v>
@@ -3270,7 +3183,7 @@
         <v>5000000000</v>
       </c>
       <c r="I30" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J30" s="23">
         <v>50000000</v>
@@ -3302,7 +3215,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D31" s="24">
         <v>102400026</v>
@@ -3317,13 +3230,13 @@
         <v>42</v>
       </c>
       <c r="H31" s="28">
-        <v>500000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="I31" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J31" s="23">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K31" s="26" t="s">
         <v>36</v>
@@ -3352,7 +3265,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D32" s="24">
         <v>101800001</v>
@@ -3361,16 +3274,16 @@
         <v>1</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H32" s="14">
         <v>50000000</v>
       </c>
       <c r="I32" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J32" s="23">
         <v>500000</v>
@@ -3402,7 +3315,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D33" s="24">
         <v>101800001</v>
@@ -3411,16 +3324,16 @@
         <v>2</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H33" s="14">
         <v>5000000000</v>
       </c>
       <c r="I33" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J33" s="23">
         <v>50000000</v>
@@ -3452,7 +3365,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D34" s="24">
         <v>101800001</v>
@@ -3461,16 +3374,16 @@
         <v>3</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H34" s="28">
         <v>500000000000</v>
       </c>
       <c r="I34" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J34" s="23">
         <v>5000000000</v>
@@ -3502,7 +3415,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D35" s="24">
         <v>102500001</v>
@@ -3511,16 +3424,16 @@
         <v>1</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H35" s="14">
         <v>50000000</v>
       </c>
       <c r="I35" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J35" s="23">
         <v>500000</v>
@@ -3552,7 +3465,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D36" s="24">
         <v>102500001</v>
@@ -3561,16 +3474,16 @@
         <v>2</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H36" s="14">
         <v>5000000000</v>
       </c>
       <c r="I36" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J36" s="23">
         <v>50000000</v>
@@ -3602,7 +3515,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D37" s="24">
         <v>102500001</v>
@@ -3611,16 +3524,16 @@
         <v>3</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H37" s="28">
         <v>500000000000</v>
       </c>
       <c r="I37" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J37" s="23">
         <v>5000000000</v>
@@ -3652,7 +3565,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D38" s="24">
         <v>102300001</v>
@@ -3661,16 +3574,16 @@
         <v>1</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H38" s="28">
         <v>50000000</v>
       </c>
       <c r="I38" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J38" s="23">
         <v>500000</v>
@@ -3702,7 +3615,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D39" s="24">
         <v>102300001</v>
@@ -3711,16 +3624,16 @@
         <v>2</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H39" s="28">
         <v>5000000000</v>
       </c>
       <c r="I39" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J39" s="23">
         <v>50000000</v>
@@ -3752,7 +3665,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D40" s="24">
         <v>102300001</v>
@@ -3761,16 +3674,16 @@
         <v>3</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H40" s="28">
         <v>500000000000</v>
       </c>
       <c r="I40" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J40" s="23">
         <v>5000000000</v>
@@ -3802,7 +3715,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D41" s="24">
         <v>103400001</v>
@@ -3811,10 +3724,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="H41" s="28">
         <v>50000000</v>
@@ -3832,7 +3745,7 @@
         <v>100</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="N41" s="21">
         <v>0</v>
@@ -3852,7 +3765,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D42" s="24">
         <v>103400001</v>
@@ -3861,10 +3774,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H42" s="28">
         <v>5000000000</v>
@@ -3902,7 +3815,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D43" s="24">
         <v>103400001</v>
@@ -3911,10 +3824,10 @@
         <v>3</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H43" s="28">
         <v>500000000000</v>
@@ -3932,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="N43" s="21">
         <v>0</v>
@@ -3952,7 +3865,7 @@
         <v>103500</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D44" s="32">
         <v>103500001</v>
@@ -3961,10 +3874,10 @@
         <v>1</v>
       </c>
       <c r="F44" s="33" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="H44" s="35">
         <v>50000000</v>
@@ -3981,8 +3894,8 @@
       <c r="L44" s="37">
         <v>100</v>
       </c>
-      <c r="M44" s="36" t="s">
-        <v>37</v>
+      <c r="M44" s="23" t="s">
+        <v>74</v>
       </c>
       <c r="N44" s="33">
         <v>0</v>
@@ -4002,7 +3915,7 @@
         <v>103500</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D45" s="32">
         <v>103500001</v>
@@ -4011,10 +3924,10 @@
         <v>2</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H45" s="35">
         <v>5000000000</v>
@@ -4031,7 +3944,7 @@
       <c r="L45" s="37">
         <v>100</v>
       </c>
-      <c r="M45" s="36" t="s">
+      <c r="M45" s="23" t="s">
         <v>40</v>
       </c>
       <c r="N45" s="33">
@@ -4052,7 +3965,7 @@
         <v>103500</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D46" s="32">
         <v>103500001</v>
@@ -4061,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H46" s="35">
         <v>500000000000</v>
@@ -4081,8 +3994,8 @@
       <c r="L46" s="37">
         <v>100</v>
       </c>
-      <c r="M46" s="36" t="s">
-        <v>43</v>
+      <c r="M46" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="N46" s="33">
         <v>0</v>
@@ -4102,7 +4015,7 @@
         <v>103501</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D47" s="32">
         <v>103501001</v>
@@ -4111,10 +4024,10 @@
         <v>1</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="H47" s="35">
         <v>50000000</v>
@@ -4131,8 +4044,8 @@
       <c r="L47" s="37">
         <v>100</v>
       </c>
-      <c r="M47" s="36" t="s">
-        <v>37</v>
+      <c r="M47" s="23" t="s">
+        <v>74</v>
       </c>
       <c r="N47" s="33">
         <v>0</v>
@@ -4152,7 +4065,7 @@
         <v>103501</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D48" s="32">
         <v>103501001</v>
@@ -4161,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H48" s="35">
         <v>5000000000</v>
@@ -4181,7 +4094,7 @@
       <c r="L48" s="37">
         <v>100</v>
       </c>
-      <c r="M48" s="36" t="s">
+      <c r="M48" s="23" t="s">
         <v>40</v>
       </c>
       <c r="N48" s="33">
@@ -4202,7 +4115,7 @@
         <v>103501</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D49" s="32">
         <v>103501001</v>
@@ -4211,10 +4124,10 @@
         <v>3</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H49" s="35">
         <v>500000000000</v>
@@ -4231,8 +4144,8 @@
       <c r="L49" s="37">
         <v>100</v>
       </c>
-      <c r="M49" s="36" t="s">
-        <v>43</v>
+      <c r="M49" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="N49" s="33">
         <v>0</v>
@@ -4261,16 +4174,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="43" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="H50" s="45">
         <v>0</v>
       </c>
       <c r="I50" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J50" s="47">
         <v>0</v>
@@ -4285,7 +4198,7 @@
         <v>37</v>
       </c>
       <c r="N50" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O50" s="43"/>
       <c r="P50" s="43"/>
@@ -4311,16 +4224,16 @@
         <v>11</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="H51" s="45">
         <v>0</v>
       </c>
       <c r="I51" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J51" s="47">
         <v>0</v>
@@ -4335,7 +4248,7 @@
         <v>40</v>
       </c>
       <c r="N51" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O51" s="43"/>
       <c r="P51" s="43"/>
@@ -4361,16 +4274,16 @@
         <v>12</v>
       </c>
       <c r="F52" s="43" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H52" s="50">
         <v>0</v>
       </c>
       <c r="I52" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J52" s="47">
         <v>0</v>
@@ -4385,7 +4298,7 @@
         <v>43</v>
       </c>
       <c r="N52" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O52" s="43"/>
       <c r="P52" s="43"/>
@@ -4411,16 +4324,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="43" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="H53" s="45">
         <v>0</v>
       </c>
       <c r="I53" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J53" s="47">
         <v>0</v>
@@ -4435,7 +4348,7 @@
         <v>37</v>
       </c>
       <c r="N53" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O53" s="43"/>
       <c r="P53" s="43"/>
@@ -4461,16 +4374,16 @@
         <v>11</v>
       </c>
       <c r="F54" s="43" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="G54" s="44" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="H54" s="45">
         <v>0</v>
       </c>
       <c r="I54" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J54" s="47">
         <v>0</v>
@@ -4485,7 +4398,7 @@
         <v>40</v>
       </c>
       <c r="N54" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O54" s="43"/>
       <c r="P54" s="43"/>
@@ -4511,16 +4424,16 @@
         <v>12</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="H55" s="50">
         <v>0</v>
       </c>
       <c r="I55" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J55" s="47">
         <v>0</v>
@@ -4535,7 +4448,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O55" s="43"/>
       <c r="P55" s="43"/>
@@ -4552,7 +4465,7 @@
         <v>100700</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D56" s="41">
         <v>100100026</v>
@@ -4561,16 +4474,16 @@
         <v>10</v>
       </c>
       <c r="F56" s="43" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H56" s="45">
         <v>0</v>
       </c>
       <c r="I56" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J56" s="47">
         <v>0</v>
@@ -4585,7 +4498,7 @@
         <v>37</v>
       </c>
       <c r="N56" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O56" s="43"/>
       <c r="P56" s="43"/>
@@ -4602,7 +4515,7 @@
         <v>100700</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D57" s="41">
         <v>100100026</v>
@@ -4611,16 +4524,16 @@
         <v>11</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H57" s="45">
         <v>0</v>
       </c>
       <c r="I57" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J57" s="47">
         <v>0</v>
@@ -4635,7 +4548,7 @@
         <v>40</v>
       </c>
       <c r="N57" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O57" s="43"/>
       <c r="P57" s="43"/>
@@ -4652,7 +4565,7 @@
         <v>100700</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D58" s="41">
         <v>100100026</v>
@@ -4661,16 +4574,16 @@
         <v>12</v>
       </c>
       <c r="F58" s="43" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H58" s="50">
         <v>0</v>
       </c>
       <c r="I58" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J58" s="47">
         <v>0</v>
@@ -4685,7 +4598,7 @@
         <v>43</v>
       </c>
       <c r="N58" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O58" s="43"/>
       <c r="P58" s="43"/>
@@ -4702,7 +4615,7 @@
         <v>101200</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D59" s="53">
         <v>101200026</v>
@@ -4711,10 +4624,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="49" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="G59" s="54" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="H59" s="45">
         <v>0</v>
@@ -4735,7 +4648,7 @@
         <v>37</v>
       </c>
       <c r="N59" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O59" s="49"/>
       <c r="P59" s="49"/>
@@ -4752,7 +4665,7 @@
         <v>101200</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D60" s="53">
         <v>101200026</v>
@@ -4761,10 +4674,10 @@
         <v>11</v>
       </c>
       <c r="F60" s="49" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="G60" s="54" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="H60" s="45">
         <v>0</v>
@@ -4785,7 +4698,7 @@
         <v>40</v>
       </c>
       <c r="N60" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O60" s="49"/>
       <c r="P60" s="49"/>
@@ -4802,7 +4715,7 @@
         <v>101200</v>
       </c>
       <c r="C61" s="42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D61" s="53">
         <v>101200026</v>
@@ -4811,10 +4724,10 @@
         <v>12</v>
       </c>
       <c r="F61" s="49" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="G61" s="54" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H61" s="50">
         <v>0</v>
@@ -4835,7 +4748,7 @@
         <v>43</v>
       </c>
       <c r="N61" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O61" s="49"/>
       <c r="P61" s="49"/>
@@ -4852,7 +4765,7 @@
         <v>101400</v>
       </c>
       <c r="C62" s="40" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D62" s="41">
         <v>100100026</v>
@@ -4861,16 +4774,16 @@
         <v>10</v>
       </c>
       <c r="F62" s="43" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G62" s="44" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="H62" s="45">
         <v>0</v>
       </c>
       <c r="I62" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J62" s="47">
         <v>0</v>
@@ -4885,7 +4798,7 @@
         <v>37</v>
       </c>
       <c r="N62" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O62" s="43"/>
       <c r="P62" s="43"/>
@@ -4902,7 +4815,7 @@
         <v>101400</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D63" s="41">
         <v>100100026</v>
@@ -4911,16 +4824,16 @@
         <v>11</v>
       </c>
       <c r="F63" s="43" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="G63" s="44" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H63" s="45">
         <v>0</v>
       </c>
       <c r="I63" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J63" s="47">
         <v>0</v>
@@ -4935,7 +4848,7 @@
         <v>40</v>
       </c>
       <c r="N63" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O63" s="43"/>
       <c r="P63" s="43"/>
@@ -4952,7 +4865,7 @@
         <v>101400</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D64" s="41">
         <v>100100026</v>
@@ -4961,16 +4874,16 @@
         <v>12</v>
       </c>
       <c r="F64" s="43" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="G64" s="44" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="H64" s="50">
         <v>0</v>
       </c>
       <c r="I64" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J64" s="47">
         <v>0</v>
@@ -4985,7 +4898,7 @@
         <v>43</v>
       </c>
       <c r="N64" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O64" s="43"/>
       <c r="P64" s="43"/>
@@ -5002,7 +4915,7 @@
         <v>101700</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D65" s="41">
         <v>101700001</v>
@@ -5011,16 +4924,16 @@
         <v>10</v>
       </c>
       <c r="F65" s="43" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="G65" s="44" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H65" s="45">
         <v>0</v>
       </c>
       <c r="I65" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J65" s="47">
         <v>0</v>
@@ -5035,7 +4948,7 @@
         <v>37</v>
       </c>
       <c r="N65" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O65" s="43"/>
       <c r="P65" s="43"/>
@@ -5052,7 +4965,7 @@
         <v>101700</v>
       </c>
       <c r="C66" s="40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D66" s="41">
         <v>101700001</v>
@@ -5061,16 +4974,16 @@
         <v>11</v>
       </c>
       <c r="F66" s="43" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G66" s="44" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H66" s="45">
         <v>0</v>
       </c>
       <c r="I66" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J66" s="47">
         <v>0</v>
@@ -5085,7 +4998,7 @@
         <v>40</v>
       </c>
       <c r="N66" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O66" s="43"/>
       <c r="P66" s="43"/>
@@ -5102,7 +5015,7 @@
         <v>101700</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D67" s="41">
         <v>101700001</v>
@@ -5111,16 +5024,16 @@
         <v>12</v>
       </c>
       <c r="F67" s="43" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G67" s="44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H67" s="50">
         <v>0</v>
       </c>
       <c r="I67" s="46">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="J67" s="47">
         <v>0</v>
@@ -5135,7 +5048,7 @@
         <v>43</v>
       </c>
       <c r="N67" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O67" s="43"/>
       <c r="P67" s="43"/>
@@ -5152,7 +5065,7 @@
         <v>102100</v>
       </c>
       <c r="C68" s="40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D68" s="41">
         <v>102100001</v>
@@ -5161,16 +5074,16 @@
         <v>10</v>
       </c>
       <c r="F68" s="43" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="G68" s="44" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H68" s="45">
         <v>0</v>
       </c>
       <c r="I68" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J68" s="47">
         <v>0</v>
@@ -5185,7 +5098,7 @@
         <v>37</v>
       </c>
       <c r="N68" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O68" s="43"/>
       <c r="P68" s="43"/>
@@ -5202,7 +5115,7 @@
         <v>102100</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D69" s="41">
         <v>102100001</v>
@@ -5211,16 +5124,16 @@
         <v>11</v>
       </c>
       <c r="F69" s="43" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G69" s="44" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H69" s="45">
         <v>0</v>
       </c>
       <c r="I69" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J69" s="47">
         <v>0</v>
@@ -5235,7 +5148,7 @@
         <v>40</v>
       </c>
       <c r="N69" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O69" s="43"/>
       <c r="P69" s="43"/>
@@ -5252,7 +5165,7 @@
         <v>102100</v>
       </c>
       <c r="C70" s="40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D70" s="41">
         <v>102100001</v>
@@ -5261,16 +5174,16 @@
         <v>12</v>
       </c>
       <c r="F70" s="43" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G70" s="44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H70" s="50">
         <v>0</v>
       </c>
       <c r="I70" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J70" s="47">
         <v>0</v>
@@ -5285,7 +5198,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O70" s="43"/>
       <c r="P70" s="43"/>
@@ -5302,7 +5215,7 @@
         <v>102200</v>
       </c>
       <c r="C71" s="40" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D71" s="41">
         <v>102200001</v>
@@ -5311,16 +5224,16 @@
         <v>10</v>
       </c>
       <c r="F71" s="43" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="G71" s="44" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H71" s="45">
         <v>0</v>
       </c>
       <c r="I71" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J71" s="47">
         <v>0</v>
@@ -5335,7 +5248,7 @@
         <v>37</v>
       </c>
       <c r="N71" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O71" s="43"/>
       <c r="P71" s="43"/>
@@ -5352,7 +5265,7 @@
         <v>102200</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D72" s="41">
         <v>102200001</v>
@@ -5361,16 +5274,16 @@
         <v>11</v>
       </c>
       <c r="F72" s="43" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G72" s="44" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H72" s="45">
         <v>0</v>
       </c>
       <c r="I72" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J72" s="47">
         <v>0</v>
@@ -5385,7 +5298,7 @@
         <v>40</v>
       </c>
       <c r="N72" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O72" s="43"/>
       <c r="P72" s="43"/>
@@ -5402,7 +5315,7 @@
         <v>102200</v>
       </c>
       <c r="C73" s="40" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D73" s="41">
         <v>102200001</v>
@@ -5411,16 +5324,16 @@
         <v>12</v>
       </c>
       <c r="F73" s="43" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G73" s="44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H73" s="50">
         <v>0</v>
       </c>
       <c r="I73" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J73" s="47">
         <v>0</v>
@@ -5435,7 +5348,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O73" s="43"/>
       <c r="P73" s="43"/>
@@ -5452,7 +5365,7 @@
         <v>102400</v>
       </c>
       <c r="C74" s="40" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D74" s="41">
         <v>102400026</v>
@@ -5461,16 +5374,16 @@
         <v>10</v>
       </c>
       <c r="F74" s="43" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="G74" s="44" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="H74" s="45">
         <v>0</v>
       </c>
       <c r="I74" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J74" s="47">
         <v>0</v>
@@ -5485,7 +5398,7 @@
         <v>37</v>
       </c>
       <c r="N74" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O74" s="43"/>
       <c r="P74" s="43"/>
@@ -5502,7 +5415,7 @@
         <v>102400</v>
       </c>
       <c r="C75" s="40" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D75" s="41">
         <v>102400026</v>
@@ -5511,16 +5424,16 @@
         <v>11</v>
       </c>
       <c r="F75" s="43" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G75" s="44" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="H75" s="45">
         <v>0</v>
       </c>
       <c r="I75" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J75" s="47">
         <v>0</v>
@@ -5535,7 +5448,7 @@
         <v>40</v>
       </c>
       <c r="N75" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O75" s="43"/>
       <c r="P75" s="43"/>
@@ -5552,7 +5465,7 @@
         <v>102400</v>
       </c>
       <c r="C76" s="40" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D76" s="41">
         <v>102400026</v>
@@ -5561,16 +5474,16 @@
         <v>12</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="G76" s="44" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H76" s="50">
         <v>0</v>
       </c>
       <c r="I76" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J76" s="47">
         <v>0</v>
@@ -5585,7 +5498,7 @@
         <v>43</v>
       </c>
       <c r="N76" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O76" s="43"/>
       <c r="P76" s="43"/>
@@ -5602,7 +5515,7 @@
         <v>101800</v>
       </c>
       <c r="C77" s="40" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D77" s="41">
         <v>101800001</v>
@@ -5611,16 +5524,16 @@
         <v>10</v>
       </c>
       <c r="F77" s="43" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="G77" s="44" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="H77" s="50">
         <v>0</v>
       </c>
       <c r="I77" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J77" s="47">
         <v>0</v>
@@ -5635,7 +5548,7 @@
         <v>37</v>
       </c>
       <c r="N77" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O77" s="43"/>
       <c r="P77" s="43"/>
@@ -5652,7 +5565,7 @@
         <v>101800</v>
       </c>
       <c r="C78" s="40" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D78" s="41">
         <v>101800001</v>
@@ -5661,16 +5574,16 @@
         <v>11</v>
       </c>
       <c r="F78" s="43" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="G78" s="44" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="H78" s="50">
         <v>0</v>
       </c>
       <c r="I78" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J78" s="47">
         <v>0</v>
@@ -5685,7 +5598,7 @@
         <v>40</v>
       </c>
       <c r="N78" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O78" s="43"/>
       <c r="P78" s="43"/>
@@ -5702,7 +5615,7 @@
         <v>101800</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D79" s="41">
         <v>101800001</v>
@@ -5711,16 +5624,16 @@
         <v>12</v>
       </c>
       <c r="F79" s="43" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="G79" s="44" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="H79" s="50">
         <v>0</v>
       </c>
       <c r="I79" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J79" s="47">
         <v>0</v>
@@ -5735,7 +5648,7 @@
         <v>43</v>
       </c>
       <c r="N79" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O79" s="43"/>
       <c r="P79" s="43"/>
@@ -5746,14 +5659,13 @@
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="38">
-        <f t="shared" ref="A80:A85" si="0">(B80*100)+E80</f>
         <v>10250010</v>
       </c>
       <c r="B80" s="39">
         <v>102500</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D80" s="41">
         <v>102500001</v>
@@ -5762,16 +5674,16 @@
         <v>10</v>
       </c>
       <c r="F80" s="43" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="G80" s="44" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="H80" s="50">
         <v>0</v>
       </c>
       <c r="I80" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J80" s="47">
         <v>0</v>
@@ -5786,7 +5698,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O80" s="43"/>
       <c r="P80" s="43"/>
@@ -5797,14 +5709,13 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="38">
-        <f t="shared" si="0"/>
         <v>10250011</v>
       </c>
       <c r="B81" s="39">
         <v>102500</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D81" s="41">
         <v>102500001</v>
@@ -5813,16 +5724,16 @@
         <v>11</v>
       </c>
       <c r="F81" s="43" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="G81" s="44" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H81" s="50">
         <v>0</v>
       </c>
       <c r="I81" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J81" s="47">
         <v>0</v>
@@ -5837,7 +5748,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O81" s="43"/>
       <c r="P81" s="43"/>
@@ -5848,14 +5759,13 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="38">
-        <f t="shared" si="0"/>
         <v>10250012</v>
       </c>
       <c r="B82" s="39">
         <v>102500</v>
       </c>
       <c r="C82" s="40" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D82" s="41">
         <v>102500001</v>
@@ -5864,16 +5774,16 @@
         <v>12</v>
       </c>
       <c r="F82" s="43" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="G82" s="44" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="H82" s="50">
         <v>0</v>
       </c>
       <c r="I82" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J82" s="47">
         <v>0</v>
@@ -5888,7 +5798,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O82" s="43"/>
       <c r="P82" s="43"/>
@@ -5899,14 +5809,13 @@
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="38">
-        <f t="shared" si="0"/>
         <v>10230010</v>
       </c>
       <c r="B83" s="39">
         <v>102300</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D83" s="41">
         <v>102300001</v>
@@ -5915,16 +5824,16 @@
         <v>10</v>
       </c>
       <c r="F83" s="43" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="G83" s="44" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="H83" s="50">
         <v>0</v>
       </c>
       <c r="I83" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J83" s="47">
         <v>0</v>
@@ -5939,7 +5848,7 @@
         <v>37</v>
       </c>
       <c r="N83" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O83" s="43"/>
       <c r="P83" s="43"/>
@@ -5950,14 +5859,13 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="38">
-        <f t="shared" si="0"/>
         <v>10230011</v>
       </c>
       <c r="B84" s="39">
         <v>102300</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D84" s="41">
         <v>102300001</v>
@@ -5966,16 +5874,16 @@
         <v>11</v>
       </c>
       <c r="F84" s="43" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="G84" s="44" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="H84" s="50">
         <v>0</v>
       </c>
       <c r="I84" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J84" s="47">
         <v>0</v>
@@ -5990,7 +5898,7 @@
         <v>40</v>
       </c>
       <c r="N84" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O84" s="43"/>
       <c r="P84" s="43"/>
@@ -6001,14 +5909,13 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="38">
-        <f t="shared" si="0"/>
         <v>10230012</v>
       </c>
       <c r="B85" s="39">
         <v>102300</v>
       </c>
       <c r="C85" s="40" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D85" s="41">
         <v>102300001</v>
@@ -6017,16 +5924,16 @@
         <v>12</v>
       </c>
       <c r="F85" s="43" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="G85" s="44" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="H85" s="50">
         <v>0</v>
       </c>
       <c r="I85" s="46">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J85" s="47">
         <v>0</v>
@@ -6041,7 +5948,7 @@
         <v>43</v>
       </c>
       <c r="N85" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O85" s="43"/>
       <c r="P85" s="43"/>
@@ -6058,7 +5965,7 @@
         <v>103400</v>
       </c>
       <c r="C86" s="40" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D86" s="41">
         <v>103400001</v>
@@ -6067,10 +5974,10 @@
         <v>10</v>
       </c>
       <c r="F86" s="43" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="G86" s="44" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="H86" s="50">
         <v>0</v>
@@ -6091,7 +5998,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O86" s="43"/>
       <c r="P86" s="43"/>
@@ -6108,7 +6015,7 @@
         <v>103400</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D87" s="41">
         <v>103400001</v>
@@ -6117,10 +6024,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="43" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G87" s="44" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="H87" s="50">
         <v>0</v>
@@ -6141,7 +6048,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O87" s="43"/>
       <c r="P87" s="43"/>
@@ -6158,7 +6065,7 @@
         <v>103400</v>
       </c>
       <c r="C88" s="40" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D88" s="41">
         <v>103400001</v>
@@ -6167,10 +6074,10 @@
         <v>12</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="G88" s="44" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="H88" s="50">
         <v>0</v>
@@ -6191,7 +6098,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O88" s="43"/>
       <c r="P88" s="43"/>
@@ -6208,7 +6115,7 @@
         <v>103500</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D89" s="41">
         <v>103500001</v>
@@ -6217,10 +6124,10 @@
         <v>10</v>
       </c>
       <c r="F89" s="43" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="G89" s="44" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="H89" s="50">
         <v>0</v>
@@ -6241,7 +6148,7 @@
         <v>37</v>
       </c>
       <c r="N89" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O89" s="43"/>
       <c r="P89" s="43"/>
@@ -6258,7 +6165,7 @@
         <v>103500</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D90" s="41">
         <v>103500001</v>
@@ -6267,10 +6174,10 @@
         <v>11</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G90" s="44" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="H90" s="50">
         <v>0</v>
@@ -6291,7 +6198,7 @@
         <v>40</v>
       </c>
       <c r="N90" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O90" s="43"/>
       <c r="P90" s="43"/>
@@ -6308,7 +6215,7 @@
         <v>103500</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D91" s="41">
         <v>103500001</v>
@@ -6317,10 +6224,10 @@
         <v>12</v>
       </c>
       <c r="F91" s="43" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="G91" s="44" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="H91" s="50">
         <v>0</v>
@@ -6341,7 +6248,7 @@
         <v>43</v>
       </c>
       <c r="N91" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O91" s="43"/>
       <c r="P91" s="43"/>
@@ -6358,7 +6265,7 @@
         <v>103501</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D92" s="41">
         <v>103501001</v>
@@ -6367,10 +6274,10 @@
         <v>10</v>
       </c>
       <c r="F92" s="43" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="G92" s="44" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="H92" s="50">
         <v>0</v>
@@ -6391,7 +6298,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="49" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O92" s="43"/>
       <c r="P92" s="43"/>
@@ -6408,7 +6315,7 @@
         <v>103501</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D93" s="41">
         <v>103501001</v>
@@ -6417,10 +6324,10 @@
         <v>11</v>
       </c>
       <c r="F93" s="43" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G93" s="44" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="H93" s="50">
         <v>0</v>
@@ -6441,7 +6348,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="49" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O93" s="43"/>
       <c r="P93" s="43"/>
@@ -6458,7 +6365,7 @@
         <v>103501</v>
       </c>
       <c r="C94" s="40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D94" s="41">
         <v>103501001</v>
@@ -6467,10 +6374,10 @@
         <v>12</v>
       </c>
       <c r="F94" s="43" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="G94" s="44" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="H94" s="50">
         <v>0</v>
@@ -6491,7 +6398,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="49" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="O94" s="43"/>
       <c r="P94" s="43"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -69,7 +69,8 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>最大押分值*10000</t>
+          <t xml:space="preserve">最大押分值*1000
+</t>
         </r>
       </text>
     </comment>
@@ -153,6 +154,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+50倍
 触发金额_多语言ID
 单局游戏获得金额大于此值时，添加至跑马灯列表播放
 当值小于等于0时，不播</t>
@@ -329,7 +331,7 @@
     <t>50000:1</t>
   </si>
   <si>
-    <t>100000_200000_500000_1000000_2000000_500000_100000000</t>
+    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
   </si>
   <si>
     <t>500000:1</t>
@@ -622,9 +624,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -633,9 +635,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -646,16 +649,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1184,7 +1186,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1259,9 +1261,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1659,7 +1658,7 @@
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="6" max="6" width="45.75" customWidth="1"/>
+    <col min="6" max="6" width="68.1916666666667" customWidth="1"/>
     <col min="7" max="7" width="14" style="5" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="6" customWidth="1"/>
     <col min="9" max="9" width="21.25" customWidth="1"/>
@@ -1854,7 +1853,8 @@
         <v>35</v>
       </c>
       <c r="H5" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I5" s="24">
         <v>9500</v>
@@ -1904,7 +1904,8 @@
         <v>39</v>
       </c>
       <c r="H6" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I6" s="24">
         <v>9500</v>
@@ -1953,8 +1954,9 @@
       <c r="G7" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="27">
-        <v>50000000000</v>
+      <c r="H7" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I7" s="24">
         <v>9500</v>
@@ -2004,7 +2006,8 @@
         <v>42</v>
       </c>
       <c r="H8" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I8" s="24">
         <v>9500</v>
@@ -2054,7 +2057,8 @@
         <v>46</v>
       </c>
       <c r="H9" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I9" s="24">
         <v>9500</v>
@@ -2103,8 +2107,9 @@
       <c r="G10" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="27">
-        <v>50000000000</v>
+      <c r="H10" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I10" s="24">
         <v>9500</v>
@@ -2154,7 +2159,8 @@
         <v>51</v>
       </c>
       <c r="H11" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I11" s="22">
         <v>9500</v>
@@ -2204,7 +2210,8 @@
         <v>53</v>
       </c>
       <c r="H12" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I12" s="22">
         <v>9500</v>
@@ -2253,8 +2260,9 @@
       <c r="G13" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="27">
-        <v>50000000000</v>
+      <c r="H13" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I13" s="22">
         <v>9500</v>
@@ -2304,7 +2312,8 @@
         <v>39</v>
       </c>
       <c r="H14" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I14" s="24">
         <v>9500</v>
@@ -2354,7 +2363,8 @@
         <v>42</v>
       </c>
       <c r="H15" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I15" s="24">
         <v>9500</v>
@@ -2403,8 +2413,9 @@
       <c r="G16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="27">
-        <v>50000000000</v>
+      <c r="H16" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I16" s="24">
         <v>9500</v>
@@ -2454,7 +2465,8 @@
         <v>39</v>
       </c>
       <c r="H17" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I17" s="24">
         <v>9500</v>
@@ -2504,7 +2516,8 @@
         <v>42</v>
       </c>
       <c r="H18" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I18" s="24">
         <v>9500</v>
@@ -2553,8 +2566,9 @@
       <c r="G19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="27">
-        <v>50000000000</v>
+      <c r="H19" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I19" s="24">
         <v>9500</v>
@@ -2604,7 +2618,8 @@
         <v>51</v>
       </c>
       <c r="H20" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I20" s="22">
         <v>9500</v>
@@ -2654,7 +2669,8 @@
         <v>53</v>
       </c>
       <c r="H21" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I21" s="22">
         <v>9500</v>
@@ -2703,8 +2719,9 @@
       <c r="G22" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H22" s="27">
-        <v>50000000000</v>
+      <c r="H22" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I22" s="22">
         <v>9500</v>
@@ -2753,8 +2770,9 @@
       <c r="G23" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="27">
-        <v>500000000</v>
+      <c r="H23" s="13">
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I23" s="22">
         <v>9500</v>
@@ -2803,8 +2821,9 @@
       <c r="G24" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="27">
-        <v>5000000000</v>
+      <c r="H24" s="13">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I24" s="22">
         <v>9500</v>
@@ -2853,8 +2872,9 @@
       <c r="G25" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H25" s="27">
-        <v>50000000000</v>
+      <c r="H25" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I25" s="22">
         <v>9500</v>
@@ -2903,8 +2923,9 @@
       <c r="G26" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H26" s="27">
-        <v>500000000</v>
+      <c r="H26" s="13">
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I26" s="22">
         <v>9500</v>
@@ -2953,8 +2974,9 @@
       <c r="G27" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="27">
-        <v>5000000000</v>
+      <c r="H27" s="13">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I27" s="22">
         <v>9500</v>
@@ -3003,8 +3025,9 @@
       <c r="G28" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="27">
-        <v>50000000000</v>
+      <c r="H28" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I28" s="22">
         <v>9500</v>
@@ -3054,7 +3077,8 @@
         <v>35</v>
       </c>
       <c r="H29" s="13">
-        <v>500000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I29" s="24">
         <v>9500</v>
@@ -3104,7 +3128,8 @@
         <v>39</v>
       </c>
       <c r="H30" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I30" s="24">
         <v>9500</v>
@@ -3153,8 +3178,9 @@
       <c r="G31" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="27">
-        <v>50000000000</v>
+      <c r="H31" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I31" s="24">
         <v>9500</v>
@@ -3204,13 +3230,14 @@
         <v>51</v>
       </c>
       <c r="H32" s="13">
-        <v>50000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I32" s="24">
         <v>9500</v>
       </c>
       <c r="J32" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K32" s="25" t="s">
         <v>36</v>
@@ -3254,7 +3281,8 @@
         <v>53</v>
       </c>
       <c r="H33" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I33" s="24">
         <v>9500</v>
@@ -3303,14 +3331,15 @@
       <c r="G34" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H34" s="27">
-        <v>500000000000</v>
+      <c r="H34" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I34" s="24">
         <v>9500</v>
       </c>
       <c r="J34" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K34" s="25" t="s">
         <v>36</v>
@@ -3354,13 +3383,14 @@
         <v>65</v>
       </c>
       <c r="H35" s="13">
-        <v>50000000</v>
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I35" s="24">
         <v>9500</v>
       </c>
       <c r="J35" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K35" s="25" t="s">
         <v>36</v>
@@ -3404,7 +3434,8 @@
         <v>67</v>
       </c>
       <c r="H36" s="13">
-        <v>5000000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I36" s="24">
         <v>9500</v>
@@ -3453,14 +3484,15 @@
       <c r="G37" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H37" s="27">
-        <v>500000000000</v>
+      <c r="H37" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I37" s="24">
         <v>9500</v>
       </c>
       <c r="J37" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K37" s="25" t="s">
         <v>36</v>
@@ -3503,14 +3535,15 @@
       <c r="G38" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H38" s="27">
-        <v>50000000</v>
+      <c r="H38" s="13">
+        <f>100000*1000</f>
+        <v>100000000</v>
       </c>
       <c r="I38" s="24">
         <v>9500</v>
       </c>
       <c r="J38" s="22">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="K38" s="25" t="s">
         <v>36</v>
@@ -3553,8 +3586,9 @@
       <c r="G39" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="27">
-        <v>5000000000</v>
+      <c r="H39" s="13">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
       <c r="I39" s="24">
         <v>9500</v>
@@ -3603,14 +3637,15 @@
       <c r="G40" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H40" s="27">
-        <v>500000000000</v>
+      <c r="H40" s="13">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
       <c r="I40" s="24">
         <v>9500</v>
       </c>
       <c r="J40" s="22">
-        <v>5000000000</v>
+        <v>500000000</v>
       </c>
       <c r="K40" s="25" t="s">
         <v>36</v>
@@ -3632,1369 +3667,1369 @@
       <c r="T40" s="22"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A41" s="28">
+      <c r="A41" s="27">
         <v>10010010</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="28">
         <v>100100</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="30">
         <v>100100026</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="31">
         <v>10</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="34" t="s">
+      <c r="G41" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="35">
-        <v>0</v>
-      </c>
-      <c r="I41" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J41" s="37">
-        <v>0</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L41" s="38">
-        <v>0</v>
-      </c>
-      <c r="M41" s="36" t="s">
+      <c r="H41" s="34">
+        <v>0</v>
+      </c>
+      <c r="I41" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J41" s="36">
+        <v>0</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="37">
+        <v>0</v>
+      </c>
+      <c r="M41" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N41" s="39" t="s">
+      <c r="N41" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A42" s="28">
+      <c r="A42" s="27">
         <v>10010011</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="28">
         <v>100100</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="30">
         <v>100100026</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="31">
         <v>11</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G42" s="34" t="s">
+      <c r="G42" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="H42" s="35">
-        <v>0</v>
-      </c>
-      <c r="I42" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J42" s="37">
-        <v>0</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L42" s="38">
-        <v>0</v>
-      </c>
-      <c r="M42" s="36" t="s">
+      <c r="H42" s="34">
+        <v>0</v>
+      </c>
+      <c r="I42" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J42" s="36">
+        <v>0</v>
+      </c>
+      <c r="K42" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="37">
+        <v>0</v>
+      </c>
+      <c r="M42" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N42" s="39" t="s">
+      <c r="N42" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="36"/>
-      <c r="T42" s="36"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A43" s="28">
+      <c r="A43" s="27">
         <v>10010012</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="28">
         <v>100100</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <v>100100026</v>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="31">
         <v>12</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G43" s="34" t="s">
+      <c r="G43" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="40">
-        <v>0</v>
-      </c>
-      <c r="I43" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J43" s="37">
-        <v>0</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L43" s="38">
-        <v>0</v>
-      </c>
-      <c r="M43" s="36" t="s">
+      <c r="H43" s="39">
+        <v>0</v>
+      </c>
+      <c r="I43" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J43" s="36">
+        <v>0</v>
+      </c>
+      <c r="K43" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="37">
+        <v>0</v>
+      </c>
+      <c r="M43" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N43" s="39" t="s">
+      <c r="N43" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A44" s="28">
+      <c r="A44" s="27">
         <v>10030010</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="28">
         <v>100300</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="30">
         <v>100100026</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="31">
         <v>10</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G44" s="34" t="s">
+      <c r="G44" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="35">
-        <v>0</v>
-      </c>
-      <c r="I44" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J44" s="37">
-        <v>0</v>
-      </c>
-      <c r="K44" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" s="41">
-        <v>0</v>
-      </c>
-      <c r="M44" s="36" t="s">
+      <c r="H44" s="34">
+        <v>0</v>
+      </c>
+      <c r="I44" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J44" s="36">
+        <v>0</v>
+      </c>
+      <c r="K44" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="40">
+        <v>0</v>
+      </c>
+      <c r="M44" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N44" s="39" t="s">
+      <c r="N44" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A45" s="28">
+      <c r="A45" s="27">
         <v>10030011</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="28">
         <v>100300</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="30">
         <v>100100026</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="31">
         <v>11</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G45" s="34" t="s">
+      <c r="G45" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="H45" s="35">
-        <v>0</v>
-      </c>
-      <c r="I45" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J45" s="37">
-        <v>0</v>
-      </c>
-      <c r="K45" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L45" s="41">
-        <v>0</v>
-      </c>
-      <c r="M45" s="36" t="s">
+      <c r="H45" s="34">
+        <v>0</v>
+      </c>
+      <c r="I45" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J45" s="36">
+        <v>0</v>
+      </c>
+      <c r="K45" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="40">
+        <v>0</v>
+      </c>
+      <c r="M45" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N45" s="39" t="s">
+      <c r="N45" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="36"/>
-      <c r="T45" s="36"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A46" s="28">
+      <c r="A46" s="27">
         <v>10030012</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="28">
         <v>100300</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C46" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="30">
         <v>100100026</v>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="31">
         <v>12</v>
       </c>
-      <c r="F46" s="33" t="s">
+      <c r="F46" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G46" s="34" t="s">
+      <c r="G46" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="H46" s="40">
-        <v>0</v>
-      </c>
-      <c r="I46" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J46" s="37">
-        <v>0</v>
-      </c>
-      <c r="K46" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L46" s="41">
-        <v>0</v>
-      </c>
-      <c r="M46" s="36" t="s">
+      <c r="H46" s="39">
+        <v>0</v>
+      </c>
+      <c r="I46" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J46" s="36">
+        <v>0</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="40">
+        <v>0</v>
+      </c>
+      <c r="M46" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N46" s="39" t="s">
+      <c r="N46" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="36"/>
-      <c r="T46" s="36"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A47" s="28">
+      <c r="A47" s="27">
         <v>10070010</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="28">
         <v>100700</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="30">
         <v>100100026</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="31">
         <v>10</v>
       </c>
-      <c r="F47" s="33" t="s">
+      <c r="F47" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G47" s="34" t="s">
+      <c r="G47" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H47" s="35">
-        <v>0</v>
-      </c>
-      <c r="I47" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J47" s="37">
-        <v>0</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L47" s="38">
-        <v>0</v>
-      </c>
-      <c r="M47" s="36" t="s">
+      <c r="H47" s="34">
+        <v>0</v>
+      </c>
+      <c r="I47" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J47" s="36">
+        <v>0</v>
+      </c>
+      <c r="K47" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="37">
+        <v>0</v>
+      </c>
+      <c r="M47" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N47" s="39" t="s">
+      <c r="N47" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="36"/>
-      <c r="T47" s="36"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A48" s="28">
+      <c r="A48" s="27">
         <v>10070011</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="28">
         <v>100700</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C48" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="30">
         <v>100100026</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="31">
         <v>11</v>
       </c>
-      <c r="F48" s="33" t="s">
+      <c r="F48" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="34" t="s">
+      <c r="G48" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="H48" s="35">
-        <v>0</v>
-      </c>
-      <c r="I48" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J48" s="37">
-        <v>0</v>
-      </c>
-      <c r="K48" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L48" s="38">
-        <v>0</v>
-      </c>
-      <c r="M48" s="36" t="s">
+      <c r="H48" s="34">
+        <v>0</v>
+      </c>
+      <c r="I48" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J48" s="36">
+        <v>0</v>
+      </c>
+      <c r="K48" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="37">
+        <v>0</v>
+      </c>
+      <c r="M48" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N48" s="39" t="s">
+      <c r="N48" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="36"/>
-      <c r="T48" s="36"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A49" s="28">
+      <c r="A49" s="27">
         <v>10070012</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="28">
         <v>100700</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="30">
         <v>100100026</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="31">
         <v>12</v>
       </c>
-      <c r="F49" s="33" t="s">
+      <c r="F49" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G49" s="34" t="s">
+      <c r="G49" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H49" s="40">
-        <v>0</v>
-      </c>
-      <c r="I49" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J49" s="37">
-        <v>0</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L49" s="38">
-        <v>0</v>
-      </c>
-      <c r="M49" s="36" t="s">
+      <c r="H49" s="39">
+        <v>0</v>
+      </c>
+      <c r="I49" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J49" s="36">
+        <v>0</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="37">
+        <v>0</v>
+      </c>
+      <c r="M49" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N49" s="39" t="s">
+      <c r="N49" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="36"/>
-      <c r="T49" s="36"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
     </row>
     <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="28">
+      <c r="A50" s="27">
         <v>10120010</v>
       </c>
-      <c r="B50" s="42">
+      <c r="B50" s="41">
         <v>101200</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="C50" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="42">
         <v>101200026</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="31">
         <v>10</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="44" t="s">
+      <c r="G50" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H50" s="35">
-        <v>0</v>
-      </c>
-      <c r="I50" s="37">
-        <v>9500</v>
-      </c>
-      <c r="J50" s="37">
-        <v>0</v>
-      </c>
-      <c r="K50" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="41">
-        <v>0</v>
-      </c>
-      <c r="M50" s="37" t="s">
+      <c r="H50" s="34">
+        <v>0</v>
+      </c>
+      <c r="I50" s="36">
+        <v>9500</v>
+      </c>
+      <c r="J50" s="36">
+        <v>0</v>
+      </c>
+      <c r="K50" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="40">
+        <v>0</v>
+      </c>
+      <c r="M50" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="N50" s="39" t="s">
+      <c r="N50" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O50" s="39"/>
-      <c r="P50" s="39"/>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="39"/>
-      <c r="S50" s="37"/>
-      <c r="T50" s="37"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A51" s="28">
+      <c r="A51" s="27">
         <v>10120011</v>
       </c>
-      <c r="B51" s="42">
+      <c r="B51" s="41">
         <v>101200</v>
       </c>
-      <c r="C51" s="32" t="s">
+      <c r="C51" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="42">
         <v>101200026</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="31">
         <v>11</v>
       </c>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G51" s="44" t="s">
+      <c r="G51" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="H51" s="35">
-        <v>0</v>
-      </c>
-      <c r="I51" s="37">
-        <v>9500</v>
-      </c>
-      <c r="J51" s="37">
-        <v>0</v>
-      </c>
-      <c r="K51" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="41">
-        <v>0</v>
-      </c>
-      <c r="M51" s="37" t="s">
+      <c r="H51" s="34">
+        <v>0</v>
+      </c>
+      <c r="I51" s="36">
+        <v>9500</v>
+      </c>
+      <c r="J51" s="36">
+        <v>0</v>
+      </c>
+      <c r="K51" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="40">
+        <v>0</v>
+      </c>
+      <c r="M51" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N51" s="39" t="s">
+      <c r="N51" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O51" s="39"/>
-      <c r="P51" s="39"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="39"/>
-      <c r="S51" s="37"/>
-      <c r="T51" s="37"/>
+      <c r="O51" s="38"/>
+      <c r="P51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51" s="38"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A52" s="28">
+      <c r="A52" s="27">
         <v>10120012</v>
       </c>
-      <c r="B52" s="42">
+      <c r="B52" s="41">
         <v>101200</v>
       </c>
-      <c r="C52" s="32" t="s">
+      <c r="C52" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="43">
+      <c r="D52" s="42">
         <v>101200026</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="31">
         <v>12</v>
       </c>
-      <c r="F52" s="39" t="s">
+      <c r="F52" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="44" t="s">
+      <c r="G52" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="H52" s="40">
-        <v>0</v>
-      </c>
-      <c r="I52" s="37">
-        <v>9500</v>
-      </c>
-      <c r="J52" s="37">
-        <v>0</v>
-      </c>
-      <c r="K52" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="41">
-        <v>0</v>
-      </c>
-      <c r="M52" s="37" t="s">
+      <c r="H52" s="39">
+        <v>0</v>
+      </c>
+      <c r="I52" s="36">
+        <v>9500</v>
+      </c>
+      <c r="J52" s="36">
+        <v>0</v>
+      </c>
+      <c r="K52" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="40">
+        <v>0</v>
+      </c>
+      <c r="M52" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="N52" s="39" t="s">
+      <c r="N52" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="37"/>
-      <c r="T52" s="37"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A53" s="28">
+      <c r="A53" s="27">
         <v>10140010</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="28">
         <v>101400</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C53" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="30">
         <v>100100026</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="31">
         <v>10</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F53" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G53" s="34" t="s">
+      <c r="G53" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="H53" s="35">
-        <v>0</v>
-      </c>
-      <c r="I53" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J53" s="37">
-        <v>0</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L53" s="38">
-        <v>0</v>
-      </c>
-      <c r="M53" s="36" t="s">
+      <c r="H53" s="34">
+        <v>0</v>
+      </c>
+      <c r="I53" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J53" s="36">
+        <v>0</v>
+      </c>
+      <c r="K53" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="37">
+        <v>0</v>
+      </c>
+      <c r="M53" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N53" s="39" t="s">
+      <c r="N53" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="36"/>
-      <c r="T53" s="36"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A54" s="28">
+      <c r="A54" s="27">
         <v>10140011</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="28">
         <v>101400</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="30">
         <v>100100026</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="31">
         <v>11</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G54" s="34" t="s">
+      <c r="G54" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H54" s="35">
-        <v>0</v>
-      </c>
-      <c r="I54" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J54" s="37">
-        <v>0</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L54" s="38">
-        <v>0</v>
-      </c>
-      <c r="M54" s="36" t="s">
+      <c r="H54" s="34">
+        <v>0</v>
+      </c>
+      <c r="I54" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J54" s="36">
+        <v>0</v>
+      </c>
+      <c r="K54" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="37">
+        <v>0</v>
+      </c>
+      <c r="M54" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N54" s="39" t="s">
+      <c r="N54" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33"/>
-      <c r="Q54" s="33"/>
-      <c r="R54" s="33"/>
-      <c r="S54" s="36"/>
-      <c r="T54" s="36"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A55" s="28">
+      <c r="A55" s="27">
         <v>10140012</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="28">
         <v>101400</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="30">
         <v>100100026</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="31">
         <v>12</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="F55" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G55" s="34" t="s">
+      <c r="G55" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="H55" s="40">
-        <v>0</v>
-      </c>
-      <c r="I55" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J55" s="37">
-        <v>0</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="38">
-        <v>0</v>
-      </c>
-      <c r="M55" s="36" t="s">
+      <c r="H55" s="39">
+        <v>0</v>
+      </c>
+      <c r="I55" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J55" s="36">
+        <v>0</v>
+      </c>
+      <c r="K55" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="37">
+        <v>0</v>
+      </c>
+      <c r="M55" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N55" s="39" t="s">
+      <c r="N55" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O55" s="33"/>
-      <c r="P55" s="33"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="33"/>
-      <c r="S55" s="36"/>
-      <c r="T55" s="36"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="35"/>
+      <c r="T55" s="35"/>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A56" s="28">
+      <c r="A56" s="27">
         <v>10170010</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="28">
         <v>101700</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C56" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="30">
         <v>101700001</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="31">
         <v>10</v>
       </c>
-      <c r="F56" s="33" t="s">
+      <c r="F56" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G56" s="34" t="s">
+      <c r="G56" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H56" s="35">
-        <v>0</v>
-      </c>
-      <c r="I56" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J56" s="37">
-        <v>0</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="38">
-        <v>0</v>
-      </c>
-      <c r="M56" s="36" t="s">
+      <c r="H56" s="34">
+        <v>0</v>
+      </c>
+      <c r="I56" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J56" s="36">
+        <v>0</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="37">
+        <v>0</v>
+      </c>
+      <c r="M56" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N56" s="39" t="s">
+      <c r="N56" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O56" s="33"/>
-      <c r="P56" s="33"/>
-      <c r="Q56" s="33"/>
-      <c r="R56" s="33"/>
-      <c r="S56" s="36"/>
-      <c r="T56" s="36"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A57" s="28">
+      <c r="A57" s="27">
         <v>10170011</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="28">
         <v>101700</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C57" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="30">
         <v>101700001</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="31">
         <v>11</v>
       </c>
-      <c r="F57" s="33" t="s">
+      <c r="F57" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="34" t="s">
+      <c r="G57" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="35">
-        <v>0</v>
-      </c>
-      <c r="I57" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J57" s="37">
-        <v>0</v>
-      </c>
-      <c r="K57" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L57" s="38">
-        <v>0</v>
-      </c>
-      <c r="M57" s="36" t="s">
+      <c r="H57" s="34">
+        <v>0</v>
+      </c>
+      <c r="I57" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J57" s="36">
+        <v>0</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="37">
+        <v>0</v>
+      </c>
+      <c r="M57" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N57" s="39" t="s">
+      <c r="N57" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O57" s="33"/>
-      <c r="P57" s="33"/>
-      <c r="Q57" s="33"/>
-      <c r="R57" s="33"/>
-      <c r="S57" s="36"/>
-      <c r="T57" s="36"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="35"/>
+      <c r="T57" s="35"/>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A58" s="28">
+      <c r="A58" s="27">
         <v>10170012</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="28">
         <v>101700</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C58" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="30">
         <v>101700001</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="31">
         <v>12</v>
       </c>
-      <c r="F58" s="33" t="s">
+      <c r="F58" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G58" s="34" t="s">
+      <c r="G58" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H58" s="40">
-        <v>0</v>
-      </c>
-      <c r="I58" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J58" s="37">
-        <v>0</v>
-      </c>
-      <c r="K58" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L58" s="38">
-        <v>0</v>
-      </c>
-      <c r="M58" s="36" t="s">
+      <c r="H58" s="39">
+        <v>0</v>
+      </c>
+      <c r="I58" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J58" s="36">
+        <v>0</v>
+      </c>
+      <c r="K58" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="37">
+        <v>0</v>
+      </c>
+      <c r="M58" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N58" s="39" t="s">
+      <c r="N58" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O58" s="33"/>
-      <c r="P58" s="33"/>
-      <c r="Q58" s="33"/>
-      <c r="R58" s="33"/>
-      <c r="S58" s="36"/>
-      <c r="T58" s="36"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="35"/>
+      <c r="T58" s="35"/>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A59" s="28">
+      <c r="A59" s="27">
         <v>10210010</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="28">
         <v>102100</v>
       </c>
-      <c r="C59" s="30" t="s">
+      <c r="C59" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="30">
         <v>102100001</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="31">
         <v>10</v>
       </c>
-      <c r="F59" s="33" t="s">
+      <c r="F59" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="34" t="s">
+      <c r="G59" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H59" s="35">
-        <v>0</v>
-      </c>
-      <c r="I59" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J59" s="37">
-        <v>0</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="41">
-        <v>0</v>
-      </c>
-      <c r="M59" s="36" t="s">
+      <c r="H59" s="34">
+        <v>0</v>
+      </c>
+      <c r="I59" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J59" s="36">
+        <v>0</v>
+      </c>
+      <c r="K59" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="40">
+        <v>0</v>
+      </c>
+      <c r="M59" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N59" s="39" t="s">
+      <c r="N59" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O59" s="33"/>
-      <c r="P59" s="33"/>
-      <c r="Q59" s="33"/>
-      <c r="R59" s="33"/>
-      <c r="S59" s="36"/>
-      <c r="T59" s="36"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A60" s="28">
+      <c r="A60" s="27">
         <v>10210011</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="28">
         <v>102100</v>
       </c>
-      <c r="C60" s="30" t="s">
+      <c r="C60" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="30">
         <v>102100001</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="31">
         <v>11</v>
       </c>
-      <c r="F60" s="33" t="s">
+      <c r="F60" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G60" s="34" t="s">
+      <c r="G60" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="H60" s="35">
-        <v>0</v>
-      </c>
-      <c r="I60" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J60" s="37">
-        <v>0</v>
-      </c>
-      <c r="K60" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="41">
-        <v>0</v>
-      </c>
-      <c r="M60" s="36" t="s">
+      <c r="H60" s="34">
+        <v>0</v>
+      </c>
+      <c r="I60" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J60" s="36">
+        <v>0</v>
+      </c>
+      <c r="K60" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="40">
+        <v>0</v>
+      </c>
+      <c r="M60" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N60" s="39" t="s">
+      <c r="N60" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O60" s="33"/>
-      <c r="P60" s="33"/>
-      <c r="Q60" s="33"/>
-      <c r="R60" s="33"/>
-      <c r="S60" s="36"/>
-      <c r="T60" s="36"/>
+      <c r="O60" s="32"/>
+      <c r="P60" s="32"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="35"/>
+      <c r="T60" s="35"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A61" s="28">
+      <c r="A61" s="27">
         <v>10210012</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="28">
         <v>102100</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="30">
         <v>102100001</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="31">
         <v>12</v>
       </c>
-      <c r="F61" s="33" t="s">
+      <c r="F61" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G61" s="34" t="s">
+      <c r="G61" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H61" s="40">
-        <v>0</v>
-      </c>
-      <c r="I61" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J61" s="37">
-        <v>0</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="41">
-        <v>0</v>
-      </c>
-      <c r="M61" s="36" t="s">
+      <c r="H61" s="39">
+        <v>0</v>
+      </c>
+      <c r="I61" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J61" s="36">
+        <v>0</v>
+      </c>
+      <c r="K61" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="40">
+        <v>0</v>
+      </c>
+      <c r="M61" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N61" s="39" t="s">
+      <c r="N61" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O61" s="33"/>
-      <c r="P61" s="33"/>
-      <c r="Q61" s="33"/>
-      <c r="R61" s="33"/>
-      <c r="S61" s="36"/>
-      <c r="T61" s="36"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="35"/>
+      <c r="T61" s="35"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="28">
+      <c r="A62" s="27">
         <v>10220010</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="28">
         <v>102200</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C62" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="30">
         <v>102200001</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="31">
         <v>10</v>
       </c>
-      <c r="F62" s="33" t="s">
+      <c r="F62" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G62" s="34" t="s">
+      <c r="G62" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H62" s="35">
-        <v>0</v>
-      </c>
-      <c r="I62" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J62" s="37">
-        <v>0</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="41">
-        <v>0</v>
-      </c>
-      <c r="M62" s="36" t="s">
+      <c r="H62" s="34">
+        <v>0</v>
+      </c>
+      <c r="I62" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J62" s="36">
+        <v>0</v>
+      </c>
+      <c r="K62" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="40">
+        <v>0</v>
+      </c>
+      <c r="M62" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N62" s="39" t="s">
+      <c r="N62" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O62" s="33"/>
-      <c r="P62" s="33"/>
-      <c r="Q62" s="33"/>
-      <c r="R62" s="33"/>
-      <c r="S62" s="36"/>
-      <c r="T62" s="36"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="35"/>
+      <c r="T62" s="35"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A63" s="28">
+      <c r="A63" s="27">
         <v>10220011</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="28">
         <v>102200</v>
       </c>
-      <c r="C63" s="30" t="s">
+      <c r="C63" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="30">
         <v>102200001</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="31">
         <v>11</v>
       </c>
-      <c r="F63" s="33" t="s">
+      <c r="F63" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G63" s="34" t="s">
+      <c r="G63" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="H63" s="35">
-        <v>0</v>
-      </c>
-      <c r="I63" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J63" s="37">
-        <v>0</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="41">
-        <v>0</v>
-      </c>
-      <c r="M63" s="36" t="s">
+      <c r="H63" s="34">
+        <v>0</v>
+      </c>
+      <c r="I63" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J63" s="36">
+        <v>0</v>
+      </c>
+      <c r="K63" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="40">
+        <v>0</v>
+      </c>
+      <c r="M63" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N63" s="39" t="s">
+      <c r="N63" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O63" s="33"/>
-      <c r="P63" s="33"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="33"/>
-      <c r="S63" s="36"/>
-      <c r="T63" s="36"/>
+      <c r="O63" s="32"/>
+      <c r="P63" s="32"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A64" s="28">
+      <c r="A64" s="27">
         <v>10220012</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="28">
         <v>102200</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D64" s="31">
+      <c r="D64" s="30">
         <v>102200001</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64" s="31">
         <v>12</v>
       </c>
-      <c r="F64" s="33" t="s">
+      <c r="F64" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G64" s="34" t="s">
+      <c r="G64" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H64" s="40">
-        <v>0</v>
-      </c>
-      <c r="I64" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J64" s="37">
-        <v>0</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="41">
-        <v>0</v>
-      </c>
-      <c r="M64" s="36" t="s">
+      <c r="H64" s="39">
+        <v>0</v>
+      </c>
+      <c r="I64" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J64" s="36">
+        <v>0</v>
+      </c>
+      <c r="K64" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="40">
+        <v>0</v>
+      </c>
+      <c r="M64" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N64" s="39" t="s">
+      <c r="N64" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O64" s="33"/>
-      <c r="P64" s="33"/>
-      <c r="Q64" s="33"/>
-      <c r="R64" s="33"/>
-      <c r="S64" s="36"/>
-      <c r="T64" s="36"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="35"/>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A65" s="28">
+      <c r="A65" s="27">
         <v>10240010</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="28">
         <v>102400</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C65" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="30">
         <v>102400026</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="31">
         <v>10</v>
       </c>
-      <c r="F65" s="33" t="s">
+      <c r="F65" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G65" s="34" t="s">
+      <c r="G65" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="H65" s="35">
-        <v>0</v>
-      </c>
-      <c r="I65" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J65" s="37">
-        <v>0</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L65" s="41">
-        <v>0</v>
-      </c>
-      <c r="M65" s="36" t="s">
+      <c r="H65" s="34">
+        <v>0</v>
+      </c>
+      <c r="I65" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J65" s="36">
+        <v>0</v>
+      </c>
+      <c r="K65" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="40">
+        <v>0</v>
+      </c>
+      <c r="M65" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N65" s="39" t="s">
+      <c r="N65" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O65" s="33"/>
-      <c r="P65" s="33"/>
-      <c r="Q65" s="33"/>
-      <c r="R65" s="33"/>
-      <c r="S65" s="36"/>
-      <c r="T65" s="36"/>
+      <c r="O65" s="32"/>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="35"/>
+      <c r="T65" s="35"/>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A66" s="28">
+      <c r="A66" s="27">
         <v>10240011</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="28">
         <v>102400</v>
       </c>
-      <c r="C66" s="30" t="s">
+      <c r="C66" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="30">
         <v>102400026</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="31">
         <v>11</v>
       </c>
-      <c r="F66" s="33" t="s">
+      <c r="F66" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G66" s="34" t="s">
+      <c r="G66" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="35">
-        <v>0</v>
-      </c>
-      <c r="I66" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J66" s="37">
-        <v>0</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L66" s="41">
-        <v>0</v>
-      </c>
-      <c r="M66" s="36" t="s">
+      <c r="H66" s="34">
+        <v>0</v>
+      </c>
+      <c r="I66" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J66" s="36">
+        <v>0</v>
+      </c>
+      <c r="K66" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="40">
+        <v>0</v>
+      </c>
+      <c r="M66" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N66" s="39" t="s">
+      <c r="N66" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O66" s="33"/>
-      <c r="P66" s="33"/>
-      <c r="Q66" s="33"/>
-      <c r="R66" s="33"/>
-      <c r="S66" s="36"/>
-      <c r="T66" s="36"/>
+      <c r="O66" s="32"/>
+      <c r="P66" s="32"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="35"/>
+      <c r="T66" s="35"/>
     </row>
     <row r="67" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A67" s="28">
+      <c r="A67" s="27">
         <v>10240012</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="28">
         <v>102400</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C67" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D67" s="31">
+      <c r="D67" s="30">
         <v>102400026</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="31">
         <v>12</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="F67" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G67" s="34" t="s">
+      <c r="G67" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H67" s="40">
-        <v>0</v>
-      </c>
-      <c r="I67" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J67" s="37">
-        <v>0</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L67" s="41">
-        <v>0</v>
-      </c>
-      <c r="M67" s="36" t="s">
+      <c r="H67" s="39">
+        <v>0</v>
+      </c>
+      <c r="I67" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J67" s="36">
+        <v>0</v>
+      </c>
+      <c r="K67" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="40">
+        <v>0</v>
+      </c>
+      <c r="M67" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N67" s="39" t="s">
+      <c r="N67" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O67" s="33"/>
-      <c r="P67" s="33"/>
-      <c r="Q67" s="33"/>
-      <c r="R67" s="33"/>
-      <c r="S67" s="36"/>
-      <c r="T67" s="36"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="35"/>
+      <c r="T67" s="35"/>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A68" s="28">
+      <c r="A68" s="27">
         <v>10180010</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="28">
         <v>101800</v>
       </c>
-      <c r="C68" s="30" t="s">
+      <c r="C68" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="30">
         <v>101800001</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="31">
         <v>10</v>
       </c>
       <c r="F68" s="20" t="s">
@@ -5003,48 +5038,48 @@
       <c r="G68" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="40">
-        <v>0</v>
-      </c>
-      <c r="I68" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J68" s="37">
-        <v>0</v>
-      </c>
-      <c r="K68" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L68" s="41">
-        <v>0</v>
-      </c>
-      <c r="M68" s="36" t="s">
+      <c r="H68" s="39">
+        <v>0</v>
+      </c>
+      <c r="I68" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J68" s="36">
+        <v>0</v>
+      </c>
+      <c r="K68" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="40">
+        <v>0</v>
+      </c>
+      <c r="M68" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N68" s="39" t="s">
+      <c r="N68" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O68" s="33"/>
-      <c r="P68" s="33"/>
-      <c r="Q68" s="33"/>
-      <c r="R68" s="33"/>
-      <c r="S68" s="36"/>
-      <c r="T68" s="36"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="35"/>
+      <c r="T68" s="35"/>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A69" s="28">
+      <c r="A69" s="27">
         <v>10180011</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="28">
         <v>101800</v>
       </c>
-      <c r="C69" s="30" t="s">
+      <c r="C69" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="30">
         <v>101800001</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="31">
         <v>11</v>
       </c>
       <c r="F69" s="20" t="s">
@@ -5053,48 +5088,48 @@
       <c r="G69" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H69" s="40">
-        <v>0</v>
-      </c>
-      <c r="I69" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J69" s="37">
-        <v>0</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L69" s="41">
-        <v>0</v>
-      </c>
-      <c r="M69" s="36" t="s">
+      <c r="H69" s="39">
+        <v>0</v>
+      </c>
+      <c r="I69" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J69" s="36">
+        <v>0</v>
+      </c>
+      <c r="K69" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="40">
+        <v>0</v>
+      </c>
+      <c r="M69" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N69" s="39" t="s">
+      <c r="N69" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O69" s="33"/>
-      <c r="P69" s="33"/>
-      <c r="Q69" s="33"/>
-      <c r="R69" s="33"/>
-      <c r="S69" s="36"/>
-      <c r="T69" s="36"/>
+      <c r="O69" s="32"/>
+      <c r="P69" s="32"/>
+      <c r="Q69" s="32"/>
+      <c r="R69" s="32"/>
+      <c r="S69" s="35"/>
+      <c r="T69" s="35"/>
     </row>
     <row r="70" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A70" s="28">
+      <c r="A70" s="27">
         <v>10180012</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="28">
         <v>101800</v>
       </c>
-      <c r="C70" s="30" t="s">
+      <c r="C70" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="31">
+      <c r="D70" s="30">
         <v>101800001</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70" s="31">
         <v>12</v>
       </c>
       <c r="F70" s="20" t="s">
@@ -5103,49 +5138,49 @@
       <c r="G70" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H70" s="40">
-        <v>0</v>
-      </c>
-      <c r="I70" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J70" s="37">
-        <v>0</v>
-      </c>
-      <c r="K70" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L70" s="41">
-        <v>0</v>
-      </c>
-      <c r="M70" s="36" t="s">
+      <c r="H70" s="39">
+        <v>0</v>
+      </c>
+      <c r="I70" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J70" s="36">
+        <v>0</v>
+      </c>
+      <c r="K70" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="40">
+        <v>0</v>
+      </c>
+      <c r="M70" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N70" s="39" t="s">
+      <c r="N70" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O70" s="33"/>
-      <c r="P70" s="33"/>
-      <c r="Q70" s="33"/>
-      <c r="R70" s="33"/>
-      <c r="S70" s="36"/>
-      <c r="T70" s="36"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="35"/>
+      <c r="T70" s="35"/>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A71" s="28">
+      <c r="A71" s="27">
         <f t="shared" ref="A71:A76" si="0">(B71*100)+E71</f>
         <v>10250010</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="28">
         <v>102500</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C71" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="30">
         <v>102500001</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="31">
         <v>10</v>
       </c>
       <c r="F71" s="20" t="s">
@@ -5154,49 +5189,49 @@
       <c r="G71" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="H71" s="40">
-        <v>0</v>
-      </c>
-      <c r="I71" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J71" s="37">
-        <v>0</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L71" s="41">
-        <v>0</v>
-      </c>
-      <c r="M71" s="36" t="s">
+      <c r="H71" s="39">
+        <v>0</v>
+      </c>
+      <c r="I71" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J71" s="36">
+        <v>0</v>
+      </c>
+      <c r="K71" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="40">
+        <v>0</v>
+      </c>
+      <c r="M71" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N71" s="39" t="s">
+      <c r="N71" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="36"/>
-      <c r="T71" s="36"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
+      <c r="S71" s="35"/>
+      <c r="T71" s="35"/>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A72" s="28">
+      <c r="A72" s="27">
         <f t="shared" si="0"/>
         <v>10250011</v>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="28">
         <v>102500</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="30">
         <v>102500001</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="31">
         <v>11</v>
       </c>
       <c r="F72" s="20" t="s">
@@ -5205,49 +5240,49 @@
       <c r="G72" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="H72" s="40">
-        <v>0</v>
-      </c>
-      <c r="I72" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J72" s="37">
-        <v>0</v>
-      </c>
-      <c r="K72" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L72" s="41">
-        <v>0</v>
-      </c>
-      <c r="M72" s="36" t="s">
+      <c r="H72" s="39">
+        <v>0</v>
+      </c>
+      <c r="I72" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J72" s="36">
+        <v>0</v>
+      </c>
+      <c r="K72" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="40">
+        <v>0</v>
+      </c>
+      <c r="M72" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N72" s="39" t="s">
+      <c r="N72" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O72" s="33"/>
-      <c r="P72" s="33"/>
-      <c r="Q72" s="33"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="36"/>
-      <c r="T72" s="36"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="35"/>
+      <c r="T72" s="35"/>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A73" s="28">
+      <c r="A73" s="27">
         <f t="shared" si="0"/>
         <v>10250012</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="28">
         <v>102500</v>
       </c>
-      <c r="C73" s="30" t="s">
+      <c r="C73" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D73" s="31">
+      <c r="D73" s="30">
         <v>102500001</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="31">
         <v>12</v>
       </c>
       <c r="F73" s="20" t="s">
@@ -5256,49 +5291,49 @@
       <c r="G73" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H73" s="40">
-        <v>0</v>
-      </c>
-      <c r="I73" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J73" s="37">
-        <v>0</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L73" s="41">
-        <v>0</v>
-      </c>
-      <c r="M73" s="36" t="s">
+      <c r="H73" s="39">
+        <v>0</v>
+      </c>
+      <c r="I73" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J73" s="36">
+        <v>0</v>
+      </c>
+      <c r="K73" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="40">
+        <v>0</v>
+      </c>
+      <c r="M73" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N73" s="39" t="s">
+      <c r="N73" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O73" s="33"/>
-      <c r="P73" s="33"/>
-      <c r="Q73" s="33"/>
-      <c r="R73" s="33"/>
-      <c r="S73" s="36"/>
-      <c r="T73" s="36"/>
+      <c r="O73" s="32"/>
+      <c r="P73" s="32"/>
+      <c r="Q73" s="32"/>
+      <c r="R73" s="32"/>
+      <c r="S73" s="35"/>
+      <c r="T73" s="35"/>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A74" s="28">
+      <c r="A74" s="27">
         <f t="shared" si="0"/>
         <v>10230010</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="28">
         <v>102300</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="C74" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D74" s="31">
+      <c r="D74" s="30">
         <v>102300001</v>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="31">
         <v>10</v>
       </c>
       <c r="F74" s="20" t="s">
@@ -5307,49 +5342,49 @@
       <c r="G74" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="40">
-        <v>0</v>
-      </c>
-      <c r="I74" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J74" s="37">
-        <v>0</v>
-      </c>
-      <c r="K74" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L74" s="41">
-        <v>0</v>
-      </c>
-      <c r="M74" s="36" t="s">
+      <c r="H74" s="39">
+        <v>0</v>
+      </c>
+      <c r="I74" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J74" s="36">
+        <v>0</v>
+      </c>
+      <c r="K74" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="40">
+        <v>0</v>
+      </c>
+      <c r="M74" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N74" s="39" t="s">
+      <c r="N74" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="O74" s="33"/>
-      <c r="P74" s="33"/>
-      <c r="Q74" s="33"/>
-      <c r="R74" s="33"/>
-      <c r="S74" s="36"/>
-      <c r="T74" s="36"/>
+      <c r="O74" s="32"/>
+      <c r="P74" s="32"/>
+      <c r="Q74" s="32"/>
+      <c r="R74" s="32"/>
+      <c r="S74" s="35"/>
+      <c r="T74" s="35"/>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A75" s="28">
+      <c r="A75" s="27">
         <f t="shared" si="0"/>
         <v>10230011</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="28">
         <v>102300</v>
       </c>
-      <c r="C75" s="30" t="s">
+      <c r="C75" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D75" s="31">
+      <c r="D75" s="30">
         <v>102300001</v>
       </c>
-      <c r="E75" s="32">
+      <c r="E75" s="31">
         <v>11</v>
       </c>
       <c r="F75" s="20" t="s">
@@ -5358,49 +5393,49 @@
       <c r="G75" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="40">
-        <v>0</v>
-      </c>
-      <c r="I75" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J75" s="37">
-        <v>0</v>
-      </c>
-      <c r="K75" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L75" s="41">
-        <v>0</v>
-      </c>
-      <c r="M75" s="36" t="s">
+      <c r="H75" s="39">
+        <v>0</v>
+      </c>
+      <c r="I75" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J75" s="36">
+        <v>0</v>
+      </c>
+      <c r="K75" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="40">
+        <v>0</v>
+      </c>
+      <c r="M75" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N75" s="39" t="s">
+      <c r="N75" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="O75" s="33"/>
-      <c r="P75" s="33"/>
-      <c r="Q75" s="33"/>
-      <c r="R75" s="33"/>
-      <c r="S75" s="36"/>
-      <c r="T75" s="36"/>
+      <c r="O75" s="32"/>
+      <c r="P75" s="32"/>
+      <c r="Q75" s="32"/>
+      <c r="R75" s="32"/>
+      <c r="S75" s="35"/>
+      <c r="T75" s="35"/>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A76" s="28">
+      <c r="A76" s="27">
         <f t="shared" si="0"/>
         <v>10230012</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="28">
         <v>102300</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D76" s="31">
+      <c r="D76" s="30">
         <v>102300001</v>
       </c>
-      <c r="E76" s="32">
+      <c r="E76" s="31">
         <v>12</v>
       </c>
       <c r="F76" s="20" t="s">
@@ -5409,33 +5444,33 @@
       <c r="G76" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H76" s="40">
-        <v>0</v>
-      </c>
-      <c r="I76" s="36">
-        <v>9500</v>
-      </c>
-      <c r="J76" s="37">
-        <v>0</v>
-      </c>
-      <c r="K76" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="41">
-        <v>0</v>
-      </c>
-      <c r="M76" s="36" t="s">
+      <c r="H76" s="39">
+        <v>0</v>
+      </c>
+      <c r="I76" s="35">
+        <v>9500</v>
+      </c>
+      <c r="J76" s="36">
+        <v>0</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="40">
+        <v>0</v>
+      </c>
+      <c r="M76" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="N76" s="39" t="s">
+      <c r="N76" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O76" s="33"/>
-      <c r="P76" s="33"/>
-      <c r="Q76" s="33"/>
-      <c r="R76" s="33"/>
-      <c r="S76" s="36"/>
-      <c r="T76" s="36"/>
+      <c r="O76" s="32"/>
+      <c r="P76" s="32"/>
+      <c r="Q76" s="32"/>
+      <c r="R76" s="32"/>
+      <c r="S76" s="35"/>
+      <c r="T76" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -637,7 +637,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -649,9 +648,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -661,9 +661,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1853,8 +1853,8 @@
         <v>35</v>
       </c>
       <c r="H5" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I5" s="24">
         <v>9500</v>
@@ -1904,8 +1904,8 @@
         <v>39</v>
       </c>
       <c r="H6" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I6" s="24">
         <v>9500</v>
@@ -1955,8 +1955,8 @@
         <v>42</v>
       </c>
       <c r="H7" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I7" s="24">
         <v>9500</v>
@@ -2006,8 +2006,8 @@
         <v>42</v>
       </c>
       <c r="H8" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I8" s="24">
         <v>9500</v>
@@ -2057,8 +2057,8 @@
         <v>46</v>
       </c>
       <c r="H9" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I9" s="24">
         <v>9500</v>
@@ -2108,8 +2108,8 @@
         <v>48</v>
       </c>
       <c r="H10" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I10" s="24">
         <v>9500</v>
@@ -2159,8 +2159,8 @@
         <v>51</v>
       </c>
       <c r="H11" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I11" s="22">
         <v>9500</v>
@@ -2210,8 +2210,8 @@
         <v>53</v>
       </c>
       <c r="H12" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I12" s="22">
         <v>9500</v>
@@ -2261,8 +2261,8 @@
         <v>55</v>
       </c>
       <c r="H13" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I13" s="22">
         <v>9500</v>
@@ -2312,8 +2312,8 @@
         <v>39</v>
       </c>
       <c r="H14" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I14" s="24">
         <v>9500</v>
@@ -2363,8 +2363,8 @@
         <v>42</v>
       </c>
       <c r="H15" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I15" s="24">
         <v>9500</v>
@@ -2414,8 +2414,8 @@
         <v>46</v>
       </c>
       <c r="H16" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I16" s="24">
         <v>9500</v>
@@ -2465,8 +2465,8 @@
         <v>39</v>
       </c>
       <c r="H17" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I17" s="24">
         <v>9500</v>
@@ -2516,8 +2516,8 @@
         <v>42</v>
       </c>
       <c r="H18" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I18" s="24">
         <v>9500</v>
@@ -2567,8 +2567,8 @@
         <v>46</v>
       </c>
       <c r="H19" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I19" s="24">
         <v>9500</v>
@@ -2618,8 +2618,8 @@
         <v>51</v>
       </c>
       <c r="H20" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I20" s="22">
         <v>9500</v>
@@ -2669,8 +2669,8 @@
         <v>53</v>
       </c>
       <c r="H21" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I21" s="22">
         <v>9500</v>
@@ -2720,8 +2720,8 @@
         <v>55</v>
       </c>
       <c r="H22" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I22" s="22">
         <v>9500</v>
@@ -2771,8 +2771,8 @@
         <v>51</v>
       </c>
       <c r="H23" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I23" s="22">
         <v>9500</v>
@@ -2822,8 +2822,8 @@
         <v>53</v>
       </c>
       <c r="H24" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I24" s="22">
         <v>9500</v>
@@ -2873,8 +2873,8 @@
         <v>55</v>
       </c>
       <c r="H25" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I25" s="22">
         <v>9500</v>
@@ -2924,8 +2924,8 @@
         <v>51</v>
       </c>
       <c r="H26" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I26" s="22">
         <v>9500</v>
@@ -2975,8 +2975,8 @@
         <v>53</v>
       </c>
       <c r="H27" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I27" s="22">
         <v>9500</v>
@@ -3026,8 +3026,8 @@
         <v>55</v>
       </c>
       <c r="H28" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I28" s="22">
         <v>9500</v>
@@ -3077,8 +3077,8 @@
         <v>35</v>
       </c>
       <c r="H29" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I29" s="24">
         <v>9500</v>
@@ -3128,8 +3128,8 @@
         <v>39</v>
       </c>
       <c r="H30" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I30" s="24">
         <v>9500</v>
@@ -3179,8 +3179,8 @@
         <v>42</v>
       </c>
       <c r="H31" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I31" s="24">
         <v>9500</v>
@@ -3230,8 +3230,8 @@
         <v>51</v>
       </c>
       <c r="H32" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I32" s="24">
         <v>9500</v>
@@ -3281,8 +3281,8 @@
         <v>53</v>
       </c>
       <c r="H33" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I33" s="24">
         <v>9500</v>
@@ -3332,8 +3332,8 @@
         <v>55</v>
       </c>
       <c r="H34" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I34" s="24">
         <v>9500</v>
@@ -3383,8 +3383,8 @@
         <v>65</v>
       </c>
       <c r="H35" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I35" s="24">
         <v>9500</v>
@@ -3434,8 +3434,8 @@
         <v>67</v>
       </c>
       <c r="H36" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I36" s="24">
         <v>9500</v>
@@ -3485,8 +3485,8 @@
         <v>69</v>
       </c>
       <c r="H37" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I37" s="24">
         <v>9500</v>
@@ -3536,8 +3536,8 @@
         <v>51</v>
       </c>
       <c r="H38" s="13">
-        <f>100000*1000</f>
-        <v>100000000</v>
+        <f>100000*100</f>
+        <v>10000000</v>
       </c>
       <c r="I38" s="24">
         <v>9500</v>
@@ -3587,8 +3587,8 @@
         <v>53</v>
       </c>
       <c r="H39" s="13">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>1000000*100</f>
+        <v>100000000</v>
       </c>
       <c r="I39" s="24">
         <v>9500</v>
@@ -3638,8 +3638,8 @@
         <v>55</v>
       </c>
       <c r="H40" s="13">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+        <f>10000000*100</f>
+        <v>1000000000</v>
       </c>
       <c r="I40" s="24">
         <v>9500</v>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -295,69 +295,69 @@
     <t>10_20_50_100_200_500_1000</t>
   </si>
   <si>
+    <t>10:1</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>100_200_500_1000_2000_5000_10000</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
+  </si>
+  <si>
+    <t>1000:1</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+  </si>
+  <si>
+    <t>10000:1</t>
+  </si>
+  <si>
+    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
+  </si>
+  <si>
+    <t>100000:1</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>50_100_250_500_1000_2500_5000</t>
+  </si>
+  <si>
     <t>50:1</t>
   </si>
   <si>
-    <t>0,5000,10000</t>
-  </si>
-  <si>
-    <t>5000000_17001</t>
-  </si>
-  <si>
-    <t>100_200_500_1000_2000_5000_10000</t>
+    <t>500_1000_2500_5000_10000_25000_50000</t>
   </si>
   <si>
     <t>500:1</t>
   </si>
   <si>
-    <t>50000000_17001</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000_50000_100000</t>
+    <t>5000_10000_25000_50000_100000_250000_500000</t>
   </si>
   <si>
     <t>5000:1</t>
   </si>
   <si>
-    <t>500000000_17001</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>10000_20000_50000_100000_200000_500000_1000000</t>
-  </si>
-  <si>
-    <t>50000:1</t>
-  </si>
-  <si>
-    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
-  </si>
-  <si>
-    <t>500000:1</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>50_100_250_500_1000_2500_5000</t>
-  </si>
-  <si>
-    <t>250:1</t>
-  </si>
-  <si>
-    <t>500_1000_2500_5000_10000_25000_50000</t>
-  </si>
-  <si>
-    <t>2500:1</t>
-  </si>
-  <si>
-    <t>5000_10000_25000_50000_100000_250000_500000</t>
-  </si>
-  <si>
-    <t>25000:1</t>
-  </si>
-  <si>
     <t>财神</t>
   </si>
   <si>
@@ -385,19 +385,19 @@
     <t>20_40_100_200_400_1000_2000</t>
   </si>
   <si>
-    <t>100:1</t>
+    <t>20:1</t>
   </si>
   <si>
     <t>200_400_1000_2000_4000_10000_20000</t>
   </si>
   <si>
-    <t>1000:1</t>
+    <t>200:1</t>
   </si>
   <si>
     <t>2000_4000_10000_20000_40000_100000_200000</t>
   </si>
   <si>
-    <t>10000:1</t>
+    <t>2000:1</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -625,26 +625,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -658,6 +639,25 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="81">
   <si>
     <t>id</t>
   </si>
@@ -293,69 +293,69 @@
     <t>10_20_50_100_200_500_1000</t>
   </si>
   <si>
+    <t>10:1</t>
+  </si>
+  <si>
+    <t>0,5000,10000</t>
+  </si>
+  <si>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>100_200_500_1000_2000_5000_10000</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
+  </si>
+  <si>
+    <t>1000:1</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+  </si>
+  <si>
+    <t>10000:1</t>
+  </si>
+  <si>
+    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
+  </si>
+  <si>
+    <t>100000:1</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>50_100_250_500_1000_2500_5000</t>
+  </si>
+  <si>
     <t>50:1</t>
   </si>
   <si>
-    <t>0,5000,10000</t>
-  </si>
-  <si>
-    <t>5000000_17001</t>
-  </si>
-  <si>
-    <t>100_200_500_1000_2000_5000_10000</t>
+    <t>500_1000_2500_5000_10000_25000_50000</t>
   </si>
   <si>
     <t>500:1</t>
   </si>
   <si>
-    <t>50000000_17001</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000_50000_100000</t>
+    <t>5000_10000_25000_50000_100000_250000_500000</t>
   </si>
   <si>
     <t>5000:1</t>
   </si>
   <si>
-    <t>500000000_17001</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>10000_20000_50000_100000_200000_500000_1000000</t>
-  </si>
-  <si>
-    <t>50000:1</t>
-  </si>
-  <si>
-    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
-  </si>
-  <si>
-    <t>500000:1</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>50_100_250_500_1000_2500_5000</t>
-  </si>
-  <si>
-    <t>250:1</t>
-  </si>
-  <si>
-    <t>500_1000_2500_5000_10000_25000_50000</t>
-  </si>
-  <si>
-    <t>2500:1</t>
-  </si>
-  <si>
-    <t>5000_10000_25000_50000_100000_250000_500000</t>
-  </si>
-  <si>
-    <t>25000:1</t>
-  </si>
-  <si>
     <t>财神</t>
   </si>
   <si>
@@ -383,19 +383,19 @@
     <t>20_40_100_200_400_1000_2000</t>
   </si>
   <si>
-    <t>100:1</t>
+    <t>20:1</t>
   </si>
   <si>
     <t>200_400_1000_2000_4000_10000_20000</t>
   </si>
   <si>
-    <t>1000:1</t>
+    <t>200:1</t>
   </si>
   <si>
     <t>2000_4000_10000_20000_40000_100000_200000</t>
   </si>
   <si>
-    <t>10000:1</t>
+    <t>2000:1</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -404,16 +404,22 @@
     <t>神马飞扬</t>
   </si>
   <si>
+    <t>20000_40000_100000_200000_400000_1000000_2000000</t>
+  </si>
+  <si>
+    <t>20000:1</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
     <t>2_4_10_20_40_100_200</t>
-  </si>
-  <si>
-    <t>10:1</t>
-  </si>
-  <si>
-    <t>金蛇招财</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -642,13 +648,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -661,8 +667,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -674,8 +680,8 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1199,7 +1205,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1315,27 +1321,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
@@ -1348,7 +1351,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1691,7 +1694,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1891,7 +1894,7 @@
         <v>35</v>
       </c>
       <c r="H5" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I5" s="25">
         <v>9500</v>
@@ -1941,7 +1944,7 @@
         <v>39</v>
       </c>
       <c r="H6" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I6" s="25">
         <v>9500</v>
@@ -1991,7 +1994,7 @@
         <v>42</v>
       </c>
       <c r="H7" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I7" s="25">
         <v>9500</v>
@@ -2041,7 +2044,7 @@
         <v>42</v>
       </c>
       <c r="H8" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I8" s="25">
         <v>9500</v>
@@ -2091,7 +2094,7 @@
         <v>46</v>
       </c>
       <c r="H9" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I9" s="25">
         <v>9500</v>
@@ -2141,7 +2144,7 @@
         <v>48</v>
       </c>
       <c r="H10" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I10" s="25">
         <v>9500</v>
@@ -2191,7 +2194,7 @@
         <v>51</v>
       </c>
       <c r="H11" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I11" s="23">
         <v>9500</v>
@@ -2241,7 +2244,7 @@
         <v>53</v>
       </c>
       <c r="H12" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I12" s="23">
         <v>9500</v>
@@ -2291,7 +2294,7 @@
         <v>55</v>
       </c>
       <c r="H13" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I13" s="23">
         <v>9500</v>
@@ -2341,7 +2344,7 @@
         <v>39</v>
       </c>
       <c r="H14" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I14" s="25">
         <v>9500</v>
@@ -2391,7 +2394,7 @@
         <v>42</v>
       </c>
       <c r="H15" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I15" s="25">
         <v>9500</v>
@@ -2441,7 +2444,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I16" s="25">
         <v>9500</v>
@@ -2491,7 +2494,7 @@
         <v>39</v>
       </c>
       <c r="H17" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I17" s="25">
         <v>9500</v>
@@ -2541,7 +2544,7 @@
         <v>42</v>
       </c>
       <c r="H18" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I18" s="25">
         <v>9500</v>
@@ -2591,7 +2594,7 @@
         <v>46</v>
       </c>
       <c r="H19" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I19" s="25">
         <v>9500</v>
@@ -2641,7 +2644,7 @@
         <v>51</v>
       </c>
       <c r="H20" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I20" s="23">
         <v>9500</v>
@@ -2691,7 +2694,7 @@
         <v>53</v>
       </c>
       <c r="H21" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I21" s="23">
         <v>9500</v>
@@ -2741,7 +2744,7 @@
         <v>55</v>
       </c>
       <c r="H22" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I22" s="23">
         <v>9500</v>
@@ -2791,7 +2794,7 @@
         <v>51</v>
       </c>
       <c r="H23" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I23" s="23">
         <v>9500</v>
@@ -2841,7 +2844,7 @@
         <v>53</v>
       </c>
       <c r="H24" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I24" s="23">
         <v>9500</v>
@@ -2891,7 +2894,7 @@
         <v>55</v>
       </c>
       <c r="H25" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I25" s="23">
         <v>9500</v>
@@ -2941,7 +2944,7 @@
         <v>51</v>
       </c>
       <c r="H26" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I26" s="23">
         <v>9500</v>
@@ -2991,7 +2994,7 @@
         <v>53</v>
       </c>
       <c r="H27" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I27" s="23">
         <v>9500</v>
@@ -3041,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="H28" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I28" s="23">
         <v>9500</v>
@@ -3091,7 +3094,7 @@
         <v>35</v>
       </c>
       <c r="H29" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I29" s="25">
         <v>9500</v>
@@ -3141,7 +3144,7 @@
         <v>39</v>
       </c>
       <c r="H30" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I30" s="25">
         <v>9500</v>
@@ -3191,7 +3194,7 @@
         <v>42</v>
       </c>
       <c r="H31" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I31" s="25">
         <v>9500</v>
@@ -3241,7 +3244,7 @@
         <v>51</v>
       </c>
       <c r="H32" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I32" s="25">
         <v>9500</v>
@@ -3291,7 +3294,7 @@
         <v>53</v>
       </c>
       <c r="H33" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I33" s="25">
         <v>9500</v>
@@ -3341,7 +3344,7 @@
         <v>55</v>
       </c>
       <c r="H34" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I34" s="25">
         <v>9500</v>
@@ -3391,7 +3394,7 @@
         <v>65</v>
       </c>
       <c r="H35" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I35" s="25">
         <v>9500</v>
@@ -3441,7 +3444,7 @@
         <v>67</v>
       </c>
       <c r="H36" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I36" s="25">
         <v>9500</v>
@@ -3491,7 +3494,7 @@
         <v>69</v>
       </c>
       <c r="H37" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I37" s="25">
         <v>9500</v>
@@ -3541,7 +3544,7 @@
         <v>51</v>
       </c>
       <c r="H38" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I38" s="25">
         <v>9500</v>
@@ -3591,7 +3594,7 @@
         <v>53</v>
       </c>
       <c r="H39" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I39" s="25">
         <v>9500</v>
@@ -3641,7 +3644,7 @@
         <v>55</v>
       </c>
       <c r="H40" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I40" s="25">
         <v>9500</v>
@@ -3685,13 +3688,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H41" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I41" s="25">
         <v>9600</v>
@@ -3735,13 +3738,13 @@
         <v>2</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H42" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I42" s="25">
         <v>9600</v>
@@ -3785,13 +3788,13 @@
         <v>3</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H43" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I43" s="25">
         <v>9600</v>
@@ -3835,13 +3838,13 @@
         <v>1</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H44" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I44" s="25">
         <v>9600</v>
@@ -3885,13 +3888,13 @@
         <v>2</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H45" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I45" s="25">
         <v>9600</v>
@@ -3935,13 +3938,13 @@
         <v>3</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H46" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I46" s="25">
         <v>9600</v>
@@ -3985,13 +3988,13 @@
         <v>1</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H47" s="14">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I47" s="25">
         <v>9600</v>
@@ -4035,13 +4038,13 @@
         <v>2</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H48" s="14">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="I48" s="25">
         <v>9600</v>
@@ -4085,13 +4088,13 @@
         <v>3</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H49" s="28">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="I49" s="25">
         <v>9600</v>
@@ -4118,165 +4121,165 @@
       <c r="S49" s="35"/>
       <c r="T49" s="35"/>
     </row>
-    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B50" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E50" s="40">
-        <v>10</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="42" t="s">
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A50" s="29">
+        <v>1036001</v>
+      </c>
+      <c r="B50" s="30">
+        <v>103600</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="32">
+        <v>103600001</v>
+      </c>
+      <c r="E50" s="31">
+        <v>1</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="43">
-        <v>0</v>
-      </c>
-      <c r="I50" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J50" s="45">
-        <v>0</v>
-      </c>
-      <c r="K50" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="46">
-        <v>0</v>
-      </c>
-      <c r="M50" s="44" t="s">
+      <c r="H50" s="28">
+        <v>10000000</v>
+      </c>
+      <c r="I50" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J50" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K50" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="33">
+        <v>100</v>
+      </c>
+      <c r="M50" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="34">
+        <v>0</v>
+      </c>
+      <c r="O50" s="34"/>
+      <c r="P50" s="34"/>
+      <c r="Q50" s="34"/>
+      <c r="R50" s="34"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+    </row>
+    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A51" s="29">
+        <v>1036002</v>
+      </c>
+      <c r="B51" s="30">
+        <v>103600</v>
+      </c>
+      <c r="C51" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-    </row>
-    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A51" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B51" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E51" s="40">
-        <v>11</v>
-      </c>
-      <c r="F51" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="G51" s="42" t="s">
+      <c r="D51" s="32">
+        <v>103600001</v>
+      </c>
+      <c r="E51" s="31">
+        <v>2</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H51" s="43">
-        <v>0</v>
-      </c>
-      <c r="I51" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J51" s="45">
-        <v>0</v>
-      </c>
-      <c r="K51" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="46">
-        <v>0</v>
-      </c>
-      <c r="M51" s="44" t="s">
+      <c r="H51" s="28">
+        <v>100000000</v>
+      </c>
+      <c r="I51" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J51" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K51" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="33">
+        <v>100</v>
+      </c>
+      <c r="M51" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N51" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="44"/>
-      <c r="T51" s="44"/>
-    </row>
-    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A52" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B52" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E52" s="40">
-        <v>12</v>
-      </c>
-      <c r="F52" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" s="42" t="s">
+      <c r="N51" s="34">
+        <v>0</v>
+      </c>
+      <c r="O51" s="34"/>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35"/>
+    </row>
+    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A52" s="29">
+        <v>1036003</v>
+      </c>
+      <c r="B52" s="30">
+        <v>103600</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="32">
+        <v>103600001</v>
+      </c>
+      <c r="E52" s="31">
+        <v>3</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="48">
-        <v>0</v>
-      </c>
-      <c r="I52" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J52" s="45">
-        <v>0</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="46">
-        <v>0</v>
-      </c>
-      <c r="M52" s="44" t="s">
+      <c r="H52" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I52" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J52" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K52" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="33">
+        <v>100</v>
+      </c>
+      <c r="M52" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N52" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="44"/>
-      <c r="T52" s="44"/>
+      <c r="N52" s="34">
+        <v>0</v>
+      </c>
+      <c r="O52" s="34"/>
+      <c r="P52" s="34"/>
+      <c r="Q52" s="34"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="36">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B53" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D53" s="39">
         <v>100100026</v>
@@ -4284,49 +4287,49 @@
       <c r="E53" s="40">
         <v>10</v>
       </c>
-      <c r="F53" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G53" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="H53" s="43">
-        <v>0</v>
-      </c>
-      <c r="I53" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J53" s="45">
-        <v>0</v>
-      </c>
-      <c r="K53" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L53" s="49">
-        <v>0</v>
-      </c>
-      <c r="M53" s="44" t="s">
+      <c r="F53" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="41">
+        <v>0</v>
+      </c>
+      <c r="I53" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J53" s="43">
+        <v>0</v>
+      </c>
+      <c r="K53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="44">
+        <v>0</v>
+      </c>
+      <c r="M53" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N53" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="44"/>
-      <c r="T53" s="44"/>
+      <c r="N53" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="46"/>
+      <c r="R53" s="46"/>
+      <c r="S53" s="42"/>
+      <c r="T53" s="42"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="36">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B54" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D54" s="39">
         <v>100100026</v>
@@ -4334,49 +4337,49 @@
       <c r="E54" s="40">
         <v>11</v>
       </c>
-      <c r="F54" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="H54" s="43">
-        <v>0</v>
-      </c>
-      <c r="I54" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J54" s="45">
-        <v>0</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L54" s="49">
-        <v>0</v>
-      </c>
-      <c r="M54" s="44" t="s">
+      <c r="F54" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="41">
+        <v>0</v>
+      </c>
+      <c r="I54" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J54" s="43">
+        <v>0</v>
+      </c>
+      <c r="K54" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="44">
+        <v>0</v>
+      </c>
+      <c r="M54" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N54" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="44"/>
-      <c r="T54" s="44"/>
+      <c r="N54" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O54" s="46"/>
+      <c r="P54" s="46"/>
+      <c r="Q54" s="46"/>
+      <c r="R54" s="46"/>
+      <c r="S54" s="42"/>
+      <c r="T54" s="42"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="36">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B55" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D55" s="39">
         <v>100100026</v>
@@ -4384,49 +4387,49 @@
       <c r="E55" s="40">
         <v>12</v>
       </c>
-      <c r="F55" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G55" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="H55" s="48">
-        <v>0</v>
-      </c>
-      <c r="I55" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J55" s="45">
-        <v>0</v>
-      </c>
-      <c r="K55" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="49">
-        <v>0</v>
-      </c>
-      <c r="M55" s="44" t="s">
+      <c r="F55" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="47">
+        <v>0</v>
+      </c>
+      <c r="I55" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J55" s="43">
+        <v>0</v>
+      </c>
+      <c r="K55" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="44">
+        <v>0</v>
+      </c>
+      <c r="M55" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N55" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="41"/>
-      <c r="R55" s="41"/>
-      <c r="S55" s="44"/>
-      <c r="T55" s="44"/>
+      <c r="N55" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O55" s="46"/>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="46"/>
+      <c r="R55" s="46"/>
+      <c r="S55" s="42"/>
+      <c r="T55" s="42"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="36">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B56" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D56" s="39">
         <v>100100026</v>
@@ -4434,49 +4437,49 @@
       <c r="E56" s="40">
         <v>10</v>
       </c>
-      <c r="F56" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G56" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="H56" s="43">
-        <v>0</v>
-      </c>
-      <c r="I56" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J56" s="45">
-        <v>0</v>
-      </c>
-      <c r="K56" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="46">
-        <v>0</v>
-      </c>
-      <c r="M56" s="44" t="s">
+      <c r="F56" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="41">
+        <v>0</v>
+      </c>
+      <c r="I56" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J56" s="43">
+        <v>0</v>
+      </c>
+      <c r="K56" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="48">
+        <v>0</v>
+      </c>
+      <c r="M56" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N56" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O56" s="41"/>
-      <c r="P56" s="41"/>
-      <c r="Q56" s="41"/>
-      <c r="R56" s="41"/>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
+      <c r="N56" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O56" s="46"/>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="46"/>
+      <c r="R56" s="46"/>
+      <c r="S56" s="42"/>
+      <c r="T56" s="42"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="36">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B57" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D57" s="39">
         <v>100100026</v>
@@ -4484,49 +4487,49 @@
       <c r="E57" s="40">
         <v>11</v>
       </c>
-      <c r="F57" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G57" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H57" s="43">
-        <v>0</v>
-      </c>
-      <c r="I57" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J57" s="45">
-        <v>0</v>
-      </c>
-      <c r="K57" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L57" s="46">
-        <v>0</v>
-      </c>
-      <c r="M57" s="44" t="s">
+      <c r="F57" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H57" s="41">
+        <v>0</v>
+      </c>
+      <c r="I57" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J57" s="43">
+        <v>0</v>
+      </c>
+      <c r="K57" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="48">
+        <v>0</v>
+      </c>
+      <c r="M57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N57" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O57" s="41"/>
-      <c r="P57" s="41"/>
-      <c r="Q57" s="41"/>
-      <c r="R57" s="41"/>
-      <c r="S57" s="44"/>
-      <c r="T57" s="44"/>
+      <c r="N57" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O57" s="46"/>
+      <c r="P57" s="46"/>
+      <c r="Q57" s="46"/>
+      <c r="R57" s="46"/>
+      <c r="S57" s="42"/>
+      <c r="T57" s="42"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="36">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B58" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D58" s="39">
         <v>100100026</v>
@@ -4534,1839 +4537,2139 @@
       <c r="E58" s="40">
         <v>12</v>
       </c>
-      <c r="F58" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G58" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="H58" s="48">
-        <v>0</v>
-      </c>
-      <c r="I58" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J58" s="45">
-        <v>0</v>
-      </c>
-      <c r="K58" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L58" s="46">
-        <v>0</v>
-      </c>
-      <c r="M58" s="44" t="s">
+      <c r="F58" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H58" s="47">
+        <v>0</v>
+      </c>
+      <c r="I58" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J58" s="43">
+        <v>0</v>
+      </c>
+      <c r="K58" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="48">
+        <v>0</v>
+      </c>
+      <c r="M58" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N58" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O58" s="41"/>
-      <c r="P58" s="41"/>
-      <c r="Q58" s="41"/>
-      <c r="R58" s="41"/>
-      <c r="S58" s="44"/>
-      <c r="T58" s="44"/>
-    </row>
-    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N58" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O58" s="46"/>
+      <c r="P58" s="46"/>
+      <c r="Q58" s="46"/>
+      <c r="R58" s="46"/>
+      <c r="S58" s="42"/>
+      <c r="T58" s="42"/>
+    </row>
+    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A59" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B59" s="50">
-        <v>101200</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D59" s="51">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B59" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59" s="39">
+        <v>100100026</v>
       </c>
       <c r="E59" s="40">
         <v>10</v>
       </c>
-      <c r="F59" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="H59" s="43">
-        <v>0</v>
-      </c>
-      <c r="I59" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J59" s="45">
-        <v>0</v>
-      </c>
-      <c r="K59" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="49">
-        <v>0</v>
-      </c>
-      <c r="M59" s="45" t="s">
+      <c r="F59" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H59" s="41">
+        <v>0</v>
+      </c>
+      <c r="I59" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J59" s="43">
+        <v>0</v>
+      </c>
+      <c r="K59" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="44">
+        <v>0</v>
+      </c>
+      <c r="M59" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N59" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O59" s="47"/>
-      <c r="P59" s="47"/>
-      <c r="Q59" s="47"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="45"/>
-      <c r="T59" s="45"/>
-    </row>
-    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N59" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O59" s="46"/>
+      <c r="P59" s="46"/>
+      <c r="Q59" s="46"/>
+      <c r="R59" s="46"/>
+      <c r="S59" s="42"/>
+      <c r="T59" s="42"/>
+    </row>
+    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A60" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B60" s="50">
-        <v>101200</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D60" s="51">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B60" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C60" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="39">
+        <v>100100026</v>
       </c>
       <c r="E60" s="40">
         <v>11</v>
       </c>
-      <c r="F60" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="G60" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="43">
-        <v>0</v>
-      </c>
-      <c r="I60" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J60" s="45">
-        <v>0</v>
-      </c>
-      <c r="K60" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="49">
-        <v>0</v>
-      </c>
-      <c r="M60" s="45" t="s">
+      <c r="F60" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H60" s="41">
+        <v>0</v>
+      </c>
+      <c r="I60" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J60" s="43">
+        <v>0</v>
+      </c>
+      <c r="K60" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="44">
+        <v>0</v>
+      </c>
+      <c r="M60" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N60" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O60" s="47"/>
-      <c r="P60" s="47"/>
-      <c r="Q60" s="47"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="45"/>
-      <c r="T60" s="45"/>
-    </row>
-    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N60" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O60" s="46"/>
+      <c r="P60" s="46"/>
+      <c r="Q60" s="46"/>
+      <c r="R60" s="46"/>
+      <c r="S60" s="42"/>
+      <c r="T60" s="42"/>
+    </row>
+    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A61" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B61" s="50">
-        <v>101200</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D61" s="51">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B61" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" s="39">
+        <v>100100026</v>
       </c>
       <c r="E61" s="40">
         <v>12</v>
       </c>
-      <c r="F61" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="G61" s="52" t="s">
-        <v>46</v>
-      </c>
-      <c r="H61" s="48">
-        <v>0</v>
-      </c>
-      <c r="I61" s="45">
-        <v>9500</v>
-      </c>
-      <c r="J61" s="45">
-        <v>0</v>
-      </c>
-      <c r="K61" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="49">
-        <v>0</v>
-      </c>
-      <c r="M61" s="45" t="s">
+      <c r="F61" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="47">
+        <v>0</v>
+      </c>
+      <c r="I61" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J61" s="43">
+        <v>0</v>
+      </c>
+      <c r="K61" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="44">
+        <v>0</v>
+      </c>
+      <c r="M61" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N61" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O61" s="47"/>
-      <c r="P61" s="47"/>
-      <c r="Q61" s="47"/>
-      <c r="R61" s="47"/>
-      <c r="S61" s="45"/>
-      <c r="T61" s="45"/>
-    </row>
-    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N61" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O61" s="46"/>
+      <c r="P61" s="46"/>
+      <c r="Q61" s="46"/>
+      <c r="R61" s="46"/>
+      <c r="S61" s="42"/>
+      <c r="T61" s="42"/>
+    </row>
+    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A62" s="36">
-        <v>10140010</v>
-      </c>
-      <c r="B62" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C62" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B62" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="50">
+        <v>101200026</v>
       </c>
       <c r="E62" s="40">
         <v>10</v>
       </c>
-      <c r="F62" s="41" t="s">
+      <c r="F62" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="G62" s="42" t="s">
+      <c r="G62" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H62" s="43">
-        <v>0</v>
-      </c>
-      <c r="I62" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J62" s="45">
-        <v>0</v>
-      </c>
-      <c r="K62" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="46">
-        <v>0</v>
-      </c>
-      <c r="M62" s="44" t="s">
+      <c r="H62" s="41">
+        <v>0</v>
+      </c>
+      <c r="I62" s="43">
+        <v>9500</v>
+      </c>
+      <c r="J62" s="43">
+        <v>0</v>
+      </c>
+      <c r="K62" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="48">
+        <v>0</v>
+      </c>
+      <c r="M62" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="N62" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O62" s="41"/>
-      <c r="P62" s="41"/>
-      <c r="Q62" s="41"/>
-      <c r="R62" s="41"/>
-      <c r="S62" s="44"/>
-      <c r="T62" s="44"/>
-    </row>
-    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N62" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O62" s="45"/>
+      <c r="P62" s="45"/>
+      <c r="Q62" s="45"/>
+      <c r="R62" s="45"/>
+      <c r="S62" s="43"/>
+      <c r="T62" s="43"/>
+    </row>
+    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="36">
-        <v>10140011</v>
-      </c>
-      <c r="B63" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C63" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B63" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="50">
+        <v>101200026</v>
       </c>
       <c r="E63" s="40">
         <v>11</v>
       </c>
-      <c r="F63" s="41" t="s">
+      <c r="F63" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G63" s="42" t="s">
+      <c r="G63" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="43">
-        <v>0</v>
-      </c>
-      <c r="I63" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J63" s="45">
-        <v>0</v>
-      </c>
-      <c r="K63" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="46">
-        <v>0</v>
-      </c>
-      <c r="M63" s="44" t="s">
+      <c r="H63" s="41">
+        <v>0</v>
+      </c>
+      <c r="I63" s="43">
+        <v>9500</v>
+      </c>
+      <c r="J63" s="43">
+        <v>0</v>
+      </c>
+      <c r="K63" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="48">
+        <v>0</v>
+      </c>
+      <c r="M63" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="N63" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O63" s="41"/>
-      <c r="P63" s="41"/>
-      <c r="Q63" s="41"/>
-      <c r="R63" s="41"/>
-      <c r="S63" s="44"/>
-      <c r="T63" s="44"/>
-    </row>
-    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="N63" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O63" s="45"/>
+      <c r="P63" s="45"/>
+      <c r="Q63" s="45"/>
+      <c r="R63" s="45"/>
+      <c r="S63" s="43"/>
+      <c r="T63" s="43"/>
+    </row>
+    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="36">
-        <v>10140012</v>
-      </c>
-      <c r="B64" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C64" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B64" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C64" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="50">
+        <v>101200026</v>
       </c>
       <c r="E64" s="40">
         <v>12</v>
       </c>
-      <c r="F64" s="41" t="s">
+      <c r="F64" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G64" s="42" t="s">
+      <c r="G64" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H64" s="48">
-        <v>0</v>
-      </c>
-      <c r="I64" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J64" s="45">
-        <v>0</v>
-      </c>
-      <c r="K64" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="46">
-        <v>0</v>
-      </c>
-      <c r="M64" s="44" t="s">
+      <c r="H64" s="47">
+        <v>0</v>
+      </c>
+      <c r="I64" s="43">
+        <v>9500</v>
+      </c>
+      <c r="J64" s="43">
+        <v>0</v>
+      </c>
+      <c r="K64" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="48">
+        <v>0</v>
+      </c>
+      <c r="M64" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="N64" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O64" s="41"/>
-      <c r="P64" s="41"/>
-      <c r="Q64" s="41"/>
-      <c r="R64" s="41"/>
-      <c r="S64" s="44"/>
-      <c r="T64" s="44"/>
+      <c r="N64" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O64" s="45"/>
+      <c r="P64" s="45"/>
+      <c r="Q64" s="45"/>
+      <c r="R64" s="45"/>
+      <c r="S64" s="43"/>
+      <c r="T64" s="43"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="36">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B65" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E65" s="40">
         <v>10</v>
       </c>
-      <c r="F65" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G65" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="H65" s="43">
-        <v>0</v>
-      </c>
-      <c r="I65" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J65" s="45">
-        <v>0</v>
-      </c>
-      <c r="K65" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L65" s="46">
-        <v>0</v>
-      </c>
-      <c r="M65" s="44" t="s">
+      <c r="F65" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65" s="41">
+        <v>0</v>
+      </c>
+      <c r="I65" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J65" s="43">
+        <v>0</v>
+      </c>
+      <c r="K65" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="44">
+        <v>0</v>
+      </c>
+      <c r="M65" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N65" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O65" s="41"/>
-      <c r="P65" s="41"/>
-      <c r="Q65" s="41"/>
-      <c r="R65" s="41"/>
-      <c r="S65" s="44"/>
-      <c r="T65" s="44"/>
+      <c r="N65" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O65" s="46"/>
+      <c r="P65" s="46"/>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="46"/>
+      <c r="S65" s="42"/>
+      <c r="T65" s="42"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="36">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B66" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E66" s="40">
         <v>11</v>
       </c>
-      <c r="F66" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H66" s="43">
-        <v>0</v>
-      </c>
-      <c r="I66" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J66" s="45">
-        <v>0</v>
-      </c>
-      <c r="K66" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L66" s="46">
-        <v>0</v>
-      </c>
-      <c r="M66" s="44" t="s">
+      <c r="F66" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="41">
+        <v>0</v>
+      </c>
+      <c r="I66" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J66" s="43">
+        <v>0</v>
+      </c>
+      <c r="K66" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="44">
+        <v>0</v>
+      </c>
+      <c r="M66" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N66" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O66" s="41"/>
-      <c r="P66" s="41"/>
-      <c r="Q66" s="41"/>
-      <c r="R66" s="41"/>
-      <c r="S66" s="44"/>
-      <c r="T66" s="44"/>
+      <c r="N66" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O66" s="46"/>
+      <c r="P66" s="46"/>
+      <c r="Q66" s="46"/>
+      <c r="R66" s="46"/>
+      <c r="S66" s="42"/>
+      <c r="T66" s="42"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="36">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B67" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D67" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E67" s="40">
         <v>12</v>
       </c>
-      <c r="F67" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G67" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="H67" s="48">
-        <v>0</v>
-      </c>
-      <c r="I67" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J67" s="45">
-        <v>0</v>
-      </c>
-      <c r="K67" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L67" s="46">
-        <v>0</v>
-      </c>
-      <c r="M67" s="44" t="s">
+      <c r="F67" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H67" s="47">
+        <v>0</v>
+      </c>
+      <c r="I67" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J67" s="43">
+        <v>0</v>
+      </c>
+      <c r="K67" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="44">
+        <v>0</v>
+      </c>
+      <c r="M67" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N67" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O67" s="41"/>
-      <c r="P67" s="41"/>
-      <c r="Q67" s="41"/>
-      <c r="R67" s="41"/>
-      <c r="S67" s="44"/>
-      <c r="T67" s="44"/>
+      <c r="N67" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O67" s="46"/>
+      <c r="P67" s="46"/>
+      <c r="Q67" s="46"/>
+      <c r="R67" s="46"/>
+      <c r="S67" s="42"/>
+      <c r="T67" s="42"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="36">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B68" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D68" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E68" s="40">
         <v>10</v>
       </c>
-      <c r="F68" s="41" t="s">
+      <c r="F68" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G68" s="42" t="s">
+      <c r="G68" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="43">
-        <v>0</v>
-      </c>
-      <c r="I68" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J68" s="45">
-        <v>0</v>
-      </c>
-      <c r="K68" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L68" s="49">
-        <v>0</v>
-      </c>
-      <c r="M68" s="44" t="s">
+      <c r="H68" s="41">
+        <v>0</v>
+      </c>
+      <c r="I68" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J68" s="43">
+        <v>0</v>
+      </c>
+      <c r="K68" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="44">
+        <v>0</v>
+      </c>
+      <c r="M68" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N68" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O68" s="41"/>
-      <c r="P68" s="41"/>
-      <c r="Q68" s="41"/>
-      <c r="R68" s="41"/>
-      <c r="S68" s="44"/>
-      <c r="T68" s="44"/>
+      <c r="N68" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O68" s="46"/>
+      <c r="P68" s="46"/>
+      <c r="Q68" s="46"/>
+      <c r="R68" s="46"/>
+      <c r="S68" s="42"/>
+      <c r="T68" s="42"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="36">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B69" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D69" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E69" s="40">
         <v>11</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="G69" s="42" t="s">
+      <c r="G69" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H69" s="43">
-        <v>0</v>
-      </c>
-      <c r="I69" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J69" s="45">
-        <v>0</v>
-      </c>
-      <c r="K69" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L69" s="49">
-        <v>0</v>
-      </c>
-      <c r="M69" s="44" t="s">
+      <c r="H69" s="41">
+        <v>0</v>
+      </c>
+      <c r="I69" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J69" s="43">
+        <v>0</v>
+      </c>
+      <c r="K69" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="44">
+        <v>0</v>
+      </c>
+      <c r="M69" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N69" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O69" s="41"/>
-      <c r="P69" s="41"/>
-      <c r="Q69" s="41"/>
-      <c r="R69" s="41"/>
-      <c r="S69" s="44"/>
-      <c r="T69" s="44"/>
+      <c r="N69" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O69" s="46"/>
+      <c r="P69" s="46"/>
+      <c r="Q69" s="46"/>
+      <c r="R69" s="46"/>
+      <c r="S69" s="42"/>
+      <c r="T69" s="42"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="36">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B70" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D70" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E70" s="40">
         <v>12</v>
       </c>
-      <c r="F70" s="41" t="s">
+      <c r="F70" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G70" s="42" t="s">
+      <c r="G70" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H70" s="48">
-        <v>0</v>
-      </c>
-      <c r="I70" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J70" s="45">
-        <v>0</v>
-      </c>
-      <c r="K70" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L70" s="49">
-        <v>0</v>
-      </c>
-      <c r="M70" s="44" t="s">
+      <c r="H70" s="47">
+        <v>0</v>
+      </c>
+      <c r="I70" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J70" s="43">
+        <v>0</v>
+      </c>
+      <c r="K70" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="44">
+        <v>0</v>
+      </c>
+      <c r="M70" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N70" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O70" s="41"/>
-      <c r="P70" s="41"/>
-      <c r="Q70" s="41"/>
-      <c r="R70" s="41"/>
-      <c r="S70" s="44"/>
-      <c r="T70" s="44"/>
+      <c r="N70" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O70" s="46"/>
+      <c r="P70" s="46"/>
+      <c r="Q70" s="46"/>
+      <c r="R70" s="46"/>
+      <c r="S70" s="42"/>
+      <c r="T70" s="42"/>
     </row>
     <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="36">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B71" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D71" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E71" s="40">
         <v>10</v>
       </c>
-      <c r="F71" s="41" t="s">
+      <c r="F71" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G71" s="42" t="s">
+      <c r="G71" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H71" s="43">
-        <v>0</v>
-      </c>
-      <c r="I71" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J71" s="45">
-        <v>0</v>
-      </c>
-      <c r="K71" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L71" s="49">
-        <v>0</v>
-      </c>
-      <c r="M71" s="44" t="s">
+      <c r="H71" s="41">
+        <v>0</v>
+      </c>
+      <c r="I71" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J71" s="43">
+        <v>0</v>
+      </c>
+      <c r="K71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="48">
+        <v>0</v>
+      </c>
+      <c r="M71" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N71" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O71" s="41"/>
-      <c r="P71" s="41"/>
-      <c r="Q71" s="41"/>
-      <c r="R71" s="41"/>
-      <c r="S71" s="44"/>
-      <c r="T71" s="44"/>
+      <c r="N71" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O71" s="46"/>
+      <c r="P71" s="46"/>
+      <c r="Q71" s="46"/>
+      <c r="R71" s="46"/>
+      <c r="S71" s="42"/>
+      <c r="T71" s="42"/>
     </row>
     <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="36">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B72" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D72" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E72" s="40">
         <v>11</v>
       </c>
-      <c r="F72" s="41" t="s">
+      <c r="F72" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="G72" s="42" t="s">
+      <c r="G72" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H72" s="43">
-        <v>0</v>
-      </c>
-      <c r="I72" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J72" s="45">
-        <v>0</v>
-      </c>
-      <c r="K72" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L72" s="49">
-        <v>0</v>
-      </c>
-      <c r="M72" s="44" t="s">
+      <c r="H72" s="41">
+        <v>0</v>
+      </c>
+      <c r="I72" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J72" s="43">
+        <v>0</v>
+      </c>
+      <c r="K72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="48">
+        <v>0</v>
+      </c>
+      <c r="M72" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N72" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O72" s="41"/>
-      <c r="P72" s="41"/>
-      <c r="Q72" s="41"/>
-      <c r="R72" s="41"/>
-      <c r="S72" s="44"/>
-      <c r="T72" s="44"/>
+      <c r="N72" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O72" s="46"/>
+      <c r="P72" s="46"/>
+      <c r="Q72" s="46"/>
+      <c r="R72" s="46"/>
+      <c r="S72" s="42"/>
+      <c r="T72" s="42"/>
     </row>
     <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="36">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B73" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E73" s="40">
         <v>12</v>
       </c>
-      <c r="F73" s="41" t="s">
+      <c r="F73" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G73" s="42" t="s">
+      <c r="G73" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H73" s="48">
-        <v>0</v>
-      </c>
-      <c r="I73" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J73" s="45">
-        <v>0</v>
-      </c>
-      <c r="K73" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L73" s="49">
-        <v>0</v>
-      </c>
-      <c r="M73" s="44" t="s">
+      <c r="H73" s="47">
+        <v>0</v>
+      </c>
+      <c r="I73" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J73" s="43">
+        <v>0</v>
+      </c>
+      <c r="K73" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="48">
+        <v>0</v>
+      </c>
+      <c r="M73" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N73" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O73" s="41"/>
-      <c r="P73" s="41"/>
-      <c r="Q73" s="41"/>
-      <c r="R73" s="41"/>
-      <c r="S73" s="44"/>
-      <c r="T73" s="44"/>
+      <c r="N73" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O73" s="46"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="46"/>
+      <c r="R73" s="46"/>
+      <c r="S73" s="42"/>
+      <c r="T73" s="42"/>
     </row>
     <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B74" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E74" s="40">
         <v>10</v>
       </c>
-      <c r="F74" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="G74" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="H74" s="43">
-        <v>0</v>
-      </c>
-      <c r="I74" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J74" s="45">
-        <v>0</v>
-      </c>
-      <c r="K74" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L74" s="49">
-        <v>0</v>
-      </c>
-      <c r="M74" s="44" t="s">
+      <c r="F74" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H74" s="41">
+        <v>0</v>
+      </c>
+      <c r="I74" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J74" s="43">
+        <v>0</v>
+      </c>
+      <c r="K74" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="48">
+        <v>0</v>
+      </c>
+      <c r="M74" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N74" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O74" s="41"/>
-      <c r="P74" s="41"/>
-      <c r="Q74" s="41"/>
-      <c r="R74" s="41"/>
-      <c r="S74" s="44"/>
-      <c r="T74" s="44"/>
+      <c r="N74" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O74" s="46"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="46"/>
+      <c r="R74" s="46"/>
+      <c r="S74" s="42"/>
+      <c r="T74" s="42"/>
     </row>
     <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B75" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E75" s="40">
         <v>11</v>
       </c>
-      <c r="F75" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="G75" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="H75" s="43">
-        <v>0</v>
-      </c>
-      <c r="I75" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J75" s="45">
-        <v>0</v>
-      </c>
-      <c r="K75" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L75" s="49">
-        <v>0</v>
-      </c>
-      <c r="M75" s="44" t="s">
+      <c r="F75" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="41">
+        <v>0</v>
+      </c>
+      <c r="I75" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J75" s="43">
+        <v>0</v>
+      </c>
+      <c r="K75" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="48">
+        <v>0</v>
+      </c>
+      <c r="M75" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N75" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O75" s="41"/>
-      <c r="P75" s="41"/>
-      <c r="Q75" s="41"/>
-      <c r="R75" s="41"/>
-      <c r="S75" s="44"/>
-      <c r="T75" s="44"/>
+      <c r="N75" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O75" s="46"/>
+      <c r="P75" s="46"/>
+      <c r="Q75" s="46"/>
+      <c r="R75" s="46"/>
+      <c r="S75" s="42"/>
+      <c r="T75" s="42"/>
     </row>
     <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B76" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D76" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E76" s="40">
         <v>12</v>
       </c>
-      <c r="F76" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G76" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="H76" s="48">
-        <v>0</v>
-      </c>
-      <c r="I76" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J76" s="45">
-        <v>0</v>
-      </c>
-      <c r="K76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="49">
-        <v>0</v>
-      </c>
-      <c r="M76" s="44" t="s">
+      <c r="F76" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G76" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H76" s="47">
+        <v>0</v>
+      </c>
+      <c r="I76" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J76" s="43">
+        <v>0</v>
+      </c>
+      <c r="K76" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="48">
+        <v>0</v>
+      </c>
+      <c r="M76" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N76" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O76" s="41"/>
-      <c r="P76" s="41"/>
-      <c r="Q76" s="41"/>
-      <c r="R76" s="41"/>
-      <c r="S76" s="44"/>
-      <c r="T76" s="44"/>
+      <c r="N76" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O76" s="46"/>
+      <c r="P76" s="46"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="46"/>
+      <c r="S76" s="42"/>
+      <c r="T76" s="42"/>
     </row>
     <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B77" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D77" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
       </c>
-      <c r="F77" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G77" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="H77" s="48">
-        <v>0</v>
-      </c>
-      <c r="I77" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J77" s="45">
-        <v>0</v>
-      </c>
-      <c r="K77" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L77" s="49">
-        <v>0</v>
-      </c>
-      <c r="M77" s="44" t="s">
+      <c r="F77" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G77" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H77" s="41">
+        <v>0</v>
+      </c>
+      <c r="I77" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J77" s="43">
+        <v>0</v>
+      </c>
+      <c r="K77" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="48">
+        <v>0</v>
+      </c>
+      <c r="M77" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N77" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O77" s="41"/>
-      <c r="P77" s="41"/>
-      <c r="Q77" s="41"/>
-      <c r="R77" s="41"/>
-      <c r="S77" s="44"/>
-      <c r="T77" s="44"/>
+      <c r="N77" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O77" s="46"/>
+      <c r="P77" s="46"/>
+      <c r="Q77" s="46"/>
+      <c r="R77" s="46"/>
+      <c r="S77" s="42"/>
+      <c r="T77" s="42"/>
     </row>
     <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B78" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D78" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
       </c>
-      <c r="F78" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G78" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" s="48">
-        <v>0</v>
-      </c>
-      <c r="I78" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J78" s="45">
-        <v>0</v>
-      </c>
-      <c r="K78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L78" s="49">
-        <v>0</v>
-      </c>
-      <c r="M78" s="44" t="s">
+      <c r="F78" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G78" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78" s="41">
+        <v>0</v>
+      </c>
+      <c r="I78" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J78" s="43">
+        <v>0</v>
+      </c>
+      <c r="K78" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="48">
+        <v>0</v>
+      </c>
+      <c r="M78" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N78" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O78" s="41"/>
-      <c r="P78" s="41"/>
-      <c r="Q78" s="41"/>
-      <c r="R78" s="41"/>
-      <c r="S78" s="44"/>
-      <c r="T78" s="44"/>
+      <c r="N78" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="46"/>
+      <c r="R78" s="46"/>
+      <c r="S78" s="42"/>
+      <c r="T78" s="42"/>
     </row>
     <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B79" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D79" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
       </c>
-      <c r="F79" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G79" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="H79" s="48">
-        <v>0</v>
-      </c>
-      <c r="I79" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J79" s="45">
-        <v>0</v>
-      </c>
-      <c r="K79" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L79" s="49">
-        <v>0</v>
-      </c>
-      <c r="M79" s="44" t="s">
+      <c r="F79" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H79" s="47">
+        <v>0</v>
+      </c>
+      <c r="I79" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J79" s="43">
+        <v>0</v>
+      </c>
+      <c r="K79" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="48">
+        <v>0</v>
+      </c>
+      <c r="M79" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N79" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O79" s="41"/>
-      <c r="P79" s="41"/>
-      <c r="Q79" s="41"/>
-      <c r="R79" s="41"/>
-      <c r="S79" s="44"/>
-      <c r="T79" s="44"/>
+      <c r="N79" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O79" s="46"/>
+      <c r="P79" s="46"/>
+      <c r="Q79" s="46"/>
+      <c r="R79" s="46"/>
+      <c r="S79" s="42"/>
+      <c r="T79" s="42"/>
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B80" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D80" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E80" s="40">
         <v>10</v>
       </c>
-      <c r="F80" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G80" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="H80" s="48">
-        <v>0</v>
-      </c>
-      <c r="I80" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J80" s="45">
-        <v>0</v>
-      </c>
-      <c r="K80" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L80" s="49">
-        <v>0</v>
-      </c>
-      <c r="M80" s="44" t="s">
+      <c r="F80" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G80" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H80" s="47">
+        <v>0</v>
+      </c>
+      <c r="I80" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J80" s="43">
+        <v>0</v>
+      </c>
+      <c r="K80" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="48">
+        <v>0</v>
+      </c>
+      <c r="M80" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N80" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O80" s="41"/>
-      <c r="P80" s="41"/>
-      <c r="Q80" s="41"/>
-      <c r="R80" s="41"/>
-      <c r="S80" s="44"/>
-      <c r="T80" s="44"/>
+      <c r="N80" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O80" s="46"/>
+      <c r="P80" s="46"/>
+      <c r="Q80" s="46"/>
+      <c r="R80" s="46"/>
+      <c r="S80" s="42"/>
+      <c r="T80" s="42"/>
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B81" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D81" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E81" s="40">
         <v>11</v>
       </c>
-      <c r="F81" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G81" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H81" s="48">
-        <v>0</v>
-      </c>
-      <c r="I81" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J81" s="45">
-        <v>0</v>
-      </c>
-      <c r="K81" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L81" s="49">
-        <v>0</v>
-      </c>
-      <c r="M81" s="44" t="s">
+      <c r="F81" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="47">
+        <v>0</v>
+      </c>
+      <c r="I81" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J81" s="43">
+        <v>0</v>
+      </c>
+      <c r="K81" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="48">
+        <v>0</v>
+      </c>
+      <c r="M81" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N81" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O81" s="41"/>
-      <c r="P81" s="41"/>
-      <c r="Q81" s="41"/>
-      <c r="R81" s="41"/>
-      <c r="S81" s="44"/>
-      <c r="T81" s="44"/>
+      <c r="N81" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O81" s="46"/>
+      <c r="P81" s="46"/>
+      <c r="Q81" s="46"/>
+      <c r="R81" s="46"/>
+      <c r="S81" s="42"/>
+      <c r="T81" s="42"/>
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B82" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D82" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E82" s="40">
         <v>12</v>
       </c>
-      <c r="F82" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G82" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="H82" s="48">
-        <v>0</v>
-      </c>
-      <c r="I82" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J82" s="45">
-        <v>0</v>
-      </c>
-      <c r="K82" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L82" s="49">
-        <v>0</v>
-      </c>
-      <c r="M82" s="44" t="s">
+      <c r="F82" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" s="47">
+        <v>0</v>
+      </c>
+      <c r="I82" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J82" s="43">
+        <v>0</v>
+      </c>
+      <c r="K82" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="48">
+        <v>0</v>
+      </c>
+      <c r="M82" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N82" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O82" s="41"/>
-      <c r="P82" s="41"/>
-      <c r="Q82" s="41"/>
-      <c r="R82" s="41"/>
-      <c r="S82" s="44"/>
-      <c r="T82" s="44"/>
+      <c r="N82" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O82" s="46"/>
+      <c r="P82" s="46"/>
+      <c r="Q82" s="46"/>
+      <c r="R82" s="46"/>
+      <c r="S82" s="42"/>
+      <c r="T82" s="42"/>
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B83" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D83" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
       </c>
-      <c r="F83" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G83" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="H83" s="48">
-        <v>0</v>
-      </c>
-      <c r="I83" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J83" s="45">
-        <v>0</v>
-      </c>
-      <c r="K83" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L83" s="49">
-        <v>0</v>
-      </c>
-      <c r="M83" s="44" t="s">
+      <c r="F83" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H83" s="47">
+        <v>0</v>
+      </c>
+      <c r="I83" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J83" s="43">
+        <v>0</v>
+      </c>
+      <c r="K83" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="48">
+        <v>0</v>
+      </c>
+      <c r="M83" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N83" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O83" s="41"/>
-      <c r="P83" s="41"/>
-      <c r="Q83" s="41"/>
-      <c r="R83" s="41"/>
-      <c r="S83" s="44"/>
-      <c r="T83" s="44"/>
+      <c r="N83" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O83" s="46"/>
+      <c r="P83" s="46"/>
+      <c r="Q83" s="46"/>
+      <c r="R83" s="46"/>
+      <c r="S83" s="42"/>
+      <c r="T83" s="42"/>
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B84" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D84" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
       </c>
-      <c r="F84" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G84" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H84" s="48">
-        <v>0</v>
-      </c>
-      <c r="I84" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J84" s="45">
-        <v>0</v>
-      </c>
-      <c r="K84" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L84" s="49">
-        <v>0</v>
-      </c>
-      <c r="M84" s="44" t="s">
+      <c r="F84" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G84" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H84" s="47">
+        <v>0</v>
+      </c>
+      <c r="I84" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J84" s="43">
+        <v>0</v>
+      </c>
+      <c r="K84" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="48">
+        <v>0</v>
+      </c>
+      <c r="M84" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N84" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O84" s="41"/>
-      <c r="P84" s="41"/>
-      <c r="Q84" s="41"/>
-      <c r="R84" s="41"/>
-      <c r="S84" s="44"/>
-      <c r="T84" s="44"/>
+      <c r="N84" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O84" s="46"/>
+      <c r="P84" s="46"/>
+      <c r="Q84" s="46"/>
+      <c r="R84" s="46"/>
+      <c r="S84" s="42"/>
+      <c r="T84" s="42"/>
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B85" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D85" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
       </c>
-      <c r="F85" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G85" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="H85" s="48">
-        <v>0</v>
-      </c>
-      <c r="I85" s="44">
-        <v>9500</v>
-      </c>
-      <c r="J85" s="45">
-        <v>0</v>
-      </c>
-      <c r="K85" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L85" s="49">
-        <v>0</v>
-      </c>
-      <c r="M85" s="44" t="s">
+      <c r="F85" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H85" s="47">
+        <v>0</v>
+      </c>
+      <c r="I85" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J85" s="43">
+        <v>0</v>
+      </c>
+      <c r="K85" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="48">
+        <v>0</v>
+      </c>
+      <c r="M85" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N85" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O85" s="41"/>
-      <c r="P85" s="41"/>
-      <c r="Q85" s="41"/>
-      <c r="R85" s="41"/>
-      <c r="S85" s="44"/>
-      <c r="T85" s="44"/>
+      <c r="N85" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O85" s="46"/>
+      <c r="P85" s="46"/>
+      <c r="Q85" s="46"/>
+      <c r="R85" s="46"/>
+      <c r="S85" s="42"/>
+      <c r="T85" s="42"/>
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B86" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D86" s="39">
-        <v>103400001</v>
+        <v>102300001</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
       </c>
-      <c r="F86" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="G86" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="48">
-        <v>0</v>
-      </c>
-      <c r="I86" s="44">
-        <v>9600</v>
-      </c>
-      <c r="J86" s="45">
-        <v>0</v>
-      </c>
-      <c r="K86" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L86" s="49">
-        <v>0</v>
-      </c>
-      <c r="M86" s="44" t="s">
+      <c r="F86" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H86" s="47">
+        <v>0</v>
+      </c>
+      <c r="I86" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J86" s="43">
+        <v>0</v>
+      </c>
+      <c r="K86" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="48">
+        <v>0</v>
+      </c>
+      <c r="M86" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N86" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O86" s="41"/>
-      <c r="P86" s="41"/>
-      <c r="Q86" s="41"/>
-      <c r="R86" s="41"/>
-      <c r="S86" s="44"/>
-      <c r="T86" s="44"/>
+      <c r="N86" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O86" s="46"/>
+      <c r="P86" s="46"/>
+      <c r="Q86" s="46"/>
+      <c r="R86" s="46"/>
+      <c r="S86" s="42"/>
+      <c r="T86" s="42"/>
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B87" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D87" s="39">
-        <v>103400001</v>
+        <v>102300001</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
       </c>
-      <c r="F87" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G87" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="H87" s="48">
-        <v>0</v>
-      </c>
-      <c r="I87" s="44">
-        <v>9600</v>
-      </c>
-      <c r="J87" s="45">
-        <v>0</v>
-      </c>
-      <c r="K87" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L87" s="49">
-        <v>0</v>
-      </c>
-      <c r="M87" s="44" t="s">
+      <c r="F87" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="47">
+        <v>0</v>
+      </c>
+      <c r="I87" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J87" s="43">
+        <v>0</v>
+      </c>
+      <c r="K87" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="48">
+        <v>0</v>
+      </c>
+      <c r="M87" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N87" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O87" s="41"/>
-      <c r="P87" s="41"/>
-      <c r="Q87" s="41"/>
-      <c r="R87" s="41"/>
-      <c r="S87" s="44"/>
-      <c r="T87" s="44"/>
+      <c r="N87" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O87" s="46"/>
+      <c r="P87" s="46"/>
+      <c r="Q87" s="46"/>
+      <c r="R87" s="46"/>
+      <c r="S87" s="42"/>
+      <c r="T87" s="42"/>
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B88" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D88" s="39">
-        <v>103400001</v>
+        <v>102300001</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
       </c>
-      <c r="F88" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G88" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H88" s="48">
-        <v>0</v>
-      </c>
-      <c r="I88" s="44">
-        <v>9600</v>
-      </c>
-      <c r="J88" s="45">
-        <v>0</v>
-      </c>
-      <c r="K88" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L88" s="49">
-        <v>0</v>
-      </c>
-      <c r="M88" s="44" t="s">
+      <c r="F88" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H88" s="47">
+        <v>0</v>
+      </c>
+      <c r="I88" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J88" s="43">
+        <v>0</v>
+      </c>
+      <c r="K88" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="48">
+        <v>0</v>
+      </c>
+      <c r="M88" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N88" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O88" s="41"/>
-      <c r="P88" s="41"/>
-      <c r="Q88" s="41"/>
-      <c r="R88" s="41"/>
-      <c r="S88" s="44"/>
-      <c r="T88" s="44"/>
+      <c r="N88" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O88" s="46"/>
+      <c r="P88" s="46"/>
+      <c r="Q88" s="46"/>
+      <c r="R88" s="46"/>
+      <c r="S88" s="42"/>
+      <c r="T88" s="42"/>
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B89" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D89" s="39">
-        <v>103500001</v>
+        <v>103400001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
-      <c r="F89" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="G89" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="48">
-        <v>0</v>
-      </c>
-      <c r="I89" s="44">
+      <c r="F89" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G89" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H89" s="47">
+        <v>0</v>
+      </c>
+      <c r="I89" s="42">
         <v>9600</v>
       </c>
-      <c r="J89" s="45">
-        <v>0</v>
-      </c>
-      <c r="K89" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L89" s="49">
-        <v>0</v>
-      </c>
-      <c r="M89" s="44" t="s">
+      <c r="J89" s="43">
+        <v>0</v>
+      </c>
+      <c r="K89" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="48">
+        <v>0</v>
+      </c>
+      <c r="M89" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N89" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O89" s="41"/>
-      <c r="P89" s="41"/>
-      <c r="Q89" s="41"/>
-      <c r="R89" s="41"/>
-      <c r="S89" s="44"/>
-      <c r="T89" s="44"/>
+      <c r="N89" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O89" s="46"/>
+      <c r="P89" s="46"/>
+      <c r="Q89" s="46"/>
+      <c r="R89" s="46"/>
+      <c r="S89" s="42"/>
+      <c r="T89" s="42"/>
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B90" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D90" s="39">
-        <v>103500001</v>
+        <v>103400001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
-      <c r="F90" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G90" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="H90" s="48">
-        <v>0</v>
-      </c>
-      <c r="I90" s="44">
+      <c r="F90" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G90" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H90" s="47">
+        <v>0</v>
+      </c>
+      <c r="I90" s="42">
         <v>9600</v>
       </c>
-      <c r="J90" s="45">
-        <v>0</v>
-      </c>
-      <c r="K90" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L90" s="49">
-        <v>0</v>
-      </c>
-      <c r="M90" s="44" t="s">
+      <c r="J90" s="43">
+        <v>0</v>
+      </c>
+      <c r="K90" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="48">
+        <v>0</v>
+      </c>
+      <c r="M90" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N90" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O90" s="41"/>
-      <c r="P90" s="41"/>
-      <c r="Q90" s="41"/>
-      <c r="R90" s="41"/>
-      <c r="S90" s="44"/>
-      <c r="T90" s="44"/>
+      <c r="N90" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O90" s="46"/>
+      <c r="P90" s="46"/>
+      <c r="Q90" s="46"/>
+      <c r="R90" s="46"/>
+      <c r="S90" s="42"/>
+      <c r="T90" s="42"/>
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B91" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D91" s="39">
-        <v>103500001</v>
+        <v>103400001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
-      <c r="F91" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G91" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H91" s="48">
-        <v>0</v>
-      </c>
-      <c r="I91" s="44">
+      <c r="F91" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G91" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H91" s="47">
+        <v>0</v>
+      </c>
+      <c r="I91" s="42">
         <v>9600</v>
       </c>
-      <c r="J91" s="45">
-        <v>0</v>
-      </c>
-      <c r="K91" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L91" s="49">
-        <v>0</v>
-      </c>
-      <c r="M91" s="44" t="s">
+      <c r="J91" s="43">
+        <v>0</v>
+      </c>
+      <c r="K91" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="48">
+        <v>0</v>
+      </c>
+      <c r="M91" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N91" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O91" s="41"/>
-      <c r="P91" s="41"/>
-      <c r="Q91" s="41"/>
-      <c r="R91" s="41"/>
-      <c r="S91" s="44"/>
-      <c r="T91" s="44"/>
+      <c r="N91" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O91" s="46"/>
+      <c r="P91" s="46"/>
+      <c r="Q91" s="46"/>
+      <c r="R91" s="46"/>
+      <c r="S91" s="42"/>
+      <c r="T91" s="42"/>
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B92" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D92" s="39">
-        <v>103501001</v>
+        <v>103500001</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
-      <c r="F92" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="G92" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="H92" s="48">
-        <v>0</v>
-      </c>
-      <c r="I92" s="44">
+      <c r="F92" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G92" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H92" s="47">
+        <v>0</v>
+      </c>
+      <c r="I92" s="42">
         <v>9600</v>
       </c>
-      <c r="J92" s="45">
-        <v>0</v>
-      </c>
-      <c r="K92" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L92" s="49">
-        <v>0</v>
-      </c>
-      <c r="M92" s="44" t="s">
+      <c r="J92" s="43">
+        <v>0</v>
+      </c>
+      <c r="K92" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="48">
+        <v>0</v>
+      </c>
+      <c r="M92" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N92" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="O92" s="41"/>
-      <c r="P92" s="41"/>
-      <c r="Q92" s="41"/>
-      <c r="R92" s="41"/>
-      <c r="S92" s="44"/>
-      <c r="T92" s="44"/>
+      <c r="N92" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O92" s="46"/>
+      <c r="P92" s="46"/>
+      <c r="Q92" s="46"/>
+      <c r="R92" s="46"/>
+      <c r="S92" s="42"/>
+      <c r="T92" s="42"/>
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B93" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D93" s="39">
-        <v>103501001</v>
+        <v>103500001</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
-      <c r="F93" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G93" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="H93" s="48">
-        <v>0</v>
-      </c>
-      <c r="I93" s="44">
+      <c r="F93" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H93" s="47">
+        <v>0</v>
+      </c>
+      <c r="I93" s="42">
         <v>9600</v>
       </c>
-      <c r="J93" s="45">
-        <v>0</v>
-      </c>
-      <c r="K93" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L93" s="49">
-        <v>0</v>
-      </c>
-      <c r="M93" s="44" t="s">
+      <c r="J93" s="43">
+        <v>0</v>
+      </c>
+      <c r="K93" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="48">
+        <v>0</v>
+      </c>
+      <c r="M93" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N93" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="O93" s="41"/>
-      <c r="P93" s="41"/>
-      <c r="Q93" s="41"/>
-      <c r="R93" s="41"/>
-      <c r="S93" s="44"/>
-      <c r="T93" s="44"/>
+      <c r="N93" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O93" s="46"/>
+      <c r="P93" s="46"/>
+      <c r="Q93" s="46"/>
+      <c r="R93" s="46"/>
+      <c r="S93" s="42"/>
+      <c r="T93" s="42"/>
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B94" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D94" s="39">
-        <v>103501001</v>
+        <v>103500001</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
-      <c r="F94" s="41" t="s">
+      <c r="F94" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G94" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H94" s="47">
+        <v>0</v>
+      </c>
+      <c r="I94" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J94" s="43">
+        <v>0</v>
+      </c>
+      <c r="K94" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" s="48">
+        <v>0</v>
+      </c>
+      <c r="M94" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N94" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O94" s="46"/>
+      <c r="P94" s="46"/>
+      <c r="Q94" s="46"/>
+      <c r="R94" s="46"/>
+      <c r="S94" s="42"/>
+      <c r="T94" s="42"/>
+    </row>
+    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A95" s="36">
+        <v>10350110</v>
+      </c>
+      <c r="B95" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C95" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E95" s="40">
+        <v>10</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G95" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95" s="47">
+        <v>0</v>
+      </c>
+      <c r="I95" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J95" s="43">
+        <v>0</v>
+      </c>
+      <c r="K95" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="48">
+        <v>0</v>
+      </c>
+      <c r="M95" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O95" s="46"/>
+      <c r="P95" s="46"/>
+      <c r="Q95" s="46"/>
+      <c r="R95" s="46"/>
+      <c r="S95" s="42"/>
+      <c r="T95" s="42"/>
+    </row>
+    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A96" s="36">
+        <v>10350111</v>
+      </c>
+      <c r="B96" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C96" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D96" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E96" s="40">
+        <v>11</v>
+      </c>
+      <c r="F96" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H96" s="47">
+        <v>0</v>
+      </c>
+      <c r="I96" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J96" s="43">
+        <v>0</v>
+      </c>
+      <c r="K96" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" s="48">
+        <v>0</v>
+      </c>
+      <c r="M96" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N96" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O96" s="46"/>
+      <c r="P96" s="46"/>
+      <c r="Q96" s="46"/>
+      <c r="R96" s="46"/>
+      <c r="S96" s="42"/>
+      <c r="T96" s="42"/>
+    </row>
+    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A97" s="36">
+        <v>10350112</v>
+      </c>
+      <c r="B97" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D97" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E97" s="40">
+        <v>12</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H97" s="47">
+        <v>0</v>
+      </c>
+      <c r="I97" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J97" s="43">
+        <v>0</v>
+      </c>
+      <c r="K97" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="48">
+        <v>0</v>
+      </c>
+      <c r="M97" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N97" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O97" s="46"/>
+      <c r="P97" s="46"/>
+      <c r="Q97" s="46"/>
+      <c r="R97" s="46"/>
+      <c r="S97" s="42"/>
+      <c r="T97" s="42"/>
+    </row>
+    <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A98" s="36">
+        <v>10360010</v>
+      </c>
+      <c r="B98" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C98" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D98" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E98" s="40">
+        <v>10</v>
+      </c>
+      <c r="F98" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="G98" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" s="47">
+        <v>0</v>
+      </c>
+      <c r="I98" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J98" s="43">
+        <v>0</v>
+      </c>
+      <c r="K98" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" s="48">
+        <v>0</v>
+      </c>
+      <c r="M98" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O98" s="46"/>
+      <c r="P98" s="46"/>
+      <c r="Q98" s="46"/>
+      <c r="R98" s="46"/>
+      <c r="S98" s="42"/>
+      <c r="T98" s="42"/>
+    </row>
+    <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A99" s="36">
+        <v>10360011</v>
+      </c>
+      <c r="B99" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C99" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D99" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E99" s="40">
+        <v>11</v>
+      </c>
+      <c r="F99" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G99" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H99" s="47">
+        <v>0</v>
+      </c>
+      <c r="I99" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J99" s="43">
+        <v>0</v>
+      </c>
+      <c r="K99" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="48">
+        <v>0</v>
+      </c>
+      <c r="M99" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N99" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="O99" s="46"/>
+      <c r="P99" s="46"/>
+      <c r="Q99" s="46"/>
+      <c r="R99" s="46"/>
+      <c r="S99" s="42"/>
+      <c r="T99" s="42"/>
+    </row>
+    <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A100" s="36">
+        <v>10360012</v>
+      </c>
+      <c r="B100" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C100" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D100" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E100" s="40">
+        <v>12</v>
+      </c>
+      <c r="F100" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G94" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H94" s="48">
-        <v>0</v>
-      </c>
-      <c r="I94" s="44">
+      <c r="G100" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H100" s="47">
+        <v>0</v>
+      </c>
+      <c r="I100" s="42">
         <v>9600</v>
       </c>
-      <c r="J94" s="45">
-        <v>0</v>
-      </c>
-      <c r="K94" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L94" s="49">
-        <v>0</v>
-      </c>
-      <c r="M94" s="44" t="s">
+      <c r="J100" s="43">
+        <v>0</v>
+      </c>
+      <c r="K100" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" s="48">
+        <v>0</v>
+      </c>
+      <c r="M100" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N94" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="O94" s="41"/>
-      <c r="P94" s="41"/>
-      <c r="Q94" s="41"/>
-      <c r="R94" s="41"/>
-      <c r="S94" s="44"/>
-      <c r="T94" s="44"/>
+      <c r="N100" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="O100" s="46"/>
+      <c r="P100" s="46"/>
+      <c r="Q100" s="46"/>
+      <c r="R100" s="46"/>
+      <c r="S100" s="42"/>
+      <c r="T100" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -420,6 +420,15 @@
   </si>
   <si>
     <t>2_4_10_20_40_100_200</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -649,6 +658,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -676,12 +691,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1694,7 +1703,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:T118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3682,7 +3691,7 @@
         <v>71</v>
       </c>
       <c r="D41" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E41" s="20">
         <v>1</v>
@@ -3732,7 +3741,7 @@
         <v>71</v>
       </c>
       <c r="D42" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E42" s="20">
         <v>2</v>
@@ -3782,7 +3791,7 @@
         <v>71</v>
       </c>
       <c r="D43" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E43" s="20">
         <v>3</v>
@@ -3832,7 +3841,7 @@
         <v>74</v>
       </c>
       <c r="D44" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E44" s="31">
         <v>1</v>
@@ -3882,7 +3891,7 @@
         <v>74</v>
       </c>
       <c r="D45" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E45" s="31">
         <v>2</v>
@@ -3932,7 +3941,7 @@
         <v>74</v>
       </c>
       <c r="D46" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E46" s="31">
         <v>3</v>
@@ -4271,615 +4280,615 @@
       <c r="S52" s="35"/>
       <c r="T52" s="35"/>
     </row>
-    <row r="53" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A53" s="36">
+    <row r="53" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A53" s="29">
+        <v>1028001</v>
+      </c>
+      <c r="B53" s="30">
+        <v>102800</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="32">
+        <v>102800001</v>
+      </c>
+      <c r="E53" s="31">
+        <v>1</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="28">
+        <v>10000000</v>
+      </c>
+      <c r="I53" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J53" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K53" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="33">
+        <v>100</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" s="34">
+        <v>0</v>
+      </c>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+    </row>
+    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A54" s="29">
+        <v>1028002</v>
+      </c>
+      <c r="B54" s="30">
+        <v>102800</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="32">
+        <v>102800001</v>
+      </c>
+      <c r="E54" s="31">
+        <v>2</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="28">
+        <v>100000000</v>
+      </c>
+      <c r="I54" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J54" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K54" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="33">
+        <v>100</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="34">
+        <v>0</v>
+      </c>
+      <c r="O54" s="34"/>
+      <c r="P54" s="34"/>
+      <c r="Q54" s="34"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+    </row>
+    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A55" s="29">
+        <v>1028003</v>
+      </c>
+      <c r="B55" s="30">
+        <v>102800</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D55" s="32">
+        <v>102800001</v>
+      </c>
+      <c r="E55" s="31">
+        <v>3</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I55" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J55" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K55" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="33">
+        <v>100</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N55" s="34">
+        <v>0</v>
+      </c>
+      <c r="O55" s="34"/>
+      <c r="P55" s="34"/>
+      <c r="Q55" s="34"/>
+      <c r="R55" s="34"/>
+      <c r="S55" s="35"/>
+      <c r="T55" s="35"/>
+    </row>
+    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A56" s="29">
+        <v>1020001</v>
+      </c>
+      <c r="B56" s="30">
+        <v>102000</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="32">
+        <v>102000001</v>
+      </c>
+      <c r="E56" s="31">
+        <v>1</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H56" s="28">
+        <v>10000000</v>
+      </c>
+      <c r="I56" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J56" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K56" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="33">
+        <v>100</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" s="34">
+        <v>0</v>
+      </c>
+      <c r="O56" s="34"/>
+      <c r="P56" s="34"/>
+      <c r="Q56" s="34"/>
+      <c r="R56" s="34"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+    </row>
+    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A57" s="29">
+        <v>1020002</v>
+      </c>
+      <c r="B57" s="30">
+        <v>102000</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="32">
+        <v>102000001</v>
+      </c>
+      <c r="E57" s="31">
+        <v>2</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H57" s="28">
+        <v>100000000</v>
+      </c>
+      <c r="I57" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J57" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K57" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="33">
+        <v>100</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N57" s="34">
+        <v>0</v>
+      </c>
+      <c r="O57" s="34"/>
+      <c r="P57" s="34"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="34"/>
+      <c r="S57" s="35"/>
+      <c r="T57" s="35"/>
+    </row>
+    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A58" s="29">
+        <v>1020003</v>
+      </c>
+      <c r="B58" s="30">
+        <v>102000</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="32">
+        <v>102000001</v>
+      </c>
+      <c r="E58" s="31">
+        <v>3</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I58" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J58" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K58" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="33">
+        <v>100</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N58" s="34">
+        <v>0</v>
+      </c>
+      <c r="O58" s="34"/>
+      <c r="P58" s="34"/>
+      <c r="Q58" s="34"/>
+      <c r="R58" s="34"/>
+      <c r="S58" s="35"/>
+      <c r="T58" s="35"/>
+    </row>
+    <row r="59" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A59" s="19">
+        <v>1034011</v>
+      </c>
+      <c r="B59" s="19">
+        <v>103401</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E59" s="20">
+        <v>1</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I59" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J59" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K59" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="27">
+        <v>100</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" s="21">
+        <v>0</v>
+      </c>
+      <c r="O59" s="21"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
+      <c r="R59" s="21"/>
+      <c r="S59" s="23"/>
+      <c r="T59" s="23"/>
+    </row>
+    <row r="60" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A60" s="19">
+        <v>1034012</v>
+      </c>
+      <c r="B60" s="19">
+        <v>103401</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E60" s="20">
+        <v>2</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H60" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I60" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J60" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K60" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="27">
+        <v>100</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N60" s="21">
+        <v>0</v>
+      </c>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
+      <c r="R60" s="21"/>
+      <c r="S60" s="23"/>
+      <c r="T60" s="23"/>
+    </row>
+    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A61" s="19">
+        <v>1034013</v>
+      </c>
+      <c r="B61" s="19">
+        <v>103401</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E61" s="20">
+        <v>3</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I61" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J61" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K61" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="27">
+        <v>100</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N61" s="21">
+        <v>0</v>
+      </c>
+      <c r="O61" s="21"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="21"/>
+      <c r="R61" s="21"/>
+      <c r="S61" s="23"/>
+      <c r="T61" s="23"/>
+    </row>
+    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A62" s="36">
         <v>10010010</v>
       </c>
-      <c r="B53" s="37">
+      <c r="B62" s="37">
         <v>100100</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C62" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="39">
+      <c r="D62" s="39">
         <v>100100026</v>
-      </c>
-      <c r="E53" s="40">
-        <v>10</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H53" s="41">
-        <v>0</v>
-      </c>
-      <c r="I53" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J53" s="43">
-        <v>0</v>
-      </c>
-      <c r="K53" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L53" s="44">
-        <v>0</v>
-      </c>
-      <c r="M53" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N53" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46"/>
-      <c r="R53" s="46"/>
-      <c r="S53" s="42"/>
-      <c r="T53" s="42"/>
-    </row>
-    <row r="54" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A54" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B54" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E54" s="40">
-        <v>11</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H54" s="41">
-        <v>0</v>
-      </c>
-      <c r="I54" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J54" s="43">
-        <v>0</v>
-      </c>
-      <c r="K54" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L54" s="44">
-        <v>0</v>
-      </c>
-      <c r="M54" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="46"/>
-      <c r="R54" s="46"/>
-      <c r="S54" s="42"/>
-      <c r="T54" s="42"/>
-    </row>
-    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A55" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B55" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E55" s="40">
-        <v>12</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="47">
-        <v>0</v>
-      </c>
-      <c r="I55" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J55" s="43">
-        <v>0</v>
-      </c>
-      <c r="K55" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="44">
-        <v>0</v>
-      </c>
-      <c r="M55" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N55" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="46"/>
-      <c r="R55" s="46"/>
-      <c r="S55" s="42"/>
-      <c r="T55" s="42"/>
-    </row>
-    <row r="56" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A56" s="36">
-        <v>10030010</v>
-      </c>
-      <c r="B56" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E56" s="40">
-        <v>10</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G56" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="41">
-        <v>0</v>
-      </c>
-      <c r="I56" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J56" s="43">
-        <v>0</v>
-      </c>
-      <c r="K56" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="48">
-        <v>0</v>
-      </c>
-      <c r="M56" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N56" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46"/>
-      <c r="R56" s="46"/>
-      <c r="S56" s="42"/>
-      <c r="T56" s="42"/>
-    </row>
-    <row r="57" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A57" s="36">
-        <v>10030011</v>
-      </c>
-      <c r="B57" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E57" s="40">
-        <v>11</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H57" s="41">
-        <v>0</v>
-      </c>
-      <c r="I57" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J57" s="43">
-        <v>0</v>
-      </c>
-      <c r="K57" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L57" s="48">
-        <v>0</v>
-      </c>
-      <c r="M57" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N57" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="46"/>
-      <c r="R57" s="46"/>
-      <c r="S57" s="42"/>
-      <c r="T57" s="42"/>
-    </row>
-    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A58" s="36">
-        <v>10030012</v>
-      </c>
-      <c r="B58" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E58" s="40">
-        <v>12</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="H58" s="47">
-        <v>0</v>
-      </c>
-      <c r="I58" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J58" s="43">
-        <v>0</v>
-      </c>
-      <c r="K58" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L58" s="48">
-        <v>0</v>
-      </c>
-      <c r="M58" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N58" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O58" s="46"/>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="46"/>
-      <c r="S58" s="42"/>
-      <c r="T58" s="42"/>
-    </row>
-    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A59" s="36">
-        <v>10070010</v>
-      </c>
-      <c r="B59" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E59" s="40">
-        <v>10</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G59" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H59" s="41">
-        <v>0</v>
-      </c>
-      <c r="I59" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J59" s="43">
-        <v>0</v>
-      </c>
-      <c r="K59" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="44">
-        <v>0</v>
-      </c>
-      <c r="M59" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N59" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="46"/>
-      <c r="R59" s="46"/>
-      <c r="S59" s="42"/>
-      <c r="T59" s="42"/>
-    </row>
-    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A60" s="36">
-        <v>10070011</v>
-      </c>
-      <c r="B60" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C60" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E60" s="40">
-        <v>11</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H60" s="41">
-        <v>0</v>
-      </c>
-      <c r="I60" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J60" s="43">
-        <v>0</v>
-      </c>
-      <c r="K60" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="44">
-        <v>0</v>
-      </c>
-      <c r="M60" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N60" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="46"/>
-      <c r="R60" s="46"/>
-      <c r="S60" s="42"/>
-      <c r="T60" s="42"/>
-    </row>
-    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A61" s="36">
-        <v>10070012</v>
-      </c>
-      <c r="B61" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E61" s="40">
-        <v>12</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H61" s="47">
-        <v>0</v>
-      </c>
-      <c r="I61" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J61" s="43">
-        <v>0</v>
-      </c>
-      <c r="K61" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="44">
-        <v>0</v>
-      </c>
-      <c r="M61" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N61" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="46"/>
-      <c r="R61" s="46"/>
-      <c r="S61" s="42"/>
-      <c r="T61" s="42"/>
-    </row>
-    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B62" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="50">
-        <v>101200026</v>
       </c>
       <c r="E62" s="40">
         <v>10</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H62" s="41">
         <v>0</v>
       </c>
-      <c r="I62" s="43">
+      <c r="I62" s="42">
         <v>9500</v>
       </c>
       <c r="J62" s="43">
         <v>0</v>
       </c>
-      <c r="K62" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="48">
-        <v>0</v>
-      </c>
-      <c r="M62" s="43" t="s">
+      <c r="K62" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="44">
+        <v>0</v>
+      </c>
+      <c r="M62" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N62" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O62" s="45"/>
-      <c r="P62" s="45"/>
-      <c r="Q62" s="45"/>
-      <c r="R62" s="45"/>
-      <c r="S62" s="43"/>
-      <c r="T62" s="43"/>
-    </row>
-    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>81</v>
+      </c>
+      <c r="O62" s="46"/>
+      <c r="P62" s="46"/>
+      <c r="Q62" s="46"/>
+      <c r="R62" s="46"/>
+      <c r="S62" s="42"/>
+      <c r="T62" s="42"/>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B63" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D63" s="50">
-        <v>101200026</v>
+        <v>10010011</v>
+      </c>
+      <c r="B63" s="37">
+        <v>100100</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="39">
+        <v>100100026</v>
       </c>
       <c r="E63" s="40">
         <v>11</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H63" s="41">
         <v>0</v>
       </c>
-      <c r="I63" s="43">
+      <c r="I63" s="42">
         <v>9500</v>
       </c>
       <c r="J63" s="43">
         <v>0</v>
       </c>
-      <c r="K63" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="48">
-        <v>0</v>
-      </c>
-      <c r="M63" s="43" t="s">
+      <c r="K63" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="44">
+        <v>0</v>
+      </c>
+      <c r="M63" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N63" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O63" s="45"/>
-      <c r="P63" s="45"/>
-      <c r="Q63" s="45"/>
-      <c r="R63" s="45"/>
-      <c r="S63" s="43"/>
-      <c r="T63" s="43"/>
-    </row>
-    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="O63" s="46"/>
+      <c r="P63" s="46"/>
+      <c r="Q63" s="46"/>
+      <c r="R63" s="46"/>
+      <c r="S63" s="42"/>
+      <c r="T63" s="42"/>
+    </row>
+    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B64" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C64" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D64" s="50">
-        <v>101200026</v>
+        <v>10010012</v>
+      </c>
+      <c r="B64" s="37">
+        <v>100100</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="39">
+        <v>100100026</v>
       </c>
       <c r="E64" s="40">
         <v>12</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H64" s="47">
         <v>0</v>
       </c>
-      <c r="I64" s="43">
+      <c r="I64" s="42">
         <v>9500</v>
       </c>
       <c r="J64" s="43">
         <v>0</v>
       </c>
-      <c r="K64" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="48">
-        <v>0</v>
-      </c>
-      <c r="M64" s="43" t="s">
+      <c r="K64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="44">
+        <v>0</v>
+      </c>
+      <c r="M64" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O64" s="45"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="45"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="43"/>
-      <c r="T64" s="43"/>
+        <v>83</v>
+      </c>
+      <c r="O64" s="46"/>
+      <c r="P64" s="46"/>
+      <c r="Q64" s="46"/>
+      <c r="R64" s="46"/>
+      <c r="S64" s="42"/>
+      <c r="T64" s="42"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="36">
-        <v>10140010</v>
+        <v>10030010</v>
       </c>
       <c r="B65" s="37">
-        <v>101400</v>
+        <v>100300</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D65" s="39">
         <v>100100026</v>
@@ -4888,10 +4897,10 @@
         <v>10</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H65" s="41">
         <v>0</v>
@@ -4905,14 +4914,14 @@
       <c r="K65" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L65" s="44">
+      <c r="L65" s="48">
         <v>0</v>
       </c>
       <c r="M65" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N65" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O65" s="46"/>
       <c r="P65" s="46"/>
@@ -4923,13 +4932,13 @@
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="36">
-        <v>10140011</v>
+        <v>10030011</v>
       </c>
       <c r="B66" s="37">
-        <v>101400</v>
+        <v>100300</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D66" s="39">
         <v>100100026</v>
@@ -4938,10 +4947,10 @@
         <v>11</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H66" s="41">
         <v>0</v>
@@ -4955,14 +4964,14 @@
       <c r="K66" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L66" s="44">
+      <c r="L66" s="48">
         <v>0</v>
       </c>
       <c r="M66" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N66" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O66" s="46"/>
       <c r="P66" s="46"/>
@@ -4973,13 +4982,13 @@
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="36">
-        <v>10140012</v>
+        <v>10030012</v>
       </c>
       <c r="B67" s="37">
-        <v>101400</v>
+        <v>100300</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D67" s="39">
         <v>100100026</v>
@@ -4988,10 +4997,10 @@
         <v>12</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H67" s="47">
         <v>0</v>
@@ -5005,14 +5014,14 @@
       <c r="K67" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L67" s="44">
+      <c r="L67" s="48">
         <v>0</v>
       </c>
       <c r="M67" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N67" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O67" s="46"/>
       <c r="P67" s="46"/>
@@ -5023,16 +5032,16 @@
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="36">
-        <v>10170010</v>
+        <v>10070010</v>
       </c>
       <c r="B68" s="37">
-        <v>101700</v>
+        <v>100700</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D68" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E68" s="40">
         <v>10</v>
@@ -5062,7 +5071,7 @@
         <v>37</v>
       </c>
       <c r="N68" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O68" s="46"/>
       <c r="P68" s="46"/>
@@ -5073,16 +5082,16 @@
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="36">
-        <v>10170011</v>
+        <v>10070011</v>
       </c>
       <c r="B69" s="37">
-        <v>101700</v>
+        <v>100700</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D69" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E69" s="40">
         <v>11</v>
@@ -5112,7 +5121,7 @@
         <v>40</v>
       </c>
       <c r="N69" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O69" s="46"/>
       <c r="P69" s="46"/>
@@ -5123,16 +5132,16 @@
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="36">
-        <v>10170012</v>
+        <v>10070012</v>
       </c>
       <c r="B70" s="37">
-        <v>101700</v>
+        <v>100700</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D70" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E70" s="40">
         <v>12</v>
@@ -5162,7 +5171,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O70" s="46"/>
       <c r="P70" s="46"/>
@@ -5171,177 +5180,177 @@
       <c r="S70" s="42"/>
       <c r="T70" s="42"/>
     </row>
-    <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="71" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="36">
-        <v>10210010</v>
-      </c>
-      <c r="B71" s="37">
-        <v>102100</v>
-      </c>
-      <c r="C71" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D71" s="39">
-        <v>102100001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B71" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C71" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D71" s="50">
+        <v>101200026</v>
       </c>
       <c r="E71" s="40">
         <v>10</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H71" s="41">
         <v>0</v>
       </c>
-      <c r="I71" s="42">
+      <c r="I71" s="43">
         <v>9500</v>
       </c>
       <c r="J71" s="43">
         <v>0</v>
       </c>
-      <c r="K71" s="44" t="s">
+      <c r="K71" s="48" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="48">
         <v>0</v>
       </c>
-      <c r="M71" s="42" t="s">
+      <c r="M71" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N71" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O71" s="46"/>
-      <c r="P71" s="46"/>
-      <c r="Q71" s="46"/>
-      <c r="R71" s="46"/>
-      <c r="S71" s="42"/>
-      <c r="T71" s="42"/>
-    </row>
-    <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>81</v>
+      </c>
+      <c r="O71" s="45"/>
+      <c r="P71" s="45"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="43"/>
+      <c r="T71" s="43"/>
+    </row>
+    <row r="72" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="36">
-        <v>10210011</v>
-      </c>
-      <c r="B72" s="37">
-        <v>102100</v>
-      </c>
-      <c r="C72" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D72" s="39">
-        <v>102100001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B72" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C72" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D72" s="50">
+        <v>101200026</v>
       </c>
       <c r="E72" s="40">
         <v>11</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H72" s="41">
         <v>0</v>
       </c>
-      <c r="I72" s="42">
+      <c r="I72" s="43">
         <v>9500</v>
       </c>
       <c r="J72" s="43">
         <v>0</v>
       </c>
-      <c r="K72" s="44" t="s">
+      <c r="K72" s="48" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="48">
         <v>0</v>
       </c>
-      <c r="M72" s="42" t="s">
+      <c r="M72" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N72" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O72" s="46"/>
-      <c r="P72" s="46"/>
-      <c r="Q72" s="46"/>
-      <c r="R72" s="46"/>
-      <c r="S72" s="42"/>
-      <c r="T72" s="42"/>
-    </row>
-    <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="O72" s="45"/>
+      <c r="P72" s="45"/>
+      <c r="Q72" s="45"/>
+      <c r="R72" s="45"/>
+      <c r="S72" s="43"/>
+      <c r="T72" s="43"/>
+    </row>
+    <row r="73" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="36">
-        <v>10210012</v>
-      </c>
-      <c r="B73" s="37">
-        <v>102100</v>
-      </c>
-      <c r="C73" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" s="39">
-        <v>102100001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B73" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C73" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D73" s="50">
+        <v>101200026</v>
       </c>
       <c r="E73" s="40">
         <v>12</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H73" s="47">
         <v>0</v>
       </c>
-      <c r="I73" s="42">
+      <c r="I73" s="43">
         <v>9500</v>
       </c>
       <c r="J73" s="43">
         <v>0</v>
       </c>
-      <c r="K73" s="44" t="s">
+      <c r="K73" s="48" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="48">
         <v>0</v>
       </c>
-      <c r="M73" s="42" t="s">
+      <c r="M73" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N73" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O73" s="46"/>
-      <c r="P73" s="46"/>
-      <c r="Q73" s="46"/>
-      <c r="R73" s="46"/>
-      <c r="S73" s="42"/>
-      <c r="T73" s="42"/>
+        <v>83</v>
+      </c>
+      <c r="O73" s="45"/>
+      <c r="P73" s="45"/>
+      <c r="Q73" s="45"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="43"/>
+      <c r="T73" s="43"/>
     </row>
     <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10220010</v>
+        <v>10140010</v>
       </c>
       <c r="B74" s="37">
-        <v>102200</v>
+        <v>101400</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D74" s="39">
-        <v>102200001</v>
+        <v>100100026</v>
       </c>
       <c r="E74" s="40">
         <v>10</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H74" s="41">
         <v>0</v>
@@ -5355,14 +5364,14 @@
       <c r="K74" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L74" s="48">
+      <c r="L74" s="44">
         <v>0</v>
       </c>
       <c r="M74" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N74" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O74" s="46"/>
       <c r="P74" s="46"/>
@@ -5373,25 +5382,25 @@
     </row>
     <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10220011</v>
+        <v>10140011</v>
       </c>
       <c r="B75" s="37">
-        <v>102200</v>
+        <v>101400</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D75" s="39">
-        <v>102200001</v>
+        <v>100100026</v>
       </c>
       <c r="E75" s="40">
         <v>11</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H75" s="41">
         <v>0</v>
@@ -5405,14 +5414,14 @@
       <c r="K75" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L75" s="48">
+      <c r="L75" s="44">
         <v>0</v>
       </c>
       <c r="M75" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N75" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O75" s="46"/>
       <c r="P75" s="46"/>
@@ -5423,25 +5432,25 @@
     </row>
     <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10220012</v>
+        <v>10140012</v>
       </c>
       <c r="B76" s="37">
-        <v>102200</v>
+        <v>101400</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D76" s="39">
-        <v>102200001</v>
+        <v>100100026</v>
       </c>
       <c r="E76" s="40">
         <v>12</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H76" s="47">
         <v>0</v>
@@ -5455,14 +5464,14 @@
       <c r="K76" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L76" s="48">
+      <c r="L76" s="44">
         <v>0</v>
       </c>
       <c r="M76" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N76" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O76" s="46"/>
       <c r="P76" s="46"/>
@@ -5473,25 +5482,25 @@
     </row>
     <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10240010</v>
+        <v>10170010</v>
       </c>
       <c r="B77" s="37">
-        <v>102400</v>
+        <v>101700</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D77" s="39">
-        <v>102400026</v>
+        <v>101700001</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H77" s="41">
         <v>0</v>
@@ -5505,14 +5514,14 @@
       <c r="K77" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L77" s="48">
+      <c r="L77" s="44">
         <v>0</v>
       </c>
       <c r="M77" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N77" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O77" s="46"/>
       <c r="P77" s="46"/>
@@ -5523,25 +5532,25 @@
     </row>
     <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10240011</v>
+        <v>10170011</v>
       </c>
       <c r="B78" s="37">
-        <v>102400</v>
+        <v>101700</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D78" s="39">
-        <v>102400026</v>
+        <v>101700001</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H78" s="41">
         <v>0</v>
@@ -5555,14 +5564,14 @@
       <c r="K78" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L78" s="48">
+      <c r="L78" s="44">
         <v>0</v>
       </c>
       <c r="M78" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N78" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O78" s="46"/>
       <c r="P78" s="46"/>
@@ -5573,25 +5582,25 @@
     </row>
     <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10240012</v>
+        <v>10170012</v>
       </c>
       <c r="B79" s="37">
-        <v>102400</v>
+        <v>101700</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D79" s="39">
-        <v>102400026</v>
+        <v>101700001</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H79" s="47">
         <v>0</v>
@@ -5605,14 +5614,14 @@
       <c r="K79" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L79" s="48">
+      <c r="L79" s="44">
         <v>0</v>
       </c>
       <c r="M79" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N79" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O79" s="46"/>
       <c r="P79" s="46"/>
@@ -5623,16 +5632,16 @@
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10180010</v>
+        <v>10210010</v>
       </c>
       <c r="B80" s="37">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D80" s="39">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="E80" s="40">
         <v>10</v>
@@ -5643,7 +5652,7 @@
       <c r="G80" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H80" s="47">
+      <c r="H80" s="41">
         <v>0</v>
       </c>
       <c r="I80" s="42">
@@ -5662,7 +5671,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5673,16 +5682,16 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10180011</v>
+        <v>10210011</v>
       </c>
       <c r="B81" s="37">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D81" s="39">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="E81" s="40">
         <v>11</v>
@@ -5693,7 +5702,7 @@
       <c r="G81" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="47">
+      <c r="H81" s="41">
         <v>0</v>
       </c>
       <c r="I81" s="42">
@@ -5712,7 +5721,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5723,16 +5732,16 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10180012</v>
+        <v>10210012</v>
       </c>
       <c r="B82" s="37">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D82" s="39">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="E82" s="40">
         <v>12</v>
@@ -5762,7 +5771,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5773,27 +5782,27 @@
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10250010</v>
+        <v>10220010</v>
       </c>
       <c r="B83" s="37">
-        <v>102500</v>
+        <v>102200</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D83" s="39">
-        <v>102500001</v>
+        <v>102200001</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="H83" s="47">
+        <v>51</v>
+      </c>
+      <c r="H83" s="41">
         <v>0</v>
       </c>
       <c r="I83" s="42">
@@ -5812,7 +5821,7 @@
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O83" s="46"/>
       <c r="P83" s="46"/>
@@ -5823,27 +5832,27 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10250011</v>
+        <v>10220011</v>
       </c>
       <c r="B84" s="37">
-        <v>102500</v>
+        <v>102200</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D84" s="39">
-        <v>102500001</v>
+        <v>102200001</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H84" s="47">
+        <v>53</v>
+      </c>
+      <c r="H84" s="41">
         <v>0</v>
       </c>
       <c r="I84" s="42">
@@ -5862,7 +5871,7 @@
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O84" s="46"/>
       <c r="P84" s="46"/>
@@ -5873,25 +5882,25 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10250012</v>
+        <v>10220012</v>
       </c>
       <c r="B85" s="37">
-        <v>102500</v>
+        <v>102200</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D85" s="39">
-        <v>102500001</v>
+        <v>102200001</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H85" s="47">
         <v>0</v>
@@ -5912,7 +5921,7 @@
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O85" s="46"/>
       <c r="P85" s="46"/>
@@ -5923,27 +5932,27 @@
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10230010</v>
+        <v>10240010</v>
       </c>
       <c r="B86" s="37">
-        <v>102300</v>
+        <v>102400</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D86" s="39">
-        <v>102300001</v>
+        <v>102400026</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H86" s="47">
+        <v>35</v>
+      </c>
+      <c r="H86" s="41">
         <v>0</v>
       </c>
       <c r="I86" s="42">
@@ -5962,7 +5971,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -5973,27 +5982,27 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10230011</v>
+        <v>10240011</v>
       </c>
       <c r="B87" s="37">
-        <v>102300</v>
+        <v>102400</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D87" s="39">
-        <v>102300001</v>
+        <v>102400026</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H87" s="47">
+        <v>39</v>
+      </c>
+      <c r="H87" s="41">
         <v>0</v>
       </c>
       <c r="I87" s="42">
@@ -6012,7 +6021,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6023,25 +6032,25 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10230012</v>
+        <v>10240012</v>
       </c>
       <c r="B88" s="37">
-        <v>102300</v>
+        <v>102400</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D88" s="39">
-        <v>102300001</v>
+        <v>102400026</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6062,7 +6071,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6073,31 +6082,31 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10340010</v>
+        <v>10180010</v>
       </c>
       <c r="B89" s="37">
-        <v>103400</v>
+        <v>101800</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D89" s="39">
-        <v>103400001</v>
+        <v>101800001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H89" s="47">
         <v>0</v>
       </c>
       <c r="I89" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J89" s="43">
         <v>0</v>
@@ -6112,7 +6121,7 @@
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6123,31 +6132,31 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10340011</v>
+        <v>10180011</v>
       </c>
       <c r="B90" s="37">
-        <v>103400</v>
+        <v>101800</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D90" s="39">
-        <v>103400001</v>
+        <v>101800001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H90" s="47">
         <v>0</v>
       </c>
       <c r="I90" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J90" s="43">
         <v>0</v>
@@ -6162,7 +6171,7 @@
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6173,31 +6182,31 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10340012</v>
+        <v>10180012</v>
       </c>
       <c r="B91" s="37">
-        <v>103400</v>
+        <v>101800</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D91" s="39">
-        <v>103400001</v>
+        <v>101800001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
       </c>
       <c r="I91" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J91" s="43">
         <v>0</v>
@@ -6212,7 +6221,7 @@
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6223,31 +6232,31 @@
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10350010</v>
+        <v>10250010</v>
       </c>
       <c r="B92" s="37">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D92" s="39">
-        <v>103500001</v>
+        <v>102500001</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H92" s="47">
         <v>0</v>
       </c>
       <c r="I92" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J92" s="43">
         <v>0</v>
@@ -6262,7 +6271,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6273,31 +6282,31 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10350011</v>
+        <v>10250011</v>
       </c>
       <c r="B93" s="37">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D93" s="39">
-        <v>103500001</v>
+        <v>102500001</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H93" s="47">
         <v>0</v>
       </c>
       <c r="I93" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J93" s="43">
         <v>0</v>
@@ -6312,7 +6321,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6323,31 +6332,31 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10350012</v>
+        <v>10250012</v>
       </c>
       <c r="B94" s="37">
-        <v>103500</v>
+        <v>102500</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D94" s="39">
-        <v>103500001</v>
+        <v>102500001</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
       </c>
       <c r="I94" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J94" s="43">
         <v>0</v>
@@ -6362,7 +6371,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6373,31 +6382,31 @@
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10350110</v>
+        <v>10230010</v>
       </c>
       <c r="B95" s="37">
-        <v>103501</v>
+        <v>102300</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D95" s="39">
-        <v>103501001</v>
+        <v>102300001</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H95" s="47">
         <v>0</v>
       </c>
       <c r="I95" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J95" s="43">
         <v>0</v>
@@ -6412,7 +6421,7 @@
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6423,31 +6432,31 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10350111</v>
+        <v>10230011</v>
       </c>
       <c r="B96" s="37">
-        <v>103501</v>
+        <v>102300</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D96" s="39">
-        <v>103501001</v>
+        <v>102300001</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H96" s="47">
         <v>0</v>
       </c>
       <c r="I96" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J96" s="43">
         <v>0</v>
@@ -6462,7 +6471,7 @@
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6473,31 +6482,31 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10350112</v>
+        <v>10230012</v>
       </c>
       <c r="B97" s="37">
-        <v>103501</v>
+        <v>102300</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D97" s="39">
-        <v>103501001</v>
+        <v>102300001</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G97" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H97" s="47">
         <v>0</v>
       </c>
       <c r="I97" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J97" s="43">
         <v>0</v>
@@ -6512,7 +6521,7 @@
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6523,25 +6532,25 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10360010</v>
+        <v>10340010</v>
       </c>
       <c r="B98" s="37">
-        <v>103600</v>
+        <v>103400</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D98" s="39">
-        <v>103600001</v>
+        <v>103000001</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
-      <c r="F98" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G98" s="51" t="s">
-        <v>35</v>
+      <c r="F98" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G98" s="22" t="s">
+        <v>67</v>
       </c>
       <c r="H98" s="47">
         <v>0</v>
@@ -6562,7 +6571,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6573,25 +6582,25 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10360011</v>
+        <v>10340011</v>
       </c>
       <c r="B99" s="37">
-        <v>103600</v>
+        <v>103400</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D99" s="39">
-        <v>103600001</v>
+        <v>103000001</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
-      <c r="F99" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G99" s="51" t="s">
-        <v>39</v>
+      <c r="F99" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="H99" s="47">
         <v>0</v>
@@ -6612,7 +6621,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6623,25 +6632,25 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10360012</v>
+        <v>10340012</v>
       </c>
       <c r="B100" s="37">
-        <v>103600</v>
+        <v>103400</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D100" s="39">
-        <v>103600001</v>
+        <v>103000001</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
-      <c r="F100" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G100" s="51" t="s">
-        <v>42</v>
+      <c r="F100" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G100" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
@@ -6662,7 +6671,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6670,6 +6679,906 @@
       <c r="R100" s="46"/>
       <c r="S100" s="42"/>
       <c r="T100" s="42"/>
+    </row>
+    <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A101" s="36">
+        <v>10350010</v>
+      </c>
+      <c r="B101" s="37">
+        <v>103500</v>
+      </c>
+      <c r="C101" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D101" s="39">
+        <v>102900001</v>
+      </c>
+      <c r="E101" s="40">
+        <v>10</v>
+      </c>
+      <c r="F101" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G101" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101" s="47">
+        <v>0</v>
+      </c>
+      <c r="I101" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J101" s="43">
+        <v>0</v>
+      </c>
+      <c r="K101" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" s="48">
+        <v>0</v>
+      </c>
+      <c r="M101" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O101" s="46"/>
+      <c r="P101" s="46"/>
+      <c r="Q101" s="46"/>
+      <c r="R101" s="46"/>
+      <c r="S101" s="42"/>
+      <c r="T101" s="42"/>
+    </row>
+    <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A102" s="36">
+        <v>10350011</v>
+      </c>
+      <c r="B102" s="37">
+        <v>103500</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D102" s="39">
+        <v>102900001</v>
+      </c>
+      <c r="E102" s="40">
+        <v>11</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H102" s="47">
+        <v>0</v>
+      </c>
+      <c r="I102" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J102" s="43">
+        <v>0</v>
+      </c>
+      <c r="K102" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L102" s="48">
+        <v>0</v>
+      </c>
+      <c r="M102" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N102" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O102" s="46"/>
+      <c r="P102" s="46"/>
+      <c r="Q102" s="46"/>
+      <c r="R102" s="46"/>
+      <c r="S102" s="42"/>
+      <c r="T102" s="42"/>
+    </row>
+    <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A103" s="36">
+        <v>10350012</v>
+      </c>
+      <c r="B103" s="37">
+        <v>103500</v>
+      </c>
+      <c r="C103" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D103" s="39">
+        <v>102900001</v>
+      </c>
+      <c r="E103" s="40">
+        <v>12</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H103" s="47">
+        <v>0</v>
+      </c>
+      <c r="I103" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J103" s="43">
+        <v>0</v>
+      </c>
+      <c r="K103" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L103" s="48">
+        <v>0</v>
+      </c>
+      <c r="M103" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N103" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O103" s="46"/>
+      <c r="P103" s="46"/>
+      <c r="Q103" s="46"/>
+      <c r="R103" s="46"/>
+      <c r="S103" s="42"/>
+      <c r="T103" s="42"/>
+    </row>
+    <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A104" s="36">
+        <v>10350110</v>
+      </c>
+      <c r="B104" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C104" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D104" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E104" s="40">
+        <v>10</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G104" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H104" s="47">
+        <v>0</v>
+      </c>
+      <c r="I104" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J104" s="43">
+        <v>0</v>
+      </c>
+      <c r="K104" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" s="48">
+        <v>0</v>
+      </c>
+      <c r="M104" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O104" s="46"/>
+      <c r="P104" s="46"/>
+      <c r="Q104" s="46"/>
+      <c r="R104" s="46"/>
+      <c r="S104" s="42"/>
+      <c r="T104" s="42"/>
+    </row>
+    <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A105" s="36">
+        <v>10350111</v>
+      </c>
+      <c r="B105" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C105" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D105" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E105" s="40">
+        <v>11</v>
+      </c>
+      <c r="F105" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G105" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H105" s="47">
+        <v>0</v>
+      </c>
+      <c r="I105" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J105" s="43">
+        <v>0</v>
+      </c>
+      <c r="K105" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" s="48">
+        <v>0</v>
+      </c>
+      <c r="M105" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N105" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O105" s="46"/>
+      <c r="P105" s="46"/>
+      <c r="Q105" s="46"/>
+      <c r="R105" s="46"/>
+      <c r="S105" s="42"/>
+      <c r="T105" s="42"/>
+    </row>
+    <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A106" s="36">
+        <v>10350112</v>
+      </c>
+      <c r="B106" s="37">
+        <v>103501</v>
+      </c>
+      <c r="C106" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D106" s="39">
+        <v>103501001</v>
+      </c>
+      <c r="E106" s="40">
+        <v>12</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G106" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H106" s="47">
+        <v>0</v>
+      </c>
+      <c r="I106" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J106" s="43">
+        <v>0</v>
+      </c>
+      <c r="K106" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="48">
+        <v>0</v>
+      </c>
+      <c r="M106" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N106" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O106" s="46"/>
+      <c r="P106" s="46"/>
+      <c r="Q106" s="46"/>
+      <c r="R106" s="46"/>
+      <c r="S106" s="42"/>
+      <c r="T106" s="42"/>
+    </row>
+    <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A107" s="36">
+        <v>10360010</v>
+      </c>
+      <c r="B107" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C107" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D107" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E107" s="40">
+        <v>10</v>
+      </c>
+      <c r="F107" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="G107" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H107" s="47">
+        <v>0</v>
+      </c>
+      <c r="I107" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J107" s="43">
+        <v>0</v>
+      </c>
+      <c r="K107" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" s="48">
+        <v>0</v>
+      </c>
+      <c r="M107" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O107" s="46"/>
+      <c r="P107" s="46"/>
+      <c r="Q107" s="46"/>
+      <c r="R107" s="46"/>
+      <c r="S107" s="42"/>
+      <c r="T107" s="42"/>
+    </row>
+    <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A108" s="36">
+        <v>10360011</v>
+      </c>
+      <c r="B108" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C108" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D108" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E108" s="40">
+        <v>11</v>
+      </c>
+      <c r="F108" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G108" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H108" s="47">
+        <v>0</v>
+      </c>
+      <c r="I108" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J108" s="43">
+        <v>0</v>
+      </c>
+      <c r="K108" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" s="48">
+        <v>0</v>
+      </c>
+      <c r="M108" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N108" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O108" s="46"/>
+      <c r="P108" s="46"/>
+      <c r="Q108" s="46"/>
+      <c r="R108" s="46"/>
+      <c r="S108" s="42"/>
+      <c r="T108" s="42"/>
+    </row>
+    <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A109" s="36">
+        <v>10360012</v>
+      </c>
+      <c r="B109" s="37">
+        <v>103600</v>
+      </c>
+      <c r="C109" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D109" s="39">
+        <v>103600001</v>
+      </c>
+      <c r="E109" s="40">
+        <v>12</v>
+      </c>
+      <c r="F109" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G109" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H109" s="47">
+        <v>0</v>
+      </c>
+      <c r="I109" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J109" s="43">
+        <v>0</v>
+      </c>
+      <c r="K109" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L109" s="48">
+        <v>0</v>
+      </c>
+      <c r="M109" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N109" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O109" s="46"/>
+      <c r="P109" s="46"/>
+      <c r="Q109" s="46"/>
+      <c r="R109" s="46"/>
+      <c r="S109" s="42"/>
+      <c r="T109" s="42"/>
+    </row>
+    <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A110" s="36">
+        <v>10280010</v>
+      </c>
+      <c r="B110" s="37">
+        <v>102800</v>
+      </c>
+      <c r="C110" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D110" s="39">
+        <v>102800001</v>
+      </c>
+      <c r="E110" s="40">
+        <v>10</v>
+      </c>
+      <c r="F110" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G110" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H110" s="47">
+        <v>0</v>
+      </c>
+      <c r="I110" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J110" s="43">
+        <v>0</v>
+      </c>
+      <c r="K110" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L110" s="48">
+        <v>0</v>
+      </c>
+      <c r="M110" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N110" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O110" s="46"/>
+      <c r="P110" s="46"/>
+      <c r="Q110" s="46"/>
+      <c r="R110" s="46"/>
+      <c r="S110" s="42"/>
+      <c r="T110" s="42"/>
+    </row>
+    <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A111" s="36">
+        <v>10280011</v>
+      </c>
+      <c r="B111" s="37">
+        <v>102800</v>
+      </c>
+      <c r="C111" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D111" s="39">
+        <v>102800001</v>
+      </c>
+      <c r="E111" s="40">
+        <v>11</v>
+      </c>
+      <c r="F111" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G111" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H111" s="47">
+        <v>0</v>
+      </c>
+      <c r="I111" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J111" s="43">
+        <v>0</v>
+      </c>
+      <c r="K111" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L111" s="48">
+        <v>0</v>
+      </c>
+      <c r="M111" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N111" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O111" s="46"/>
+      <c r="P111" s="46"/>
+      <c r="Q111" s="46"/>
+      <c r="R111" s="46"/>
+      <c r="S111" s="42"/>
+      <c r="T111" s="42"/>
+    </row>
+    <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A112" s="36">
+        <v>10280012</v>
+      </c>
+      <c r="B112" s="37">
+        <v>102800</v>
+      </c>
+      <c r="C112" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D112" s="39">
+        <v>102800001</v>
+      </c>
+      <c r="E112" s="40">
+        <v>12</v>
+      </c>
+      <c r="F112" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" s="47">
+        <v>0</v>
+      </c>
+      <c r="I112" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J112" s="43">
+        <v>0</v>
+      </c>
+      <c r="K112" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" s="48">
+        <v>0</v>
+      </c>
+      <c r="M112" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N112" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O112" s="46"/>
+      <c r="P112" s="46"/>
+      <c r="Q112" s="46"/>
+      <c r="R112" s="46"/>
+      <c r="S112" s="42"/>
+      <c r="T112" s="42"/>
+    </row>
+    <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A113" s="36">
+        <v>10200010</v>
+      </c>
+      <c r="B113" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C113" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D113" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E113" s="40">
+        <v>10</v>
+      </c>
+      <c r="F113" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G113" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H113" s="47">
+        <v>0</v>
+      </c>
+      <c r="I113" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J113" s="43">
+        <v>0</v>
+      </c>
+      <c r="K113" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="48">
+        <v>0</v>
+      </c>
+      <c r="M113" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O113" s="46"/>
+      <c r="P113" s="46"/>
+      <c r="Q113" s="46"/>
+      <c r="R113" s="46"/>
+      <c r="S113" s="42"/>
+      <c r="T113" s="42"/>
+    </row>
+    <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A114" s="36">
+        <v>10200011</v>
+      </c>
+      <c r="B114" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C114" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D114" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E114" s="40">
+        <v>11</v>
+      </c>
+      <c r="F114" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G114" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H114" s="47">
+        <v>0</v>
+      </c>
+      <c r="I114" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J114" s="43">
+        <v>0</v>
+      </c>
+      <c r="K114" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="48">
+        <v>0</v>
+      </c>
+      <c r="M114" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N114" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O114" s="46"/>
+      <c r="P114" s="46"/>
+      <c r="Q114" s="46"/>
+      <c r="R114" s="46"/>
+      <c r="S114" s="42"/>
+      <c r="T114" s="42"/>
+    </row>
+    <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A115" s="36">
+        <v>10200012</v>
+      </c>
+      <c r="B115" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C115" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D115" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E115" s="40">
+        <v>12</v>
+      </c>
+      <c r="F115" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H115" s="47">
+        <v>0</v>
+      </c>
+      <c r="I115" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J115" s="43">
+        <v>0</v>
+      </c>
+      <c r="K115" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" s="48">
+        <v>0</v>
+      </c>
+      <c r="M115" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N115" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O115" s="46"/>
+      <c r="P115" s="46"/>
+      <c r="Q115" s="46"/>
+      <c r="R115" s="46"/>
+      <c r="S115" s="42"/>
+      <c r="T115" s="42"/>
+    </row>
+    <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A116" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B116" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C116" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D116" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E116" s="40">
+        <v>10</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G116" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H116" s="47">
+        <v>0</v>
+      </c>
+      <c r="I116" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J116" s="43">
+        <v>0</v>
+      </c>
+      <c r="K116" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" s="48">
+        <v>0</v>
+      </c>
+      <c r="M116" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N116" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="O116" s="46"/>
+      <c r="P116" s="46"/>
+      <c r="Q116" s="46"/>
+      <c r="R116" s="46"/>
+      <c r="S116" s="42"/>
+      <c r="T116" s="42"/>
+    </row>
+    <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A117" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B117" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C117" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D117" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E117" s="40">
+        <v>11</v>
+      </c>
+      <c r="F117" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H117" s="47">
+        <v>0</v>
+      </c>
+      <c r="I117" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J117" s="43">
+        <v>0</v>
+      </c>
+      <c r="K117" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" s="48">
+        <v>0</v>
+      </c>
+      <c r="M117" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N117" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O117" s="46"/>
+      <c r="P117" s="46"/>
+      <c r="Q117" s="46"/>
+      <c r="R117" s="46"/>
+      <c r="S117" s="42"/>
+      <c r="T117" s="42"/>
+    </row>
+    <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A118" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B118" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C118" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D118" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E118" s="40">
+        <v>12</v>
+      </c>
+      <c r="F118" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G118" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H118" s="47">
+        <v>0</v>
+      </c>
+      <c r="I118" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J118" s="43">
+        <v>0</v>
+      </c>
+      <c r="K118" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="48">
+        <v>0</v>
+      </c>
+      <c r="M118" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N118" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O118" s="46"/>
+      <c r="P118" s="46"/>
+      <c r="Q118" s="46"/>
+      <c r="R118" s="46"/>
+      <c r="S118" s="42"/>
+      <c r="T118" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -414,12 +414,6 @@
   </si>
   <si>
     <t>金钱兔</t>
-  </si>
-  <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>2_4_10_20_40_100_200</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -643,6 +637,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -657,23 +657,17 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1205,7 +1199,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1350,9 +1344,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1694,7 +1685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -4121,165 +4112,165 @@
       <c r="S49" s="35"/>
       <c r="T49" s="35"/>
     </row>
-    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="29">
-        <v>1036001</v>
-      </c>
-      <c r="B50" s="30">
-        <v>103600</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="32">
-        <v>103600001</v>
-      </c>
-      <c r="E50" s="31">
-        <v>1</v>
+    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A50" s="36">
+        <v>10010010</v>
+      </c>
+      <c r="B50" s="37">
+        <v>100100</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="39">
+        <v>100100026</v>
+      </c>
+      <c r="E50" s="40">
+        <v>10</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="G50" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="28">
-        <v>10000000</v>
-      </c>
-      <c r="I50" s="25">
-        <v>9600</v>
-      </c>
-      <c r="J50" s="23">
-        <v>5000000</v>
-      </c>
-      <c r="K50" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="33">
-        <v>100</v>
-      </c>
-      <c r="M50" s="23" t="s">
+      <c r="H50" s="41">
+        <v>0</v>
+      </c>
+      <c r="I50" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J50" s="43">
+        <v>0</v>
+      </c>
+      <c r="K50" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="44">
+        <v>0</v>
+      </c>
+      <c r="M50" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="N50" s="34">
-        <v>0</v>
-      </c>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-    </row>
-    <row r="51" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A51" s="29">
-        <v>1036002</v>
-      </c>
-      <c r="B51" s="30">
-        <v>103600</v>
-      </c>
-      <c r="C51" s="31" t="s">
+      <c r="N50" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="D51" s="32">
-        <v>103600001</v>
-      </c>
-      <c r="E51" s="31">
-        <v>2</v>
+      <c r="O50" s="46"/>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="46"/>
+      <c r="S50" s="42"/>
+      <c r="T50" s="42"/>
+    </row>
+    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A51" s="36">
+        <v>10010011</v>
+      </c>
+      <c r="B51" s="37">
+        <v>100100</v>
+      </c>
+      <c r="C51" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="39">
+        <v>100100026</v>
+      </c>
+      <c r="E51" s="40">
+        <v>11</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="G51" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H51" s="28">
-        <v>100000000</v>
-      </c>
-      <c r="I51" s="25">
-        <v>9600</v>
-      </c>
-      <c r="J51" s="23">
-        <v>50000000</v>
-      </c>
-      <c r="K51" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="33">
-        <v>100</v>
-      </c>
-      <c r="M51" s="23" t="s">
+      <c r="H51" s="41">
+        <v>0</v>
+      </c>
+      <c r="I51" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J51" s="43">
+        <v>0</v>
+      </c>
+      <c r="K51" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="44">
+        <v>0</v>
+      </c>
+      <c r="M51" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="N51" s="34">
-        <v>0</v>
-      </c>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="34"/>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35"/>
-    </row>
-    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A52" s="29">
-        <v>1036003</v>
-      </c>
-      <c r="B52" s="30">
-        <v>103600</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" s="32">
-        <v>103600001</v>
-      </c>
-      <c r="E52" s="31">
-        <v>3</v>
+      <c r="N51" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="46"/>
+      <c r="S51" s="42"/>
+      <c r="T51" s="42"/>
+    </row>
+    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A52" s="36">
+        <v>10010012</v>
+      </c>
+      <c r="B52" s="37">
+        <v>100100</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="39">
+        <v>100100026</v>
+      </c>
+      <c r="E52" s="40">
+        <v>12</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G52" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="28">
-        <v>1000000000</v>
-      </c>
-      <c r="I52" s="25">
-        <v>9600</v>
-      </c>
-      <c r="J52" s="23">
-        <v>500000000</v>
-      </c>
-      <c r="K52" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="33">
-        <v>100</v>
-      </c>
-      <c r="M52" s="23" t="s">
+      <c r="H52" s="47">
+        <v>0</v>
+      </c>
+      <c r="I52" s="42">
+        <v>9500</v>
+      </c>
+      <c r="J52" s="43">
+        <v>0</v>
+      </c>
+      <c r="K52" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="44">
+        <v>0</v>
+      </c>
+      <c r="M52" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="N52" s="34">
-        <v>0</v>
-      </c>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
+      <c r="N52" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="46"/>
+      <c r="S52" s="42"/>
+      <c r="T52" s="42"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A53" s="36">
-        <v>10010010</v>
+        <v>10030010</v>
       </c>
       <c r="B53" s="37">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D53" s="39">
         <v>100100026</v>
@@ -4288,10 +4279,10 @@
         <v>10</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H53" s="41">
         <v>0</v>
@@ -4305,14 +4296,14 @@
       <c r="K53" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L53" s="44">
+      <c r="L53" s="48">
         <v>0</v>
       </c>
       <c r="M53" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N53" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O53" s="46"/>
       <c r="P53" s="46"/>
@@ -4323,13 +4314,13 @@
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A54" s="36">
-        <v>10010011</v>
+        <v>10030011</v>
       </c>
       <c r="B54" s="37">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D54" s="39">
         <v>100100026</v>
@@ -4338,10 +4329,10 @@
         <v>11</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H54" s="41">
         <v>0</v>
@@ -4355,14 +4346,14 @@
       <c r="K54" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L54" s="44">
+      <c r="L54" s="48">
         <v>0</v>
       </c>
       <c r="M54" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N54" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O54" s="46"/>
       <c r="P54" s="46"/>
@@ -4373,13 +4364,13 @@
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A55" s="36">
-        <v>10010012</v>
+        <v>10030012</v>
       </c>
       <c r="B55" s="37">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D55" s="39">
         <v>100100026</v>
@@ -4388,10 +4379,10 @@
         <v>12</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H55" s="47">
         <v>0</v>
@@ -4405,14 +4396,14 @@
       <c r="K55" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L55" s="44">
+      <c r="L55" s="48">
         <v>0</v>
       </c>
       <c r="M55" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N55" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O55" s="46"/>
       <c r="P55" s="46"/>
@@ -4423,13 +4414,13 @@
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A56" s="36">
-        <v>10030010</v>
+        <v>10070010</v>
       </c>
       <c r="B56" s="37">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D56" s="39">
         <v>100100026</v>
@@ -4438,10 +4429,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H56" s="41">
         <v>0</v>
@@ -4455,14 +4446,14 @@
       <c r="K56" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L56" s="48">
+      <c r="L56" s="44">
         <v>0</v>
       </c>
       <c r="M56" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N56" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O56" s="46"/>
       <c r="P56" s="46"/>
@@ -4473,13 +4464,13 @@
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A57" s="36">
-        <v>10030011</v>
+        <v>10070011</v>
       </c>
       <c r="B57" s="37">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D57" s="39">
         <v>100100026</v>
@@ -4488,10 +4479,10 @@
         <v>11</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H57" s="41">
         <v>0</v>
@@ -4505,14 +4496,14 @@
       <c r="K57" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L57" s="48">
+      <c r="L57" s="44">
         <v>0</v>
       </c>
       <c r="M57" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N57" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O57" s="46"/>
       <c r="P57" s="46"/>
@@ -4523,13 +4514,13 @@
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A58" s="36">
-        <v>10030012</v>
+        <v>10070012</v>
       </c>
       <c r="B58" s="37">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D58" s="39">
         <v>100100026</v>
@@ -4538,10 +4529,10 @@
         <v>12</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H58" s="47">
         <v>0</v>
@@ -4555,14 +4546,14 @@
       <c r="K58" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L58" s="48">
+      <c r="L58" s="44">
         <v>0</v>
       </c>
       <c r="M58" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O58" s="46"/>
       <c r="P58" s="46"/>
@@ -4571,168 +4562,168 @@
       <c r="S58" s="42"/>
       <c r="T58" s="42"/>
     </row>
-    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A59" s="36">
-        <v>10070010</v>
-      </c>
-      <c r="B59" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B59" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="50">
+        <v>101200026</v>
       </c>
       <c r="E59" s="40">
         <v>10</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H59" s="41">
         <v>0</v>
       </c>
-      <c r="I59" s="42">
+      <c r="I59" s="43">
         <v>9500</v>
       </c>
       <c r="J59" s="43">
         <v>0</v>
       </c>
-      <c r="K59" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="44">
-        <v>0</v>
-      </c>
-      <c r="M59" s="42" t="s">
+      <c r="K59" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="48">
+        <v>0</v>
+      </c>
+      <c r="M59" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N59" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="46"/>
-      <c r="R59" s="46"/>
-      <c r="S59" s="42"/>
-      <c r="T59" s="42"/>
-    </row>
-    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>76</v>
+      </c>
+      <c r="O59" s="45"/>
+      <c r="P59" s="45"/>
+      <c r="Q59" s="45"/>
+      <c r="R59" s="45"/>
+      <c r="S59" s="43"/>
+      <c r="T59" s="43"/>
+    </row>
+    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A60" s="36">
-        <v>10070011</v>
-      </c>
-      <c r="B60" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C60" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B60" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="50">
+        <v>101200026</v>
       </c>
       <c r="E60" s="40">
         <v>11</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H60" s="41">
         <v>0</v>
       </c>
-      <c r="I60" s="42">
+      <c r="I60" s="43">
         <v>9500</v>
       </c>
       <c r="J60" s="43">
         <v>0</v>
       </c>
-      <c r="K60" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="44">
-        <v>0</v>
-      </c>
-      <c r="M60" s="42" t="s">
+      <c r="K60" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="48">
+        <v>0</v>
+      </c>
+      <c r="M60" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N60" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="46"/>
-      <c r="R60" s="46"/>
-      <c r="S60" s="42"/>
-      <c r="T60" s="42"/>
-    </row>
-    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>77</v>
+      </c>
+      <c r="O60" s="45"/>
+      <c r="P60" s="45"/>
+      <c r="Q60" s="45"/>
+      <c r="R60" s="45"/>
+      <c r="S60" s="43"/>
+      <c r="T60" s="43"/>
+    </row>
+    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A61" s="36">
-        <v>10070012</v>
-      </c>
-      <c r="B61" s="37">
-        <v>100700</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B61" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="50">
+        <v>101200026</v>
       </c>
       <c r="E61" s="40">
         <v>12</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H61" s="47">
         <v>0</v>
       </c>
-      <c r="I61" s="42">
+      <c r="I61" s="43">
         <v>9500</v>
       </c>
       <c r="J61" s="43">
         <v>0</v>
       </c>
-      <c r="K61" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="44">
-        <v>0</v>
-      </c>
-      <c r="M61" s="42" t="s">
+      <c r="K61" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="48">
+        <v>0</v>
+      </c>
+      <c r="M61" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N61" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="46"/>
-      <c r="R61" s="46"/>
-      <c r="S61" s="42"/>
-      <c r="T61" s="42"/>
-    </row>
-    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>78</v>
+      </c>
+      <c r="O61" s="45"/>
+      <c r="P61" s="45"/>
+      <c r="Q61" s="45"/>
+      <c r="R61" s="45"/>
+      <c r="S61" s="43"/>
+      <c r="T61" s="43"/>
+    </row>
+    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A62" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B62" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" s="50">
-        <v>101200026</v>
+        <v>10140010</v>
+      </c>
+      <c r="B62" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="39">
+        <v>100100026</v>
       </c>
       <c r="E62" s="40">
         <v>10</v>
@@ -4746,43 +4737,43 @@
       <c r="H62" s="41">
         <v>0</v>
       </c>
-      <c r="I62" s="43">
+      <c r="I62" s="42">
         <v>9500</v>
       </c>
       <c r="J62" s="43">
         <v>0</v>
       </c>
-      <c r="K62" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="48">
-        <v>0</v>
-      </c>
-      <c r="M62" s="43" t="s">
+      <c r="K62" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="44">
+        <v>0</v>
+      </c>
+      <c r="M62" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N62" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O62" s="45"/>
-      <c r="P62" s="45"/>
-      <c r="Q62" s="45"/>
-      <c r="R62" s="45"/>
-      <c r="S62" s="43"/>
-      <c r="T62" s="43"/>
-    </row>
-    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>76</v>
+      </c>
+      <c r="O62" s="46"/>
+      <c r="P62" s="46"/>
+      <c r="Q62" s="46"/>
+      <c r="R62" s="46"/>
+      <c r="S62" s="42"/>
+      <c r="T62" s="42"/>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A63" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B63" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D63" s="50">
-        <v>101200026</v>
+        <v>10140011</v>
+      </c>
+      <c r="B63" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="39">
+        <v>100100026</v>
       </c>
       <c r="E63" s="40">
         <v>11</v>
@@ -4796,43 +4787,43 @@
       <c r="H63" s="41">
         <v>0</v>
       </c>
-      <c r="I63" s="43">
+      <c r="I63" s="42">
         <v>9500</v>
       </c>
       <c r="J63" s="43">
         <v>0</v>
       </c>
-      <c r="K63" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="48">
-        <v>0</v>
-      </c>
-      <c r="M63" s="43" t="s">
+      <c r="K63" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="44">
+        <v>0</v>
+      </c>
+      <c r="M63" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N63" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O63" s="45"/>
-      <c r="P63" s="45"/>
-      <c r="Q63" s="45"/>
-      <c r="R63" s="45"/>
-      <c r="S63" s="43"/>
-      <c r="T63" s="43"/>
-    </row>
-    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>77</v>
+      </c>
+      <c r="O63" s="46"/>
+      <c r="P63" s="46"/>
+      <c r="Q63" s="46"/>
+      <c r="R63" s="46"/>
+      <c r="S63" s="42"/>
+      <c r="T63" s="42"/>
+    </row>
+    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A64" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B64" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C64" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D64" s="50">
-        <v>101200026</v>
+        <v>10140012</v>
+      </c>
+      <c r="B64" s="37">
+        <v>101400</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="39">
+        <v>100100026</v>
       </c>
       <c r="E64" s="40">
         <v>12</v>
@@ -4846,52 +4837,52 @@
       <c r="H64" s="47">
         <v>0</v>
       </c>
-      <c r="I64" s="43">
+      <c r="I64" s="42">
         <v>9500</v>
       </c>
       <c r="J64" s="43">
         <v>0</v>
       </c>
-      <c r="K64" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="48">
-        <v>0</v>
-      </c>
-      <c r="M64" s="43" t="s">
+      <c r="K64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="44">
+        <v>0</v>
+      </c>
+      <c r="M64" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O64" s="45"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="45"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="43"/>
-      <c r="T64" s="43"/>
+        <v>78</v>
+      </c>
+      <c r="O64" s="46"/>
+      <c r="P64" s="46"/>
+      <c r="Q64" s="46"/>
+      <c r="R64" s="46"/>
+      <c r="S64" s="42"/>
+      <c r="T64" s="42"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="36">
-        <v>10140010</v>
+        <v>10170010</v>
       </c>
       <c r="B65" s="37">
-        <v>101400</v>
+        <v>101700</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D65" s="39">
-        <v>100100026</v>
+        <v>101700001</v>
       </c>
       <c r="E65" s="40">
         <v>10</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H65" s="41">
         <v>0</v>
@@ -4912,7 +4903,7 @@
         <v>37</v>
       </c>
       <c r="N65" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O65" s="46"/>
       <c r="P65" s="46"/>
@@ -4923,25 +4914,25 @@
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="36">
-        <v>10140011</v>
+        <v>10170011</v>
       </c>
       <c r="B66" s="37">
-        <v>101400</v>
+        <v>101700</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D66" s="39">
-        <v>100100026</v>
+        <v>101700001</v>
       </c>
       <c r="E66" s="40">
         <v>11</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H66" s="41">
         <v>0</v>
@@ -4962,7 +4953,7 @@
         <v>40</v>
       </c>
       <c r="N66" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O66" s="46"/>
       <c r="P66" s="46"/>
@@ -4973,25 +4964,25 @@
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="36">
-        <v>10140012</v>
+        <v>10170012</v>
       </c>
       <c r="B67" s="37">
-        <v>101400</v>
+        <v>101700</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D67" s="39">
-        <v>100100026</v>
+        <v>101700001</v>
       </c>
       <c r="E67" s="40">
         <v>12</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H67" s="47">
         <v>0</v>
@@ -5012,7 +5003,7 @@
         <v>43</v>
       </c>
       <c r="N67" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O67" s="46"/>
       <c r="P67" s="46"/>
@@ -5023,16 +5014,16 @@
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="36">
-        <v>10170010</v>
+        <v>10210010</v>
       </c>
       <c r="B68" s="37">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D68" s="39">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="E68" s="40">
         <v>10</v>
@@ -5055,14 +5046,14 @@
       <c r="K68" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L68" s="44">
+      <c r="L68" s="48">
         <v>0</v>
       </c>
       <c r="M68" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N68" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O68" s="46"/>
       <c r="P68" s="46"/>
@@ -5073,16 +5064,16 @@
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="36">
-        <v>10170011</v>
+        <v>10210011</v>
       </c>
       <c r="B69" s="37">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D69" s="39">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="E69" s="40">
         <v>11</v>
@@ -5105,14 +5096,14 @@
       <c r="K69" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L69" s="44">
+      <c r="L69" s="48">
         <v>0</v>
       </c>
       <c r="M69" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N69" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O69" s="46"/>
       <c r="P69" s="46"/>
@@ -5123,16 +5114,16 @@
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="36">
-        <v>10170012</v>
+        <v>10210012</v>
       </c>
       <c r="B70" s="37">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D70" s="39">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="E70" s="40">
         <v>12</v>
@@ -5155,14 +5146,14 @@
       <c r="K70" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L70" s="44">
+      <c r="L70" s="48">
         <v>0</v>
       </c>
       <c r="M70" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N70" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O70" s="46"/>
       <c r="P70" s="46"/>
@@ -5173,16 +5164,16 @@
     </row>
     <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="36">
-        <v>10210010</v>
+        <v>10220010</v>
       </c>
       <c r="B71" s="37">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D71" s="39">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="E71" s="40">
         <v>10</v>
@@ -5212,7 +5203,7 @@
         <v>37</v>
       </c>
       <c r="N71" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O71" s="46"/>
       <c r="P71" s="46"/>
@@ -5223,16 +5214,16 @@
     </row>
     <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="36">
-        <v>10210011</v>
+        <v>10220011</v>
       </c>
       <c r="B72" s="37">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D72" s="39">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="E72" s="40">
         <v>11</v>
@@ -5262,7 +5253,7 @@
         <v>40</v>
       </c>
       <c r="N72" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O72" s="46"/>
       <c r="P72" s="46"/>
@@ -5273,16 +5264,16 @@
     </row>
     <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="36">
-        <v>10210012</v>
+        <v>10220012</v>
       </c>
       <c r="B73" s="37">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D73" s="39">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="E73" s="40">
         <v>12</v>
@@ -5312,7 +5303,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O73" s="46"/>
       <c r="P73" s="46"/>
@@ -5323,25 +5314,25 @@
     </row>
     <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10220010</v>
+        <v>10240010</v>
       </c>
       <c r="B74" s="37">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D74" s="39">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="E74" s="40">
         <v>10</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H74" s="41">
         <v>0</v>
@@ -5362,7 +5353,7 @@
         <v>37</v>
       </c>
       <c r="N74" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O74" s="46"/>
       <c r="P74" s="46"/>
@@ -5373,25 +5364,25 @@
     </row>
     <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10220011</v>
+        <v>10240011</v>
       </c>
       <c r="B75" s="37">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D75" s="39">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="E75" s="40">
         <v>11</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H75" s="41">
         <v>0</v>
@@ -5412,7 +5403,7 @@
         <v>40</v>
       </c>
       <c r="N75" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O75" s="46"/>
       <c r="P75" s="46"/>
@@ -5423,25 +5414,25 @@
     </row>
     <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10220012</v>
+        <v>10240012</v>
       </c>
       <c r="B76" s="37">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D76" s="39">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="E76" s="40">
         <v>12</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H76" s="47">
         <v>0</v>
@@ -5462,7 +5453,7 @@
         <v>43</v>
       </c>
       <c r="N76" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O76" s="46"/>
       <c r="P76" s="46"/>
@@ -5473,27 +5464,27 @@
     </row>
     <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10240010</v>
+        <v>10180010</v>
       </c>
       <c r="B77" s="37">
-        <v>102400</v>
+        <v>101800</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D77" s="39">
-        <v>102400026</v>
+        <v>101800001</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H77" s="41">
+        <v>51</v>
+      </c>
+      <c r="H77" s="47">
         <v>0</v>
       </c>
       <c r="I77" s="42">
@@ -5512,7 +5503,7 @@
         <v>37</v>
       </c>
       <c r="N77" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O77" s="46"/>
       <c r="P77" s="46"/>
@@ -5523,27 +5514,27 @@
     </row>
     <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10240011</v>
+        <v>10180011</v>
       </c>
       <c r="B78" s="37">
-        <v>102400</v>
+        <v>101800</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D78" s="39">
-        <v>102400026</v>
+        <v>101800001</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H78" s="41">
+        <v>53</v>
+      </c>
+      <c r="H78" s="47">
         <v>0</v>
       </c>
       <c r="I78" s="42">
@@ -5562,7 +5553,7 @@
         <v>40</v>
       </c>
       <c r="N78" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O78" s="46"/>
       <c r="P78" s="46"/>
@@ -5573,25 +5564,25 @@
     </row>
     <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10240012</v>
+        <v>10180012</v>
       </c>
       <c r="B79" s="37">
-        <v>102400</v>
+        <v>101800</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D79" s="39">
-        <v>102400026</v>
+        <v>101800001</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H79" s="47">
         <v>0</v>
@@ -5612,7 +5603,7 @@
         <v>43</v>
       </c>
       <c r="N79" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O79" s="46"/>
       <c r="P79" s="46"/>
@@ -5623,25 +5614,25 @@
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10180010</v>
+        <v>10250010</v>
       </c>
       <c r="B80" s="37">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D80" s="39">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="E80" s="40">
         <v>10</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H80" s="47">
         <v>0</v>
@@ -5662,7 +5653,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5673,25 +5664,25 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10180011</v>
+        <v>10250011</v>
       </c>
       <c r="B81" s="37">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D81" s="39">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="E81" s="40">
         <v>11</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H81" s="47">
         <v>0</v>
@@ -5712,7 +5703,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5723,25 +5714,25 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10180012</v>
+        <v>10250012</v>
       </c>
       <c r="B82" s="37">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D82" s="39">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="E82" s="40">
         <v>12</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H82" s="47">
         <v>0</v>
@@ -5762,7 +5753,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5773,25 +5764,25 @@
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10250010</v>
+        <v>10230010</v>
       </c>
       <c r="B83" s="37">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D83" s="39">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H83" s="47">
         <v>0</v>
@@ -5812,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O83" s="46"/>
       <c r="P83" s="46"/>
@@ -5823,25 +5814,25 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10250011</v>
+        <v>10230011</v>
       </c>
       <c r="B84" s="37">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D84" s="39">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H84" s="47">
         <v>0</v>
@@ -5862,7 +5853,7 @@
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O84" s="46"/>
       <c r="P84" s="46"/>
@@ -5873,25 +5864,25 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10250012</v>
+        <v>10230012</v>
       </c>
       <c r="B85" s="37">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D85" s="39">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H85" s="47">
         <v>0</v>
@@ -5912,7 +5903,7 @@
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O85" s="46"/>
       <c r="P85" s="46"/>
@@ -5923,31 +5914,31 @@
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10230010</v>
+        <v>10340010</v>
       </c>
       <c r="B86" s="37">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D86" s="39">
-        <v>102300001</v>
+        <v>103400001</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H86" s="47">
         <v>0</v>
       </c>
       <c r="I86" s="42">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="J86" s="43">
         <v>0</v>
@@ -5962,7 +5953,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -5973,31 +5964,31 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10230011</v>
+        <v>10340011</v>
       </c>
       <c r="B87" s="37">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D87" s="39">
-        <v>102300001</v>
+        <v>103400001</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="H87" s="47">
         <v>0</v>
       </c>
       <c r="I87" s="42">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="J87" s="43">
         <v>0</v>
@@ -6012,7 +6003,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6023,31 +6014,31 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10230012</v>
+        <v>10340012</v>
       </c>
       <c r="B88" s="37">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D88" s="39">
-        <v>102300001</v>
+        <v>103400001</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
       </c>
       <c r="I88" s="42">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="J88" s="43">
         <v>0</v>
@@ -6062,7 +6053,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6073,25 +6064,25 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10340010</v>
+        <v>10350010</v>
       </c>
       <c r="B89" s="37">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D89" s="39">
-        <v>103400001</v>
+        <v>103500001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="H89" s="47">
         <v>0</v>
@@ -6112,7 +6103,7 @@
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6123,25 +6114,25 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10340011</v>
+        <v>10350011</v>
       </c>
       <c r="B90" s="37">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D90" s="39">
-        <v>103400001</v>
+        <v>103500001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H90" s="47">
         <v>0</v>
@@ -6162,7 +6153,7 @@
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6173,25 +6164,25 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10340012</v>
+        <v>10350012</v>
       </c>
       <c r="B91" s="37">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D91" s="39">
-        <v>103400001</v>
+        <v>103500001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
@@ -6212,7 +6203,7 @@
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6223,16 +6214,16 @@
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10350010</v>
+        <v>10350110</v>
       </c>
       <c r="B92" s="37">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D92" s="39">
-        <v>103500001</v>
+        <v>103501001</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
@@ -6262,7 +6253,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6273,16 +6264,16 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10350011</v>
+        <v>10350111</v>
       </c>
       <c r="B93" s="37">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D93" s="39">
-        <v>103500001</v>
+        <v>103501001</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
@@ -6312,7 +6303,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6323,16 +6314,16 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10350012</v>
+        <v>10350112</v>
       </c>
       <c r="B94" s="37">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D94" s="39">
-        <v>103500001</v>
+        <v>103501001</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
@@ -6362,7 +6353,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6370,306 +6361,6 @@
       <c r="R94" s="46"/>
       <c r="S94" s="42"/>
       <c r="T94" s="42"/>
-    </row>
-    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A95" s="36">
-        <v>10350110</v>
-      </c>
-      <c r="B95" s="37">
-        <v>103501</v>
-      </c>
-      <c r="C95" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D95" s="39">
-        <v>103501001</v>
-      </c>
-      <c r="E95" s="40">
-        <v>10</v>
-      </c>
-      <c r="F95" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G95" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H95" s="47">
-        <v>0</v>
-      </c>
-      <c r="I95" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J95" s="43">
-        <v>0</v>
-      </c>
-      <c r="K95" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L95" s="48">
-        <v>0</v>
-      </c>
-      <c r="M95" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N95" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O95" s="46"/>
-      <c r="P95" s="46"/>
-      <c r="Q95" s="46"/>
-      <c r="R95" s="46"/>
-      <c r="S95" s="42"/>
-      <c r="T95" s="42"/>
-    </row>
-    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A96" s="36">
-        <v>10350111</v>
-      </c>
-      <c r="B96" s="37">
-        <v>103501</v>
-      </c>
-      <c r="C96" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D96" s="39">
-        <v>103501001</v>
-      </c>
-      <c r="E96" s="40">
-        <v>11</v>
-      </c>
-      <c r="F96" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G96" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H96" s="47">
-        <v>0</v>
-      </c>
-      <c r="I96" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J96" s="43">
-        <v>0</v>
-      </c>
-      <c r="K96" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L96" s="48">
-        <v>0</v>
-      </c>
-      <c r="M96" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N96" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O96" s="46"/>
-      <c r="P96" s="46"/>
-      <c r="Q96" s="46"/>
-      <c r="R96" s="46"/>
-      <c r="S96" s="42"/>
-      <c r="T96" s="42"/>
-    </row>
-    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A97" s="36">
-        <v>10350112</v>
-      </c>
-      <c r="B97" s="37">
-        <v>103501</v>
-      </c>
-      <c r="C97" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D97" s="39">
-        <v>103501001</v>
-      </c>
-      <c r="E97" s="40">
-        <v>12</v>
-      </c>
-      <c r="F97" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G97" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H97" s="47">
-        <v>0</v>
-      </c>
-      <c r="I97" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J97" s="43">
-        <v>0</v>
-      </c>
-      <c r="K97" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L97" s="48">
-        <v>0</v>
-      </c>
-      <c r="M97" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N97" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O97" s="46"/>
-      <c r="P97" s="46"/>
-      <c r="Q97" s="46"/>
-      <c r="R97" s="46"/>
-      <c r="S97" s="42"/>
-      <c r="T97" s="42"/>
-    </row>
-    <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A98" s="36">
-        <v>10360010</v>
-      </c>
-      <c r="B98" s="37">
-        <v>103600</v>
-      </c>
-      <c r="C98" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D98" s="39">
-        <v>103600001</v>
-      </c>
-      <c r="E98" s="40">
-        <v>10</v>
-      </c>
-      <c r="F98" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G98" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="H98" s="47">
-        <v>0</v>
-      </c>
-      <c r="I98" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J98" s="43">
-        <v>0</v>
-      </c>
-      <c r="K98" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L98" s="48">
-        <v>0</v>
-      </c>
-      <c r="M98" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N98" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O98" s="46"/>
-      <c r="P98" s="46"/>
-      <c r="Q98" s="46"/>
-      <c r="R98" s="46"/>
-      <c r="S98" s="42"/>
-      <c r="T98" s="42"/>
-    </row>
-    <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A99" s="36">
-        <v>10360011</v>
-      </c>
-      <c r="B99" s="37">
-        <v>103600</v>
-      </c>
-      <c r="C99" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D99" s="39">
-        <v>103600001</v>
-      </c>
-      <c r="E99" s="40">
-        <v>11</v>
-      </c>
-      <c r="F99" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G99" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="H99" s="47">
-        <v>0</v>
-      </c>
-      <c r="I99" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J99" s="43">
-        <v>0</v>
-      </c>
-      <c r="K99" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L99" s="48">
-        <v>0</v>
-      </c>
-      <c r="M99" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N99" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="O99" s="46"/>
-      <c r="P99" s="46"/>
-      <c r="Q99" s="46"/>
-      <c r="R99" s="46"/>
-      <c r="S99" s="42"/>
-      <c r="T99" s="42"/>
-    </row>
-    <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A100" s="36">
-        <v>10360012</v>
-      </c>
-      <c r="B100" s="37">
-        <v>103600</v>
-      </c>
-      <c r="C100" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D100" s="39">
-        <v>103600001</v>
-      </c>
-      <c r="E100" s="40">
-        <v>12</v>
-      </c>
-      <c r="F100" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G100" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="H100" s="47">
-        <v>0</v>
-      </c>
-      <c r="I100" s="42">
-        <v>9600</v>
-      </c>
-      <c r="J100" s="43">
-        <v>0</v>
-      </c>
-      <c r="K100" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L100" s="48">
-        <v>0</v>
-      </c>
-      <c r="M100" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N100" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="O100" s="46"/>
-      <c r="P100" s="46"/>
-      <c r="Q100" s="46"/>
-      <c r="R100" s="46"/>
-      <c r="S100" s="42"/>
-      <c r="T100" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -658,12 +661,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -676,19 +673,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1703,7 +1706,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T118"/>
+  <dimension ref="A1:T124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -4730,165 +4733,165 @@
       <c r="S61" s="23"/>
       <c r="T61" s="23"/>
     </row>
-    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B62" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C62" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E62" s="40">
-        <v>10</v>
+    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A62" s="19">
+        <v>1038001</v>
+      </c>
+      <c r="B62" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E62" s="20">
+        <v>1</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H62" s="41">
-        <v>0</v>
-      </c>
-      <c r="I62" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J62" s="43">
-        <v>0</v>
-      </c>
-      <c r="K62" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="44">
-        <v>0</v>
-      </c>
-      <c r="M62" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="H62" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I62" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J62" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K62" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="27">
+        <v>100</v>
+      </c>
+      <c r="M62" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N62" s="45" t="s">
+      <c r="N62" s="21">
+        <v>0</v>
+      </c>
+      <c r="O62" s="21"/>
+      <c r="P62" s="21"/>
+      <c r="Q62" s="21"/>
+      <c r="R62" s="21"/>
+      <c r="S62" s="23"/>
+      <c r="T62" s="23"/>
+    </row>
+    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A63" s="19">
+        <v>1038002</v>
+      </c>
+      <c r="B63" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="O62" s="46"/>
-      <c r="P62" s="46"/>
-      <c r="Q62" s="46"/>
-      <c r="R62" s="46"/>
-      <c r="S62" s="42"/>
-      <c r="T62" s="42"/>
-    </row>
-    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A63" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B63" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C63" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E63" s="40">
-        <v>11</v>
+      <c r="D63" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E63" s="20">
+        <v>2</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H63" s="41">
-        <v>0</v>
-      </c>
-      <c r="I63" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J63" s="43">
-        <v>0</v>
-      </c>
-      <c r="K63" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="44">
-        <v>0</v>
-      </c>
-      <c r="M63" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I63" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J63" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K63" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="27">
+        <v>100</v>
+      </c>
+      <c r="M63" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N63" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46"/>
-      <c r="Q63" s="46"/>
-      <c r="R63" s="46"/>
-      <c r="S63" s="42"/>
-      <c r="T63" s="42"/>
-    </row>
-    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A64" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B64" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C64" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E64" s="40">
-        <v>12</v>
+      <c r="N63" s="21">
+        <v>0</v>
+      </c>
+      <c r="O63" s="21"/>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="21"/>
+      <c r="R63" s="21"/>
+      <c r="S63" s="23"/>
+      <c r="T63" s="23"/>
+    </row>
+    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A64" s="19">
+        <v>1038003</v>
+      </c>
+      <c r="B64" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E64" s="20">
+        <v>3</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H64" s="47">
-        <v>0</v>
-      </c>
-      <c r="I64" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J64" s="43">
-        <v>0</v>
-      </c>
-      <c r="K64" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="44">
-        <v>0</v>
-      </c>
-      <c r="M64" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I64" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J64" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K64" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="27">
+        <v>100</v>
+      </c>
+      <c r="M64" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N64" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O64" s="46"/>
-      <c r="P64" s="46"/>
-      <c r="Q64" s="46"/>
-      <c r="R64" s="46"/>
-      <c r="S64" s="42"/>
-      <c r="T64" s="42"/>
+      <c r="N64" s="21">
+        <v>0</v>
+      </c>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+      <c r="R64" s="21"/>
+      <c r="S64" s="23"/>
+      <c r="T64" s="23"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A65" s="36">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B65" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D65" s="39">
         <v>100100026</v>
@@ -4897,10 +4900,10 @@
         <v>10</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H65" s="41">
         <v>0</v>
@@ -4914,14 +4917,14 @@
       <c r="K65" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L65" s="48">
+      <c r="L65" s="44">
         <v>0</v>
       </c>
       <c r="M65" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N65" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O65" s="46"/>
       <c r="P65" s="46"/>
@@ -4932,13 +4935,13 @@
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A66" s="36">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B66" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D66" s="39">
         <v>100100026</v>
@@ -4947,10 +4950,10 @@
         <v>11</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H66" s="41">
         <v>0</v>
@@ -4964,14 +4967,14 @@
       <c r="K66" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L66" s="48">
+      <c r="L66" s="44">
         <v>0</v>
       </c>
       <c r="M66" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N66" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O66" s="46"/>
       <c r="P66" s="46"/>
@@ -4982,13 +4985,13 @@
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A67" s="36">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B67" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D67" s="39">
         <v>100100026</v>
@@ -4997,10 +5000,10 @@
         <v>12</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H67" s="47">
         <v>0</v>
@@ -5014,14 +5017,14 @@
       <c r="K67" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L67" s="48">
+      <c r="L67" s="44">
         <v>0</v>
       </c>
       <c r="M67" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N67" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O67" s="46"/>
       <c r="P67" s="46"/>
@@ -5032,13 +5035,13 @@
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="36">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B68" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D68" s="39">
         <v>100100026</v>
@@ -5047,10 +5050,10 @@
         <v>10</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H68" s="41">
         <v>0</v>
@@ -5064,14 +5067,14 @@
       <c r="K68" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L68" s="44">
+      <c r="L68" s="48">
         <v>0</v>
       </c>
       <c r="M68" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N68" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O68" s="46"/>
       <c r="P68" s="46"/>
@@ -5082,13 +5085,13 @@
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="36">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B69" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D69" s="39">
         <v>100100026</v>
@@ -5097,10 +5100,10 @@
         <v>11</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H69" s="41">
         <v>0</v>
@@ -5114,14 +5117,14 @@
       <c r="K69" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L69" s="44">
+      <c r="L69" s="48">
         <v>0</v>
       </c>
       <c r="M69" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N69" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O69" s="46"/>
       <c r="P69" s="46"/>
@@ -5132,13 +5135,13 @@
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="36">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B70" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D70" s="39">
         <v>100100026</v>
@@ -5147,10 +5150,10 @@
         <v>12</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H70" s="47">
         <v>0</v>
@@ -5164,14 +5167,14 @@
       <c r="K70" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L70" s="44">
+      <c r="L70" s="48">
         <v>0</v>
       </c>
       <c r="M70" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N70" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O70" s="46"/>
       <c r="P70" s="46"/>
@@ -5180,168 +5183,168 @@
       <c r="S70" s="42"/>
       <c r="T70" s="42"/>
     </row>
-    <row r="71" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B71" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C71" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D71" s="50">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B71" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" s="39">
+        <v>100100026</v>
       </c>
       <c r="E71" s="40">
         <v>10</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H71" s="41">
         <v>0</v>
       </c>
-      <c r="I71" s="43">
+      <c r="I71" s="42">
         <v>9500</v>
       </c>
       <c r="J71" s="43">
         <v>0</v>
       </c>
-      <c r="K71" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L71" s="48">
-        <v>0</v>
-      </c>
-      <c r="M71" s="43" t="s">
+      <c r="K71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="44">
+        <v>0</v>
+      </c>
+      <c r="M71" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N71" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="O71" s="45"/>
-      <c r="P71" s="45"/>
-      <c r="Q71" s="45"/>
-      <c r="R71" s="45"/>
-      <c r="S71" s="43"/>
-      <c r="T71" s="43"/>
-    </row>
-    <row r="72" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="O71" s="46"/>
+      <c r="P71" s="46"/>
+      <c r="Q71" s="46"/>
+      <c r="R71" s="46"/>
+      <c r="S71" s="42"/>
+      <c r="T71" s="42"/>
+    </row>
+    <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B72" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C72" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D72" s="50">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B72" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C72" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" s="39">
+        <v>100100026</v>
       </c>
       <c r="E72" s="40">
         <v>11</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H72" s="41">
         <v>0</v>
       </c>
-      <c r="I72" s="43">
+      <c r="I72" s="42">
         <v>9500</v>
       </c>
       <c r="J72" s="43">
         <v>0</v>
       </c>
-      <c r="K72" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L72" s="48">
-        <v>0</v>
-      </c>
-      <c r="M72" s="43" t="s">
+      <c r="K72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="44">
+        <v>0</v>
+      </c>
+      <c r="M72" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N72" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O72" s="45"/>
-      <c r="P72" s="45"/>
-      <c r="Q72" s="45"/>
-      <c r="R72" s="45"/>
-      <c r="S72" s="43"/>
-      <c r="T72" s="43"/>
-    </row>
-    <row r="73" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>83</v>
+      </c>
+      <c r="O72" s="46"/>
+      <c r="P72" s="46"/>
+      <c r="Q72" s="46"/>
+      <c r="R72" s="46"/>
+      <c r="S72" s="42"/>
+      <c r="T72" s="42"/>
+    </row>
+    <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B73" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C73" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D73" s="50">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B73" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C73" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" s="39">
+        <v>100100026</v>
       </c>
       <c r="E73" s="40">
         <v>12</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H73" s="47">
         <v>0</v>
       </c>
-      <c r="I73" s="43">
+      <c r="I73" s="42">
         <v>9500</v>
       </c>
       <c r="J73" s="43">
         <v>0</v>
       </c>
-      <c r="K73" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L73" s="48">
-        <v>0</v>
-      </c>
-      <c r="M73" s="43" t="s">
+      <c r="K73" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="44">
+        <v>0</v>
+      </c>
+      <c r="M73" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N73" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O73" s="45"/>
-      <c r="P73" s="45"/>
-      <c r="Q73" s="45"/>
-      <c r="R73" s="45"/>
-      <c r="S73" s="43"/>
-      <c r="T73" s="43"/>
-    </row>
-    <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>84</v>
+      </c>
+      <c r="O73" s="46"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="46"/>
+      <c r="R73" s="46"/>
+      <c r="S73" s="42"/>
+      <c r="T73" s="42"/>
+    </row>
+    <row r="74" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10140010</v>
-      </c>
-      <c r="B74" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C74" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B74" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C74" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" s="50">
+        <v>101200026</v>
       </c>
       <c r="E74" s="40">
         <v>10</v>
@@ -5355,43 +5358,43 @@
       <c r="H74" s="41">
         <v>0</v>
       </c>
-      <c r="I74" s="42">
+      <c r="I74" s="43">
         <v>9500</v>
       </c>
       <c r="J74" s="43">
         <v>0</v>
       </c>
-      <c r="K74" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L74" s="44">
-        <v>0</v>
-      </c>
-      <c r="M74" s="42" t="s">
+      <c r="K74" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="48">
+        <v>0</v>
+      </c>
+      <c r="M74" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N74" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="O74" s="46"/>
-      <c r="P74" s="46"/>
-      <c r="Q74" s="46"/>
-      <c r="R74" s="46"/>
-      <c r="S74" s="42"/>
-      <c r="T74" s="42"/>
-    </row>
-    <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="O74" s="45"/>
+      <c r="P74" s="45"/>
+      <c r="Q74" s="45"/>
+      <c r="R74" s="45"/>
+      <c r="S74" s="43"/>
+      <c r="T74" s="43"/>
+    </row>
+    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10140011</v>
-      </c>
-      <c r="B75" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D75" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B75" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C75" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" s="50">
+        <v>101200026</v>
       </c>
       <c r="E75" s="40">
         <v>11</v>
@@ -5405,43 +5408,43 @@
       <c r="H75" s="41">
         <v>0</v>
       </c>
-      <c r="I75" s="42">
+      <c r="I75" s="43">
         <v>9500</v>
       </c>
       <c r="J75" s="43">
         <v>0</v>
       </c>
-      <c r="K75" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L75" s="44">
-        <v>0</v>
-      </c>
-      <c r="M75" s="42" t="s">
+      <c r="K75" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="48">
+        <v>0</v>
+      </c>
+      <c r="M75" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N75" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O75" s="46"/>
-      <c r="P75" s="46"/>
-      <c r="Q75" s="46"/>
-      <c r="R75" s="46"/>
-      <c r="S75" s="42"/>
-      <c r="T75" s="42"/>
-    </row>
-    <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>83</v>
+      </c>
+      <c r="O75" s="45"/>
+      <c r="P75" s="45"/>
+      <c r="Q75" s="45"/>
+      <c r="R75" s="45"/>
+      <c r="S75" s="43"/>
+      <c r="T75" s="43"/>
+    </row>
+    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10140012</v>
-      </c>
-      <c r="B76" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C76" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B76" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C76" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D76" s="50">
+        <v>101200026</v>
       </c>
       <c r="E76" s="40">
         <v>12</v>
@@ -5455,52 +5458,52 @@
       <c r="H76" s="47">
         <v>0</v>
       </c>
-      <c r="I76" s="42">
+      <c r="I76" s="43">
         <v>9500</v>
       </c>
       <c r="J76" s="43">
         <v>0</v>
       </c>
-      <c r="K76" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="44">
-        <v>0</v>
-      </c>
-      <c r="M76" s="42" t="s">
+      <c r="K76" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="48">
+        <v>0</v>
+      </c>
+      <c r="M76" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N76" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O76" s="46"/>
-      <c r="P76" s="46"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="46"/>
-      <c r="S76" s="42"/>
-      <c r="T76" s="42"/>
+        <v>84</v>
+      </c>
+      <c r="O76" s="45"/>
+      <c r="P76" s="45"/>
+      <c r="Q76" s="45"/>
+      <c r="R76" s="45"/>
+      <c r="S76" s="43"/>
+      <c r="T76" s="43"/>
     </row>
     <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B77" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D77" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H77" s="41">
         <v>0</v>
@@ -5521,7 +5524,7 @@
         <v>37</v>
       </c>
       <c r="N77" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O77" s="46"/>
       <c r="P77" s="46"/>
@@ -5532,25 +5535,25 @@
     </row>
     <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B78" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D78" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H78" s="41">
         <v>0</v>
@@ -5571,7 +5574,7 @@
         <v>40</v>
       </c>
       <c r="N78" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O78" s="46"/>
       <c r="P78" s="46"/>
@@ -5582,25 +5585,25 @@
     </row>
     <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B79" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D79" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H79" s="47">
         <v>0</v>
@@ -5621,7 +5624,7 @@
         <v>43</v>
       </c>
       <c r="N79" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O79" s="46"/>
       <c r="P79" s="46"/>
@@ -5632,16 +5635,16 @@
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B80" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D80" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E80" s="40">
         <v>10</v>
@@ -5664,14 +5667,14 @@
       <c r="K80" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L80" s="48">
+      <c r="L80" s="44">
         <v>0</v>
       </c>
       <c r="M80" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5682,16 +5685,16 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B81" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D81" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E81" s="40">
         <v>11</v>
@@ -5714,14 +5717,14 @@
       <c r="K81" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L81" s="48">
+      <c r="L81" s="44">
         <v>0</v>
       </c>
       <c r="M81" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5732,16 +5735,16 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B82" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D82" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E82" s="40">
         <v>12</v>
@@ -5764,14 +5767,14 @@
       <c r="K82" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L82" s="48">
+      <c r="L82" s="44">
         <v>0</v>
       </c>
       <c r="M82" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5782,16 +5785,16 @@
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B83" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D83" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
@@ -5821,7 +5824,7 @@
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O83" s="46"/>
       <c r="P83" s="46"/>
@@ -5832,16 +5835,16 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B84" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
@@ -5871,7 +5874,7 @@
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O84" s="46"/>
       <c r="P84" s="46"/>
@@ -5882,16 +5885,16 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B85" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
@@ -5921,7 +5924,7 @@
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O85" s="46"/>
       <c r="P85" s="46"/>
@@ -5932,25 +5935,25 @@
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B86" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D86" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H86" s="41">
         <v>0</v>
@@ -5971,7 +5974,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -5982,25 +5985,25 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B87" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D87" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H87" s="41">
         <v>0</v>
@@ -6021,7 +6024,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6032,25 +6035,25 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B88" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D88" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6071,7 +6074,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6082,27 +6085,27 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B89" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D89" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H89" s="47">
+        <v>35</v>
+      </c>
+      <c r="H89" s="41">
         <v>0</v>
       </c>
       <c r="I89" s="42">
@@ -6121,7 +6124,7 @@
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6132,27 +6135,27 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B90" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D90" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H90" s="47">
+        <v>39</v>
+      </c>
+      <c r="H90" s="41">
         <v>0</v>
       </c>
       <c r="I90" s="42">
@@ -6171,7 +6174,7 @@
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6182,25 +6185,25 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B91" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D91" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
@@ -6221,7 +6224,7 @@
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6232,25 +6235,25 @@
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B92" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D92" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H92" s="47">
         <v>0</v>
@@ -6271,7 +6274,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6282,25 +6285,25 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B93" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D93" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H93" s="47">
         <v>0</v>
@@ -6321,7 +6324,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6332,25 +6335,25 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B94" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D94" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
@@ -6371,7 +6374,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6382,25 +6385,25 @@
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B95" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D95" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H95" s="47">
         <v>0</v>
@@ -6421,7 +6424,7 @@
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6432,25 +6435,25 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B96" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D96" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H96" s="47">
         <v>0</v>
@@ -6471,7 +6474,7 @@
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6482,25 +6485,25 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B97" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D97" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G97" s="22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H97" s="47">
         <v>0</v>
@@ -6521,7 +6524,7 @@
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6532,31 +6535,31 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B98" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D98" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H98" s="47">
         <v>0</v>
       </c>
       <c r="I98" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J98" s="43">
         <v>0</v>
@@ -6571,7 +6574,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6582,31 +6585,31 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B99" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D99" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H99" s="47">
         <v>0</v>
       </c>
       <c r="I99" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J99" s="43">
         <v>0</v>
@@ -6621,7 +6624,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6632,31 +6635,31 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B100" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D100" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
       </c>
       <c r="I100" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J100" s="43">
         <v>0</v>
@@ -6671,7 +6674,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6682,25 +6685,25 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B101" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D101" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G101" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H101" s="47">
         <v>0</v>
@@ -6721,7 +6724,7 @@
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6732,25 +6735,25 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B102" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D102" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H102" s="47">
         <v>0</v>
@@ -6771,7 +6774,7 @@
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6782,25 +6785,25 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B103" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D103" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
       </c>
       <c r="F103" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G103" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H103" s="47">
         <v>0</v>
@@ -6821,7 +6824,7 @@
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6832,16 +6835,16 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B104" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D104" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
@@ -6871,7 +6874,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6882,16 +6885,16 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B105" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D105" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
@@ -6921,7 +6924,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6932,16 +6935,16 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B106" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D106" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
@@ -6971,7 +6974,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -6982,25 +6985,25 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B107" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D107" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
       </c>
-      <c r="F107" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G107" s="51" t="s">
-        <v>35</v>
+      <c r="F107" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H107" s="47">
         <v>0</v>
@@ -7021,7 +7024,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7032,25 +7035,25 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B108" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D108" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
       </c>
-      <c r="F108" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G108" s="51" t="s">
-        <v>39</v>
+      <c r="F108" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G108" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H108" s="47">
         <v>0</v>
@@ -7071,7 +7074,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7082,25 +7085,25 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B109" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D109" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
       </c>
-      <c r="F109" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G109" s="51" t="s">
-        <v>42</v>
+      <c r="F109" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G109" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H109" s="47">
         <v>0</v>
@@ -7121,7 +7124,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7132,25 +7135,25 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B110" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D110" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
       <c r="F110" s="46" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G110" s="51" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="H110" s="47">
         <v>0</v>
@@ -7171,7 +7174,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7182,25 +7185,25 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B111" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D111" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
       <c r="F111" s="46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G111" s="51" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="H111" s="47">
         <v>0</v>
@@ -7221,7 +7224,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7232,25 +7235,25 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B112" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D112" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
       <c r="F112" s="46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G112" s="51" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
@@ -7271,7 +7274,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7282,16 +7285,16 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B113" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D113" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
@@ -7321,7 +7324,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7332,16 +7335,16 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B114" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D114" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
@@ -7371,7 +7374,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7382,16 +7385,16 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B115" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D115" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
@@ -7421,7 +7424,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7432,25 +7435,25 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B116" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D116" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D116" s="39">
+        <v>102000001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
       </c>
-      <c r="F116" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G116" s="22" t="s">
-        <v>67</v>
+      <c r="F116" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G116" s="51" t="s">
+        <v>65</v>
       </c>
       <c r="H116" s="47">
         <v>0</v>
@@ -7471,7 +7474,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7482,25 +7485,25 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B117" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D117" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D117" s="39">
+        <v>102000001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
       </c>
-      <c r="F117" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G117" s="22" t="s">
-        <v>69</v>
+      <c r="F117" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G117" s="51" t="s">
+        <v>67</v>
       </c>
       <c r="H117" s="47">
         <v>0</v>
@@ -7521,7 +7524,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7532,25 +7535,25 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B118" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D118" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D118" s="39">
+        <v>102000001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
       </c>
-      <c r="F118" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="G118" s="22" t="s">
-        <v>73</v>
+      <c r="F118" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G118" s="51" t="s">
+        <v>69</v>
       </c>
       <c r="H118" s="47">
         <v>0</v>
@@ -7571,7 +7574,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7579,6 +7582,306 @@
       <c r="R118" s="46"/>
       <c r="S118" s="42"/>
       <c r="T118" s="42"/>
+    </row>
+    <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A119" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B119" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C119" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D119" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E119" s="40">
+        <v>10</v>
+      </c>
+      <c r="F119" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G119" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H119" s="47">
+        <v>0</v>
+      </c>
+      <c r="I119" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J119" s="43">
+        <v>0</v>
+      </c>
+      <c r="K119" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L119" s="48">
+        <v>0</v>
+      </c>
+      <c r="M119" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O119" s="46"/>
+      <c r="P119" s="46"/>
+      <c r="Q119" s="46"/>
+      <c r="R119" s="46"/>
+      <c r="S119" s="42"/>
+      <c r="T119" s="42"/>
+    </row>
+    <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A120" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B120" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C120" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D120" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E120" s="40">
+        <v>11</v>
+      </c>
+      <c r="F120" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G120" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H120" s="47">
+        <v>0</v>
+      </c>
+      <c r="I120" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J120" s="43">
+        <v>0</v>
+      </c>
+      <c r="K120" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L120" s="48">
+        <v>0</v>
+      </c>
+      <c r="M120" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N120" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O120" s="46"/>
+      <c r="P120" s="46"/>
+      <c r="Q120" s="46"/>
+      <c r="R120" s="46"/>
+      <c r="S120" s="42"/>
+      <c r="T120" s="42"/>
+    </row>
+    <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A121" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B121" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C121" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D121" s="24">
+        <v>103400001</v>
+      </c>
+      <c r="E121" s="40">
+        <v>12</v>
+      </c>
+      <c r="F121" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H121" s="47">
+        <v>0</v>
+      </c>
+      <c r="I121" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J121" s="43">
+        <v>0</v>
+      </c>
+      <c r="K121" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L121" s="48">
+        <v>0</v>
+      </c>
+      <c r="M121" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N121" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="O121" s="46"/>
+      <c r="P121" s="46"/>
+      <c r="Q121" s="46"/>
+      <c r="R121" s="46"/>
+      <c r="S121" s="42"/>
+      <c r="T121" s="42"/>
+    </row>
+    <row r="122" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A122" s="19">
+        <v>10380010</v>
+      </c>
+      <c r="B122" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D122" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E122" s="20">
+        <v>11</v>
+      </c>
+      <c r="F122" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G122" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H122" s="47">
+        <v>0</v>
+      </c>
+      <c r="I122" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J122" s="43">
+        <v>0</v>
+      </c>
+      <c r="K122" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L122" s="48">
+        <v>0</v>
+      </c>
+      <c r="M122" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N122" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="O122" s="21"/>
+      <c r="P122" s="21"/>
+      <c r="Q122" s="21"/>
+      <c r="R122" s="21"/>
+      <c r="S122" s="23"/>
+      <c r="T122" s="23"/>
+    </row>
+    <row r="123" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A123" s="19">
+        <v>10380011</v>
+      </c>
+      <c r="B123" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D123" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E123" s="20">
+        <v>12</v>
+      </c>
+      <c r="F123" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G123" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H123" s="47">
+        <v>0</v>
+      </c>
+      <c r="I123" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J123" s="43">
+        <v>0</v>
+      </c>
+      <c r="K123" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" s="48">
+        <v>0</v>
+      </c>
+      <c r="M123" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N123" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O123" s="21"/>
+      <c r="P123" s="21"/>
+      <c r="Q123" s="21"/>
+      <c r="R123" s="21"/>
+      <c r="S123" s="23"/>
+      <c r="T123" s="23"/>
+    </row>
+    <row r="124" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A124" s="19">
+        <v>10380012</v>
+      </c>
+      <c r="B124" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D124" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E124" s="20">
+        <v>13</v>
+      </c>
+      <c r="F124" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G124" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H124" s="47">
+        <v>0</v>
+      </c>
+      <c r="I124" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J124" s="43">
+        <v>0</v>
+      </c>
+      <c r="K124" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L124" s="48">
+        <v>0</v>
+      </c>
+      <c r="M124" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N124" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="O124" s="21"/>
+      <c r="P124" s="21"/>
+      <c r="Q124" s="21"/>
+      <c r="R124" s="21"/>
+      <c r="S124" s="23"/>
+      <c r="T124" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -429,13 +429,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0_);[Red]\(&quot;￥&quot;#,##0\)"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -637,6 +638,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -648,6 +656,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -655,27 +669,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1199,7 +1200,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1344,6 +1345,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1685,7 +1692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3673,7 +3680,7 @@
         <v>71</v>
       </c>
       <c r="D41" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E41" s="20">
         <v>1</v>
@@ -3723,7 +3730,7 @@
         <v>71</v>
       </c>
       <c r="D42" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E42" s="20">
         <v>2</v>
@@ -3773,7 +3780,7 @@
         <v>71</v>
       </c>
       <c r="D43" s="24">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E43" s="20">
         <v>3</v>
@@ -3823,7 +3830,7 @@
         <v>74</v>
       </c>
       <c r="D44" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E44" s="31">
         <v>1</v>
@@ -3873,7 +3880,7 @@
         <v>74</v>
       </c>
       <c r="D45" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E45" s="31">
         <v>2</v>
@@ -3923,7 +3930,7 @@
         <v>74</v>
       </c>
       <c r="D46" s="32">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E46" s="31">
         <v>3</v>
@@ -5923,7 +5930,7 @@
         <v>71</v>
       </c>
       <c r="D86" s="39">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
@@ -5973,7 +5980,7 @@
         <v>71</v>
       </c>
       <c r="D87" s="39">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
@@ -6023,7 +6030,7 @@
         <v>71</v>
       </c>
       <c r="D88" s="39">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
@@ -6073,7 +6080,7 @@
         <v>74</v>
       </c>
       <c r="D89" s="39">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
@@ -6123,7 +6130,7 @@
         <v>74</v>
       </c>
       <c r="D90" s="39">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
@@ -6173,7 +6180,7 @@
         <v>74</v>
       </c>
       <c r="D91" s="39">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
@@ -6361,6 +6368,13 @@
       <c r="R94" s="46"/>
       <c r="S94" s="42"/>
       <c r="T94" s="42"/>
+    </row>
+    <row r="98" spans="6:7">
+      <c r="F98" s="51"/>
+      <c r="G98" s="52"/>
+    </row>
+    <row r="99" spans="6:7">
+      <c r="G99" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="86">
   <si>
     <t>id</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>象财神</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -661,6 +664,13 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -673,22 +683,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1706,7 +1709,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T124"/>
+  <dimension ref="A1:T130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -4883,165 +4886,165 @@
       <c r="S64" s="23"/>
       <c r="T64" s="23"/>
     </row>
-    <row r="65" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A65" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B65" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C65" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D65" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E65" s="40">
-        <v>10</v>
+    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A65" s="19">
+        <v>1027001</v>
+      </c>
+      <c r="B65" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E65" s="20">
+        <v>1</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H65" s="41">
-        <v>0</v>
-      </c>
-      <c r="I65" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J65" s="43">
-        <v>0</v>
-      </c>
-      <c r="K65" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L65" s="44">
-        <v>0</v>
-      </c>
-      <c r="M65" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I65" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J65" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K65" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="27">
+        <v>100</v>
+      </c>
+      <c r="M65" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N65" s="45" t="s">
+      <c r="N65" s="21">
+        <v>0</v>
+      </c>
+      <c r="O65" s="21"/>
+      <c r="P65" s="21"/>
+      <c r="Q65" s="21"/>
+      <c r="R65" s="21"/>
+      <c r="S65" s="23"/>
+      <c r="T65" s="23"/>
+    </row>
+    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A66" s="19">
+        <v>1027002</v>
+      </c>
+      <c r="B66" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C66" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="O65" s="46"/>
-      <c r="P65" s="46"/>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="46"/>
-      <c r="S65" s="42"/>
-      <c r="T65" s="42"/>
-    </row>
-    <row r="66" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A66" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B66" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C66" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E66" s="40">
-        <v>11</v>
+      <c r="D66" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E66" s="20">
+        <v>2</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H66" s="41">
-        <v>0</v>
-      </c>
-      <c r="I66" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J66" s="43">
-        <v>0</v>
-      </c>
-      <c r="K66" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L66" s="44">
-        <v>0</v>
-      </c>
-      <c r="M66" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H66" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I66" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J66" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K66" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="27">
+        <v>100</v>
+      </c>
+      <c r="M66" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N66" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O66" s="46"/>
-      <c r="P66" s="46"/>
-      <c r="Q66" s="46"/>
-      <c r="R66" s="46"/>
-      <c r="S66" s="42"/>
-      <c r="T66" s="42"/>
-    </row>
-    <row r="67" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A67" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B67" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C67" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E67" s="40">
-        <v>12</v>
+      <c r="N66" s="21">
+        <v>0</v>
+      </c>
+      <c r="O66" s="21"/>
+      <c r="P66" s="21"/>
+      <c r="Q66" s="21"/>
+      <c r="R66" s="21"/>
+      <c r="S66" s="23"/>
+      <c r="T66" s="23"/>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A67" s="19">
+        <v>1027003</v>
+      </c>
+      <c r="B67" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E67" s="20">
+        <v>3</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H67" s="47">
-        <v>0</v>
-      </c>
-      <c r="I67" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J67" s="43">
-        <v>0</v>
-      </c>
-      <c r="K67" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L67" s="44">
-        <v>0</v>
-      </c>
-      <c r="M67" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="H67" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I67" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J67" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K67" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="27">
+        <v>100</v>
+      </c>
+      <c r="M67" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N67" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O67" s="46"/>
-      <c r="P67" s="46"/>
-      <c r="Q67" s="46"/>
-      <c r="R67" s="46"/>
-      <c r="S67" s="42"/>
-      <c r="T67" s="42"/>
+      <c r="N67" s="21">
+        <v>0</v>
+      </c>
+      <c r="O67" s="21"/>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="21"/>
+      <c r="R67" s="21"/>
+      <c r="S67" s="23"/>
+      <c r="T67" s="23"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A68" s="36">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B68" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D68" s="39">
         <v>100100026</v>
@@ -5050,10 +5053,10 @@
         <v>10</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H68" s="41">
         <v>0</v>
@@ -5067,14 +5070,14 @@
       <c r="K68" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L68" s="48">
+      <c r="L68" s="44">
         <v>0</v>
       </c>
       <c r="M68" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N68" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O68" s="46"/>
       <c r="P68" s="46"/>
@@ -5085,13 +5088,13 @@
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A69" s="36">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B69" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D69" s="39">
         <v>100100026</v>
@@ -5100,10 +5103,10 @@
         <v>11</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H69" s="41">
         <v>0</v>
@@ -5117,14 +5120,14 @@
       <c r="K69" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L69" s="48">
+      <c r="L69" s="44">
         <v>0</v>
       </c>
       <c r="M69" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N69" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O69" s="46"/>
       <c r="P69" s="46"/>
@@ -5135,13 +5138,13 @@
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A70" s="36">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B70" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D70" s="39">
         <v>100100026</v>
@@ -5150,10 +5153,10 @@
         <v>12</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H70" s="47">
         <v>0</v>
@@ -5167,14 +5170,14 @@
       <c r="K70" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L70" s="48">
+      <c r="L70" s="44">
         <v>0</v>
       </c>
       <c r="M70" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N70" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O70" s="46"/>
       <c r="P70" s="46"/>
@@ -5185,13 +5188,13 @@
     </row>
     <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A71" s="36">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B71" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D71" s="39">
         <v>100100026</v>
@@ -5200,10 +5203,10 @@
         <v>10</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H71" s="41">
         <v>0</v>
@@ -5217,14 +5220,14 @@
       <c r="K71" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L71" s="44">
+      <c r="L71" s="48">
         <v>0</v>
       </c>
       <c r="M71" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N71" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O71" s="46"/>
       <c r="P71" s="46"/>
@@ -5235,13 +5238,13 @@
     </row>
     <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A72" s="36">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B72" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D72" s="39">
         <v>100100026</v>
@@ -5250,10 +5253,10 @@
         <v>11</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H72" s="41">
         <v>0</v>
@@ -5267,14 +5270,14 @@
       <c r="K72" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L72" s="44">
+      <c r="L72" s="48">
         <v>0</v>
       </c>
       <c r="M72" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N72" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O72" s="46"/>
       <c r="P72" s="46"/>
@@ -5285,13 +5288,13 @@
     </row>
     <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A73" s="36">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B73" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D73" s="39">
         <v>100100026</v>
@@ -5300,10 +5303,10 @@
         <v>12</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H73" s="47">
         <v>0</v>
@@ -5317,14 +5320,14 @@
       <c r="K73" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L73" s="44">
+      <c r="L73" s="48">
         <v>0</v>
       </c>
       <c r="M73" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N73" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O73" s="46"/>
       <c r="P73" s="46"/>
@@ -5333,168 +5336,168 @@
       <c r="S73" s="42"/>
       <c r="T73" s="42"/>
     </row>
-    <row r="74" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B74" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C74" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D74" s="50">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B74" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C74" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74" s="39">
+        <v>100100026</v>
       </c>
       <c r="E74" s="40">
         <v>10</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H74" s="41">
         <v>0</v>
       </c>
-      <c r="I74" s="43">
+      <c r="I74" s="42">
         <v>9500</v>
       </c>
       <c r="J74" s="43">
         <v>0</v>
       </c>
-      <c r="K74" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L74" s="48">
-        <v>0</v>
-      </c>
-      <c r="M74" s="43" t="s">
+      <c r="K74" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="44">
+        <v>0</v>
+      </c>
+      <c r="M74" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N74" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O74" s="45"/>
-      <c r="P74" s="45"/>
-      <c r="Q74" s="45"/>
-      <c r="R74" s="45"/>
-      <c r="S74" s="43"/>
-      <c r="T74" s="43"/>
-    </row>
-    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>83</v>
+      </c>
+      <c r="O74" s="46"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="46"/>
+      <c r="R74" s="46"/>
+      <c r="S74" s="42"/>
+      <c r="T74" s="42"/>
+    </row>
+    <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B75" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C75" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D75" s="50">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B75" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C75" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D75" s="39">
+        <v>100100026</v>
       </c>
       <c r="E75" s="40">
         <v>11</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H75" s="41">
         <v>0</v>
       </c>
-      <c r="I75" s="43">
+      <c r="I75" s="42">
         <v>9500</v>
       </c>
       <c r="J75" s="43">
         <v>0</v>
       </c>
-      <c r="K75" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L75" s="48">
-        <v>0</v>
-      </c>
-      <c r="M75" s="43" t="s">
+      <c r="K75" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="44">
+        <v>0</v>
+      </c>
+      <c r="M75" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N75" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O75" s="45"/>
-      <c r="P75" s="45"/>
-      <c r="Q75" s="45"/>
-      <c r="R75" s="45"/>
-      <c r="S75" s="43"/>
-      <c r="T75" s="43"/>
-    </row>
-    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>84</v>
+      </c>
+      <c r="O75" s="46"/>
+      <c r="P75" s="46"/>
+      <c r="Q75" s="46"/>
+      <c r="R75" s="46"/>
+      <c r="S75" s="42"/>
+      <c r="T75" s="42"/>
+    </row>
+    <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B76" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C76" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D76" s="50">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B76" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C76" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76" s="39">
+        <v>100100026</v>
       </c>
       <c r="E76" s="40">
         <v>12</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H76" s="47">
         <v>0</v>
       </c>
-      <c r="I76" s="43">
+      <c r="I76" s="42">
         <v>9500</v>
       </c>
       <c r="J76" s="43">
         <v>0</v>
       </c>
-      <c r="K76" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="48">
-        <v>0</v>
-      </c>
-      <c r="M76" s="43" t="s">
+      <c r="K76" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="44">
+        <v>0</v>
+      </c>
+      <c r="M76" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N76" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O76" s="45"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" s="45"/>
-      <c r="R76" s="45"/>
-      <c r="S76" s="43"/>
-      <c r="T76" s="43"/>
-    </row>
-    <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>85</v>
+      </c>
+      <c r="O76" s="46"/>
+      <c r="P76" s="46"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="46"/>
+      <c r="S76" s="42"/>
+      <c r="T76" s="42"/>
+    </row>
+    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10140010</v>
-      </c>
-      <c r="B77" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D77" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B77" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C77" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D77" s="50">
+        <v>101200026</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
@@ -5508,43 +5511,43 @@
       <c r="H77" s="41">
         <v>0</v>
       </c>
-      <c r="I77" s="42">
+      <c r="I77" s="43">
         <v>9500</v>
       </c>
       <c r="J77" s="43">
         <v>0</v>
       </c>
-      <c r="K77" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L77" s="44">
-        <v>0</v>
-      </c>
-      <c r="M77" s="42" t="s">
+      <c r="K77" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="48">
+        <v>0</v>
+      </c>
+      <c r="M77" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N77" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="46"/>
-      <c r="R77" s="46"/>
-      <c r="S77" s="42"/>
-      <c r="T77" s="42"/>
-    </row>
-    <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>83</v>
+      </c>
+      <c r="O77" s="45"/>
+      <c r="P77" s="45"/>
+      <c r="Q77" s="45"/>
+      <c r="R77" s="45"/>
+      <c r="S77" s="43"/>
+      <c r="T77" s="43"/>
+    </row>
+    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10140011</v>
-      </c>
-      <c r="B78" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B78" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C78" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D78" s="50">
+        <v>101200026</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
@@ -5558,43 +5561,43 @@
       <c r="H78" s="41">
         <v>0</v>
       </c>
-      <c r="I78" s="42">
+      <c r="I78" s="43">
         <v>9500</v>
       </c>
       <c r="J78" s="43">
         <v>0</v>
       </c>
-      <c r="K78" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L78" s="44">
-        <v>0</v>
-      </c>
-      <c r="M78" s="42" t="s">
+      <c r="K78" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="48">
+        <v>0</v>
+      </c>
+      <c r="M78" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N78" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="46"/>
-      <c r="R78" s="46"/>
-      <c r="S78" s="42"/>
-      <c r="T78" s="42"/>
-    </row>
-    <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>84</v>
+      </c>
+      <c r="O78" s="45"/>
+      <c r="P78" s="45"/>
+      <c r="Q78" s="45"/>
+      <c r="R78" s="45"/>
+      <c r="S78" s="43"/>
+      <c r="T78" s="43"/>
+    </row>
+    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10140012</v>
-      </c>
-      <c r="B79" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D79" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B79" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C79" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="50">
+        <v>101200026</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
@@ -5608,52 +5611,52 @@
       <c r="H79" s="47">
         <v>0</v>
       </c>
-      <c r="I79" s="42">
+      <c r="I79" s="43">
         <v>9500</v>
       </c>
       <c r="J79" s="43">
         <v>0</v>
       </c>
-      <c r="K79" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L79" s="44">
-        <v>0</v>
-      </c>
-      <c r="M79" s="42" t="s">
+      <c r="K79" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="48">
+        <v>0</v>
+      </c>
+      <c r="M79" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N79" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O79" s="46"/>
-      <c r="P79" s="46"/>
-      <c r="Q79" s="46"/>
-      <c r="R79" s="46"/>
-      <c r="S79" s="42"/>
-      <c r="T79" s="42"/>
+        <v>85</v>
+      </c>
+      <c r="O79" s="45"/>
+      <c r="P79" s="45"/>
+      <c r="Q79" s="45"/>
+      <c r="R79" s="45"/>
+      <c r="S79" s="43"/>
+      <c r="T79" s="43"/>
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B80" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D80" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E80" s="40">
         <v>10</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H80" s="41">
         <v>0</v>
@@ -5674,7 +5677,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5685,25 +5688,25 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B81" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D81" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E81" s="40">
         <v>11</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H81" s="41">
         <v>0</v>
@@ -5724,7 +5727,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5735,25 +5738,25 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B82" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E82" s="40">
         <v>12</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H82" s="47">
         <v>0</v>
@@ -5774,7 +5777,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5785,16 +5788,16 @@
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B83" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
@@ -5817,14 +5820,14 @@
       <c r="K83" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L83" s="48">
+      <c r="L83" s="44">
         <v>0</v>
       </c>
       <c r="M83" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O83" s="46"/>
       <c r="P83" s="46"/>
@@ -5835,16 +5838,16 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B84" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D84" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
@@ -5867,14 +5870,14 @@
       <c r="K84" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L84" s="48">
+      <c r="L84" s="44">
         <v>0</v>
       </c>
       <c r="M84" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O84" s="46"/>
       <c r="P84" s="46"/>
@@ -5885,16 +5888,16 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B85" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D85" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
@@ -5917,14 +5920,14 @@
       <c r="K85" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L85" s="48">
+      <c r="L85" s="44">
         <v>0</v>
       </c>
       <c r="M85" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O85" s="46"/>
       <c r="P85" s="46"/>
@@ -5935,16 +5938,16 @@
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B86" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D86" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
@@ -5974,7 +5977,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -5985,16 +5988,16 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B87" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D87" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
@@ -6024,7 +6027,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6035,16 +6038,16 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B88" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D88" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
@@ -6074,7 +6077,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6085,25 +6088,25 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B89" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D89" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H89" s="41">
         <v>0</v>
@@ -6124,7 +6127,7 @@
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6135,25 +6138,25 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B90" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D90" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H90" s="41">
         <v>0</v>
@@ -6174,7 +6177,7 @@
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6185,25 +6188,25 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B91" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D91" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
@@ -6224,7 +6227,7 @@
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6235,27 +6238,27 @@
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B92" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D92" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H92" s="47">
+        <v>35</v>
+      </c>
+      <c r="H92" s="41">
         <v>0</v>
       </c>
       <c r="I92" s="42">
@@ -6274,7 +6277,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6285,27 +6288,27 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B93" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D93" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H93" s="47">
+        <v>39</v>
+      </c>
+      <c r="H93" s="41">
         <v>0</v>
       </c>
       <c r="I93" s="42">
@@ -6324,7 +6327,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6335,25 +6338,25 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B94" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D94" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
@@ -6374,7 +6377,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6385,25 +6388,25 @@
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B95" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D95" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H95" s="47">
         <v>0</v>
@@ -6424,7 +6427,7 @@
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6435,25 +6438,25 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B96" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D96" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H96" s="47">
         <v>0</v>
@@ -6474,7 +6477,7 @@
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6485,25 +6488,25 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B97" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D97" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G97" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H97" s="47">
         <v>0</v>
@@ -6524,7 +6527,7 @@
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6535,25 +6538,25 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B98" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D98" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H98" s="47">
         <v>0</v>
@@ -6574,7 +6577,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6585,25 +6588,25 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B99" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D99" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H99" s="47">
         <v>0</v>
@@ -6624,7 +6627,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6635,25 +6638,25 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B100" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D100" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
@@ -6674,7 +6677,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6685,31 +6688,31 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B101" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D101" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G101" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H101" s="47">
         <v>0</v>
       </c>
       <c r="I101" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J101" s="43">
         <v>0</v>
@@ -6724,7 +6727,7 @@
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6735,31 +6738,31 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B102" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D102" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H102" s="47">
         <v>0</v>
       </c>
       <c r="I102" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J102" s="43">
         <v>0</v>
@@ -6774,7 +6777,7 @@
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6785,31 +6788,31 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B103" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D103" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
       </c>
       <c r="F103" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G103" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H103" s="47">
         <v>0</v>
       </c>
       <c r="I103" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J103" s="43">
         <v>0</v>
@@ -6824,7 +6827,7 @@
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6835,25 +6838,25 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B104" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D104" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H104" s="47">
         <v>0</v>
@@ -6874,7 +6877,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6885,25 +6888,25 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B105" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D105" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H105" s="47">
         <v>0</v>
@@ -6924,7 +6927,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6935,25 +6938,25 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B106" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D106" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H106" s="47">
         <v>0</v>
@@ -6974,7 +6977,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -6985,16 +6988,16 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B107" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D107" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
@@ -7024,7 +7027,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7035,16 +7038,16 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B108" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D108" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
@@ -7074,7 +7077,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7085,16 +7088,16 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B109" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D109" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
@@ -7124,7 +7127,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7135,25 +7138,25 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B110" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D110" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
-      <c r="F110" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G110" s="51" t="s">
-        <v>35</v>
+      <c r="F110" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G110" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H110" s="47">
         <v>0</v>
@@ -7174,7 +7177,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7185,25 +7188,25 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B111" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D111" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
-      <c r="F111" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G111" s="51" t="s">
-        <v>39</v>
+      <c r="F111" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H111" s="47">
         <v>0</v>
@@ -7224,7 +7227,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7235,25 +7238,25 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B112" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D112" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
-      <c r="F112" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G112" s="51" t="s">
-        <v>42</v>
+      <c r="F112" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G112" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
@@ -7274,7 +7277,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7285,25 +7288,25 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B113" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D113" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
       </c>
       <c r="F113" s="46" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G113" s="51" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="H113" s="47">
         <v>0</v>
@@ -7324,7 +7327,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7335,25 +7338,25 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B114" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D114" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
       </c>
       <c r="F114" s="46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G114" s="51" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="H114" s="47">
         <v>0</v>
@@ -7374,7 +7377,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7385,25 +7388,25 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B115" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D115" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
       </c>
       <c r="F115" s="46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G115" s="51" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H115" s="47">
         <v>0</v>
@@ -7424,7 +7427,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7435,16 +7438,16 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B116" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D116" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
@@ -7474,7 +7477,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7485,16 +7488,16 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B117" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D117" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
@@ -7524,7 +7527,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7535,16 +7538,16 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B118" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D118" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
@@ -7574,7 +7577,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7585,16 +7588,16 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="36">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B119" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D119" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D119" s="39">
+        <v>102000001</v>
       </c>
       <c r="E119" s="40">
         <v>10</v>
@@ -7624,7 +7627,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O119" s="46"/>
       <c r="P119" s="46"/>
@@ -7635,16 +7638,16 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="36">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B120" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D120" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D120" s="39">
+        <v>102000001</v>
       </c>
       <c r="E120" s="40">
         <v>11</v>
@@ -7674,7 +7677,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O120" s="46"/>
       <c r="P120" s="46"/>
@@ -7685,16 +7688,16 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="36">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B121" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D121" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D121" s="39">
+        <v>102000001</v>
       </c>
       <c r="E121" s="40">
         <v>12</v>
@@ -7724,7 +7727,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O121" s="46"/>
       <c r="P121" s="46"/>
@@ -7733,21 +7736,21 @@
       <c r="S121" s="42"/>
       <c r="T121" s="42"/>
     </row>
-    <row r="122" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A122" s="19">
-        <v>10380010</v>
-      </c>
-      <c r="B122" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>81</v>
+    <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A122" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B122" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C122" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D122" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E122" s="20">
-        <v>11</v>
+        <v>103400001</v>
+      </c>
+      <c r="E122" s="40">
+        <v>10</v>
       </c>
       <c r="F122" s="46" t="s">
         <v>64</v>
@@ -7774,30 +7777,30 @@
         <v>37</v>
       </c>
       <c r="N122" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="O122" s="21"/>
-      <c r="P122" s="21"/>
-      <c r="Q122" s="21"/>
-      <c r="R122" s="21"/>
-      <c r="S122" s="23"/>
-      <c r="T122" s="23"/>
-    </row>
-    <row r="123" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A123" s="19">
-        <v>10380011</v>
-      </c>
-      <c r="B123" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="O122" s="46"/>
+      <c r="P122" s="46"/>
+      <c r="Q122" s="46"/>
+      <c r="R122" s="46"/>
+      <c r="S122" s="42"/>
+      <c r="T122" s="42"/>
+    </row>
+    <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A123" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B123" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C123" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D123" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E123" s="20">
-        <v>12</v>
+        <v>103400001</v>
+      </c>
+      <c r="E123" s="40">
+        <v>11</v>
       </c>
       <c r="F123" s="46" t="s">
         <v>66</v>
@@ -7824,30 +7827,30 @@
         <v>40</v>
       </c>
       <c r="N123" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O123" s="21"/>
-      <c r="P123" s="21"/>
-      <c r="Q123" s="21"/>
-      <c r="R123" s="21"/>
-      <c r="S123" s="23"/>
-      <c r="T123" s="23"/>
-    </row>
-    <row r="124" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A124" s="19">
-        <v>10380012</v>
-      </c>
-      <c r="B124" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="O123" s="46"/>
+      <c r="P123" s="46"/>
+      <c r="Q123" s="46"/>
+      <c r="R123" s="46"/>
+      <c r="S123" s="42"/>
+      <c r="T123" s="42"/>
+    </row>
+    <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A124" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B124" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C124" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D124" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E124" s="20">
-        <v>13</v>
+        <v>103400001</v>
+      </c>
+      <c r="E124" s="40">
+        <v>12</v>
       </c>
       <c r="F124" s="46" t="s">
         <v>68</v>
@@ -7874,14 +7877,314 @@
         <v>43</v>
       </c>
       <c r="N124" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="O124" s="46"/>
+      <c r="P124" s="46"/>
+      <c r="Q124" s="46"/>
+      <c r="R124" s="46"/>
+      <c r="S124" s="42"/>
+      <c r="T124" s="42"/>
+    </row>
+    <row r="125" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A125" s="19">
+        <v>10380010</v>
+      </c>
+      <c r="B125" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C125" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D125" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E125" s="20">
+        <v>11</v>
+      </c>
+      <c r="F125" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G125" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H125" s="47">
+        <v>0</v>
+      </c>
+      <c r="I125" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J125" s="43">
+        <v>0</v>
+      </c>
+      <c r="K125" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L125" s="48">
+        <v>0</v>
+      </c>
+      <c r="M125" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N125" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O125" s="21"/>
+      <c r="P125" s="21"/>
+      <c r="Q125" s="21"/>
+      <c r="R125" s="21"/>
+      <c r="S125" s="23"/>
+      <c r="T125" s="23"/>
+    </row>
+    <row r="126" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A126" s="19">
+        <v>10380011</v>
+      </c>
+      <c r="B126" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C126" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D126" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E126" s="20">
+        <v>12</v>
+      </c>
+      <c r="F126" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G126" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H126" s="47">
+        <v>0</v>
+      </c>
+      <c r="I126" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J126" s="43">
+        <v>0</v>
+      </c>
+      <c r="K126" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" s="48">
+        <v>0</v>
+      </c>
+      <c r="M126" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N126" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="O124" s="21"/>
-      <c r="P124" s="21"/>
-      <c r="Q124" s="21"/>
-      <c r="R124" s="21"/>
-      <c r="S124" s="23"/>
-      <c r="T124" s="23"/>
+      <c r="O126" s="21"/>
+      <c r="P126" s="21"/>
+      <c r="Q126" s="21"/>
+      <c r="R126" s="21"/>
+      <c r="S126" s="23"/>
+      <c r="T126" s="23"/>
+    </row>
+    <row r="127" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A127" s="19">
+        <v>10380012</v>
+      </c>
+      <c r="B127" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D127" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E127" s="20">
+        <v>13</v>
+      </c>
+      <c r="F127" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G127" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H127" s="47">
+        <v>0</v>
+      </c>
+      <c r="I127" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J127" s="43">
+        <v>0</v>
+      </c>
+      <c r="K127" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L127" s="48">
+        <v>0</v>
+      </c>
+      <c r="M127" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N127" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="O127" s="21"/>
+      <c r="P127" s="21"/>
+      <c r="Q127" s="21"/>
+      <c r="R127" s="21"/>
+      <c r="S127" s="23"/>
+      <c r="T127" s="23"/>
+    </row>
+    <row r="128" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A128" s="19">
+        <v>10270010</v>
+      </c>
+      <c r="B128" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C128" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D128" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E128" s="20">
+        <v>11</v>
+      </c>
+      <c r="F128" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G128" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H128" s="47">
+        <v>0</v>
+      </c>
+      <c r="I128" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J128" s="43">
+        <v>0</v>
+      </c>
+      <c r="K128" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L128" s="48">
+        <v>0</v>
+      </c>
+      <c r="M128" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N128" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="O128" s="21"/>
+      <c r="P128" s="21"/>
+      <c r="Q128" s="21"/>
+      <c r="R128" s="21"/>
+      <c r="S128" s="23"/>
+      <c r="T128" s="23"/>
+    </row>
+    <row r="129" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A129" s="19">
+        <v>10270011</v>
+      </c>
+      <c r="B129" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C129" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D129" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E129" s="20">
+        <v>12</v>
+      </c>
+      <c r="F129" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G129" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H129" s="47">
+        <v>0</v>
+      </c>
+      <c r="I129" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J129" s="43">
+        <v>0</v>
+      </c>
+      <c r="K129" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L129" s="48">
+        <v>0</v>
+      </c>
+      <c r="M129" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N129" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="O129" s="21"/>
+      <c r="P129" s="21"/>
+      <c r="Q129" s="21"/>
+      <c r="R129" s="21"/>
+      <c r="S129" s="23"/>
+      <c r="T129" s="23"/>
+    </row>
+    <row r="130" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A130" s="19">
+        <v>10270012</v>
+      </c>
+      <c r="B130" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C130" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D130" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E130" s="20">
+        <v>13</v>
+      </c>
+      <c r="F130" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G130" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H130" s="47">
+        <v>0</v>
+      </c>
+      <c r="I130" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J130" s="43">
+        <v>0</v>
+      </c>
+      <c r="K130" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L130" s="48">
+        <v>0</v>
+      </c>
+      <c r="M130" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N130" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="O130" s="21"/>
+      <c r="P130" s="21"/>
+      <c r="Q130" s="21"/>
+      <c r="R130" s="21"/>
+      <c r="S130" s="23"/>
+      <c r="T130" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -435,6 +435,18 @@
   </si>
   <si>
     <t>象财神</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>11倍金牛</t>
+  </si>
+  <si>
+    <t>12倍金牛</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
   </si>
   <si>
     <t>1980000_500000</t>
@@ -664,13 +676,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -683,6 +688,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -691,12 +702,13 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1709,7 +1721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T130"/>
+  <dimension ref="A1:T142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -4303,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H53" s="28">
         <v>10000000</v>
@@ -4353,10 +4365,10 @@
         <v>2</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H54" s="28">
         <v>100000000</v>
@@ -4403,10 +4415,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H55" s="28">
         <v>1000000000</v>
@@ -4453,10 +4465,10 @@
         <v>1</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H56" s="28">
         <v>10000000</v>
@@ -4503,10 +4515,10 @@
         <v>2</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H57" s="28">
         <v>100000000</v>
@@ -4553,10 +4565,10 @@
         <v>3</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H58" s="28">
         <v>1000000000</v>
@@ -4753,10 +4765,10 @@
         <v>1</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H62" s="14">
         <v>10000000</v>
@@ -4803,10 +4815,10 @@
         <v>2</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H63" s="14">
         <v>100000000</v>
@@ -4853,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H64" s="28">
         <v>1000000000</v>
@@ -4903,10 +4915,10 @@
         <v>1</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H65" s="14">
         <v>10000000</v>
@@ -4953,10 +4965,10 @@
         <v>2</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H66" s="14">
         <v>100000000</v>
@@ -5003,10 +5015,10 @@
         <v>3</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H67" s="28">
         <v>1000000000</v>
@@ -5036,315 +5048,315 @@
       <c r="S67" s="23"/>
       <c r="T67" s="23"/>
     </row>
-    <row r="68" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A68" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B68" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C68" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D68" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E68" s="40">
-        <v>10</v>
+    <row r="68" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A68" s="19">
+        <v>1037001</v>
+      </c>
+      <c r="B68" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E68" s="20">
+        <v>1</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H68" s="41">
-        <v>0</v>
-      </c>
-      <c r="I68" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J68" s="43">
-        <v>0</v>
-      </c>
-      <c r="K68" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L68" s="44">
-        <v>0</v>
-      </c>
-      <c r="M68" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I68" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J68" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K68" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="27">
+        <v>100</v>
+      </c>
+      <c r="M68" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N68" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O68" s="46"/>
-      <c r="P68" s="46"/>
-      <c r="Q68" s="46"/>
-      <c r="R68" s="46"/>
-      <c r="S68" s="42"/>
-      <c r="T68" s="42"/>
-    </row>
-    <row r="69" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A69" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B69" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C69" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D69" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E69" s="40">
-        <v>11</v>
+      <c r="N68" s="21">
+        <v>0</v>
+      </c>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="23"/>
+      <c r="T68" s="23"/>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A69" s="19">
+        <v>1037002</v>
+      </c>
+      <c r="B69" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E69" s="20">
+        <v>2</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H69" s="41">
-        <v>0</v>
-      </c>
-      <c r="I69" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J69" s="43">
-        <v>0</v>
-      </c>
-      <c r="K69" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L69" s="44">
-        <v>0</v>
-      </c>
-      <c r="M69" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I69" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J69" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K69" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="27">
+        <v>100</v>
+      </c>
+      <c r="M69" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N69" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O69" s="46"/>
-      <c r="P69" s="46"/>
-      <c r="Q69" s="46"/>
-      <c r="R69" s="46"/>
-      <c r="S69" s="42"/>
-      <c r="T69" s="42"/>
-    </row>
-    <row r="70" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A70" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B70" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C70" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E70" s="40">
-        <v>12</v>
+      <c r="N69" s="21">
+        <v>0</v>
+      </c>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="23"/>
+      <c r="T69" s="23"/>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A70" s="19">
+        <v>1037003</v>
+      </c>
+      <c r="B70" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E70" s="20">
+        <v>3</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H70" s="47">
-        <v>0</v>
-      </c>
-      <c r="I70" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J70" s="43">
-        <v>0</v>
-      </c>
-      <c r="K70" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L70" s="44">
-        <v>0</v>
-      </c>
-      <c r="M70" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="H70" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I70" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J70" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K70" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="27">
+        <v>100</v>
+      </c>
+      <c r="M70" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N70" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O70" s="46"/>
-      <c r="P70" s="46"/>
-      <c r="Q70" s="46"/>
-      <c r="R70" s="46"/>
-      <c r="S70" s="42"/>
-      <c r="T70" s="42"/>
-    </row>
-    <row r="71" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A71" s="36">
-        <v>10030010</v>
-      </c>
-      <c r="B71" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C71" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E71" s="40">
-        <v>10</v>
+      <c r="N70" s="21">
+        <v>0</v>
+      </c>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="21"/>
+      <c r="R70" s="21"/>
+      <c r="S70" s="23"/>
+      <c r="T70" s="23"/>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A71" s="19">
+        <v>1031001</v>
+      </c>
+      <c r="B71" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E71" s="20">
+        <v>1</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H71" s="41">
-        <v>0</v>
-      </c>
-      <c r="I71" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J71" s="43">
-        <v>0</v>
-      </c>
-      <c r="K71" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L71" s="48">
-        <v>0</v>
-      </c>
-      <c r="M71" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H71" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I71" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J71" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K71" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="27">
+        <v>100</v>
+      </c>
+      <c r="M71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N71" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O71" s="46"/>
-      <c r="P71" s="46"/>
-      <c r="Q71" s="46"/>
-      <c r="R71" s="46"/>
-      <c r="S71" s="42"/>
-      <c r="T71" s="42"/>
-    </row>
-    <row r="72" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A72" s="36">
-        <v>10030011</v>
-      </c>
-      <c r="B72" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C72" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E72" s="40">
-        <v>11</v>
+      <c r="N71" s="21">
+        <v>0</v>
+      </c>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="21"/>
+      <c r="R71" s="21"/>
+      <c r="S71" s="23"/>
+      <c r="T71" s="23"/>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A72" s="19">
+        <v>1031002</v>
+      </c>
+      <c r="B72" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E72" s="20">
+        <v>2</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H72" s="41">
-        <v>0</v>
-      </c>
-      <c r="I72" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J72" s="43">
-        <v>0</v>
-      </c>
-      <c r="K72" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L72" s="48">
-        <v>0</v>
-      </c>
-      <c r="M72" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I72" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J72" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K72" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="27">
+        <v>100</v>
+      </c>
+      <c r="M72" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N72" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O72" s="46"/>
-      <c r="P72" s="46"/>
-      <c r="Q72" s="46"/>
-      <c r="R72" s="46"/>
-      <c r="S72" s="42"/>
-      <c r="T72" s="42"/>
-    </row>
-    <row r="73" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A73" s="36">
-        <v>10030012</v>
-      </c>
-      <c r="B73" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C73" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E73" s="40">
-        <v>12</v>
+      <c r="N72" s="21">
+        <v>0</v>
+      </c>
+      <c r="O72" s="21"/>
+      <c r="P72" s="21"/>
+      <c r="Q72" s="21"/>
+      <c r="R72" s="21"/>
+      <c r="S72" s="23"/>
+      <c r="T72" s="23"/>
+    </row>
+    <row r="73" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A73" s="19">
+        <v>1031003</v>
+      </c>
+      <c r="B73" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D73" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E73" s="20">
+        <v>3</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="H73" s="47">
-        <v>0</v>
-      </c>
-      <c r="I73" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J73" s="43">
-        <v>0</v>
-      </c>
-      <c r="K73" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L73" s="48">
-        <v>0</v>
-      </c>
-      <c r="M73" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H73" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I73" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J73" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K73" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="27">
+        <v>100</v>
+      </c>
+      <c r="M73" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N73" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O73" s="46"/>
-      <c r="P73" s="46"/>
-      <c r="Q73" s="46"/>
-      <c r="R73" s="46"/>
-      <c r="S73" s="42"/>
-      <c r="T73" s="42"/>
+      <c r="N73" s="21">
+        <v>0</v>
+      </c>
+      <c r="O73" s="21"/>
+      <c r="P73" s="21"/>
+      <c r="Q73" s="21"/>
+      <c r="R73" s="21"/>
+      <c r="S73" s="23"/>
+      <c r="T73" s="23"/>
     </row>
     <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A74" s="36">
-        <v>10070010</v>
+        <v>10010010</v>
       </c>
       <c r="B74" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D74" s="39">
         <v>100100026</v>
@@ -5353,10 +5365,10 @@
         <v>10</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H74" s="41">
         <v>0</v>
@@ -5377,7 +5389,7 @@
         <v>37</v>
       </c>
       <c r="N74" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O74" s="46"/>
       <c r="P74" s="46"/>
@@ -5388,13 +5400,13 @@
     </row>
     <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A75" s="36">
-        <v>10070011</v>
+        <v>10010011</v>
       </c>
       <c r="B75" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D75" s="39">
         <v>100100026</v>
@@ -5403,10 +5415,10 @@
         <v>11</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H75" s="41">
         <v>0</v>
@@ -5427,7 +5439,7 @@
         <v>40</v>
       </c>
       <c r="N75" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O75" s="46"/>
       <c r="P75" s="46"/>
@@ -5438,13 +5450,13 @@
     </row>
     <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A76" s="36">
-        <v>10070012</v>
+        <v>10010012</v>
       </c>
       <c r="B76" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D76" s="39">
         <v>100100026</v>
@@ -5453,10 +5465,10 @@
         <v>12</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H76" s="47">
         <v>0</v>
@@ -5477,7 +5489,7 @@
         <v>43</v>
       </c>
       <c r="N76" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O76" s="46"/>
       <c r="P76" s="46"/>
@@ -5486,165 +5498,165 @@
       <c r="S76" s="42"/>
       <c r="T76" s="42"/>
     </row>
-    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A77" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B77" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C77" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D77" s="50">
-        <v>101200026</v>
+        <v>10030010</v>
+      </c>
+      <c r="B77" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="39">
+        <v>100100026</v>
       </c>
       <c r="E77" s="40">
         <v>10</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H77" s="41">
         <v>0</v>
       </c>
-      <c r="I77" s="43">
+      <c r="I77" s="42">
         <v>9500</v>
       </c>
       <c r="J77" s="43">
         <v>0</v>
       </c>
-      <c r="K77" s="48" t="s">
+      <c r="K77" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L77" s="48">
         <v>0</v>
       </c>
-      <c r="M77" s="43" t="s">
+      <c r="M77" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N77" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O77" s="45"/>
-      <c r="P77" s="45"/>
-      <c r="Q77" s="45"/>
-      <c r="R77" s="45"/>
-      <c r="S77" s="43"/>
-      <c r="T77" s="43"/>
-    </row>
-    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>87</v>
+      </c>
+      <c r="O77" s="46"/>
+      <c r="P77" s="46"/>
+      <c r="Q77" s="46"/>
+      <c r="R77" s="46"/>
+      <c r="S77" s="42"/>
+      <c r="T77" s="42"/>
+    </row>
+    <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A78" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B78" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C78" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D78" s="50">
-        <v>101200026</v>
+        <v>10030011</v>
+      </c>
+      <c r="B78" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C78" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="39">
+        <v>100100026</v>
       </c>
       <c r="E78" s="40">
         <v>11</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H78" s="41">
         <v>0</v>
       </c>
-      <c r="I78" s="43">
+      <c r="I78" s="42">
         <v>9500</v>
       </c>
       <c r="J78" s="43">
         <v>0</v>
       </c>
-      <c r="K78" s="48" t="s">
+      <c r="K78" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L78" s="48">
         <v>0</v>
       </c>
-      <c r="M78" s="43" t="s">
+      <c r="M78" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N78" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O78" s="45"/>
-      <c r="P78" s="45"/>
-      <c r="Q78" s="45"/>
-      <c r="R78" s="45"/>
-      <c r="S78" s="43"/>
-      <c r="T78" s="43"/>
-    </row>
-    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>88</v>
+      </c>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="46"/>
+      <c r="R78" s="46"/>
+      <c r="S78" s="42"/>
+      <c r="T78" s="42"/>
+    </row>
+    <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A79" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B79" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C79" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="50">
-        <v>101200026</v>
+        <v>10030012</v>
+      </c>
+      <c r="B79" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" s="39">
+        <v>100100026</v>
       </c>
       <c r="E79" s="40">
         <v>12</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H79" s="47">
         <v>0</v>
       </c>
-      <c r="I79" s="43">
+      <c r="I79" s="42">
         <v>9500</v>
       </c>
       <c r="J79" s="43">
         <v>0</v>
       </c>
-      <c r="K79" s="48" t="s">
+      <c r="K79" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L79" s="48">
         <v>0</v>
       </c>
-      <c r="M79" s="43" t="s">
+      <c r="M79" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N79" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O79" s="45"/>
-      <c r="P79" s="45"/>
-      <c r="Q79" s="45"/>
-      <c r="R79" s="45"/>
-      <c r="S79" s="43"/>
-      <c r="T79" s="43"/>
+        <v>89</v>
+      </c>
+      <c r="O79" s="46"/>
+      <c r="P79" s="46"/>
+      <c r="Q79" s="46"/>
+      <c r="R79" s="46"/>
+      <c r="S79" s="42"/>
+      <c r="T79" s="42"/>
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10140010</v>
+        <v>10070010</v>
       </c>
       <c r="B80" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D80" s="39">
         <v>100100026</v>
@@ -5653,10 +5665,10 @@
         <v>10</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H80" s="41">
         <v>0</v>
@@ -5677,7 +5689,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5688,13 +5700,13 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10140011</v>
+        <v>10070011</v>
       </c>
       <c r="B81" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D81" s="39">
         <v>100100026</v>
@@ -5703,10 +5715,10 @@
         <v>11</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H81" s="41">
         <v>0</v>
@@ -5727,7 +5739,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5738,13 +5750,13 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10140012</v>
+        <v>10070012</v>
       </c>
       <c r="B82" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D82" s="39">
         <v>100100026</v>
@@ -5753,10 +5765,10 @@
         <v>12</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H82" s="47">
         <v>0</v>
@@ -5777,7 +5789,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5786,177 +5798,177 @@
       <c r="S82" s="42"/>
       <c r="T82" s="42"/>
     </row>
-    <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="83" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10170010</v>
-      </c>
-      <c r="B83" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C83" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D83" s="39">
-        <v>101700001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B83" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C83" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D83" s="50">
+        <v>101200026</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H83" s="41">
         <v>0</v>
       </c>
-      <c r="I83" s="42">
+      <c r="I83" s="43">
         <v>9500</v>
       </c>
       <c r="J83" s="43">
         <v>0</v>
       </c>
-      <c r="K83" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L83" s="44">
-        <v>0</v>
-      </c>
-      <c r="M83" s="42" t="s">
+      <c r="K83" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="48">
+        <v>0</v>
+      </c>
+      <c r="M83" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O83" s="46"/>
-      <c r="P83" s="46"/>
-      <c r="Q83" s="46"/>
-      <c r="R83" s="46"/>
-      <c r="S83" s="42"/>
-      <c r="T83" s="42"/>
-    </row>
-    <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>87</v>
+      </c>
+      <c r="O83" s="45"/>
+      <c r="P83" s="45"/>
+      <c r="Q83" s="45"/>
+      <c r="R83" s="45"/>
+      <c r="S83" s="43"/>
+      <c r="T83" s="43"/>
+    </row>
+    <row r="84" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10170011</v>
-      </c>
-      <c r="B84" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C84" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D84" s="39">
-        <v>101700001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B84" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C84" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D84" s="50">
+        <v>101200026</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H84" s="41">
         <v>0</v>
       </c>
-      <c r="I84" s="42">
+      <c r="I84" s="43">
         <v>9500</v>
       </c>
       <c r="J84" s="43">
         <v>0</v>
       </c>
-      <c r="K84" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L84" s="44">
-        <v>0</v>
-      </c>
-      <c r="M84" s="42" t="s">
+      <c r="K84" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="48">
+        <v>0</v>
+      </c>
+      <c r="M84" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O84" s="46"/>
-      <c r="P84" s="46"/>
-      <c r="Q84" s="46"/>
-      <c r="R84" s="46"/>
-      <c r="S84" s="42"/>
-      <c r="T84" s="42"/>
-    </row>
-    <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>88</v>
+      </c>
+      <c r="O84" s="45"/>
+      <c r="P84" s="45"/>
+      <c r="Q84" s="45"/>
+      <c r="R84" s="45"/>
+      <c r="S84" s="43"/>
+      <c r="T84" s="43"/>
+    </row>
+    <row r="85" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10170012</v>
-      </c>
-      <c r="B85" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C85" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D85" s="39">
-        <v>101700001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B85" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C85" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D85" s="50">
+        <v>101200026</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H85" s="47">
         <v>0</v>
       </c>
-      <c r="I85" s="42">
+      <c r="I85" s="43">
         <v>9500</v>
       </c>
       <c r="J85" s="43">
         <v>0</v>
       </c>
-      <c r="K85" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L85" s="44">
-        <v>0</v>
-      </c>
-      <c r="M85" s="42" t="s">
+      <c r="K85" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="48">
+        <v>0</v>
+      </c>
+      <c r="M85" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O85" s="46"/>
-      <c r="P85" s="46"/>
-      <c r="Q85" s="46"/>
-      <c r="R85" s="46"/>
-      <c r="S85" s="42"/>
-      <c r="T85" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="O85" s="45"/>
+      <c r="P85" s="45"/>
+      <c r="Q85" s="45"/>
+      <c r="R85" s="45"/>
+      <c r="S85" s="43"/>
+      <c r="T85" s="43"/>
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10210010</v>
+        <v>10140010</v>
       </c>
       <c r="B86" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D86" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E86" s="40">
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H86" s="41">
         <v>0</v>
@@ -5970,14 +5982,14 @@
       <c r="K86" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L86" s="48">
+      <c r="L86" s="44">
         <v>0</v>
       </c>
       <c r="M86" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -5988,25 +6000,25 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10210011</v>
+        <v>10140011</v>
       </c>
       <c r="B87" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D87" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E87" s="40">
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H87" s="41">
         <v>0</v>
@@ -6020,14 +6032,14 @@
       <c r="K87" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L87" s="48">
+      <c r="L87" s="44">
         <v>0</v>
       </c>
       <c r="M87" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6038,25 +6050,25 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10210012</v>
+        <v>10140012</v>
       </c>
       <c r="B88" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D88" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E88" s="40">
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6070,14 +6082,14 @@
       <c r="K88" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L88" s="48">
+      <c r="L88" s="44">
         <v>0</v>
       </c>
       <c r="M88" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6088,16 +6100,16 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10220010</v>
+        <v>10170010</v>
       </c>
       <c r="B89" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D89" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
@@ -6120,14 +6132,14 @@
       <c r="K89" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L89" s="48">
+      <c r="L89" s="44">
         <v>0</v>
       </c>
       <c r="M89" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6138,16 +6150,16 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10220011</v>
+        <v>10170011</v>
       </c>
       <c r="B90" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D90" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
@@ -6170,14 +6182,14 @@
       <c r="K90" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L90" s="48">
+      <c r="L90" s="44">
         <v>0</v>
       </c>
       <c r="M90" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6188,16 +6200,16 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10220012</v>
+        <v>10170012</v>
       </c>
       <c r="B91" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D91" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
@@ -6220,14 +6232,14 @@
       <c r="K91" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L91" s="48">
+      <c r="L91" s="44">
         <v>0</v>
       </c>
       <c r="M91" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6238,25 +6250,25 @@
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10240010</v>
+        <v>10210010</v>
       </c>
       <c r="B92" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D92" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H92" s="41">
         <v>0</v>
@@ -6277,7 +6289,7 @@
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6288,25 +6300,25 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10240011</v>
+        <v>10210011</v>
       </c>
       <c r="B93" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D93" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H93" s="41">
         <v>0</v>
@@ -6327,7 +6339,7 @@
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6338,25 +6350,25 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10240012</v>
+        <v>10210012</v>
       </c>
       <c r="B94" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D94" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
@@ -6377,7 +6389,7 @@
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6388,16 +6400,16 @@
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10180010</v>
+        <v>10220010</v>
       </c>
       <c r="B95" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D95" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
@@ -6408,7 +6420,7 @@
       <c r="G95" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H95" s="47">
+      <c r="H95" s="41">
         <v>0</v>
       </c>
       <c r="I95" s="42">
@@ -6427,7 +6439,7 @@
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6438,16 +6450,16 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10180011</v>
+        <v>10220011</v>
       </c>
       <c r="B96" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D96" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
@@ -6458,7 +6470,7 @@
       <c r="G96" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H96" s="47">
+      <c r="H96" s="41">
         <v>0</v>
       </c>
       <c r="I96" s="42">
@@ -6477,7 +6489,7 @@
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6488,16 +6500,16 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10180012</v>
+        <v>10220012</v>
       </c>
       <c r="B97" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D97" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
@@ -6527,7 +6539,7 @@
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6538,27 +6550,27 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10250010</v>
+        <v>10240010</v>
       </c>
       <c r="B98" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D98" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="H98" s="47">
+        <v>35</v>
+      </c>
+      <c r="H98" s="41">
         <v>0</v>
       </c>
       <c r="I98" s="42">
@@ -6577,7 +6589,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6588,27 +6600,27 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10250011</v>
+        <v>10240011</v>
       </c>
       <c r="B99" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D99" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H99" s="47">
+        <v>39</v>
+      </c>
+      <c r="H99" s="41">
         <v>0</v>
       </c>
       <c r="I99" s="42">
@@ -6627,7 +6639,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6638,25 +6650,25 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10250012</v>
+        <v>10240012</v>
       </c>
       <c r="B100" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D100" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
@@ -6677,7 +6689,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6688,16 +6700,16 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10230010</v>
+        <v>10180010</v>
       </c>
       <c r="B101" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D101" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
@@ -6727,7 +6739,7 @@
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6738,16 +6750,16 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10230011</v>
+        <v>10180011</v>
       </c>
       <c r="B102" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D102" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
@@ -6777,7 +6789,7 @@
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6788,16 +6800,16 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10230012</v>
+        <v>10180012</v>
       </c>
       <c r="B103" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D103" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
@@ -6827,7 +6839,7 @@
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6838,31 +6850,31 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10340010</v>
+        <v>10250010</v>
       </c>
       <c r="B104" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D104" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H104" s="47">
         <v>0</v>
       </c>
       <c r="I104" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J104" s="43">
         <v>0</v>
@@ -6877,7 +6889,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6888,31 +6900,31 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10340011</v>
+        <v>10250011</v>
       </c>
       <c r="B105" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D105" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H105" s="47">
         <v>0</v>
       </c>
       <c r="I105" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J105" s="43">
         <v>0</v>
@@ -6927,7 +6939,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6938,31 +6950,31 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10340012</v>
+        <v>10250012</v>
       </c>
       <c r="B106" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D106" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H106" s="47">
         <v>0</v>
       </c>
       <c r="I106" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J106" s="43">
         <v>0</v>
@@ -6977,7 +6989,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -6988,31 +7000,31 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10350010</v>
+        <v>10230010</v>
       </c>
       <c r="B107" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D107" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H107" s="47">
         <v>0</v>
       </c>
       <c r="I107" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J107" s="43">
         <v>0</v>
@@ -7027,7 +7039,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7038,31 +7050,31 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10350011</v>
+        <v>10230011</v>
       </c>
       <c r="B108" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D108" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G108" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H108" s="47">
         <v>0</v>
       </c>
       <c r="I108" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J108" s="43">
         <v>0</v>
@@ -7077,7 +7089,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7088,31 +7100,31 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10350012</v>
+        <v>10230012</v>
       </c>
       <c r="B109" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D109" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H109" s="47">
         <v>0</v>
       </c>
       <c r="I109" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J109" s="43">
         <v>0</v>
@@ -7127,7 +7139,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7138,25 +7150,25 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10350110</v>
+        <v>10340010</v>
       </c>
       <c r="B110" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D110" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H110" s="47">
         <v>0</v>
@@ -7177,7 +7189,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7188,25 +7200,25 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10350111</v>
+        <v>10340011</v>
       </c>
       <c r="B111" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D111" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H111" s="47">
         <v>0</v>
@@ -7227,7 +7239,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7238,25 +7250,25 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10350112</v>
+        <v>10340012</v>
       </c>
       <c r="B112" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D112" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
@@ -7277,7 +7289,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7288,25 +7300,25 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10360010</v>
+        <v>10350010</v>
       </c>
       <c r="B113" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D113" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
       </c>
-      <c r="F113" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G113" s="51" t="s">
-        <v>35</v>
+      <c r="F113" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H113" s="47">
         <v>0</v>
@@ -7327,7 +7339,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7338,25 +7350,25 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10360011</v>
+        <v>10350011</v>
       </c>
       <c r="B114" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D114" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
       </c>
-      <c r="F114" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G114" s="51" t="s">
-        <v>39</v>
+      <c r="F114" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G114" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H114" s="47">
         <v>0</v>
@@ -7377,7 +7389,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7388,25 +7400,25 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10360012</v>
+        <v>10350012</v>
       </c>
       <c r="B115" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D115" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
       </c>
-      <c r="F115" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G115" s="51" t="s">
-        <v>42</v>
+      <c r="F115" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H115" s="47">
         <v>0</v>
@@ -7427,7 +7439,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7438,25 +7450,25 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10280010</v>
+        <v>10350110</v>
       </c>
       <c r="B116" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D116" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
       </c>
-      <c r="F116" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G116" s="51" t="s">
-        <v>65</v>
+      <c r="F116" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H116" s="47">
         <v>0</v>
@@ -7477,7 +7489,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7488,25 +7500,25 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10280011</v>
+        <v>10350111</v>
       </c>
       <c r="B117" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D117" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
       </c>
-      <c r="F117" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G117" s="51" t="s">
-        <v>67</v>
+      <c r="F117" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H117" s="47">
         <v>0</v>
@@ -7527,7 +7539,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7538,25 +7550,25 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10280012</v>
+        <v>10350112</v>
       </c>
       <c r="B118" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D118" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
       </c>
-      <c r="F118" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="G118" s="51" t="s">
-        <v>69</v>
+      <c r="F118" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G118" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H118" s="47">
         <v>0</v>
@@ -7577,7 +7589,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7588,25 +7600,25 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="36">
-        <v>10200010</v>
+        <v>10360010</v>
       </c>
       <c r="B119" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D119" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E119" s="40">
         <v>10</v>
       </c>
       <c r="F119" s="46" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G119" s="51" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="H119" s="47">
         <v>0</v>
@@ -7627,7 +7639,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O119" s="46"/>
       <c r="P119" s="46"/>
@@ -7638,25 +7650,25 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="36">
-        <v>10200011</v>
+        <v>10360011</v>
       </c>
       <c r="B120" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D120" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E120" s="40">
         <v>11</v>
       </c>
       <c r="F120" s="46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G120" s="51" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="H120" s="47">
         <v>0</v>
@@ -7677,7 +7689,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O120" s="46"/>
       <c r="P120" s="46"/>
@@ -7688,25 +7700,25 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="36">
-        <v>10200012</v>
+        <v>10360012</v>
       </c>
       <c r="B121" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D121" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E121" s="40">
         <v>12</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G121" s="51" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H121" s="47">
         <v>0</v>
@@ -7727,7 +7739,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O121" s="46"/>
       <c r="P121" s="46"/>
@@ -7738,25 +7750,25 @@
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="36">
-        <v>10340110</v>
+        <v>10280010</v>
       </c>
       <c r="B122" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D122" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D122" s="39">
+        <v>102800001</v>
       </c>
       <c r="E122" s="40">
         <v>10</v>
       </c>
       <c r="F122" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G122" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H122" s="47">
         <v>0</v>
@@ -7777,7 +7789,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="45" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O122" s="46"/>
       <c r="P122" s="46"/>
@@ -7788,25 +7800,25 @@
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="36">
-        <v>10340111</v>
+        <v>10280011</v>
       </c>
       <c r="B123" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C123" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D123" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D123" s="39">
+        <v>102800001</v>
       </c>
       <c r="E123" s="40">
         <v>11</v>
       </c>
       <c r="F123" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G123" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H123" s="47">
         <v>0</v>
@@ -7827,7 +7839,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="45" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O123" s="46"/>
       <c r="P123" s="46"/>
@@ -7838,25 +7850,25 @@
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="36">
-        <v>10340112</v>
+        <v>10280012</v>
       </c>
       <c r="B124" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D124" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D124" s="39">
+        <v>102800001</v>
       </c>
       <c r="E124" s="40">
         <v>12</v>
       </c>
       <c r="F124" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G124" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H124" s="47">
         <v>0</v>
@@ -7877,7 +7889,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O124" s="46"/>
       <c r="P124" s="46"/>
@@ -7886,27 +7898,27 @@
       <c r="S124" s="42"/>
       <c r="T124" s="42"/>
     </row>
-    <row r="125" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A125" s="19">
-        <v>10380010</v>
-      </c>
-      <c r="B125" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D125" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E125" s="20">
-        <v>11</v>
+    <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A125" s="36">
+        <v>10200010</v>
+      </c>
+      <c r="B125" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C125" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E125" s="40">
+        <v>10</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G125" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H125" s="47">
         <v>0</v>
@@ -7927,36 +7939,36 @@
         <v>37</v>
       </c>
       <c r="N125" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O125" s="21"/>
-      <c r="P125" s="21"/>
-      <c r="Q125" s="21"/>
-      <c r="R125" s="21"/>
-      <c r="S125" s="23"/>
-      <c r="T125" s="23"/>
-    </row>
-    <row r="126" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A126" s="19">
-        <v>10380011</v>
-      </c>
-      <c r="B126" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C126" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D126" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E126" s="20">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="O125" s="46"/>
+      <c r="P125" s="46"/>
+      <c r="Q125" s="46"/>
+      <c r="R125" s="46"/>
+      <c r="S125" s="42"/>
+      <c r="T125" s="42"/>
+    </row>
+    <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A126" s="36">
+        <v>10200011</v>
+      </c>
+      <c r="B126" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C126" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D126" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E126" s="40">
+        <v>11</v>
       </c>
       <c r="F126" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G126" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H126" s="47">
         <v>0</v>
@@ -7977,36 +7989,36 @@
         <v>40</v>
       </c>
       <c r="N126" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O126" s="21"/>
-      <c r="P126" s="21"/>
-      <c r="Q126" s="21"/>
-      <c r="R126" s="21"/>
-      <c r="S126" s="23"/>
-      <c r="T126" s="23"/>
-    </row>
-    <row r="127" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A127" s="19">
-        <v>10380012</v>
-      </c>
-      <c r="B127" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D127" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E127" s="20">
-        <v>13</v>
+        <v>88</v>
+      </c>
+      <c r="O126" s="46"/>
+      <c r="P126" s="46"/>
+      <c r="Q126" s="46"/>
+      <c r="R126" s="46"/>
+      <c r="S126" s="42"/>
+      <c r="T126" s="42"/>
+    </row>
+    <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A127" s="36">
+        <v>10200012</v>
+      </c>
+      <c r="B127" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C127" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D127" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E127" s="40">
+        <v>12</v>
       </c>
       <c r="F127" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G127" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H127" s="47">
         <v>0</v>
@@ -8027,30 +8039,30 @@
         <v>43</v>
       </c>
       <c r="N127" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O127" s="21"/>
-      <c r="P127" s="21"/>
-      <c r="Q127" s="21"/>
-      <c r="R127" s="21"/>
-      <c r="S127" s="23"/>
-      <c r="T127" s="23"/>
-    </row>
-    <row r="128" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A128" s="19">
-        <v>10270010</v>
-      </c>
-      <c r="B128" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>82</v>
+        <v>89</v>
+      </c>
+      <c r="O127" s="46"/>
+      <c r="P127" s="46"/>
+      <c r="Q127" s="46"/>
+      <c r="R127" s="46"/>
+      <c r="S127" s="42"/>
+      <c r="T127" s="42"/>
+    </row>
+    <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A128" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B128" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C128" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D128" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E128" s="20">
-        <v>11</v>
+        <v>103400001</v>
+      </c>
+      <c r="E128" s="40">
+        <v>10</v>
       </c>
       <c r="F128" s="46" t="s">
         <v>64</v>
@@ -8077,30 +8089,30 @@
         <v>37</v>
       </c>
       <c r="N128" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="O128" s="21"/>
-      <c r="P128" s="21"/>
-      <c r="Q128" s="21"/>
-      <c r="R128" s="21"/>
-      <c r="S128" s="23"/>
-      <c r="T128" s="23"/>
-    </row>
-    <row r="129" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A129" s="19">
-        <v>10270011</v>
-      </c>
-      <c r="B129" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C129" s="20" t="s">
-        <v>82</v>
+        <v>87</v>
+      </c>
+      <c r="O128" s="46"/>
+      <c r="P128" s="46"/>
+      <c r="Q128" s="46"/>
+      <c r="R128" s="46"/>
+      <c r="S128" s="42"/>
+      <c r="T128" s="42"/>
+    </row>
+    <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A129" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B129" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C129" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D129" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E129" s="20">
-        <v>12</v>
+        <v>103400001</v>
+      </c>
+      <c r="E129" s="40">
+        <v>11</v>
       </c>
       <c r="F129" s="46" t="s">
         <v>66</v>
@@ -8127,30 +8139,30 @@
         <v>40</v>
       </c>
       <c r="N129" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="O129" s="21"/>
-      <c r="P129" s="21"/>
-      <c r="Q129" s="21"/>
-      <c r="R129" s="21"/>
-      <c r="S129" s="23"/>
-      <c r="T129" s="23"/>
-    </row>
-    <row r="130" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A130" s="19">
-        <v>10270012</v>
-      </c>
-      <c r="B130" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C130" s="20" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="O129" s="46"/>
+      <c r="P129" s="46"/>
+      <c r="Q129" s="46"/>
+      <c r="R129" s="46"/>
+      <c r="S129" s="42"/>
+      <c r="T129" s="42"/>
+    </row>
+    <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A130" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B130" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C130" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D130" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E130" s="20">
-        <v>13</v>
+        <v>103400001</v>
+      </c>
+      <c r="E130" s="40">
+        <v>12</v>
       </c>
       <c r="F130" s="46" t="s">
         <v>68</v>
@@ -8177,14 +8189,614 @@
         <v>43</v>
       </c>
       <c r="N130" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="O130" s="21"/>
-      <c r="P130" s="21"/>
-      <c r="Q130" s="21"/>
-      <c r="R130" s="21"/>
-      <c r="S130" s="23"/>
-      <c r="T130" s="23"/>
+        <v>89</v>
+      </c>
+      <c r="O130" s="46"/>
+      <c r="P130" s="46"/>
+      <c r="Q130" s="46"/>
+      <c r="R130" s="46"/>
+      <c r="S130" s="42"/>
+      <c r="T130" s="42"/>
+    </row>
+    <row r="131" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A131" s="19">
+        <v>10380010</v>
+      </c>
+      <c r="B131" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C131" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D131" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E131" s="20">
+        <v>11</v>
+      </c>
+      <c r="F131" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G131" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H131" s="47">
+        <v>0</v>
+      </c>
+      <c r="I131" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J131" s="43">
+        <v>0</v>
+      </c>
+      <c r="K131" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L131" s="48">
+        <v>0</v>
+      </c>
+      <c r="M131" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N131" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O131" s="21"/>
+      <c r="P131" s="21"/>
+      <c r="Q131" s="21"/>
+      <c r="R131" s="21"/>
+      <c r="S131" s="23"/>
+      <c r="T131" s="23"/>
+    </row>
+    <row r="132" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A132" s="19">
+        <v>10380011</v>
+      </c>
+      <c r="B132" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C132" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D132" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E132" s="20">
+        <v>12</v>
+      </c>
+      <c r="F132" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H132" s="47">
+        <v>0</v>
+      </c>
+      <c r="I132" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J132" s="43">
+        <v>0</v>
+      </c>
+      <c r="K132" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L132" s="48">
+        <v>0</v>
+      </c>
+      <c r="M132" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N132" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O132" s="21"/>
+      <c r="P132" s="21"/>
+      <c r="Q132" s="21"/>
+      <c r="R132" s="21"/>
+      <c r="S132" s="23"/>
+      <c r="T132" s="23"/>
+    </row>
+    <row r="133" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A133" s="19">
+        <v>10380012</v>
+      </c>
+      <c r="B133" s="19">
+        <v>103800</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D133" s="24">
+        <v>103800001</v>
+      </c>
+      <c r="E133" s="20">
+        <v>13</v>
+      </c>
+      <c r="F133" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G133" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H133" s="47">
+        <v>0</v>
+      </c>
+      <c r="I133" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J133" s="43">
+        <v>0</v>
+      </c>
+      <c r="K133" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L133" s="48">
+        <v>0</v>
+      </c>
+      <c r="M133" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N133" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O133" s="21"/>
+      <c r="P133" s="21"/>
+      <c r="Q133" s="21"/>
+      <c r="R133" s="21"/>
+      <c r="S133" s="23"/>
+      <c r="T133" s="23"/>
+    </row>
+    <row r="134" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A134" s="19">
+        <v>10270010</v>
+      </c>
+      <c r="B134" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D134" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E134" s="20">
+        <v>11</v>
+      </c>
+      <c r="F134" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G134" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H134" s="47">
+        <v>0</v>
+      </c>
+      <c r="I134" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J134" s="43">
+        <v>0</v>
+      </c>
+      <c r="K134" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L134" s="48">
+        <v>0</v>
+      </c>
+      <c r="M134" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N134" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O134" s="21"/>
+      <c r="P134" s="21"/>
+      <c r="Q134" s="21"/>
+      <c r="R134" s="21"/>
+      <c r="S134" s="23"/>
+      <c r="T134" s="23"/>
+    </row>
+    <row r="135" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A135" s="19">
+        <v>10270011</v>
+      </c>
+      <c r="B135" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D135" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E135" s="20">
+        <v>12</v>
+      </c>
+      <c r="F135" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G135" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H135" s="47">
+        <v>0</v>
+      </c>
+      <c r="I135" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J135" s="43">
+        <v>0</v>
+      </c>
+      <c r="K135" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L135" s="48">
+        <v>0</v>
+      </c>
+      <c r="M135" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N135" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O135" s="21"/>
+      <c r="P135" s="21"/>
+      <c r="Q135" s="21"/>
+      <c r="R135" s="21"/>
+      <c r="S135" s="23"/>
+      <c r="T135" s="23"/>
+    </row>
+    <row r="136" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A136" s="19">
+        <v>10270012</v>
+      </c>
+      <c r="B136" s="19">
+        <v>102700</v>
+      </c>
+      <c r="C136" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D136" s="24">
+        <v>102700001</v>
+      </c>
+      <c r="E136" s="20">
+        <v>13</v>
+      </c>
+      <c r="F136" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G136" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H136" s="47">
+        <v>0</v>
+      </c>
+      <c r="I136" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J136" s="43">
+        <v>0</v>
+      </c>
+      <c r="K136" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L136" s="48">
+        <v>0</v>
+      </c>
+      <c r="M136" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N136" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O136" s="21"/>
+      <c r="P136" s="21"/>
+      <c r="Q136" s="21"/>
+      <c r="R136" s="21"/>
+      <c r="S136" s="23"/>
+      <c r="T136" s="23"/>
+    </row>
+    <row r="137" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A137" s="19">
+        <v>10370010</v>
+      </c>
+      <c r="B137" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C137" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D137" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E137" s="20">
+        <v>11</v>
+      </c>
+      <c r="F137" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G137" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H137" s="47">
+        <v>0</v>
+      </c>
+      <c r="I137" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J137" s="43">
+        <v>0</v>
+      </c>
+      <c r="K137" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L137" s="48">
+        <v>0</v>
+      </c>
+      <c r="M137" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N137" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O137" s="21"/>
+      <c r="P137" s="21"/>
+      <c r="Q137" s="21"/>
+      <c r="R137" s="21"/>
+      <c r="S137" s="23"/>
+      <c r="T137" s="23"/>
+    </row>
+    <row r="138" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A138" s="19">
+        <v>10370011</v>
+      </c>
+      <c r="B138" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C138" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D138" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E138" s="20">
+        <v>12</v>
+      </c>
+      <c r="F138" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G138" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H138" s="47">
+        <v>0</v>
+      </c>
+      <c r="I138" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J138" s="43">
+        <v>0</v>
+      </c>
+      <c r="K138" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L138" s="48">
+        <v>0</v>
+      </c>
+      <c r="M138" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N138" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O138" s="21"/>
+      <c r="P138" s="21"/>
+      <c r="Q138" s="21"/>
+      <c r="R138" s="21"/>
+      <c r="S138" s="23"/>
+      <c r="T138" s="23"/>
+    </row>
+    <row r="139" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A139" s="19">
+        <v>10370012</v>
+      </c>
+      <c r="B139" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C139" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D139" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E139" s="20">
+        <v>13</v>
+      </c>
+      <c r="F139" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G139" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H139" s="47">
+        <v>0</v>
+      </c>
+      <c r="I139" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J139" s="43">
+        <v>0</v>
+      </c>
+      <c r="K139" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L139" s="48">
+        <v>0</v>
+      </c>
+      <c r="M139" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N139" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O139" s="21"/>
+      <c r="P139" s="21"/>
+      <c r="Q139" s="21"/>
+      <c r="R139" s="21"/>
+      <c r="S139" s="23"/>
+      <c r="T139" s="23"/>
+    </row>
+    <row r="140" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A140" s="19">
+        <v>10310010</v>
+      </c>
+      <c r="B140" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D140" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E140" s="20">
+        <v>11</v>
+      </c>
+      <c r="F140" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G140" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H140" s="47">
+        <v>0</v>
+      </c>
+      <c r="I140" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J140" s="43">
+        <v>0</v>
+      </c>
+      <c r="K140" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L140" s="48">
+        <v>0</v>
+      </c>
+      <c r="M140" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N140" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="O140" s="21"/>
+      <c r="P140" s="21"/>
+      <c r="Q140" s="21"/>
+      <c r="R140" s="21"/>
+      <c r="S140" s="23"/>
+      <c r="T140" s="23"/>
+    </row>
+    <row r="141" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A141" s="19">
+        <v>10310011</v>
+      </c>
+      <c r="B141" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C141" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D141" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E141" s="20">
+        <v>12</v>
+      </c>
+      <c r="F141" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G141" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H141" s="47">
+        <v>0</v>
+      </c>
+      <c r="I141" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J141" s="43">
+        <v>0</v>
+      </c>
+      <c r="K141" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L141" s="48">
+        <v>0</v>
+      </c>
+      <c r="M141" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N141" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="O141" s="21"/>
+      <c r="P141" s="21"/>
+      <c r="Q141" s="21"/>
+      <c r="R141" s="21"/>
+      <c r="S141" s="23"/>
+      <c r="T141" s="23"/>
+    </row>
+    <row r="142" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A142" s="19">
+        <v>10310012</v>
+      </c>
+      <c r="B142" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C142" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D142" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E142" s="20">
+        <v>13</v>
+      </c>
+      <c r="F142" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G142" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H142" s="47">
+        <v>0</v>
+      </c>
+      <c r="I142" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J142" s="43">
+        <v>0</v>
+      </c>
+      <c r="K142" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L142" s="48">
+        <v>0</v>
+      </c>
+      <c r="M142" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N142" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O142" s="21"/>
+      <c r="P142" s="21"/>
+      <c r="Q142" s="21"/>
+      <c r="R142" s="21"/>
+      <c r="S142" s="23"/>
+      <c r="T142" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -449,6 +449,12 @@
     <t>绿巨人</t>
   </si>
   <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
     <t>1980000_500000</t>
   </si>
   <si>
@@ -670,6 +676,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -688,8 +701,8 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -700,15 +713,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1721,7 +1727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T142"/>
+  <dimension ref="A1:T154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -5348,315 +5354,315 @@
       <c r="S73" s="23"/>
       <c r="T73" s="23"/>
     </row>
-    <row r="74" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A74" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B74" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C74" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D74" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E74" s="40">
-        <v>10</v>
+    <row r="74" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A74" s="19">
+        <v>1040001</v>
+      </c>
+      <c r="B74" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E74" s="20">
+        <v>1</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H74" s="41">
-        <v>0</v>
-      </c>
-      <c r="I74" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J74" s="43">
-        <v>0</v>
-      </c>
-      <c r="K74" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L74" s="44">
-        <v>0</v>
-      </c>
-      <c r="M74" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H74" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I74" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J74" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K74" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="27">
+        <v>100</v>
+      </c>
+      <c r="M74" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N74" s="45" t="s">
+      <c r="N74" s="21">
+        <v>0</v>
+      </c>
+      <c r="O74" s="21"/>
+      <c r="P74" s="21"/>
+      <c r="Q74" s="21"/>
+      <c r="R74" s="21"/>
+      <c r="S74" s="23"/>
+      <c r="T74" s="23"/>
+    </row>
+    <row r="75" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A75" s="19">
+        <v>1040002</v>
+      </c>
+      <c r="B75" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C75" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="O74" s="46"/>
-      <c r="P74" s="46"/>
-      <c r="Q74" s="46"/>
-      <c r="R74" s="46"/>
-      <c r="S74" s="42"/>
-      <c r="T74" s="42"/>
-    </row>
-    <row r="75" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A75" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B75" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D75" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E75" s="40">
-        <v>11</v>
+      <c r="D75" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E75" s="20">
+        <v>2</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H75" s="41">
-        <v>0</v>
-      </c>
-      <c r="I75" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J75" s="43">
-        <v>0</v>
-      </c>
-      <c r="K75" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L75" s="44">
-        <v>0</v>
-      </c>
-      <c r="M75" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I75" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J75" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K75" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="27">
+        <v>100</v>
+      </c>
+      <c r="M75" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N75" s="45" t="s">
+      <c r="N75" s="21">
+        <v>0</v>
+      </c>
+      <c r="O75" s="21"/>
+      <c r="P75" s="21"/>
+      <c r="Q75" s="21"/>
+      <c r="R75" s="21"/>
+      <c r="S75" s="23"/>
+      <c r="T75" s="23"/>
+    </row>
+    <row r="76" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A76" s="19">
+        <v>1040003</v>
+      </c>
+      <c r="B76" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D76" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E76" s="20">
+        <v>3</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G76" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H76" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I76" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J76" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K76" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="27">
+        <v>100</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="N76" s="21">
+        <v>0</v>
+      </c>
+      <c r="O76" s="21"/>
+      <c r="P76" s="21"/>
+      <c r="Q76" s="21"/>
+      <c r="R76" s="21"/>
+      <c r="S76" s="23"/>
+      <c r="T76" s="23"/>
+    </row>
+    <row r="77" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A77" s="19">
+        <v>1039001</v>
+      </c>
+      <c r="B77" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C77" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="O75" s="46"/>
-      <c r="P75" s="46"/>
-      <c r="Q75" s="46"/>
-      <c r="R75" s="46"/>
-      <c r="S75" s="42"/>
-      <c r="T75" s="42"/>
-    </row>
-    <row r="76" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A76" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B76" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C76" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D76" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E76" s="40">
-        <v>12</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G76" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H76" s="47">
-        <v>0</v>
-      </c>
-      <c r="I76" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J76" s="43">
-        <v>0</v>
-      </c>
-      <c r="K76" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="44">
-        <v>0</v>
-      </c>
-      <c r="M76" s="42" t="s">
+      <c r="D77" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E77" s="20">
+        <v>1</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G77" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H77" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I77" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J77" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K77" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="27">
+        <v>100</v>
+      </c>
+      <c r="M77" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" s="21">
+        <v>0</v>
+      </c>
+      <c r="O77" s="21"/>
+      <c r="P77" s="21"/>
+      <c r="Q77" s="21"/>
+      <c r="R77" s="21"/>
+      <c r="S77" s="23"/>
+      <c r="T77" s="23"/>
+    </row>
+    <row r="78" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A78" s="19">
+        <v>1039002</v>
+      </c>
+      <c r="B78" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D78" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E78" s="20">
+        <v>2</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I78" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J78" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K78" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="27">
+        <v>100</v>
+      </c>
+      <c r="M78" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N78" s="21">
+        <v>0</v>
+      </c>
+      <c r="O78" s="21"/>
+      <c r="P78" s="21"/>
+      <c r="Q78" s="21"/>
+      <c r="R78" s="21"/>
+      <c r="S78" s="23"/>
+      <c r="T78" s="23"/>
+    </row>
+    <row r="79" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A79" s="19">
+        <v>1039003</v>
+      </c>
+      <c r="B79" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E79" s="20">
+        <v>3</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H79" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I79" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J79" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K79" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="27">
+        <v>100</v>
+      </c>
+      <c r="M79" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N76" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O76" s="46"/>
-      <c r="P76" s="46"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="46"/>
-      <c r="S76" s="42"/>
-      <c r="T76" s="42"/>
-    </row>
-    <row r="77" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A77" s="36">
-        <v>10030010</v>
-      </c>
-      <c r="B77" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E77" s="40">
-        <v>10</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="G77" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H77" s="41">
-        <v>0</v>
-      </c>
-      <c r="I77" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J77" s="43">
-        <v>0</v>
-      </c>
-      <c r="K77" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L77" s="48">
-        <v>0</v>
-      </c>
-      <c r="M77" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N77" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="46"/>
-      <c r="R77" s="46"/>
-      <c r="S77" s="42"/>
-      <c r="T77" s="42"/>
-    </row>
-    <row r="78" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A78" s="36">
-        <v>10030011</v>
-      </c>
-      <c r="B78" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E78" s="40">
-        <v>11</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G78" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H78" s="41">
-        <v>0</v>
-      </c>
-      <c r="I78" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J78" s="43">
-        <v>0</v>
-      </c>
-      <c r="K78" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L78" s="48">
-        <v>0</v>
-      </c>
-      <c r="M78" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N78" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="46"/>
-      <c r="R78" s="46"/>
-      <c r="S78" s="42"/>
-      <c r="T78" s="42"/>
-    </row>
-    <row r="79" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A79" s="36">
-        <v>10030012</v>
-      </c>
-      <c r="B79" s="37">
-        <v>100300</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D79" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E79" s="40">
-        <v>12</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G79" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="H79" s="47">
-        <v>0</v>
-      </c>
-      <c r="I79" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J79" s="43">
-        <v>0</v>
-      </c>
-      <c r="K79" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L79" s="48">
-        <v>0</v>
-      </c>
-      <c r="M79" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N79" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O79" s="46"/>
-      <c r="P79" s="46"/>
-      <c r="Q79" s="46"/>
-      <c r="R79" s="46"/>
-      <c r="S79" s="42"/>
-      <c r="T79" s="42"/>
+      <c r="N79" s="21">
+        <v>0</v>
+      </c>
+      <c r="O79" s="21"/>
+      <c r="P79" s="21"/>
+      <c r="Q79" s="21"/>
+      <c r="R79" s="21"/>
+      <c r="S79" s="23"/>
+      <c r="T79" s="23"/>
     </row>
     <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A80" s="36">
-        <v>10070010</v>
+        <v>10010010</v>
       </c>
       <c r="B80" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D80" s="39">
         <v>100100026</v>
@@ -5665,10 +5671,10 @@
         <v>10</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H80" s="41">
         <v>0</v>
@@ -5689,7 +5695,7 @@
         <v>37</v>
       </c>
       <c r="N80" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O80" s="46"/>
       <c r="P80" s="46"/>
@@ -5700,13 +5706,13 @@
     </row>
     <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A81" s="36">
-        <v>10070011</v>
+        <v>10010011</v>
       </c>
       <c r="B81" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D81" s="39">
         <v>100100026</v>
@@ -5715,10 +5721,10 @@
         <v>11</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H81" s="41">
         <v>0</v>
@@ -5739,7 +5745,7 @@
         <v>40</v>
       </c>
       <c r="N81" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O81" s="46"/>
       <c r="P81" s="46"/>
@@ -5750,13 +5756,13 @@
     </row>
     <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A82" s="36">
-        <v>10070012</v>
+        <v>10010012</v>
       </c>
       <c r="B82" s="37">
-        <v>100700</v>
+        <v>100100</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D82" s="39">
         <v>100100026</v>
@@ -5765,10 +5771,10 @@
         <v>12</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H82" s="47">
         <v>0</v>
@@ -5789,7 +5795,7 @@
         <v>43</v>
       </c>
       <c r="N82" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O82" s="46"/>
       <c r="P82" s="46"/>
@@ -5798,165 +5804,165 @@
       <c r="S82" s="42"/>
       <c r="T82" s="42"/>
     </row>
-    <row r="83" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B83" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C83" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D83" s="50">
-        <v>101200026</v>
+        <v>10030010</v>
+      </c>
+      <c r="B83" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C83" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="39">
+        <v>100100026</v>
       </c>
       <c r="E83" s="40">
         <v>10</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H83" s="41">
         <v>0</v>
       </c>
-      <c r="I83" s="43">
+      <c r="I83" s="42">
         <v>9500</v>
       </c>
       <c r="J83" s="43">
         <v>0</v>
       </c>
-      <c r="K83" s="48" t="s">
+      <c r="K83" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="48">
         <v>0</v>
       </c>
-      <c r="M83" s="43" t="s">
+      <c r="M83" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="O83" s="45"/>
-      <c r="P83" s="45"/>
-      <c r="Q83" s="45"/>
-      <c r="R83" s="45"/>
-      <c r="S83" s="43"/>
-      <c r="T83" s="43"/>
-    </row>
-    <row r="84" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>89</v>
+      </c>
+      <c r="O83" s="46"/>
+      <c r="P83" s="46"/>
+      <c r="Q83" s="46"/>
+      <c r="R83" s="46"/>
+      <c r="S83" s="42"/>
+      <c r="T83" s="42"/>
+    </row>
+    <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B84" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C84" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D84" s="50">
-        <v>101200026</v>
+        <v>10030011</v>
+      </c>
+      <c r="B84" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C84" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" s="39">
+        <v>100100026</v>
       </c>
       <c r="E84" s="40">
         <v>11</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H84" s="41">
         <v>0</v>
       </c>
-      <c r="I84" s="43">
+      <c r="I84" s="42">
         <v>9500</v>
       </c>
       <c r="J84" s="43">
         <v>0</v>
       </c>
-      <c r="K84" s="48" t="s">
+      <c r="K84" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="48">
         <v>0</v>
       </c>
-      <c r="M84" s="43" t="s">
+      <c r="M84" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="O84" s="45"/>
-      <c r="P84" s="45"/>
-      <c r="Q84" s="45"/>
-      <c r="R84" s="45"/>
-      <c r="S84" s="43"/>
-      <c r="T84" s="43"/>
-    </row>
-    <row r="85" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O84" s="46"/>
+      <c r="P84" s="46"/>
+      <c r="Q84" s="46"/>
+      <c r="R84" s="46"/>
+      <c r="S84" s="42"/>
+      <c r="T84" s="42"/>
+    </row>
+    <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B85" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C85" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D85" s="50">
-        <v>101200026</v>
+        <v>10030012</v>
+      </c>
+      <c r="B85" s="37">
+        <v>100300</v>
+      </c>
+      <c r="C85" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="39">
+        <v>100100026</v>
       </c>
       <c r="E85" s="40">
         <v>12</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H85" s="47">
         <v>0</v>
       </c>
-      <c r="I85" s="43">
+      <c r="I85" s="42">
         <v>9500</v>
       </c>
       <c r="J85" s="43">
         <v>0</v>
       </c>
-      <c r="K85" s="48" t="s">
+      <c r="K85" s="44" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="48">
         <v>0</v>
       </c>
-      <c r="M85" s="43" t="s">
+      <c r="M85" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O85" s="45"/>
-      <c r="P85" s="45"/>
-      <c r="Q85" s="45"/>
-      <c r="R85" s="45"/>
-      <c r="S85" s="43"/>
-      <c r="T85" s="43"/>
+        <v>91</v>
+      </c>
+      <c r="O85" s="46"/>
+      <c r="P85" s="46"/>
+      <c r="Q85" s="46"/>
+      <c r="R85" s="46"/>
+      <c r="S85" s="42"/>
+      <c r="T85" s="42"/>
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10140010</v>
+        <v>10070010</v>
       </c>
       <c r="B86" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D86" s="39">
         <v>100100026</v>
@@ -5965,10 +5971,10 @@
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H86" s="41">
         <v>0</v>
@@ -5989,7 +5995,7 @@
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -6000,13 +6006,13 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10140011</v>
+        <v>10070011</v>
       </c>
       <c r="B87" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D87" s="39">
         <v>100100026</v>
@@ -6015,10 +6021,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H87" s="41">
         <v>0</v>
@@ -6039,7 +6045,7 @@
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6050,13 +6056,13 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10140012</v>
+        <v>10070012</v>
       </c>
       <c r="B88" s="37">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D88" s="39">
         <v>100100026</v>
@@ -6065,10 +6071,10 @@
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6089,7 +6095,7 @@
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6098,177 +6104,177 @@
       <c r="S88" s="42"/>
       <c r="T88" s="42"/>
     </row>
-    <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
+    <row r="89" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10170010</v>
-      </c>
-      <c r="B89" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D89" s="39">
-        <v>101700001</v>
+        <v>10120010</v>
+      </c>
+      <c r="B89" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C89" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="50">
+        <v>101200026</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H89" s="41">
         <v>0</v>
       </c>
-      <c r="I89" s="42">
+      <c r="I89" s="43">
         <v>9500</v>
       </c>
       <c r="J89" s="43">
         <v>0</v>
       </c>
-      <c r="K89" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L89" s="44">
-        <v>0</v>
-      </c>
-      <c r="M89" s="42" t="s">
+      <c r="K89" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="48">
+        <v>0</v>
+      </c>
+      <c r="M89" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="O89" s="46"/>
-      <c r="P89" s="46"/>
-      <c r="Q89" s="46"/>
-      <c r="R89" s="46"/>
-      <c r="S89" s="42"/>
-      <c r="T89" s="42"/>
-    </row>
-    <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>89</v>
+      </c>
+      <c r="O89" s="45"/>
+      <c r="P89" s="45"/>
+      <c r="Q89" s="45"/>
+      <c r="R89" s="45"/>
+      <c r="S89" s="43"/>
+      <c r="T89" s="43"/>
+    </row>
+    <row r="90" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10170011</v>
-      </c>
-      <c r="B90" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C90" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D90" s="39">
-        <v>101700001</v>
+        <v>10120011</v>
+      </c>
+      <c r="B90" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D90" s="50">
+        <v>101200026</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H90" s="41">
         <v>0</v>
       </c>
-      <c r="I90" s="42">
+      <c r="I90" s="43">
         <v>9500</v>
       </c>
       <c r="J90" s="43">
         <v>0</v>
       </c>
-      <c r="K90" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L90" s="44">
-        <v>0</v>
-      </c>
-      <c r="M90" s="42" t="s">
+      <c r="K90" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="48">
+        <v>0</v>
+      </c>
+      <c r="M90" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="O90" s="46"/>
-      <c r="P90" s="46"/>
-      <c r="Q90" s="46"/>
-      <c r="R90" s="46"/>
-      <c r="S90" s="42"/>
-      <c r="T90" s="42"/>
-    </row>
-    <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O90" s="45"/>
+      <c r="P90" s="45"/>
+      <c r="Q90" s="45"/>
+      <c r="R90" s="45"/>
+      <c r="S90" s="43"/>
+      <c r="T90" s="43"/>
+    </row>
+    <row r="91" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10170012</v>
-      </c>
-      <c r="B91" s="37">
-        <v>101700</v>
-      </c>
-      <c r="C91" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D91" s="39">
-        <v>101700001</v>
+        <v>10120012</v>
+      </c>
+      <c r="B91" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C91" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D91" s="50">
+        <v>101200026</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
       </c>
-      <c r="I91" s="42">
+      <c r="I91" s="43">
         <v>9500</v>
       </c>
       <c r="J91" s="43">
         <v>0</v>
       </c>
-      <c r="K91" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L91" s="44">
-        <v>0</v>
-      </c>
-      <c r="M91" s="42" t="s">
+      <c r="K91" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="48">
+        <v>0</v>
+      </c>
+      <c r="M91" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O91" s="46"/>
-      <c r="P91" s="46"/>
-      <c r="Q91" s="46"/>
-      <c r="R91" s="46"/>
-      <c r="S91" s="42"/>
-      <c r="T91" s="42"/>
+        <v>91</v>
+      </c>
+      <c r="O91" s="45"/>
+      <c r="P91" s="45"/>
+      <c r="Q91" s="45"/>
+      <c r="R91" s="45"/>
+      <c r="S91" s="43"/>
+      <c r="T91" s="43"/>
     </row>
     <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10210010</v>
+        <v>10140010</v>
       </c>
       <c r="B92" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D92" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H92" s="41">
         <v>0</v>
@@ -6282,14 +6288,14 @@
       <c r="K92" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L92" s="48">
+      <c r="L92" s="44">
         <v>0</v>
       </c>
       <c r="M92" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O92" s="46"/>
       <c r="P92" s="46"/>
@@ -6300,25 +6306,25 @@
     </row>
     <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10210011</v>
+        <v>10140011</v>
       </c>
       <c r="B93" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D93" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H93" s="41">
         <v>0</v>
@@ -6332,14 +6338,14 @@
       <c r="K93" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L93" s="48">
+      <c r="L93" s="44">
         <v>0</v>
       </c>
       <c r="M93" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O93" s="46"/>
       <c r="P93" s="46"/>
@@ -6350,25 +6356,25 @@
     </row>
     <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10210012</v>
+        <v>10140012</v>
       </c>
       <c r="B94" s="37">
-        <v>102100</v>
+        <v>101400</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D94" s="39">
-        <v>102100001</v>
+        <v>100100026</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
@@ -6382,14 +6388,14 @@
       <c r="K94" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L94" s="48">
+      <c r="L94" s="44">
         <v>0</v>
       </c>
       <c r="M94" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O94" s="46"/>
       <c r="P94" s="46"/>
@@ -6400,16 +6406,16 @@
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10220010</v>
+        <v>10170010</v>
       </c>
       <c r="B95" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D95" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
@@ -6432,14 +6438,14 @@
       <c r="K95" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L95" s="48">
+      <c r="L95" s="44">
         <v>0</v>
       </c>
       <c r="M95" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6450,16 +6456,16 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10220011</v>
+        <v>10170011</v>
       </c>
       <c r="B96" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D96" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
@@ -6482,14 +6488,14 @@
       <c r="K96" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L96" s="48">
+      <c r="L96" s="44">
         <v>0</v>
       </c>
       <c r="M96" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6500,16 +6506,16 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10220012</v>
+        <v>10170012</v>
       </c>
       <c r="B97" s="37">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D97" s="39">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
@@ -6532,14 +6538,14 @@
       <c r="K97" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L97" s="48">
+      <c r="L97" s="44">
         <v>0</v>
       </c>
       <c r="M97" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6550,25 +6556,25 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10240010</v>
+        <v>10210010</v>
       </c>
       <c r="B98" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D98" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H98" s="41">
         <v>0</v>
@@ -6589,7 +6595,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6600,25 +6606,25 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10240011</v>
+        <v>10210011</v>
       </c>
       <c r="B99" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D99" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H99" s="41">
         <v>0</v>
@@ -6639,7 +6645,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6650,25 +6656,25 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10240012</v>
+        <v>10210012</v>
       </c>
       <c r="B100" s="37">
-        <v>102400</v>
+        <v>102100</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D100" s="39">
-        <v>102400026</v>
+        <v>102100001</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
@@ -6689,7 +6695,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6700,16 +6706,16 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10180010</v>
+        <v>10220010</v>
       </c>
       <c r="B101" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D101" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
@@ -6720,7 +6726,7 @@
       <c r="G101" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H101" s="47">
+      <c r="H101" s="41">
         <v>0</v>
       </c>
       <c r="I101" s="42">
@@ -6739,7 +6745,7 @@
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6750,16 +6756,16 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10180011</v>
+        <v>10220011</v>
       </c>
       <c r="B102" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D102" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
@@ -6770,7 +6776,7 @@
       <c r="G102" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H102" s="47">
+      <c r="H102" s="41">
         <v>0</v>
       </c>
       <c r="I102" s="42">
@@ -6789,7 +6795,7 @@
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6800,16 +6806,16 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10180012</v>
+        <v>10220012</v>
       </c>
       <c r="B103" s="37">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D103" s="39">
-        <v>101800001</v>
+        <v>102200001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
@@ -6839,7 +6845,7 @@
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6850,27 +6856,27 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10250010</v>
+        <v>10240010</v>
       </c>
       <c r="B104" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D104" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="H104" s="47">
+        <v>35</v>
+      </c>
+      <c r="H104" s="41">
         <v>0</v>
       </c>
       <c r="I104" s="42">
@@ -6889,7 +6895,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6900,27 +6906,27 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10250011</v>
+        <v>10240011</v>
       </c>
       <c r="B105" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D105" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H105" s="47">
+        <v>39</v>
+      </c>
+      <c r="H105" s="41">
         <v>0</v>
       </c>
       <c r="I105" s="42">
@@ -6939,7 +6945,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6950,25 +6956,25 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10250012</v>
+        <v>10240012</v>
       </c>
       <c r="B106" s="37">
-        <v>102500</v>
+        <v>102400</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D106" s="39">
-        <v>102500001</v>
+        <v>102400026</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H106" s="47">
         <v>0</v>
@@ -6989,7 +6995,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -7000,16 +7006,16 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10230010</v>
+        <v>10180010</v>
       </c>
       <c r="B107" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D107" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
@@ -7039,7 +7045,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7050,16 +7056,16 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10230011</v>
+        <v>10180011</v>
       </c>
       <c r="B108" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D108" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
@@ -7089,7 +7095,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7100,16 +7106,16 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10230012</v>
+        <v>10180012</v>
       </c>
       <c r="B109" s="37">
-        <v>102300</v>
+        <v>101800</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D109" s="39">
-        <v>102300001</v>
+        <v>101800001</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
@@ -7139,7 +7145,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7150,31 +7156,31 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10340010</v>
+        <v>10250010</v>
       </c>
       <c r="B110" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D110" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H110" s="47">
         <v>0</v>
       </c>
       <c r="I110" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J110" s="43">
         <v>0</v>
@@ -7189,7 +7195,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7200,31 +7206,31 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10340011</v>
+        <v>10250011</v>
       </c>
       <c r="B111" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D111" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H111" s="47">
         <v>0</v>
       </c>
       <c r="I111" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J111" s="43">
         <v>0</v>
@@ -7239,7 +7245,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7250,31 +7256,31 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10340012</v>
+        <v>10250012</v>
       </c>
       <c r="B112" s="37">
-        <v>103400</v>
+        <v>102500</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D112" s="39">
-        <v>103000001</v>
+        <v>102500001</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
       </c>
       <c r="I112" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J112" s="43">
         <v>0</v>
@@ -7289,7 +7295,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7300,31 +7306,31 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10350010</v>
+        <v>10230010</v>
       </c>
       <c r="B113" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D113" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
       </c>
       <c r="F113" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H113" s="47">
         <v>0</v>
       </c>
       <c r="I113" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J113" s="43">
         <v>0</v>
@@ -7339,7 +7345,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7350,31 +7356,31 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10350011</v>
+        <v>10230011</v>
       </c>
       <c r="B114" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D114" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G114" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H114" s="47">
         <v>0</v>
       </c>
       <c r="I114" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J114" s="43">
         <v>0</v>
@@ -7389,7 +7395,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7400,31 +7406,31 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10350012</v>
+        <v>10230012</v>
       </c>
       <c r="B115" s="37">
-        <v>103500</v>
+        <v>102300</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D115" s="39">
-        <v>102900001</v>
+        <v>102300001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
       </c>
       <c r="F115" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H115" s="47">
         <v>0</v>
       </c>
       <c r="I115" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J115" s="43">
         <v>0</v>
@@ -7439,7 +7445,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7450,25 +7456,25 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10350110</v>
+        <v>10340010</v>
       </c>
       <c r="B116" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D116" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G116" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H116" s="47">
         <v>0</v>
@@ -7489,7 +7495,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7500,25 +7506,25 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10350111</v>
+        <v>10340011</v>
       </c>
       <c r="B117" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D117" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
       </c>
       <c r="F117" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G117" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H117" s="47">
         <v>0</v>
@@ -7539,7 +7545,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7550,25 +7556,25 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10350112</v>
+        <v>10340012</v>
       </c>
       <c r="B118" s="37">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D118" s="39">
-        <v>103501001</v>
+        <v>103000001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G118" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H118" s="47">
         <v>0</v>
@@ -7589,7 +7595,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7600,25 +7606,25 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="36">
-        <v>10360010</v>
+        <v>10350010</v>
       </c>
       <c r="B119" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D119" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E119" s="40">
         <v>10</v>
       </c>
-      <c r="F119" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G119" s="51" t="s">
-        <v>35</v>
+      <c r="F119" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G119" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H119" s="47">
         <v>0</v>
@@ -7639,7 +7645,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O119" s="46"/>
       <c r="P119" s="46"/>
@@ -7650,25 +7656,25 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="36">
-        <v>10360011</v>
+        <v>10350011</v>
       </c>
       <c r="B120" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D120" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E120" s="40">
         <v>11</v>
       </c>
-      <c r="F120" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G120" s="51" t="s">
-        <v>39</v>
+      <c r="F120" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G120" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H120" s="47">
         <v>0</v>
@@ -7689,7 +7695,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O120" s="46"/>
       <c r="P120" s="46"/>
@@ -7700,25 +7706,25 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="36">
-        <v>10360012</v>
+        <v>10350012</v>
       </c>
       <c r="B121" s="37">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D121" s="39">
-        <v>103600001</v>
+        <v>102900001</v>
       </c>
       <c r="E121" s="40">
         <v>12</v>
       </c>
-      <c r="F121" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G121" s="51" t="s">
-        <v>42</v>
+      <c r="F121" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G121" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H121" s="47">
         <v>0</v>
@@ -7739,7 +7745,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O121" s="46"/>
       <c r="P121" s="46"/>
@@ -7750,25 +7756,25 @@
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="36">
-        <v>10280010</v>
+        <v>10350110</v>
       </c>
       <c r="B122" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D122" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E122" s="40">
         <v>10</v>
       </c>
-      <c r="F122" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="G122" s="51" t="s">
-        <v>51</v>
+      <c r="F122" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G122" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H122" s="47">
         <v>0</v>
@@ -7789,7 +7795,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O122" s="46"/>
       <c r="P122" s="46"/>
@@ -7800,25 +7806,25 @@
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="36">
-        <v>10280011</v>
+        <v>10350111</v>
       </c>
       <c r="B123" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C123" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D123" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E123" s="40">
         <v>11</v>
       </c>
-      <c r="F123" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="G123" s="51" t="s">
-        <v>53</v>
+      <c r="F123" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G123" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H123" s="47">
         <v>0</v>
@@ -7839,7 +7845,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O123" s="46"/>
       <c r="P123" s="46"/>
@@ -7850,25 +7856,25 @@
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="36">
-        <v>10280012</v>
+        <v>10350112</v>
       </c>
       <c r="B124" s="37">
-        <v>102800</v>
+        <v>103501</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D124" s="39">
-        <v>102800001</v>
+        <v>103501001</v>
       </c>
       <c r="E124" s="40">
         <v>12</v>
       </c>
-      <c r="F124" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="G124" s="51" t="s">
-        <v>55</v>
+      <c r="F124" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G124" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H124" s="47">
         <v>0</v>
@@ -7889,7 +7895,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O124" s="46"/>
       <c r="P124" s="46"/>
@@ -7900,25 +7906,25 @@
     </row>
     <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A125" s="36">
-        <v>10200010</v>
+        <v>10360010</v>
       </c>
       <c r="B125" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C125" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D125" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E125" s="40">
         <v>10</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G125" s="51" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H125" s="47">
         <v>0</v>
@@ -7939,7 +7945,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O125" s="46"/>
       <c r="P125" s="46"/>
@@ -7950,25 +7956,25 @@
     </row>
     <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A126" s="36">
-        <v>10200011</v>
+        <v>10360011</v>
       </c>
       <c r="B126" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D126" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E126" s="40">
         <v>11</v>
       </c>
       <c r="F126" s="46" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G126" s="51" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H126" s="47">
         <v>0</v>
@@ -7989,7 +7995,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O126" s="46"/>
       <c r="P126" s="46"/>
@@ -8000,25 +8006,25 @@
     </row>
     <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A127" s="36">
-        <v>10200012</v>
+        <v>10360012</v>
       </c>
       <c r="B127" s="37">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C127" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D127" s="39">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="E127" s="40">
         <v>12</v>
       </c>
       <c r="F127" s="46" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G127" s="51" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H127" s="47">
         <v>0</v>
@@ -8039,7 +8045,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O127" s="46"/>
       <c r="P127" s="46"/>
@@ -8050,25 +8056,25 @@
     </row>
     <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A128" s="36">
-        <v>10340110</v>
+        <v>10280010</v>
       </c>
       <c r="B128" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D128" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D128" s="39">
+        <v>102800001</v>
       </c>
       <c r="E128" s="40">
         <v>10</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G128" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H128" s="47">
         <v>0</v>
@@ -8089,7 +8095,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O128" s="46"/>
       <c r="P128" s="46"/>
@@ -8100,25 +8106,25 @@
     </row>
     <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A129" s="36">
-        <v>10340111</v>
+        <v>10280011</v>
       </c>
       <c r="B129" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C129" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D129" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D129" s="39">
+        <v>102800001</v>
       </c>
       <c r="E129" s="40">
         <v>11</v>
       </c>
       <c r="F129" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G129" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H129" s="47">
         <v>0</v>
@@ -8139,7 +8145,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O129" s="46"/>
       <c r="P129" s="46"/>
@@ -8150,25 +8156,25 @@
     </row>
     <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A130" s="36">
-        <v>10340112</v>
+        <v>10280012</v>
       </c>
       <c r="B130" s="37">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D130" s="24">
-        <v>103400001</v>
+        <v>78</v>
+      </c>
+      <c r="D130" s="39">
+        <v>102800001</v>
       </c>
       <c r="E130" s="40">
         <v>12</v>
       </c>
       <c r="F130" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G130" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H130" s="47">
         <v>0</v>
@@ -8189,7 +8195,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O130" s="46"/>
       <c r="P130" s="46"/>
@@ -8198,21 +8204,21 @@
       <c r="S130" s="42"/>
       <c r="T130" s="42"/>
     </row>
-    <row r="131" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A131" s="19">
-        <v>10380010</v>
-      </c>
-      <c r="B131" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C131" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D131" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E131" s="20">
-        <v>11</v>
+    <row r="131" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A131" s="36">
+        <v>10200010</v>
+      </c>
+      <c r="B131" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C131" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D131" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E131" s="40">
+        <v>10</v>
       </c>
       <c r="F131" s="46" t="s">
         <v>50</v>
@@ -8239,30 +8245,30 @@
         <v>37</v>
       </c>
       <c r="N131" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="O131" s="21"/>
-      <c r="P131" s="21"/>
-      <c r="Q131" s="21"/>
-      <c r="R131" s="21"/>
-      <c r="S131" s="23"/>
-      <c r="T131" s="23"/>
-    </row>
-    <row r="132" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A132" s="19">
-        <v>10380011</v>
-      </c>
-      <c r="B132" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C132" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D132" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E132" s="20">
-        <v>12</v>
+        <v>89</v>
+      </c>
+      <c r="O131" s="46"/>
+      <c r="P131" s="46"/>
+      <c r="Q131" s="46"/>
+      <c r="R131" s="46"/>
+      <c r="S131" s="42"/>
+      <c r="T131" s="42"/>
+    </row>
+    <row r="132" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A132" s="36">
+        <v>10200011</v>
+      </c>
+      <c r="B132" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C132" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D132" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E132" s="40">
+        <v>11</v>
       </c>
       <c r="F132" s="46" t="s">
         <v>52</v>
@@ -8289,30 +8295,30 @@
         <v>40</v>
       </c>
       <c r="N132" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="O132" s="21"/>
-      <c r="P132" s="21"/>
-      <c r="Q132" s="21"/>
-      <c r="R132" s="21"/>
-      <c r="S132" s="23"/>
-      <c r="T132" s="23"/>
-    </row>
-    <row r="133" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A133" s="19">
-        <v>10380012</v>
-      </c>
-      <c r="B133" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C133" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D133" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E133" s="20">
-        <v>13</v>
+        <v>90</v>
+      </c>
+      <c r="O132" s="46"/>
+      <c r="P132" s="46"/>
+      <c r="Q132" s="46"/>
+      <c r="R132" s="46"/>
+      <c r="S132" s="42"/>
+      <c r="T132" s="42"/>
+    </row>
+    <row r="133" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A133" s="36">
+        <v>10200012</v>
+      </c>
+      <c r="B133" s="37">
+        <v>102000</v>
+      </c>
+      <c r="C133" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D133" s="39">
+        <v>102000001</v>
+      </c>
+      <c r="E133" s="40">
+        <v>12</v>
       </c>
       <c r="F133" s="46" t="s">
         <v>54</v>
@@ -8339,36 +8345,36 @@
         <v>43</v>
       </c>
       <c r="N133" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O133" s="21"/>
-      <c r="P133" s="21"/>
-      <c r="Q133" s="21"/>
-      <c r="R133" s="21"/>
-      <c r="S133" s="23"/>
-      <c r="T133" s="23"/>
-    </row>
-    <row r="134" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A134" s="19">
-        <v>10270010</v>
-      </c>
-      <c r="B134" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="O133" s="46"/>
+      <c r="P133" s="46"/>
+      <c r="Q133" s="46"/>
+      <c r="R133" s="46"/>
+      <c r="S133" s="42"/>
+      <c r="T133" s="42"/>
+    </row>
+    <row r="134" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A134" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B134" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C134" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D134" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E134" s="20">
-        <v>11</v>
+        <v>103400001</v>
+      </c>
+      <c r="E134" s="40">
+        <v>10</v>
       </c>
       <c r="F134" s="46" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G134" s="51" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H134" s="47">
         <v>0</v>
@@ -8389,36 +8395,36 @@
         <v>37</v>
       </c>
       <c r="N134" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="O134" s="21"/>
-      <c r="P134" s="21"/>
-      <c r="Q134" s="21"/>
-      <c r="R134" s="21"/>
-      <c r="S134" s="23"/>
-      <c r="T134" s="23"/>
-    </row>
-    <row r="135" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A135" s="19">
-        <v>10270011</v>
-      </c>
-      <c r="B135" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>82</v>
+        <v>89</v>
+      </c>
+      <c r="O134" s="46"/>
+      <c r="P134" s="46"/>
+      <c r="Q134" s="46"/>
+      <c r="R134" s="46"/>
+      <c r="S134" s="42"/>
+      <c r="T134" s="42"/>
+    </row>
+    <row r="135" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A135" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B135" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C135" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D135" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E135" s="20">
-        <v>12</v>
+        <v>103400001</v>
+      </c>
+      <c r="E135" s="40">
+        <v>11</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G135" s="51" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H135" s="47">
         <v>0</v>
@@ -8439,36 +8445,36 @@
         <v>40</v>
       </c>
       <c r="N135" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="O135" s="21"/>
-      <c r="P135" s="21"/>
-      <c r="Q135" s="21"/>
-      <c r="R135" s="21"/>
-      <c r="S135" s="23"/>
-      <c r="T135" s="23"/>
-    </row>
-    <row r="136" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A136" s="19">
-        <v>10270012</v>
-      </c>
-      <c r="B136" s="19">
-        <v>102700</v>
-      </c>
-      <c r="C136" s="20" t="s">
-        <v>82</v>
+        <v>90</v>
+      </c>
+      <c r="O135" s="46"/>
+      <c r="P135" s="46"/>
+      <c r="Q135" s="46"/>
+      <c r="R135" s="46"/>
+      <c r="S135" s="42"/>
+      <c r="T135" s="42"/>
+    </row>
+    <row r="136" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A136" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B136" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C136" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D136" s="24">
-        <v>102700001</v>
-      </c>
-      <c r="E136" s="20">
-        <v>13</v>
+        <v>103400001</v>
+      </c>
+      <c r="E136" s="40">
+        <v>12</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G136" s="51" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H136" s="47">
         <v>0</v>
@@ -8489,36 +8495,36 @@
         <v>43</v>
       </c>
       <c r="N136" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O136" s="21"/>
-      <c r="P136" s="21"/>
-      <c r="Q136" s="21"/>
-      <c r="R136" s="21"/>
-      <c r="S136" s="23"/>
-      <c r="T136" s="23"/>
+        <v>91</v>
+      </c>
+      <c r="O136" s="46"/>
+      <c r="P136" s="46"/>
+      <c r="Q136" s="46"/>
+      <c r="R136" s="46"/>
+      <c r="S136" s="42"/>
+      <c r="T136" s="42"/>
     </row>
     <row r="137" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A137" s="19">
-        <v>10370010</v>
+        <v>10380010</v>
       </c>
       <c r="B137" s="19">
-        <v>103700</v>
+        <v>103800</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D137" s="24">
-        <v>103700001</v>
+        <v>103800001</v>
       </c>
       <c r="E137" s="20">
         <v>11</v>
       </c>
       <c r="F137" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G137" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H137" s="47">
         <v>0</v>
@@ -8539,7 +8545,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O137" s="21"/>
       <c r="P137" s="21"/>
@@ -8550,25 +8556,25 @@
     </row>
     <row r="138" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A138" s="19">
-        <v>10370011</v>
+        <v>10380011</v>
       </c>
       <c r="B138" s="19">
-        <v>103700</v>
+        <v>103800</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D138" s="24">
-        <v>103700001</v>
+        <v>103800001</v>
       </c>
       <c r="E138" s="20">
         <v>12</v>
       </c>
       <c r="F138" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G138" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H138" s="47">
         <v>0</v>
@@ -8589,7 +8595,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O138" s="21"/>
       <c r="P138" s="21"/>
@@ -8600,25 +8606,25 @@
     </row>
     <row r="139" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A139" s="19">
-        <v>10370012</v>
+        <v>10380012</v>
       </c>
       <c r="B139" s="19">
-        <v>103700</v>
+        <v>103800</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D139" s="24">
-        <v>103100001</v>
+        <v>103800001</v>
       </c>
       <c r="E139" s="20">
         <v>13</v>
       </c>
       <c r="F139" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G139" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H139" s="47">
         <v>0</v>
@@ -8639,7 +8645,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O139" s="21"/>
       <c r="P139" s="21"/>
@@ -8650,16 +8656,16 @@
     </row>
     <row r="140" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A140" s="19">
-        <v>10310010</v>
+        <v>10270010</v>
       </c>
       <c r="B140" s="19">
-        <v>103100</v>
+        <v>102700</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D140" s="24">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E140" s="20">
         <v>11</v>
@@ -8689,7 +8695,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O140" s="21"/>
       <c r="P140" s="21"/>
@@ -8700,16 +8706,16 @@
     </row>
     <row r="141" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A141" s="19">
-        <v>10310011</v>
+        <v>10270011</v>
       </c>
       <c r="B141" s="19">
-        <v>103100</v>
+        <v>102700</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D141" s="24">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E141" s="20">
         <v>12</v>
@@ -8739,7 +8745,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O141" s="21"/>
       <c r="P141" s="21"/>
@@ -8750,16 +8756,16 @@
     </row>
     <row r="142" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A142" s="19">
-        <v>10310012</v>
+        <v>10270012</v>
       </c>
       <c r="B142" s="19">
-        <v>103100</v>
+        <v>102700</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D142" s="24">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E142" s="20">
         <v>13</v>
@@ -8789,7 +8795,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O142" s="21"/>
       <c r="P142" s="21"/>
@@ -8797,6 +8803,588 @@
       <c r="R142" s="21"/>
       <c r="S142" s="23"/>
       <c r="T142" s="23"/>
+    </row>
+    <row r="143" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A143" s="19">
+        <v>10370010</v>
+      </c>
+      <c r="B143" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C143" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D143" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E143" s="20">
+        <v>11</v>
+      </c>
+      <c r="F143" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G143" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H143" s="47">
+        <v>0</v>
+      </c>
+      <c r="I143" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J143" s="43">
+        <v>0</v>
+      </c>
+      <c r="K143" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L143" s="48">
+        <v>0</v>
+      </c>
+      <c r="M143" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N143" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O143" s="21"/>
+      <c r="P143" s="21"/>
+      <c r="Q143" s="21"/>
+      <c r="R143" s="21"/>
+      <c r="S143" s="23"/>
+      <c r="T143" s="23"/>
+    </row>
+    <row r="144" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A144" s="19">
+        <v>10370011</v>
+      </c>
+      <c r="B144" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C144" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D144" s="24">
+        <v>103700001</v>
+      </c>
+      <c r="E144" s="20">
+        <v>12</v>
+      </c>
+      <c r="F144" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G144" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H144" s="47">
+        <v>0</v>
+      </c>
+      <c r="I144" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J144" s="43">
+        <v>0</v>
+      </c>
+      <c r="K144" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L144" s="48">
+        <v>0</v>
+      </c>
+      <c r="M144" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N144" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="O144" s="21"/>
+      <c r="P144" s="21"/>
+      <c r="Q144" s="21"/>
+      <c r="R144" s="21"/>
+      <c r="S144" s="23"/>
+      <c r="T144" s="23"/>
+    </row>
+    <row r="145" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A145" s="19">
+        <v>10370012</v>
+      </c>
+      <c r="B145" s="19">
+        <v>103700</v>
+      </c>
+      <c r="C145" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D145" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E145" s="20">
+        <v>13</v>
+      </c>
+      <c r="F145" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G145" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H145" s="47">
+        <v>0</v>
+      </c>
+      <c r="I145" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J145" s="43">
+        <v>0</v>
+      </c>
+      <c r="K145" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L145" s="48">
+        <v>0</v>
+      </c>
+      <c r="M145" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N145" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O145" s="21"/>
+      <c r="P145" s="21"/>
+      <c r="Q145" s="21"/>
+      <c r="R145" s="21"/>
+      <c r="S145" s="23"/>
+      <c r="T145" s="23"/>
+    </row>
+    <row r="146" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A146" s="19">
+        <v>10310010</v>
+      </c>
+      <c r="B146" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C146" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D146" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E146" s="20">
+        <v>11</v>
+      </c>
+      <c r="F146" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G146" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H146" s="47">
+        <v>0</v>
+      </c>
+      <c r="I146" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J146" s="43">
+        <v>0</v>
+      </c>
+      <c r="K146" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L146" s="48">
+        <v>0</v>
+      </c>
+      <c r="M146" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N146" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O146" s="21"/>
+      <c r="P146" s="21"/>
+      <c r="Q146" s="21"/>
+      <c r="R146" s="21"/>
+      <c r="S146" s="23"/>
+      <c r="T146" s="23"/>
+    </row>
+    <row r="147" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A147" s="19">
+        <v>10310011</v>
+      </c>
+      <c r="B147" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C147" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D147" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E147" s="20">
+        <v>12</v>
+      </c>
+      <c r="F147" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G147" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H147" s="47">
+        <v>0</v>
+      </c>
+      <c r="I147" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J147" s="43">
+        <v>0</v>
+      </c>
+      <c r="K147" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L147" s="48">
+        <v>0</v>
+      </c>
+      <c r="M147" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N147" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="O147" s="21"/>
+      <c r="P147" s="21"/>
+      <c r="Q147" s="21"/>
+      <c r="R147" s="21"/>
+      <c r="S147" s="23"/>
+      <c r="T147" s="23"/>
+    </row>
+    <row r="148" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A148" s="19">
+        <v>10310012</v>
+      </c>
+      <c r="B148" s="19">
+        <v>103100</v>
+      </c>
+      <c r="C148" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D148" s="24">
+        <v>103100001</v>
+      </c>
+      <c r="E148" s="20">
+        <v>13</v>
+      </c>
+      <c r="F148" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G148" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H148" s="47">
+        <v>0</v>
+      </c>
+      <c r="I148" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J148" s="43">
+        <v>0</v>
+      </c>
+      <c r="K148" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L148" s="48">
+        <v>0</v>
+      </c>
+      <c r="M148" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N148" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O148" s="21"/>
+      <c r="P148" s="21"/>
+      <c r="Q148" s="21"/>
+      <c r="R148" s="21"/>
+      <c r="S148" s="23"/>
+      <c r="T148" s="23"/>
+    </row>
+    <row r="149" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A149" s="19">
+        <v>10400010</v>
+      </c>
+      <c r="B149" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D149" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E149" s="20">
+        <v>11</v>
+      </c>
+      <c r="F149" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G149" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H149" s="47">
+        <v>0</v>
+      </c>
+      <c r="I149" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J149" s="43">
+        <v>0</v>
+      </c>
+      <c r="K149" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L149" s="48">
+        <v>0</v>
+      </c>
+      <c r="M149" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N149" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="O149" s="21"/>
+      <c r="P149" s="21"/>
+      <c r="Q149" s="21"/>
+      <c r="R149" s="21"/>
+      <c r="S149" s="23"/>
+      <c r="T149" s="23"/>
+    </row>
+    <row r="150" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A150" s="19">
+        <v>10400011</v>
+      </c>
+      <c r="B150" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C150" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D150" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E150" s="20">
+        <v>12</v>
+      </c>
+      <c r="F150" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G150" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H150" s="47">
+        <v>0</v>
+      </c>
+      <c r="I150" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J150" s="43">
+        <v>0</v>
+      </c>
+      <c r="K150" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L150" s="48">
+        <v>0</v>
+      </c>
+      <c r="M150" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N150" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="O150" s="21"/>
+      <c r="P150" s="21"/>
+      <c r="Q150" s="21"/>
+      <c r="R150" s="21"/>
+      <c r="S150" s="23"/>
+      <c r="T150" s="23"/>
+    </row>
+    <row r="151" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A151" s="19">
+        <v>10400012</v>
+      </c>
+      <c r="B151" s="19">
+        <v>104000</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D151" s="24">
+        <v>104000001</v>
+      </c>
+      <c r="E151" s="20">
+        <v>13</v>
+      </c>
+      <c r="F151" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G151" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H151" s="47">
+        <v>0</v>
+      </c>
+      <c r="I151" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J151" s="43">
+        <v>0</v>
+      </c>
+      <c r="K151" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L151" s="48">
+        <v>0</v>
+      </c>
+      <c r="M151" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N151" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O151" s="21"/>
+      <c r="P151" s="21"/>
+      <c r="Q151" s="21"/>
+      <c r="R151" s="21"/>
+      <c r="S151" s="23"/>
+      <c r="T151" s="23"/>
+    </row>
+    <row r="152" ht="16.5" spans="1:20">
+      <c r="A152" s="19">
+        <v>10390010</v>
+      </c>
+      <c r="B152" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E152" s="20">
+        <v>11</v>
+      </c>
+      <c r="F152" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G152" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H152" s="47">
+        <v>0</v>
+      </c>
+      <c r="I152" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J152" s="43">
+        <v>0</v>
+      </c>
+      <c r="K152" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L152" s="48">
+        <v>0</v>
+      </c>
+      <c r="M152" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N152" s="45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="153" ht="16.5" spans="1:20">
+      <c r="A153" s="19">
+        <v>10390011</v>
+      </c>
+      <c r="B153" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D153" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E153" s="20">
+        <v>12</v>
+      </c>
+      <c r="F153" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G153" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H153" s="47">
+        <v>0</v>
+      </c>
+      <c r="I153" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J153" s="43">
+        <v>0</v>
+      </c>
+      <c r="K153" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L153" s="48">
+        <v>0</v>
+      </c>
+      <c r="M153" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N153" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="154" ht="16.5" spans="1:20">
+      <c r="A154" s="19">
+        <v>10390012</v>
+      </c>
+      <c r="B154" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D154" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E154" s="20">
+        <v>13</v>
+      </c>
+      <c r="F154" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G154" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H154" s="47">
+        <v>0</v>
+      </c>
+      <c r="I154" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J154" s="43">
+        <v>0</v>
+      </c>
+      <c r="K154" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L154" s="48">
+        <v>0</v>
+      </c>
+      <c r="M154" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N154" s="45" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -455,6 +455,9 @@
     <t>愤怒的小鸡</t>
   </si>
   <si>
+    <t>热血足球</t>
+  </si>
+  <si>
     <t>1980000_500000</t>
   </si>
   <si>
@@ -678,6 +681,11 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -685,6 +693,12 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -697,22 +711,11 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1727,7 +1730,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T154"/>
+  <dimension ref="A1:T160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -5654,165 +5657,165 @@
       <c r="S79" s="23"/>
       <c r="T79" s="23"/>
     </row>
-    <row r="80" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A80" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B80" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C80" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D80" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E80" s="40">
-        <v>10</v>
+    <row r="80" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A80" s="19">
+        <v>1016001</v>
+      </c>
+      <c r="B80" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E80" s="20">
+        <v>1</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H80" s="41">
-        <v>0</v>
-      </c>
-      <c r="I80" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J80" s="43">
-        <v>0</v>
-      </c>
-      <c r="K80" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L80" s="44">
-        <v>0</v>
-      </c>
-      <c r="M80" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H80" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I80" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J80" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K80" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="27">
+        <v>100</v>
+      </c>
+      <c r="M80" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N80" s="45" t="s">
+      <c r="N80" s="21">
+        <v>0</v>
+      </c>
+      <c r="O80" s="21"/>
+      <c r="P80" s="21"/>
+      <c r="Q80" s="21"/>
+      <c r="R80" s="21"/>
+      <c r="S80" s="23"/>
+      <c r="T80" s="23"/>
+    </row>
+    <row r="81" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A81" s="19">
+        <v>1016002</v>
+      </c>
+      <c r="B81" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C81" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="O80" s="46"/>
-      <c r="P80" s="46"/>
-      <c r="Q80" s="46"/>
-      <c r="R80" s="46"/>
-      <c r="S80" s="42"/>
-      <c r="T80" s="42"/>
-    </row>
-    <row r="81" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A81" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B81" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C81" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D81" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E81" s="40">
-        <v>11</v>
+      <c r="D81" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E81" s="20">
+        <v>2</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H81" s="41">
-        <v>0</v>
-      </c>
-      <c r="I81" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J81" s="43">
-        <v>0</v>
-      </c>
-      <c r="K81" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L81" s="44">
-        <v>0</v>
-      </c>
-      <c r="M81" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I81" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J81" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K81" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="27">
+        <v>100</v>
+      </c>
+      <c r="M81" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N81" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O81" s="46"/>
-      <c r="P81" s="46"/>
-      <c r="Q81" s="46"/>
-      <c r="R81" s="46"/>
-      <c r="S81" s="42"/>
-      <c r="T81" s="42"/>
-    </row>
-    <row r="82" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A82" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B82" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C82" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E82" s="40">
-        <v>12</v>
+      <c r="N81" s="21">
+        <v>0</v>
+      </c>
+      <c r="O81" s="21"/>
+      <c r="P81" s="21"/>
+      <c r="Q81" s="21"/>
+      <c r="R81" s="21"/>
+      <c r="S81" s="23"/>
+      <c r="T81" s="23"/>
+    </row>
+    <row r="82" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A82" s="19">
+        <v>1016003</v>
+      </c>
+      <c r="B82" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D82" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E82" s="20">
+        <v>3</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H82" s="47">
-        <v>0</v>
-      </c>
-      <c r="I82" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J82" s="43">
-        <v>0</v>
-      </c>
-      <c r="K82" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L82" s="44">
-        <v>0</v>
-      </c>
-      <c r="M82" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I82" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J82" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K82" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="27">
+        <v>100</v>
+      </c>
+      <c r="M82" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N82" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O82" s="46"/>
-      <c r="P82" s="46"/>
-      <c r="Q82" s="46"/>
-      <c r="R82" s="46"/>
-      <c r="S82" s="42"/>
-      <c r="T82" s="42"/>
+      <c r="N82" s="21">
+        <v>0</v>
+      </c>
+      <c r="O82" s="21"/>
+      <c r="P82" s="21"/>
+      <c r="Q82" s="21"/>
+      <c r="R82" s="21"/>
+      <c r="S82" s="23"/>
+      <c r="T82" s="23"/>
     </row>
     <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A83" s="36">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B83" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D83" s="39">
         <v>100100026</v>
@@ -5821,10 +5824,10 @@
         <v>10</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H83" s="41">
         <v>0</v>
@@ -5838,14 +5841,14 @@
       <c r="K83" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L83" s="48">
+      <c r="L83" s="44">
         <v>0</v>
       </c>
       <c r="M83" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N83" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O83" s="46"/>
       <c r="P83" s="46"/>
@@ -5856,13 +5859,13 @@
     </row>
     <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A84" s="36">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B84" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D84" s="39">
         <v>100100026</v>
@@ -5871,10 +5874,10 @@
         <v>11</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H84" s="41">
         <v>0</v>
@@ -5888,14 +5891,14 @@
       <c r="K84" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L84" s="48">
+      <c r="L84" s="44">
         <v>0</v>
       </c>
       <c r="M84" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N84" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O84" s="46"/>
       <c r="P84" s="46"/>
@@ -5906,13 +5909,13 @@
     </row>
     <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A85" s="36">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B85" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D85" s="39">
         <v>100100026</v>
@@ -5921,10 +5924,10 @@
         <v>12</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H85" s="47">
         <v>0</v>
@@ -5938,14 +5941,14 @@
       <c r="K85" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L85" s="48">
+      <c r="L85" s="44">
         <v>0</v>
       </c>
       <c r="M85" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O85" s="46"/>
       <c r="P85" s="46"/>
@@ -5956,13 +5959,13 @@
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B86" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D86" s="39">
         <v>100100026</v>
@@ -5971,10 +5974,10 @@
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H86" s="41">
         <v>0</v>
@@ -5988,14 +5991,14 @@
       <c r="K86" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L86" s="44">
+      <c r="L86" s="48">
         <v>0</v>
       </c>
       <c r="M86" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -6006,13 +6009,13 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B87" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D87" s="39">
         <v>100100026</v>
@@ -6021,10 +6024,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H87" s="41">
         <v>0</v>
@@ -6038,14 +6041,14 @@
       <c r="K87" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L87" s="44">
+      <c r="L87" s="48">
         <v>0</v>
       </c>
       <c r="M87" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6056,13 +6059,13 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B88" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D88" s="39">
         <v>100100026</v>
@@ -6071,10 +6074,10 @@
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6088,14 +6091,14 @@
       <c r="K88" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L88" s="44">
+      <c r="L88" s="48">
         <v>0</v>
       </c>
       <c r="M88" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6104,168 +6107,168 @@
       <c r="S88" s="42"/>
       <c r="T88" s="42"/>
     </row>
-    <row r="89" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B89" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C89" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D89" s="50">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B89" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D89" s="39">
+        <v>100100026</v>
       </c>
       <c r="E89" s="40">
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H89" s="41">
         <v>0</v>
       </c>
-      <c r="I89" s="43">
+      <c r="I89" s="42">
         <v>9500</v>
       </c>
       <c r="J89" s="43">
         <v>0</v>
       </c>
-      <c r="K89" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L89" s="48">
-        <v>0</v>
-      </c>
-      <c r="M89" s="43" t="s">
+      <c r="K89" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="44">
+        <v>0</v>
+      </c>
+      <c r="M89" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O89" s="45"/>
-      <c r="P89" s="45"/>
-      <c r="Q89" s="45"/>
-      <c r="R89" s="45"/>
-      <c r="S89" s="43"/>
-      <c r="T89" s="43"/>
-    </row>
-    <row r="90" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O89" s="46"/>
+      <c r="P89" s="46"/>
+      <c r="Q89" s="46"/>
+      <c r="R89" s="46"/>
+      <c r="S89" s="42"/>
+      <c r="T89" s="42"/>
+    </row>
+    <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B90" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C90" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D90" s="50">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B90" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C90" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D90" s="39">
+        <v>100100026</v>
       </c>
       <c r="E90" s="40">
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H90" s="41">
         <v>0</v>
       </c>
-      <c r="I90" s="43">
+      <c r="I90" s="42">
         <v>9500</v>
       </c>
       <c r="J90" s="43">
         <v>0</v>
       </c>
-      <c r="K90" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L90" s="48">
-        <v>0</v>
-      </c>
-      <c r="M90" s="43" t="s">
+      <c r="K90" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="44">
+        <v>0</v>
+      </c>
+      <c r="M90" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O90" s="45"/>
-      <c r="P90" s="45"/>
-      <c r="Q90" s="45"/>
-      <c r="R90" s="45"/>
-      <c r="S90" s="43"/>
-      <c r="T90" s="43"/>
-    </row>
-    <row r="91" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O90" s="46"/>
+      <c r="P90" s="46"/>
+      <c r="Q90" s="46"/>
+      <c r="R90" s="46"/>
+      <c r="S90" s="42"/>
+      <c r="T90" s="42"/>
+    </row>
+    <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B91" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C91" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D91" s="50">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B91" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C91" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D91" s="39">
+        <v>100100026</v>
       </c>
       <c r="E91" s="40">
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
       </c>
-      <c r="I91" s="43">
+      <c r="I91" s="42">
         <v>9500</v>
       </c>
       <c r="J91" s="43">
         <v>0</v>
       </c>
-      <c r="K91" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L91" s="48">
-        <v>0</v>
-      </c>
-      <c r="M91" s="43" t="s">
+      <c r="K91" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="44">
+        <v>0</v>
+      </c>
+      <c r="M91" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O91" s="45"/>
-      <c r="P91" s="45"/>
-      <c r="Q91" s="45"/>
-      <c r="R91" s="45"/>
-      <c r="S91" s="43"/>
-      <c r="T91" s="43"/>
-    </row>
-    <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O91" s="46"/>
+      <c r="P91" s="46"/>
+      <c r="Q91" s="46"/>
+      <c r="R91" s="46"/>
+      <c r="S91" s="42"/>
+      <c r="T91" s="42"/>
+    </row>
+    <row r="92" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10140010</v>
-      </c>
-      <c r="B92" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C92" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D92" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B92" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C92" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D92" s="50">
+        <v>101200026</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
@@ -6279,43 +6282,43 @@
       <c r="H92" s="41">
         <v>0</v>
       </c>
-      <c r="I92" s="42">
+      <c r="I92" s="43">
         <v>9500</v>
       </c>
       <c r="J92" s="43">
         <v>0</v>
       </c>
-      <c r="K92" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L92" s="44">
-        <v>0</v>
-      </c>
-      <c r="M92" s="42" t="s">
+      <c r="K92" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="48">
+        <v>0</v>
+      </c>
+      <c r="M92" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O92" s="46"/>
-      <c r="P92" s="46"/>
-      <c r="Q92" s="46"/>
-      <c r="R92" s="46"/>
-      <c r="S92" s="42"/>
-      <c r="T92" s="42"/>
-    </row>
-    <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O92" s="45"/>
+      <c r="P92" s="45"/>
+      <c r="Q92" s="45"/>
+      <c r="R92" s="45"/>
+      <c r="S92" s="43"/>
+      <c r="T92" s="43"/>
+    </row>
+    <row r="93" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10140011</v>
-      </c>
-      <c r="B93" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C93" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D93" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B93" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C93" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D93" s="50">
+        <v>101200026</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
@@ -6329,43 +6332,43 @@
       <c r="H93" s="41">
         <v>0</v>
       </c>
-      <c r="I93" s="42">
+      <c r="I93" s="43">
         <v>9500</v>
       </c>
       <c r="J93" s="43">
         <v>0</v>
       </c>
-      <c r="K93" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L93" s="44">
-        <v>0</v>
-      </c>
-      <c r="M93" s="42" t="s">
+      <c r="K93" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="48">
+        <v>0</v>
+      </c>
+      <c r="M93" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O93" s="46"/>
-      <c r="P93" s="46"/>
-      <c r="Q93" s="46"/>
-      <c r="R93" s="46"/>
-      <c r="S93" s="42"/>
-      <c r="T93" s="42"/>
-    </row>
-    <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O93" s="45"/>
+      <c r="P93" s="45"/>
+      <c r="Q93" s="45"/>
+      <c r="R93" s="45"/>
+      <c r="S93" s="43"/>
+      <c r="T93" s="43"/>
+    </row>
+    <row r="94" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10140012</v>
-      </c>
-      <c r="B94" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C94" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D94" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B94" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C94" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D94" s="50">
+        <v>101200026</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
@@ -6379,52 +6382,52 @@
       <c r="H94" s="47">
         <v>0</v>
       </c>
-      <c r="I94" s="42">
+      <c r="I94" s="43">
         <v>9500</v>
       </c>
       <c r="J94" s="43">
         <v>0</v>
       </c>
-      <c r="K94" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L94" s="44">
-        <v>0</v>
-      </c>
-      <c r="M94" s="42" t="s">
+      <c r="K94" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" s="48">
+        <v>0</v>
+      </c>
+      <c r="M94" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O94" s="46"/>
-      <c r="P94" s="46"/>
-      <c r="Q94" s="46"/>
-      <c r="R94" s="46"/>
-      <c r="S94" s="42"/>
-      <c r="T94" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="O94" s="45"/>
+      <c r="P94" s="45"/>
+      <c r="Q94" s="45"/>
+      <c r="R94" s="45"/>
+      <c r="S94" s="43"/>
+      <c r="T94" s="43"/>
     </row>
     <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B95" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D95" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H95" s="41">
         <v>0</v>
@@ -6445,7 +6448,7 @@
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O95" s="46"/>
       <c r="P95" s="46"/>
@@ -6456,25 +6459,25 @@
     </row>
     <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B96" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D96" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H96" s="41">
         <v>0</v>
@@ -6495,7 +6498,7 @@
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O96" s="46"/>
       <c r="P96" s="46"/>
@@ -6506,25 +6509,25 @@
     </row>
     <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B97" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D97" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G97" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H97" s="47">
         <v>0</v>
@@ -6545,7 +6548,7 @@
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O97" s="46"/>
       <c r="P97" s="46"/>
@@ -6556,16 +6559,16 @@
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B98" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D98" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
@@ -6588,14 +6591,14 @@
       <c r="K98" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L98" s="48">
+      <c r="L98" s="44">
         <v>0</v>
       </c>
       <c r="M98" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6606,16 +6609,16 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B99" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D99" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
@@ -6638,14 +6641,14 @@
       <c r="K99" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L99" s="48">
+      <c r="L99" s="44">
         <v>0</v>
       </c>
       <c r="M99" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6656,16 +6659,16 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B100" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D100" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
@@ -6688,14 +6691,14 @@
       <c r="K100" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L100" s="48">
+      <c r="L100" s="44">
         <v>0</v>
       </c>
       <c r="M100" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6706,16 +6709,16 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B101" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D101" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
@@ -6745,7 +6748,7 @@
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6756,16 +6759,16 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B102" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D102" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
@@ -6795,7 +6798,7 @@
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6806,16 +6809,16 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B103" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D103" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
@@ -6845,7 +6848,7 @@
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6856,25 +6859,25 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B104" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D104" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H104" s="41">
         <v>0</v>
@@ -6895,7 +6898,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6906,25 +6909,25 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B105" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D105" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H105" s="41">
         <v>0</v>
@@ -6945,7 +6948,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6956,25 +6959,25 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B106" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D106" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H106" s="47">
         <v>0</v>
@@ -6995,7 +6998,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -7006,27 +7009,27 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B107" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D107" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H107" s="47">
+        <v>35</v>
+      </c>
+      <c r="H107" s="41">
         <v>0</v>
       </c>
       <c r="I107" s="42">
@@ -7045,7 +7048,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7056,27 +7059,27 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B108" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D108" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G108" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H108" s="47">
+        <v>39</v>
+      </c>
+      <c r="H108" s="41">
         <v>0</v>
       </c>
       <c r="I108" s="42">
@@ -7095,7 +7098,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7106,25 +7109,25 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B109" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D109" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H109" s="47">
         <v>0</v>
@@ -7145,7 +7148,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7156,25 +7159,25 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B110" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D110" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H110" s="47">
         <v>0</v>
@@ -7195,7 +7198,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7206,25 +7209,25 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B111" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D111" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H111" s="47">
         <v>0</v>
@@ -7245,7 +7248,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7256,25 +7259,25 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B112" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D112" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
@@ -7295,7 +7298,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7306,25 +7309,25 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B113" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D113" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
       </c>
       <c r="F113" s="21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H113" s="47">
         <v>0</v>
@@ -7345,7 +7348,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7356,25 +7359,25 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B114" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D114" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G114" s="22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H114" s="47">
         <v>0</v>
@@ -7395,7 +7398,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7406,25 +7409,25 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B115" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D115" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
       </c>
       <c r="F115" s="21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H115" s="47">
         <v>0</v>
@@ -7445,7 +7448,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7456,31 +7459,31 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B116" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D116" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G116" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H116" s="47">
         <v>0</v>
       </c>
       <c r="I116" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J116" s="43">
         <v>0</v>
@@ -7495,7 +7498,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7506,31 +7509,31 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B117" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D117" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
       </c>
       <c r="F117" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G117" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H117" s="47">
         <v>0</v>
       </c>
       <c r="I117" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J117" s="43">
         <v>0</v>
@@ -7545,7 +7548,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7556,31 +7559,31 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B118" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D118" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G118" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H118" s="47">
         <v>0</v>
       </c>
       <c r="I118" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J118" s="43">
         <v>0</v>
@@ -7595,7 +7598,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7606,25 +7609,25 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="36">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B119" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D119" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E119" s="40">
         <v>10</v>
       </c>
       <c r="F119" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G119" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H119" s="47">
         <v>0</v>
@@ -7645,7 +7648,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O119" s="46"/>
       <c r="P119" s="46"/>
@@ -7656,25 +7659,25 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="36">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B120" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D120" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E120" s="40">
         <v>11</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G120" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H120" s="47">
         <v>0</v>
@@ -7695,7 +7698,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O120" s="46"/>
       <c r="P120" s="46"/>
@@ -7706,25 +7709,25 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="36">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B121" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D121" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E121" s="40">
         <v>12</v>
       </c>
       <c r="F121" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G121" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H121" s="47">
         <v>0</v>
@@ -7745,7 +7748,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O121" s="46"/>
       <c r="P121" s="46"/>
@@ -7756,16 +7759,16 @@
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="36">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B122" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D122" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E122" s="40">
         <v>10</v>
@@ -7795,7 +7798,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O122" s="46"/>
       <c r="P122" s="46"/>
@@ -7806,16 +7809,16 @@
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="36">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B123" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C123" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D123" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E123" s="40">
         <v>11</v>
@@ -7845,7 +7848,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O123" s="46"/>
       <c r="P123" s="46"/>
@@ -7856,16 +7859,16 @@
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="36">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B124" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D124" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E124" s="40">
         <v>12</v>
@@ -7895,7 +7898,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O124" s="46"/>
       <c r="P124" s="46"/>
@@ -7906,25 +7909,25 @@
     </row>
     <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A125" s="36">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B125" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C125" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D125" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E125" s="40">
         <v>10</v>
       </c>
-      <c r="F125" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G125" s="51" t="s">
-        <v>35</v>
+      <c r="F125" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G125" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H125" s="47">
         <v>0</v>
@@ -7945,7 +7948,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O125" s="46"/>
       <c r="P125" s="46"/>
@@ -7956,25 +7959,25 @@
     </row>
     <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A126" s="36">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B126" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D126" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E126" s="40">
         <v>11</v>
       </c>
-      <c r="F126" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G126" s="51" t="s">
-        <v>39</v>
+      <c r="F126" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G126" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H126" s="47">
         <v>0</v>
@@ -7995,7 +7998,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O126" s="46"/>
       <c r="P126" s="46"/>
@@ -8006,25 +8009,25 @@
     </row>
     <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A127" s="36">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B127" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C127" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D127" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E127" s="40">
         <v>12</v>
       </c>
-      <c r="F127" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G127" s="51" t="s">
-        <v>42</v>
+      <c r="F127" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G127" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H127" s="47">
         <v>0</v>
@@ -8045,7 +8048,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O127" s="46"/>
       <c r="P127" s="46"/>
@@ -8056,25 +8059,25 @@
     </row>
     <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A128" s="36">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B128" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D128" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E128" s="40">
         <v>10</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G128" s="51" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H128" s="47">
         <v>0</v>
@@ -8095,7 +8098,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O128" s="46"/>
       <c r="P128" s="46"/>
@@ -8106,25 +8109,25 @@
     </row>
     <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A129" s="36">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B129" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C129" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D129" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E129" s="40">
         <v>11</v>
       </c>
       <c r="F129" s="46" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G129" s="51" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H129" s="47">
         <v>0</v>
@@ -8145,7 +8148,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O129" s="46"/>
       <c r="P129" s="46"/>
@@ -8156,25 +8159,25 @@
     </row>
     <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A130" s="36">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B130" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D130" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E130" s="40">
         <v>12</v>
       </c>
       <c r="F130" s="46" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G130" s="51" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H130" s="47">
         <v>0</v>
@@ -8195,7 +8198,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O130" s="46"/>
       <c r="P130" s="46"/>
@@ -8206,16 +8209,16 @@
     </row>
     <row r="131" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A131" s="36">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B131" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C131" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D131" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E131" s="40">
         <v>10</v>
@@ -8245,7 +8248,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O131" s="46"/>
       <c r="P131" s="46"/>
@@ -8256,16 +8259,16 @@
     </row>
     <row r="132" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A132" s="36">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B132" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C132" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D132" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E132" s="40">
         <v>11</v>
@@ -8295,7 +8298,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O132" s="46"/>
       <c r="P132" s="46"/>
@@ -8306,16 +8309,16 @@
     </row>
     <row r="133" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A133" s="36">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B133" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C133" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D133" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E133" s="40">
         <v>12</v>
@@ -8345,7 +8348,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O133" s="46"/>
       <c r="P133" s="46"/>
@@ -8356,25 +8359,25 @@
     </row>
     <row r="134" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A134" s="36">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B134" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C134" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D134" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D134" s="39">
+        <v>102000001</v>
       </c>
       <c r="E134" s="40">
         <v>10</v>
       </c>
       <c r="F134" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G134" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H134" s="47">
         <v>0</v>
@@ -8395,7 +8398,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O134" s="46"/>
       <c r="P134" s="46"/>
@@ -8406,25 +8409,25 @@
     </row>
     <row r="135" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A135" s="36">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B135" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C135" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D135" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D135" s="39">
+        <v>102000001</v>
       </c>
       <c r="E135" s="40">
         <v>11</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G135" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H135" s="47">
         <v>0</v>
@@ -8445,7 +8448,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O135" s="46"/>
       <c r="P135" s="46"/>
@@ -8456,25 +8459,25 @@
     </row>
     <row r="136" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A136" s="36">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B136" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C136" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D136" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D136" s="39">
+        <v>102000001</v>
       </c>
       <c r="E136" s="40">
         <v>12</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G136" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H136" s="47">
         <v>0</v>
@@ -8495,7 +8498,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O136" s="46"/>
       <c r="P136" s="46"/>
@@ -8504,27 +8507,27 @@
       <c r="S136" s="42"/>
       <c r="T136" s="42"/>
     </row>
-    <row r="137" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A137" s="19">
-        <v>10380010</v>
-      </c>
-      <c r="B137" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C137" s="20" t="s">
-        <v>81</v>
+    <row r="137" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A137" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B137" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C137" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D137" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E137" s="20">
-        <v>11</v>
+        <v>103400001</v>
+      </c>
+      <c r="E137" s="40">
+        <v>10</v>
       </c>
       <c r="F137" s="46" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G137" s="51" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H137" s="47">
         <v>0</v>
@@ -8545,36 +8548,36 @@
         <v>37</v>
       </c>
       <c r="N137" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="O137" s="21"/>
-      <c r="P137" s="21"/>
-      <c r="Q137" s="21"/>
-      <c r="R137" s="21"/>
-      <c r="S137" s="23"/>
-      <c r="T137" s="23"/>
-    </row>
-    <row r="138" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A138" s="19">
-        <v>10380011</v>
-      </c>
-      <c r="B138" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C138" s="20" t="s">
-        <v>81</v>
+        <v>90</v>
+      </c>
+      <c r="O137" s="46"/>
+      <c r="P137" s="46"/>
+      <c r="Q137" s="46"/>
+      <c r="R137" s="46"/>
+      <c r="S137" s="42"/>
+      <c r="T137" s="42"/>
+    </row>
+    <row r="138" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A138" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B138" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C138" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D138" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E138" s="20">
-        <v>12</v>
+        <v>103400001</v>
+      </c>
+      <c r="E138" s="40">
+        <v>11</v>
       </c>
       <c r="F138" s="46" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G138" s="51" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H138" s="47">
         <v>0</v>
@@ -8595,36 +8598,36 @@
         <v>40</v>
       </c>
       <c r="N138" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O138" s="21"/>
-      <c r="P138" s="21"/>
-      <c r="Q138" s="21"/>
-      <c r="R138" s="21"/>
-      <c r="S138" s="23"/>
-      <c r="T138" s="23"/>
-    </row>
-    <row r="139" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A139" s="19">
-        <v>10380012</v>
-      </c>
-      <c r="B139" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C139" s="20" t="s">
-        <v>81</v>
+        <v>91</v>
+      </c>
+      <c r="O138" s="46"/>
+      <c r="P138" s="46"/>
+      <c r="Q138" s="46"/>
+      <c r="R138" s="46"/>
+      <c r="S138" s="42"/>
+      <c r="T138" s="42"/>
+    </row>
+    <row r="139" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A139" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B139" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C139" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D139" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E139" s="20">
-        <v>13</v>
+        <v>103400001</v>
+      </c>
+      <c r="E139" s="40">
+        <v>12</v>
       </c>
       <c r="F139" s="46" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G139" s="51" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H139" s="47">
         <v>0</v>
@@ -8645,27 +8648,27 @@
         <v>43</v>
       </c>
       <c r="N139" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O139" s="21"/>
-      <c r="P139" s="21"/>
-      <c r="Q139" s="21"/>
-      <c r="R139" s="21"/>
-      <c r="S139" s="23"/>
-      <c r="T139" s="23"/>
+        <v>92</v>
+      </c>
+      <c r="O139" s="46"/>
+      <c r="P139" s="46"/>
+      <c r="Q139" s="46"/>
+      <c r="R139" s="46"/>
+      <c r="S139" s="42"/>
+      <c r="T139" s="42"/>
     </row>
     <row r="140" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A140" s="19">
-        <v>10270010</v>
+        <v>10380010</v>
       </c>
       <c r="B140" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D140" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E140" s="20">
         <v>11</v>
@@ -8695,7 +8698,7 @@
         <v>37</v>
       </c>
       <c r="N140" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O140" s="21"/>
       <c r="P140" s="21"/>
@@ -8706,16 +8709,16 @@
     </row>
     <row r="141" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A141" s="19">
-        <v>10270011</v>
+        <v>10380011</v>
       </c>
       <c r="B141" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D141" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E141" s="20">
         <v>12</v>
@@ -8745,7 +8748,7 @@
         <v>40</v>
       </c>
       <c r="N141" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O141" s="21"/>
       <c r="P141" s="21"/>
@@ -8756,16 +8759,16 @@
     </row>
     <row r="142" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A142" s="19">
-        <v>10270012</v>
+        <v>10380012</v>
       </c>
       <c r="B142" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D142" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E142" s="20">
         <v>13</v>
@@ -8795,7 +8798,7 @@
         <v>43</v>
       </c>
       <c r="N142" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O142" s="21"/>
       <c r="P142" s="21"/>
@@ -8806,25 +8809,25 @@
     </row>
     <row r="143" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A143" s="19">
-        <v>10370010</v>
+        <v>10270010</v>
       </c>
       <c r="B143" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D143" s="24">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E143" s="20">
         <v>11</v>
       </c>
       <c r="F143" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G143" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H143" s="47">
         <v>0</v>
@@ -8845,7 +8848,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O143" s="21"/>
       <c r="P143" s="21"/>
@@ -8856,25 +8859,25 @@
     </row>
     <row r="144" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A144" s="19">
-        <v>10370011</v>
+        <v>10270011</v>
       </c>
       <c r="B144" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D144" s="24">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E144" s="20">
         <v>12</v>
       </c>
       <c r="F144" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G144" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H144" s="47">
         <v>0</v>
@@ -8895,7 +8898,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O144" s="21"/>
       <c r="P144" s="21"/>
@@ -8906,25 +8909,25 @@
     </row>
     <row r="145" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A145" s="19">
-        <v>10370012</v>
+        <v>10270012</v>
       </c>
       <c r="B145" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D145" s="24">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E145" s="20">
         <v>13</v>
       </c>
       <c r="F145" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G145" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H145" s="47">
         <v>0</v>
@@ -8945,7 +8948,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O145" s="21"/>
       <c r="P145" s="21"/>
@@ -8956,25 +8959,25 @@
     </row>
     <row r="146" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A146" s="19">
-        <v>10310010</v>
+        <v>10370010</v>
       </c>
       <c r="B146" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D146" s="24">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E146" s="20">
         <v>11</v>
       </c>
       <c r="F146" s="46" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G146" s="51" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H146" s="47">
         <v>0</v>
@@ -8995,7 +8998,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O146" s="21"/>
       <c r="P146" s="21"/>
@@ -9006,25 +9009,25 @@
     </row>
     <row r="147" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A147" s="19">
-        <v>10310011</v>
+        <v>10370011</v>
       </c>
       <c r="B147" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D147" s="24">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E147" s="20">
         <v>12</v>
       </c>
       <c r="F147" s="46" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G147" s="51" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H147" s="47">
         <v>0</v>
@@ -9045,7 +9048,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O147" s="21"/>
       <c r="P147" s="21"/>
@@ -9056,13 +9059,13 @@
     </row>
     <row r="148" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A148" s="19">
-        <v>10310012</v>
+        <v>10370012</v>
       </c>
       <c r="B148" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C148" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D148" s="24">
         <v>103100001</v>
@@ -9071,10 +9074,10 @@
         <v>13</v>
       </c>
       <c r="F148" s="46" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G148" s="51" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H148" s="47">
         <v>0</v>
@@ -9095,7 +9098,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O148" s="21"/>
       <c r="P148" s="21"/>
@@ -9106,16 +9109,16 @@
     </row>
     <row r="149" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A149" s="19">
-        <v>10400010</v>
+        <v>10310010</v>
       </c>
       <c r="B149" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D149" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E149" s="20">
         <v>11</v>
@@ -9145,7 +9148,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O149" s="21"/>
       <c r="P149" s="21"/>
@@ -9156,16 +9159,16 @@
     </row>
     <row r="150" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A150" s="19">
-        <v>10400011</v>
+        <v>10310011</v>
       </c>
       <c r="B150" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C150" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D150" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E150" s="20">
         <v>12</v>
@@ -9195,7 +9198,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O150" s="21"/>
       <c r="P150" s="21"/>
@@ -9206,16 +9209,16 @@
     </row>
     <row r="151" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A151" s="19">
-        <v>10400012</v>
+        <v>10310012</v>
       </c>
       <c r="B151" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C151" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D151" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E151" s="20">
         <v>13</v>
@@ -9245,7 +9248,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O151" s="21"/>
       <c r="P151" s="21"/>
@@ -9254,18 +9257,18 @@
       <c r="S151" s="23"/>
       <c r="T151" s="23"/>
     </row>
-    <row r="152" ht="16.5" spans="1:20">
+    <row r="152" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A152" s="19">
-        <v>10390010</v>
+        <v>10400010</v>
       </c>
       <c r="B152" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C152" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D152" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E152" s="20">
         <v>11</v>
@@ -9295,21 +9298,27 @@
         <v>37</v>
       </c>
       <c r="N152" s="45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="153" ht="16.5" spans="1:20">
+        <v>90</v>
+      </c>
+      <c r="O152" s="21"/>
+      <c r="P152" s="21"/>
+      <c r="Q152" s="21"/>
+      <c r="R152" s="21"/>
+      <c r="S152" s="23"/>
+      <c r="T152" s="23"/>
+    </row>
+    <row r="153" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A153" s="19">
-        <v>10390011</v>
+        <v>10400011</v>
       </c>
       <c r="B153" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C153" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D153" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E153" s="20">
         <v>12</v>
@@ -9339,21 +9348,27 @@
         <v>40</v>
       </c>
       <c r="N153" s="45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="154" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O153" s="21"/>
+      <c r="P153" s="21"/>
+      <c r="Q153" s="21"/>
+      <c r="R153" s="21"/>
+      <c r="S153" s="23"/>
+      <c r="T153" s="23"/>
+    </row>
+    <row r="154" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A154" s="19">
-        <v>10390012</v>
+        <v>10400012</v>
       </c>
       <c r="B154" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C154" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D154" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E154" s="20">
         <v>13</v>
@@ -9383,8 +9398,296 @@
         <v>43</v>
       </c>
       <c r="N154" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="O154" s="21"/>
+      <c r="P154" s="21"/>
+      <c r="Q154" s="21"/>
+      <c r="R154" s="21"/>
+      <c r="S154" s="23"/>
+      <c r="T154" s="23"/>
+    </row>
+    <row r="155" ht="16.5" spans="1:20">
+      <c r="A155" s="19">
+        <v>10390010</v>
+      </c>
+      <c r="B155" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D155" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E155" s="20">
+        <v>11</v>
+      </c>
+      <c r="F155" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G155" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H155" s="47">
+        <v>0</v>
+      </c>
+      <c r="I155" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J155" s="43">
+        <v>0</v>
+      </c>
+      <c r="K155" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L155" s="48">
+        <v>0</v>
+      </c>
+      <c r="M155" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N155" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="156" ht="16.5" spans="1:20">
+      <c r="A156" s="19">
+        <v>10390011</v>
+      </c>
+      <c r="B156" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C156" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D156" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E156" s="20">
+        <v>12</v>
+      </c>
+      <c r="F156" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G156" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H156" s="47">
+        <v>0</v>
+      </c>
+      <c r="I156" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J156" s="43">
+        <v>0</v>
+      </c>
+      <c r="K156" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L156" s="48">
+        <v>0</v>
+      </c>
+      <c r="M156" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N156" s="45" t="s">
         <v>91</v>
       </c>
+    </row>
+    <row r="157" ht="16.5" spans="1:20">
+      <c r="A157" s="19">
+        <v>10390012</v>
+      </c>
+      <c r="B157" s="19">
+        <v>103900</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D157" s="24">
+        <v>103900001</v>
+      </c>
+      <c r="E157" s="20">
+        <v>13</v>
+      </c>
+      <c r="F157" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G157" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H157" s="47">
+        <v>0</v>
+      </c>
+      <c r="I157" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J157" s="43">
+        <v>0</v>
+      </c>
+      <c r="K157" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L157" s="48">
+        <v>0</v>
+      </c>
+      <c r="M157" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N157" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="158" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A158" s="19">
+        <v>10160010</v>
+      </c>
+      <c r="B158" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C158" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E158" s="20">
+        <v>11</v>
+      </c>
+      <c r="F158" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G158" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H158" s="47">
+        <v>0</v>
+      </c>
+      <c r="I158" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J158" s="43">
+        <v>0</v>
+      </c>
+      <c r="K158" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L158" s="48">
+        <v>0</v>
+      </c>
+      <c r="M158" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N158" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="O158" s="21"/>
+      <c r="P158" s="21"/>
+      <c r="Q158" s="21"/>
+      <c r="R158" s="21"/>
+      <c r="S158" s="23"/>
+      <c r="T158" s="23"/>
+    </row>
+    <row r="159" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A159" s="19">
+        <v>10160011</v>
+      </c>
+      <c r="B159" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E159" s="20">
+        <v>12</v>
+      </c>
+      <c r="F159" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G159" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H159" s="47">
+        <v>0</v>
+      </c>
+      <c r="I159" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J159" s="43">
+        <v>0</v>
+      </c>
+      <c r="K159" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L159" s="48">
+        <v>0</v>
+      </c>
+      <c r="M159" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N159" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O159" s="21"/>
+      <c r="P159" s="21"/>
+      <c r="Q159" s="21"/>
+      <c r="R159" s="21"/>
+      <c r="S159" s="23"/>
+      <c r="T159" s="23"/>
+    </row>
+    <row r="160" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A160" s="19">
+        <v>10160012</v>
+      </c>
+      <c r="B160" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C160" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E160" s="20">
+        <v>13</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G160" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H160" s="47">
+        <v>0</v>
+      </c>
+      <c r="I160" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J160" s="43">
+        <v>0</v>
+      </c>
+      <c r="K160" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L160" s="48">
+        <v>0</v>
+      </c>
+      <c r="M160" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N160" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="O160" s="21"/>
+      <c r="P160" s="21"/>
+      <c r="Q160" s="21"/>
+      <c r="R160" s="21"/>
+      <c r="S160" s="23"/>
+      <c r="T160" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -458,6 +458,9 @@
     <t>热血足球</t>
   </si>
   <si>
+    <t>狼月</t>
+  </si>
+  <si>
     <t>1980000_500000</t>
   </si>
   <si>
@@ -686,23 +689,17 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
@@ -716,6 +713,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1730,7 +1733,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T160"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -5807,165 +5810,165 @@
       <c r="S82" s="23"/>
       <c r="T82" s="23"/>
     </row>
-    <row r="83" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A83" s="36">
-        <v>10010010</v>
-      </c>
-      <c r="B83" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C83" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D83" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E83" s="40">
-        <v>10</v>
+    <row r="83" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A83" s="19">
+        <v>1015001</v>
+      </c>
+      <c r="B83" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E83" s="20">
+        <v>1</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H83" s="41">
-        <v>0</v>
-      </c>
-      <c r="I83" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J83" s="43">
-        <v>0</v>
-      </c>
-      <c r="K83" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L83" s="44">
-        <v>0</v>
-      </c>
-      <c r="M83" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H83" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="I83" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J83" s="23">
+        <v>5000000</v>
+      </c>
+      <c r="K83" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="27">
+        <v>100</v>
+      </c>
+      <c r="M83" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N83" s="45" t="s">
+      <c r="N83" s="21">
+        <v>0</v>
+      </c>
+      <c r="O83" s="21"/>
+      <c r="P83" s="21"/>
+      <c r="Q83" s="21"/>
+      <c r="R83" s="21"/>
+      <c r="S83" s="23"/>
+      <c r="T83" s="23"/>
+    </row>
+    <row r="84" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A84" s="19">
+        <v>1015002</v>
+      </c>
+      <c r="B84" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C84" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="O83" s="46"/>
-      <c r="P83" s="46"/>
-      <c r="Q83" s="46"/>
-      <c r="R83" s="46"/>
-      <c r="S83" s="42"/>
-      <c r="T83" s="42"/>
-    </row>
-    <row r="84" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A84" s="36">
-        <v>10010011</v>
-      </c>
-      <c r="B84" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C84" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D84" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E84" s="40">
-        <v>11</v>
+      <c r="D84" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E84" s="20">
+        <v>2</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H84" s="41">
-        <v>0</v>
-      </c>
-      <c r="I84" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J84" s="43">
-        <v>0</v>
-      </c>
-      <c r="K84" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L84" s="44">
-        <v>0</v>
-      </c>
-      <c r="M84" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="14">
+        <v>100000000</v>
+      </c>
+      <c r="I84" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J84" s="23">
+        <v>50000000</v>
+      </c>
+      <c r="K84" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="27">
+        <v>100</v>
+      </c>
+      <c r="M84" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N84" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O84" s="46"/>
-      <c r="P84" s="46"/>
-      <c r="Q84" s="46"/>
-      <c r="R84" s="46"/>
-      <c r="S84" s="42"/>
-      <c r="T84" s="42"/>
-    </row>
-    <row r="85" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A85" s="36">
-        <v>10010012</v>
-      </c>
-      <c r="B85" s="37">
-        <v>100100</v>
-      </c>
-      <c r="C85" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D85" s="39">
-        <v>100100026</v>
-      </c>
-      <c r="E85" s="40">
-        <v>12</v>
+      <c r="N84" s="21">
+        <v>0</v>
+      </c>
+      <c r="O84" s="21"/>
+      <c r="P84" s="21"/>
+      <c r="Q84" s="21"/>
+      <c r="R84" s="21"/>
+      <c r="S84" s="23"/>
+      <c r="T84" s="23"/>
+    </row>
+    <row r="85" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A85" s="19">
+        <v>1015003</v>
+      </c>
+      <c r="B85" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E85" s="20">
+        <v>3</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H85" s="47">
-        <v>0</v>
-      </c>
-      <c r="I85" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J85" s="43">
-        <v>0</v>
-      </c>
-      <c r="K85" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L85" s="44">
-        <v>0</v>
-      </c>
-      <c r="M85" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H85" s="28">
+        <v>1000000000</v>
+      </c>
+      <c r="I85" s="25">
+        <v>9600</v>
+      </c>
+      <c r="J85" s="23">
+        <v>500000000</v>
+      </c>
+      <c r="K85" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="27">
+        <v>100</v>
+      </c>
+      <c r="M85" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N85" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="O85" s="46"/>
-      <c r="P85" s="46"/>
-      <c r="Q85" s="46"/>
-      <c r="R85" s="46"/>
-      <c r="S85" s="42"/>
-      <c r="T85" s="42"/>
+      <c r="N85" s="21">
+        <v>0</v>
+      </c>
+      <c r="O85" s="21"/>
+      <c r="P85" s="21"/>
+      <c r="Q85" s="21"/>
+      <c r="R85" s="21"/>
+      <c r="S85" s="23"/>
+      <c r="T85" s="23"/>
     </row>
     <row r="86" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A86" s="36">
-        <v>10030010</v>
+        <v>10010010</v>
       </c>
       <c r="B86" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D86" s="39">
         <v>100100026</v>
@@ -5974,10 +5977,10 @@
         <v>10</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H86" s="41">
         <v>0</v>
@@ -5991,14 +5994,14 @@
       <c r="K86" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L86" s="48">
+      <c r="L86" s="44">
         <v>0</v>
       </c>
       <c r="M86" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N86" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O86" s="46"/>
       <c r="P86" s="46"/>
@@ -6009,13 +6012,13 @@
     </row>
     <row r="87" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A87" s="36">
-        <v>10030011</v>
+        <v>10010011</v>
       </c>
       <c r="B87" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D87" s="39">
         <v>100100026</v>
@@ -6024,10 +6027,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H87" s="41">
         <v>0</v>
@@ -6041,14 +6044,14 @@
       <c r="K87" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L87" s="48">
+      <c r="L87" s="44">
         <v>0</v>
       </c>
       <c r="M87" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N87" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O87" s="46"/>
       <c r="P87" s="46"/>
@@ -6059,13 +6062,13 @@
     </row>
     <row r="88" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A88" s="36">
-        <v>10030012</v>
+        <v>10010012</v>
       </c>
       <c r="B88" s="37">
-        <v>100300</v>
+        <v>100100</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D88" s="39">
         <v>100100026</v>
@@ -6074,10 +6077,10 @@
         <v>12</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H88" s="47">
         <v>0</v>
@@ -6091,14 +6094,14 @@
       <c r="K88" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L88" s="48">
+      <c r="L88" s="44">
         <v>0</v>
       </c>
       <c r="M88" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N88" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O88" s="46"/>
       <c r="P88" s="46"/>
@@ -6109,13 +6112,13 @@
     </row>
     <row r="89" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A89" s="36">
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B89" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D89" s="39">
         <v>100100026</v>
@@ -6124,10 +6127,10 @@
         <v>10</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H89" s="41">
         <v>0</v>
@@ -6141,14 +6144,14 @@
       <c r="K89" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L89" s="44">
+      <c r="L89" s="48">
         <v>0</v>
       </c>
       <c r="M89" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N89" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O89" s="46"/>
       <c r="P89" s="46"/>
@@ -6159,13 +6162,13 @@
     </row>
     <row r="90" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A90" s="36">
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B90" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D90" s="39">
         <v>100100026</v>
@@ -6174,10 +6177,10 @@
         <v>11</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H90" s="41">
         <v>0</v>
@@ -6191,14 +6194,14 @@
       <c r="K90" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L90" s="44">
+      <c r="L90" s="48">
         <v>0</v>
       </c>
       <c r="M90" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N90" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O90" s="46"/>
       <c r="P90" s="46"/>
@@ -6209,13 +6212,13 @@
     </row>
     <row r="91" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A91" s="36">
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B91" s="37">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D91" s="39">
         <v>100100026</v>
@@ -6224,10 +6227,10 @@
         <v>12</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H91" s="47">
         <v>0</v>
@@ -6241,14 +6244,14 @@
       <c r="K91" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L91" s="44">
+      <c r="L91" s="48">
         <v>0</v>
       </c>
       <c r="M91" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N91" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O91" s="46"/>
       <c r="P91" s="46"/>
@@ -6257,168 +6260,168 @@
       <c r="S91" s="42"/>
       <c r="T91" s="42"/>
     </row>
-    <row r="92" s="5" customFormat="1" ht="16.5" spans="1:20">
+    <row r="92" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A92" s="36">
-        <v>10120010</v>
-      </c>
-      <c r="B92" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C92" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D92" s="50">
-        <v>101200026</v>
+        <v>10070010</v>
+      </c>
+      <c r="B92" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92" s="39">
+        <v>100100026</v>
       </c>
       <c r="E92" s="40">
         <v>10</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H92" s="41">
         <v>0</v>
       </c>
-      <c r="I92" s="43">
+      <c r="I92" s="42">
         <v>9500</v>
       </c>
       <c r="J92" s="43">
         <v>0</v>
       </c>
-      <c r="K92" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L92" s="48">
-        <v>0</v>
-      </c>
-      <c r="M92" s="43" t="s">
+      <c r="K92" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="44">
+        <v>0</v>
+      </c>
+      <c r="M92" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O92" s="45"/>
-      <c r="P92" s="45"/>
-      <c r="Q92" s="45"/>
-      <c r="R92" s="45"/>
-      <c r="S92" s="43"/>
-      <c r="T92" s="43"/>
-    </row>
-    <row r="93" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O92" s="46"/>
+      <c r="P92" s="46"/>
+      <c r="Q92" s="46"/>
+      <c r="R92" s="46"/>
+      <c r="S92" s="42"/>
+      <c r="T92" s="42"/>
+    </row>
+    <row r="93" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A93" s="36">
-        <v>10120011</v>
-      </c>
-      <c r="B93" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C93" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D93" s="50">
-        <v>101200026</v>
+        <v>10070011</v>
+      </c>
+      <c r="B93" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C93" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="39">
+        <v>100100026</v>
       </c>
       <c r="E93" s="40">
         <v>11</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H93" s="41">
         <v>0</v>
       </c>
-      <c r="I93" s="43">
+      <c r="I93" s="42">
         <v>9500</v>
       </c>
       <c r="J93" s="43">
         <v>0</v>
       </c>
-      <c r="K93" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L93" s="48">
-        <v>0</v>
-      </c>
-      <c r="M93" s="43" t="s">
+      <c r="K93" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="44">
+        <v>0</v>
+      </c>
+      <c r="M93" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N93" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O93" s="45"/>
-      <c r="P93" s="45"/>
-      <c r="Q93" s="45"/>
-      <c r="R93" s="45"/>
-      <c r="S93" s="43"/>
-      <c r="T93" s="43"/>
-    </row>
-    <row r="94" s="5" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O93" s="46"/>
+      <c r="P93" s="46"/>
+      <c r="Q93" s="46"/>
+      <c r="R93" s="46"/>
+      <c r="S93" s="42"/>
+      <c r="T93" s="42"/>
+    </row>
+    <row r="94" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A94" s="36">
-        <v>10120012</v>
-      </c>
-      <c r="B94" s="49">
-        <v>101200</v>
-      </c>
-      <c r="C94" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D94" s="50">
-        <v>101200026</v>
+        <v>10070012</v>
+      </c>
+      <c r="B94" s="37">
+        <v>100700</v>
+      </c>
+      <c r="C94" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94" s="39">
+        <v>100100026</v>
       </c>
       <c r="E94" s="40">
         <v>12</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H94" s="47">
         <v>0</v>
       </c>
-      <c r="I94" s="43">
+      <c r="I94" s="42">
         <v>9500</v>
       </c>
       <c r="J94" s="43">
         <v>0</v>
       </c>
-      <c r="K94" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L94" s="48">
-        <v>0</v>
-      </c>
-      <c r="M94" s="43" t="s">
+      <c r="K94" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" s="44">
+        <v>0</v>
+      </c>
+      <c r="M94" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N94" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="O94" s="45"/>
-      <c r="P94" s="45"/>
-      <c r="Q94" s="45"/>
-      <c r="R94" s="45"/>
-      <c r="S94" s="43"/>
-      <c r="T94" s="43"/>
-    </row>
-    <row r="95" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>93</v>
+      </c>
+      <c r="O94" s="46"/>
+      <c r="P94" s="46"/>
+      <c r="Q94" s="46"/>
+      <c r="R94" s="46"/>
+      <c r="S94" s="42"/>
+      <c r="T94" s="42"/>
+    </row>
+    <row r="95" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A95" s="36">
-        <v>10140010</v>
-      </c>
-      <c r="B95" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C95" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D95" s="39">
-        <v>100100026</v>
+        <v>10120010</v>
+      </c>
+      <c r="B95" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C95" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D95" s="50">
+        <v>101200026</v>
       </c>
       <c r="E95" s="40">
         <v>10</v>
@@ -6432,43 +6435,43 @@
       <c r="H95" s="41">
         <v>0</v>
       </c>
-      <c r="I95" s="42">
+      <c r="I95" s="43">
         <v>9500</v>
       </c>
       <c r="J95" s="43">
         <v>0</v>
       </c>
-      <c r="K95" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L95" s="44">
-        <v>0</v>
-      </c>
-      <c r="M95" s="42" t="s">
+      <c r="K95" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="48">
+        <v>0</v>
+      </c>
+      <c r="M95" s="43" t="s">
         <v>37</v>
       </c>
       <c r="N95" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O95" s="46"/>
-      <c r="P95" s="46"/>
-      <c r="Q95" s="46"/>
-      <c r="R95" s="46"/>
-      <c r="S95" s="42"/>
-      <c r="T95" s="42"/>
-    </row>
-    <row r="96" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O95" s="45"/>
+      <c r="P95" s="45"/>
+      <c r="Q95" s="45"/>
+      <c r="R95" s="45"/>
+      <c r="S95" s="43"/>
+      <c r="T95" s="43"/>
+    </row>
+    <row r="96" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="36">
-        <v>10140011</v>
-      </c>
-      <c r="B96" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C96" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D96" s="39">
-        <v>100100026</v>
+        <v>10120011</v>
+      </c>
+      <c r="B96" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C96" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D96" s="50">
+        <v>101200026</v>
       </c>
       <c r="E96" s="40">
         <v>11</v>
@@ -6482,43 +6485,43 @@
       <c r="H96" s="41">
         <v>0</v>
       </c>
-      <c r="I96" s="42">
+      <c r="I96" s="43">
         <v>9500</v>
       </c>
       <c r="J96" s="43">
         <v>0</v>
       </c>
-      <c r="K96" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L96" s="44">
-        <v>0</v>
-      </c>
-      <c r="M96" s="42" t="s">
+      <c r="K96" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" s="48">
+        <v>0</v>
+      </c>
+      <c r="M96" s="43" t="s">
         <v>40</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O96" s="46"/>
-      <c r="P96" s="46"/>
-      <c r="Q96" s="46"/>
-      <c r="R96" s="46"/>
-      <c r="S96" s="42"/>
-      <c r="T96" s="42"/>
-    </row>
-    <row r="97" s="4" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O96" s="45"/>
+      <c r="P96" s="45"/>
+      <c r="Q96" s="45"/>
+      <c r="R96" s="45"/>
+      <c r="S96" s="43"/>
+      <c r="T96" s="43"/>
+    </row>
+    <row r="97" s="5" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="36">
-        <v>10140012</v>
-      </c>
-      <c r="B97" s="37">
-        <v>101400</v>
-      </c>
-      <c r="C97" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D97" s="39">
-        <v>100100026</v>
+        <v>10120012</v>
+      </c>
+      <c r="B97" s="49">
+        <v>101200</v>
+      </c>
+      <c r="C97" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D97" s="50">
+        <v>101200026</v>
       </c>
       <c r="E97" s="40">
         <v>12</v>
@@ -6532,52 +6535,52 @@
       <c r="H97" s="47">
         <v>0</v>
       </c>
-      <c r="I97" s="42">
+      <c r="I97" s="43">
         <v>9500</v>
       </c>
       <c r="J97" s="43">
         <v>0</v>
       </c>
-      <c r="K97" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L97" s="44">
-        <v>0</v>
-      </c>
-      <c r="M97" s="42" t="s">
+      <c r="K97" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="48">
+        <v>0</v>
+      </c>
+      <c r="M97" s="43" t="s">
         <v>43</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="O97" s="46"/>
-      <c r="P97" s="46"/>
-      <c r="Q97" s="46"/>
-      <c r="R97" s="46"/>
-      <c r="S97" s="42"/>
-      <c r="T97" s="42"/>
+        <v>93</v>
+      </c>
+      <c r="O97" s="45"/>
+      <c r="P97" s="45"/>
+      <c r="Q97" s="45"/>
+      <c r="R97" s="45"/>
+      <c r="S97" s="43"/>
+      <c r="T97" s="43"/>
     </row>
     <row r="98" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="36">
-        <v>10170010</v>
+        <v>10140010</v>
       </c>
       <c r="B98" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D98" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E98" s="40">
         <v>10</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G98" s="22" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H98" s="41">
         <v>0</v>
@@ -6598,7 +6601,7 @@
         <v>37</v>
       </c>
       <c r="N98" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O98" s="46"/>
       <c r="P98" s="46"/>
@@ -6609,25 +6612,25 @@
     </row>
     <row r="99" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="36">
-        <v>10170011</v>
+        <v>10140011</v>
       </c>
       <c r="B99" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D99" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E99" s="40">
         <v>11</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G99" s="22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H99" s="41">
         <v>0</v>
@@ -6648,7 +6651,7 @@
         <v>40</v>
       </c>
       <c r="N99" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O99" s="46"/>
       <c r="P99" s="46"/>
@@ -6659,25 +6662,25 @@
     </row>
     <row r="100" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="36">
-        <v>10170012</v>
+        <v>10140012</v>
       </c>
       <c r="B100" s="37">
-        <v>101700</v>
+        <v>101400</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D100" s="39">
-        <v>101700001</v>
+        <v>100100026</v>
       </c>
       <c r="E100" s="40">
         <v>12</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H100" s="47">
         <v>0</v>
@@ -6698,7 +6701,7 @@
         <v>43</v>
       </c>
       <c r="N100" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O100" s="46"/>
       <c r="P100" s="46"/>
@@ -6709,16 +6712,16 @@
     </row>
     <row r="101" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="36">
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B101" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D101" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E101" s="40">
         <v>10</v>
@@ -6741,14 +6744,14 @@
       <c r="K101" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L101" s="48">
+      <c r="L101" s="44">
         <v>0</v>
       </c>
       <c r="M101" s="42" t="s">
         <v>37</v>
       </c>
       <c r="N101" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O101" s="46"/>
       <c r="P101" s="46"/>
@@ -6759,16 +6762,16 @@
     </row>
     <row r="102" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="36">
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B102" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D102" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E102" s="40">
         <v>11</v>
@@ -6791,14 +6794,14 @@
       <c r="K102" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L102" s="48">
+      <c r="L102" s="44">
         <v>0</v>
       </c>
       <c r="M102" s="42" t="s">
         <v>40</v>
       </c>
       <c r="N102" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O102" s="46"/>
       <c r="P102" s="46"/>
@@ -6809,16 +6812,16 @@
     </row>
     <row r="103" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A103" s="36">
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B103" s="37">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D103" s="39">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="E103" s="40">
         <v>12</v>
@@ -6841,14 +6844,14 @@
       <c r="K103" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="L103" s="48">
+      <c r="L103" s="44">
         <v>0</v>
       </c>
       <c r="M103" s="42" t="s">
         <v>43</v>
       </c>
       <c r="N103" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O103" s="46"/>
       <c r="P103" s="46"/>
@@ -6859,16 +6862,16 @@
     </row>
     <row r="104" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A104" s="36">
-        <v>10220010</v>
+        <v>10210010</v>
       </c>
       <c r="B104" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D104" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E104" s="40">
         <v>10</v>
@@ -6898,7 +6901,7 @@
         <v>37</v>
       </c>
       <c r="N104" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O104" s="46"/>
       <c r="P104" s="46"/>
@@ -6909,16 +6912,16 @@
     </row>
     <row r="105" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A105" s="36">
-        <v>10220011</v>
+        <v>10210011</v>
       </c>
       <c r="B105" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D105" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E105" s="40">
         <v>11</v>
@@ -6948,7 +6951,7 @@
         <v>40</v>
       </c>
       <c r="N105" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O105" s="46"/>
       <c r="P105" s="46"/>
@@ -6959,16 +6962,16 @@
     </row>
     <row r="106" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="36">
-        <v>10220012</v>
+        <v>10210012</v>
       </c>
       <c r="B106" s="37">
-        <v>102200</v>
+        <v>102100</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D106" s="39">
-        <v>102200001</v>
+        <v>102100001</v>
       </c>
       <c r="E106" s="40">
         <v>12</v>
@@ -6998,7 +7001,7 @@
         <v>43</v>
       </c>
       <c r="N106" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O106" s="46"/>
       <c r="P106" s="46"/>
@@ -7009,25 +7012,25 @@
     </row>
     <row r="107" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="36">
-        <v>10240010</v>
+        <v>10220010</v>
       </c>
       <c r="B107" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D107" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E107" s="40">
         <v>10</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H107" s="41">
         <v>0</v>
@@ -7048,7 +7051,7 @@
         <v>37</v>
       </c>
       <c r="N107" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O107" s="46"/>
       <c r="P107" s="46"/>
@@ -7059,25 +7062,25 @@
     </row>
     <row r="108" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="36">
-        <v>10240011</v>
+        <v>10220011</v>
       </c>
       <c r="B108" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D108" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E108" s="40">
         <v>11</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G108" s="22" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H108" s="41">
         <v>0</v>
@@ -7098,7 +7101,7 @@
         <v>40</v>
       </c>
       <c r="N108" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O108" s="46"/>
       <c r="P108" s="46"/>
@@ -7109,25 +7112,25 @@
     </row>
     <row r="109" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A109" s="36">
-        <v>10240012</v>
+        <v>10220012</v>
       </c>
       <c r="B109" s="37">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D109" s="39">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="E109" s="40">
         <v>12</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H109" s="47">
         <v>0</v>
@@ -7148,7 +7151,7 @@
         <v>43</v>
       </c>
       <c r="N109" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O109" s="46"/>
       <c r="P109" s="46"/>
@@ -7159,27 +7162,27 @@
     </row>
     <row r="110" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A110" s="36">
-        <v>10180010</v>
+        <v>10240010</v>
       </c>
       <c r="B110" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D110" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E110" s="40">
         <v>10</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H110" s="47">
+        <v>35</v>
+      </c>
+      <c r="H110" s="41">
         <v>0</v>
       </c>
       <c r="I110" s="42">
@@ -7198,7 +7201,7 @@
         <v>37</v>
       </c>
       <c r="N110" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O110" s="46"/>
       <c r="P110" s="46"/>
@@ -7209,27 +7212,27 @@
     </row>
     <row r="111" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A111" s="36">
-        <v>10180011</v>
+        <v>10240011</v>
       </c>
       <c r="B111" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D111" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E111" s="40">
         <v>11</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H111" s="47">
+        <v>39</v>
+      </c>
+      <c r="H111" s="41">
         <v>0</v>
       </c>
       <c r="I111" s="42">
@@ -7248,7 +7251,7 @@
         <v>40</v>
       </c>
       <c r="N111" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O111" s="46"/>
       <c r="P111" s="46"/>
@@ -7259,25 +7262,25 @@
     </row>
     <row r="112" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A112" s="36">
-        <v>10180012</v>
+        <v>10240012</v>
       </c>
       <c r="B112" s="37">
-        <v>101800</v>
+        <v>102400</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D112" s="39">
-        <v>101800001</v>
+        <v>102400026</v>
       </c>
       <c r="E112" s="40">
         <v>12</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H112" s="47">
         <v>0</v>
@@ -7298,7 +7301,7 @@
         <v>43</v>
       </c>
       <c r="N112" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O112" s="46"/>
       <c r="P112" s="46"/>
@@ -7309,25 +7312,25 @@
     </row>
     <row r="113" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="36">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B113" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D113" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E113" s="40">
         <v>10</v>
       </c>
       <c r="F113" s="21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H113" s="47">
         <v>0</v>
@@ -7348,7 +7351,7 @@
         <v>37</v>
       </c>
       <c r="N113" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O113" s="46"/>
       <c r="P113" s="46"/>
@@ -7359,25 +7362,25 @@
     </row>
     <row r="114" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A114" s="36">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B114" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D114" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E114" s="40">
         <v>11</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G114" s="22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H114" s="47">
         <v>0</v>
@@ -7398,7 +7401,7 @@
         <v>40</v>
       </c>
       <c r="N114" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O114" s="46"/>
       <c r="P114" s="46"/>
@@ -7409,25 +7412,25 @@
     </row>
     <row r="115" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A115" s="36">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B115" s="37">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D115" s="39">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="E115" s="40">
         <v>12</v>
       </c>
       <c r="F115" s="21" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H115" s="47">
         <v>0</v>
@@ -7448,7 +7451,7 @@
         <v>43</v>
       </c>
       <c r="N115" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O115" s="46"/>
       <c r="P115" s="46"/>
@@ -7459,25 +7462,25 @@
     </row>
     <row r="116" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A116" s="36">
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B116" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D116" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E116" s="40">
         <v>10</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G116" s="22" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H116" s="47">
         <v>0</v>
@@ -7498,7 +7501,7 @@
         <v>37</v>
       </c>
       <c r="N116" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O116" s="46"/>
       <c r="P116" s="46"/>
@@ -7509,25 +7512,25 @@
     </row>
     <row r="117" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A117" s="36">
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B117" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D117" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E117" s="40">
         <v>11</v>
       </c>
       <c r="F117" s="21" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G117" s="22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H117" s="47">
         <v>0</v>
@@ -7548,7 +7551,7 @@
         <v>40</v>
       </c>
       <c r="N117" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O117" s="46"/>
       <c r="P117" s="46"/>
@@ -7559,25 +7562,25 @@
     </row>
     <row r="118" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A118" s="36">
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B118" s="37">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D118" s="39">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="E118" s="40">
         <v>12</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G118" s="22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H118" s="47">
         <v>0</v>
@@ -7598,7 +7601,7 @@
         <v>43</v>
       </c>
       <c r="N118" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O118" s="46"/>
       <c r="P118" s="46"/>
@@ -7609,31 +7612,31 @@
     </row>
     <row r="119" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A119" s="36">
-        <v>10340010</v>
+        <v>10230010</v>
       </c>
       <c r="B119" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D119" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E119" s="40">
         <v>10</v>
       </c>
       <c r="F119" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G119" s="22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H119" s="47">
         <v>0</v>
       </c>
       <c r="I119" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J119" s="43">
         <v>0</v>
@@ -7648,7 +7651,7 @@
         <v>37</v>
       </c>
       <c r="N119" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O119" s="46"/>
       <c r="P119" s="46"/>
@@ -7659,31 +7662,31 @@
     </row>
     <row r="120" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A120" s="36">
-        <v>10340011</v>
+        <v>10230011</v>
       </c>
       <c r="B120" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D120" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E120" s="40">
         <v>11</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G120" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H120" s="47">
         <v>0</v>
       </c>
       <c r="I120" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J120" s="43">
         <v>0</v>
@@ -7698,7 +7701,7 @@
         <v>40</v>
       </c>
       <c r="N120" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O120" s="46"/>
       <c r="P120" s="46"/>
@@ -7709,31 +7712,31 @@
     </row>
     <row r="121" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="36">
-        <v>10340012</v>
+        <v>10230012</v>
       </c>
       <c r="B121" s="37">
-        <v>103400</v>
+        <v>102300</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D121" s="39">
-        <v>103000001</v>
+        <v>102300001</v>
       </c>
       <c r="E121" s="40">
         <v>12</v>
       </c>
       <c r="F121" s="21" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G121" s="22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H121" s="47">
         <v>0</v>
       </c>
       <c r="I121" s="42">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J121" s="43">
         <v>0</v>
@@ -7748,7 +7751,7 @@
         <v>43</v>
       </c>
       <c r="N121" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O121" s="46"/>
       <c r="P121" s="46"/>
@@ -7759,25 +7762,25 @@
     </row>
     <row r="122" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="36">
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B122" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D122" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E122" s="40">
         <v>10</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G122" s="22" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="H122" s="47">
         <v>0</v>
@@ -7798,7 +7801,7 @@
         <v>37</v>
       </c>
       <c r="N122" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O122" s="46"/>
       <c r="P122" s="46"/>
@@ -7809,25 +7812,25 @@
     </row>
     <row r="123" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="36">
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B123" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C123" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D123" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E123" s="40">
         <v>11</v>
       </c>
       <c r="F123" s="21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G123" s="22" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H123" s="47">
         <v>0</v>
@@ -7848,7 +7851,7 @@
         <v>40</v>
       </c>
       <c r="N123" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O123" s="46"/>
       <c r="P123" s="46"/>
@@ -7859,25 +7862,25 @@
     </row>
     <row r="124" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A124" s="36">
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B124" s="37">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D124" s="39">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="E124" s="40">
         <v>12</v>
       </c>
       <c r="F124" s="21" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G124" s="22" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H124" s="47">
         <v>0</v>
@@ -7898,7 +7901,7 @@
         <v>43</v>
       </c>
       <c r="N124" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O124" s="46"/>
       <c r="P124" s="46"/>
@@ -7909,16 +7912,16 @@
     </row>
     <row r="125" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A125" s="36">
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B125" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C125" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D125" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E125" s="40">
         <v>10</v>
@@ -7948,7 +7951,7 @@
         <v>37</v>
       </c>
       <c r="N125" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O125" s="46"/>
       <c r="P125" s="46"/>
@@ -7959,16 +7962,16 @@
     </row>
     <row r="126" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A126" s="36">
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B126" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D126" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E126" s="40">
         <v>11</v>
@@ -7998,7 +8001,7 @@
         <v>40</v>
       </c>
       <c r="N126" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O126" s="46"/>
       <c r="P126" s="46"/>
@@ -8009,16 +8012,16 @@
     </row>
     <row r="127" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A127" s="36">
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B127" s="37">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C127" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D127" s="39">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="E127" s="40">
         <v>12</v>
@@ -8048,7 +8051,7 @@
         <v>43</v>
       </c>
       <c r="N127" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O127" s="46"/>
       <c r="P127" s="46"/>
@@ -8059,25 +8062,25 @@
     </row>
     <row r="128" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A128" s="36">
-        <v>10360010</v>
+        <v>10350110</v>
       </c>
       <c r="B128" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D128" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E128" s="40">
         <v>10</v>
       </c>
-      <c r="F128" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G128" s="51" t="s">
-        <v>35</v>
+      <c r="F128" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G128" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="H128" s="47">
         <v>0</v>
@@ -8098,7 +8101,7 @@
         <v>37</v>
       </c>
       <c r="N128" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O128" s="46"/>
       <c r="P128" s="46"/>
@@ -8109,25 +8112,25 @@
     </row>
     <row r="129" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A129" s="36">
-        <v>10360011</v>
+        <v>10350111</v>
       </c>
       <c r="B129" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C129" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D129" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E129" s="40">
         <v>11</v>
       </c>
-      <c r="F129" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="G129" s="51" t="s">
-        <v>39</v>
+      <c r="F129" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="H129" s="47">
         <v>0</v>
@@ -8148,7 +8151,7 @@
         <v>40</v>
       </c>
       <c r="N129" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O129" s="46"/>
       <c r="P129" s="46"/>
@@ -8159,25 +8162,25 @@
     </row>
     <row r="130" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A130" s="36">
-        <v>10360012</v>
+        <v>10350112</v>
       </c>
       <c r="B130" s="37">
-        <v>103600</v>
+        <v>103501</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D130" s="39">
-        <v>103600001</v>
+        <v>103501001</v>
       </c>
       <c r="E130" s="40">
         <v>12</v>
       </c>
-      <c r="F130" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G130" s="51" t="s">
-        <v>42</v>
+      <c r="F130" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="G130" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="H130" s="47">
         <v>0</v>
@@ -8198,7 +8201,7 @@
         <v>43</v>
       </c>
       <c r="N130" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O130" s="46"/>
       <c r="P130" s="46"/>
@@ -8209,25 +8212,25 @@
     </row>
     <row r="131" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A131" s="36">
-        <v>10280010</v>
+        <v>10360010</v>
       </c>
       <c r="B131" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C131" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D131" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E131" s="40">
         <v>10</v>
       </c>
       <c r="F131" s="46" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G131" s="51" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H131" s="47">
         <v>0</v>
@@ -8248,7 +8251,7 @@
         <v>37</v>
       </c>
       <c r="N131" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O131" s="46"/>
       <c r="P131" s="46"/>
@@ -8259,25 +8262,25 @@
     </row>
     <row r="132" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A132" s="36">
-        <v>10280011</v>
+        <v>10360011</v>
       </c>
       <c r="B132" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C132" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D132" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E132" s="40">
         <v>11</v>
       </c>
       <c r="F132" s="46" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G132" s="51" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H132" s="47">
         <v>0</v>
@@ -8298,7 +8301,7 @@
         <v>40</v>
       </c>
       <c r="N132" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O132" s="46"/>
       <c r="P132" s="46"/>
@@ -8309,25 +8312,25 @@
     </row>
     <row r="133" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A133" s="36">
-        <v>10280012</v>
+        <v>10360012</v>
       </c>
       <c r="B133" s="37">
-        <v>102800</v>
+        <v>103600</v>
       </c>
       <c r="C133" s="38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D133" s="39">
-        <v>102800001</v>
+        <v>103600001</v>
       </c>
       <c r="E133" s="40">
         <v>12</v>
       </c>
       <c r="F133" s="46" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G133" s="51" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H133" s="47">
         <v>0</v>
@@ -8348,7 +8351,7 @@
         <v>43</v>
       </c>
       <c r="N133" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O133" s="46"/>
       <c r="P133" s="46"/>
@@ -8359,16 +8362,16 @@
     </row>
     <row r="134" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A134" s="36">
-        <v>10200010</v>
+        <v>10280010</v>
       </c>
       <c r="B134" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C134" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D134" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E134" s="40">
         <v>10</v>
@@ -8398,7 +8401,7 @@
         <v>37</v>
       </c>
       <c r="N134" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O134" s="46"/>
       <c r="P134" s="46"/>
@@ -8409,16 +8412,16 @@
     </row>
     <row r="135" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A135" s="36">
-        <v>10200011</v>
+        <v>10280011</v>
       </c>
       <c r="B135" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C135" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D135" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E135" s="40">
         <v>11</v>
@@ -8448,7 +8451,7 @@
         <v>40</v>
       </c>
       <c r="N135" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O135" s="46"/>
       <c r="P135" s="46"/>
@@ -8459,16 +8462,16 @@
     </row>
     <row r="136" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A136" s="36">
-        <v>10200012</v>
+        <v>10280012</v>
       </c>
       <c r="B136" s="37">
-        <v>102000</v>
+        <v>102800</v>
       </c>
       <c r="C136" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D136" s="39">
-        <v>102000001</v>
+        <v>102800001</v>
       </c>
       <c r="E136" s="40">
         <v>12</v>
@@ -8498,7 +8501,7 @@
         <v>43</v>
       </c>
       <c r="N136" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O136" s="46"/>
       <c r="P136" s="46"/>
@@ -8509,25 +8512,25 @@
     </row>
     <row r="137" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A137" s="36">
-        <v>10340110</v>
+        <v>10200010</v>
       </c>
       <c r="B137" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C137" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D137" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D137" s="39">
+        <v>102000001</v>
       </c>
       <c r="E137" s="40">
         <v>10</v>
       </c>
       <c r="F137" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G137" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H137" s="47">
         <v>0</v>
@@ -8548,7 +8551,7 @@
         <v>37</v>
       </c>
       <c r="N137" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O137" s="46"/>
       <c r="P137" s="46"/>
@@ -8559,25 +8562,25 @@
     </row>
     <row r="138" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A138" s="36">
-        <v>10340111</v>
+        <v>10200011</v>
       </c>
       <c r="B138" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C138" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D138" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D138" s="39">
+        <v>102000001</v>
       </c>
       <c r="E138" s="40">
         <v>11</v>
       </c>
       <c r="F138" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G138" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H138" s="47">
         <v>0</v>
@@ -8598,7 +8601,7 @@
         <v>40</v>
       </c>
       <c r="N138" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O138" s="46"/>
       <c r="P138" s="46"/>
@@ -8609,25 +8612,25 @@
     </row>
     <row r="139" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A139" s="36">
-        <v>10340112</v>
+        <v>10200012</v>
       </c>
       <c r="B139" s="37">
-        <v>103401</v>
+        <v>102000</v>
       </c>
       <c r="C139" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D139" s="24">
-        <v>103400001</v>
+        <v>79</v>
+      </c>
+      <c r="D139" s="39">
+        <v>102000001</v>
       </c>
       <c r="E139" s="40">
         <v>12</v>
       </c>
       <c r="F139" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G139" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H139" s="47">
         <v>0</v>
@@ -8648,7 +8651,7 @@
         <v>43</v>
       </c>
       <c r="N139" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O139" s="46"/>
       <c r="P139" s="46"/>
@@ -8657,27 +8660,27 @@
       <c r="S139" s="42"/>
       <c r="T139" s="42"/>
     </row>
-    <row r="140" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A140" s="19">
-        <v>10380010</v>
-      </c>
-      <c r="B140" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C140" s="20" t="s">
-        <v>81</v>
+    <row r="140" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A140" s="36">
+        <v>10340110</v>
+      </c>
+      <c r="B140" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C140" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D140" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E140" s="20">
-        <v>11</v>
+        <v>103400001</v>
+      </c>
+      <c r="E140" s="40">
+        <v>10</v>
       </c>
       <c r="F140" s="46" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G140" s="51" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H140" s="47">
         <v>0</v>
@@ -8698,36 +8701,36 @@
         <v>37</v>
       </c>
       <c r="N140" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O140" s="21"/>
-      <c r="P140" s="21"/>
-      <c r="Q140" s="21"/>
-      <c r="R140" s="21"/>
-      <c r="S140" s="23"/>
-      <c r="T140" s="23"/>
-    </row>
-    <row r="141" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A141" s="19">
-        <v>10380011</v>
-      </c>
-      <c r="B141" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C141" s="20" t="s">
-        <v>81</v>
+        <v>91</v>
+      </c>
+      <c r="O140" s="46"/>
+      <c r="P140" s="46"/>
+      <c r="Q140" s="46"/>
+      <c r="R140" s="46"/>
+      <c r="S140" s="42"/>
+      <c r="T140" s="42"/>
+    </row>
+    <row r="141" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A141" s="36">
+        <v>10340111</v>
+      </c>
+      <c r="B141" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C141" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D141" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E141" s="20">
-        <v>12</v>
+        <v>103400001</v>
+      </c>
+      <c r="E141" s="40">
+        <v>11</v>
       </c>
       <c r="F141" s="46" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G141" s="51" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H141" s="47">
         <v>0</v>
@@ -8748,36 +8751,36 @@
         <v>40</v>
       </c>
       <c r="N141" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O141" s="21"/>
-      <c r="P141" s="21"/>
-      <c r="Q141" s="21"/>
-      <c r="R141" s="21"/>
-      <c r="S141" s="23"/>
-      <c r="T141" s="23"/>
-    </row>
-    <row r="142" s="2" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A142" s="19">
-        <v>10380012</v>
-      </c>
-      <c r="B142" s="19">
-        <v>103800</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>81</v>
+        <v>92</v>
+      </c>
+      <c r="O141" s="46"/>
+      <c r="P141" s="46"/>
+      <c r="Q141" s="46"/>
+      <c r="R141" s="46"/>
+      <c r="S141" s="42"/>
+      <c r="T141" s="42"/>
+    </row>
+    <row r="142" s="4" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A142" s="36">
+        <v>10340112</v>
+      </c>
+      <c r="B142" s="37">
+        <v>103401</v>
+      </c>
+      <c r="C142" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="D142" s="24">
-        <v>103800001</v>
-      </c>
-      <c r="E142" s="20">
-        <v>13</v>
+        <v>103400001</v>
+      </c>
+      <c r="E142" s="40">
+        <v>12</v>
       </c>
       <c r="F142" s="46" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G142" s="51" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H142" s="47">
         <v>0</v>
@@ -8798,27 +8801,27 @@
         <v>43</v>
       </c>
       <c r="N142" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="O142" s="21"/>
-      <c r="P142" s="21"/>
-      <c r="Q142" s="21"/>
-      <c r="R142" s="21"/>
-      <c r="S142" s="23"/>
-      <c r="T142" s="23"/>
+        <v>93</v>
+      </c>
+      <c r="O142" s="46"/>
+      <c r="P142" s="46"/>
+      <c r="Q142" s="46"/>
+      <c r="R142" s="46"/>
+      <c r="S142" s="42"/>
+      <c r="T142" s="42"/>
     </row>
     <row r="143" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A143" s="19">
-        <v>10270010</v>
+        <v>10380010</v>
       </c>
       <c r="B143" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D143" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E143" s="20">
         <v>11</v>
@@ -8848,7 +8851,7 @@
         <v>37</v>
       </c>
       <c r="N143" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O143" s="21"/>
       <c r="P143" s="21"/>
@@ -8859,16 +8862,16 @@
     </row>
     <row r="144" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A144" s="19">
-        <v>10270011</v>
+        <v>10380011</v>
       </c>
       <c r="B144" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D144" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E144" s="20">
         <v>12</v>
@@ -8898,7 +8901,7 @@
         <v>40</v>
       </c>
       <c r="N144" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O144" s="21"/>
       <c r="P144" s="21"/>
@@ -8909,16 +8912,16 @@
     </row>
     <row r="145" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A145" s="19">
-        <v>10270012</v>
+        <v>10380012</v>
       </c>
       <c r="B145" s="19">
-        <v>102700</v>
+        <v>103800</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D145" s="24">
-        <v>102700001</v>
+        <v>103800001</v>
       </c>
       <c r="E145" s="20">
         <v>13</v>
@@ -8948,7 +8951,7 @@
         <v>43</v>
       </c>
       <c r="N145" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O145" s="21"/>
       <c r="P145" s="21"/>
@@ -8959,25 +8962,25 @@
     </row>
     <row r="146" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A146" s="19">
-        <v>10370010</v>
+        <v>10270010</v>
       </c>
       <c r="B146" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D146" s="24">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E146" s="20">
         <v>11</v>
       </c>
       <c r="F146" s="46" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G146" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H146" s="47">
         <v>0</v>
@@ -8998,7 +9001,7 @@
         <v>37</v>
       </c>
       <c r="N146" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O146" s="21"/>
       <c r="P146" s="21"/>
@@ -9009,25 +9012,25 @@
     </row>
     <row r="147" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A147" s="19">
-        <v>10370011</v>
+        <v>10270011</v>
       </c>
       <c r="B147" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D147" s="24">
-        <v>103700001</v>
+        <v>102700001</v>
       </c>
       <c r="E147" s="20">
         <v>12</v>
       </c>
       <c r="F147" s="46" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G147" s="51" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H147" s="47">
         <v>0</v>
@@ -9048,7 +9051,7 @@
         <v>40</v>
       </c>
       <c r="N147" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O147" s="21"/>
       <c r="P147" s="21"/>
@@ -9059,25 +9062,25 @@
     </row>
     <row r="148" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A148" s="19">
-        <v>10370012</v>
+        <v>10270012</v>
       </c>
       <c r="B148" s="19">
-        <v>103700</v>
+        <v>102700</v>
       </c>
       <c r="C148" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D148" s="24">
-        <v>103100001</v>
+        <v>102700001</v>
       </c>
       <c r="E148" s="20">
         <v>13</v>
       </c>
       <c r="F148" s="46" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G148" s="51" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H148" s="47">
         <v>0</v>
@@ -9098,7 +9101,7 @@
         <v>43</v>
       </c>
       <c r="N148" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O148" s="21"/>
       <c r="P148" s="21"/>
@@ -9109,25 +9112,25 @@
     </row>
     <row r="149" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A149" s="19">
-        <v>10310010</v>
+        <v>10370010</v>
       </c>
       <c r="B149" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D149" s="24">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E149" s="20">
         <v>11</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G149" s="51" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H149" s="47">
         <v>0</v>
@@ -9148,7 +9151,7 @@
         <v>37</v>
       </c>
       <c r="N149" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O149" s="21"/>
       <c r="P149" s="21"/>
@@ -9159,25 +9162,25 @@
     </row>
     <row r="150" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A150" s="19">
-        <v>10310011</v>
+        <v>10370011</v>
       </c>
       <c r="B150" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C150" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D150" s="24">
-        <v>103100001</v>
+        <v>103700001</v>
       </c>
       <c r="E150" s="20">
         <v>12</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G150" s="51" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H150" s="47">
         <v>0</v>
@@ -9198,7 +9201,7 @@
         <v>40</v>
       </c>
       <c r="N150" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O150" s="21"/>
       <c r="P150" s="21"/>
@@ -9209,13 +9212,13 @@
     </row>
     <row r="151" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A151" s="19">
-        <v>10310012</v>
+        <v>10370012</v>
       </c>
       <c r="B151" s="19">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C151" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D151" s="24">
         <v>103100001</v>
@@ -9224,10 +9227,10 @@
         <v>13</v>
       </c>
       <c r="F151" s="46" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G151" s="51" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H151" s="47">
         <v>0</v>
@@ -9248,7 +9251,7 @@
         <v>43</v>
       </c>
       <c r="N151" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O151" s="21"/>
       <c r="P151" s="21"/>
@@ -9259,16 +9262,16 @@
     </row>
     <row r="152" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A152" s="19">
-        <v>10400010</v>
+        <v>10310010</v>
       </c>
       <c r="B152" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C152" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D152" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E152" s="20">
         <v>11</v>
@@ -9298,7 +9301,7 @@
         <v>37</v>
       </c>
       <c r="N152" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O152" s="21"/>
       <c r="P152" s="21"/>
@@ -9309,16 +9312,16 @@
     </row>
     <row r="153" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A153" s="19">
-        <v>10400011</v>
+        <v>10310011</v>
       </c>
       <c r="B153" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C153" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D153" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E153" s="20">
         <v>12</v>
@@ -9348,7 +9351,7 @@
         <v>40</v>
       </c>
       <c r="N153" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O153" s="21"/>
       <c r="P153" s="21"/>
@@ -9359,16 +9362,16 @@
     </row>
     <row r="154" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A154" s="19">
-        <v>10400012</v>
+        <v>10310012</v>
       </c>
       <c r="B154" s="19">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C154" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D154" s="24">
-        <v>104000001</v>
+        <v>103100001</v>
       </c>
       <c r="E154" s="20">
         <v>13</v>
@@ -9398,7 +9401,7 @@
         <v>43</v>
       </c>
       <c r="N154" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O154" s="21"/>
       <c r="P154" s="21"/>
@@ -9407,18 +9410,18 @@
       <c r="S154" s="23"/>
       <c r="T154" s="23"/>
     </row>
-    <row r="155" ht="16.5" spans="1:20">
+    <row r="155" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A155" s="19">
-        <v>10390010</v>
+        <v>10400010</v>
       </c>
       <c r="B155" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C155" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D155" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E155" s="20">
         <v>11</v>
@@ -9448,21 +9451,27 @@
         <v>37</v>
       </c>
       <c r="N155" s="45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="156" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="O155" s="21"/>
+      <c r="P155" s="21"/>
+      <c r="Q155" s="21"/>
+      <c r="R155" s="21"/>
+      <c r="S155" s="23"/>
+      <c r="T155" s="23"/>
+    </row>
+    <row r="156" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A156" s="19">
-        <v>10390011</v>
+        <v>10400011</v>
       </c>
       <c r="B156" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C156" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D156" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E156" s="20">
         <v>12</v>
@@ -9492,21 +9501,27 @@
         <v>40</v>
       </c>
       <c r="N156" s="45" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="157" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+      <c r="O156" s="21"/>
+      <c r="P156" s="21"/>
+      <c r="Q156" s="21"/>
+      <c r="R156" s="21"/>
+      <c r="S156" s="23"/>
+      <c r="T156" s="23"/>
+    </row>
+    <row r="157" s="2" customFormat="1" ht="16.5" spans="1:20">
       <c r="A157" s="19">
-        <v>10390012</v>
+        <v>10400012</v>
       </c>
       <c r="B157" s="19">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C157" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D157" s="24">
-        <v>103900001</v>
+        <v>104000001</v>
       </c>
       <c r="E157" s="20">
         <v>13</v>
@@ -9536,29 +9551,35 @@
         <v>43</v>
       </c>
       <c r="N157" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="158" s="2" customFormat="1" ht="16.5" spans="1:20">
+        <v>93</v>
+      </c>
+      <c r="O157" s="21"/>
+      <c r="P157" s="21"/>
+      <c r="Q157" s="21"/>
+      <c r="R157" s="21"/>
+      <c r="S157" s="23"/>
+      <c r="T157" s="23"/>
+    </row>
+    <row r="158" ht="16.5" spans="1:20">
       <c r="A158" s="19">
-        <v>10160010</v>
+        <v>10390010</v>
       </c>
       <c r="B158" s="19">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C158" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D158" s="24">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E158" s="20">
         <v>11</v>
       </c>
-      <c r="F158" s="21" t="s">
+      <c r="F158" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="G158" s="22" t="s">
+      <c r="G158" s="51" t="s">
         <v>51</v>
       </c>
       <c r="H158" s="47">
@@ -9580,35 +9601,29 @@
         <v>37</v>
       </c>
       <c r="N158" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="O158" s="21"/>
-      <c r="P158" s="21"/>
-      <c r="Q158" s="21"/>
-      <c r="R158" s="21"/>
-      <c r="S158" s="23"/>
-      <c r="T158" s="23"/>
-    </row>
-    <row r="159" s="2" customFormat="1" ht="16.5" spans="1:20">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="159" ht="16.5" spans="1:20">
       <c r="A159" s="19">
-        <v>10160011</v>
+        <v>10390011</v>
       </c>
       <c r="B159" s="19">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C159" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D159" s="24">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E159" s="20">
         <v>12</v>
       </c>
-      <c r="F159" s="21" t="s">
+      <c r="F159" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="G159" s="22" t="s">
+      <c r="G159" s="51" t="s">
         <v>53</v>
       </c>
       <c r="H159" s="47">
@@ -9630,35 +9645,29 @@
         <v>40</v>
       </c>
       <c r="N159" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="O159" s="21"/>
-      <c r="P159" s="21"/>
-      <c r="Q159" s="21"/>
-      <c r="R159" s="21"/>
-      <c r="S159" s="23"/>
-      <c r="T159" s="23"/>
-    </row>
-    <row r="160" s="2" customFormat="1" ht="16.5" spans="1:20">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="160" ht="16.5" spans="1:20">
       <c r="A160" s="19">
-        <v>10160012</v>
+        <v>10390012</v>
       </c>
       <c r="B160" s="19">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C160" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D160" s="24">
-        <v>101600001</v>
+        <v>103900001</v>
       </c>
       <c r="E160" s="20">
         <v>13</v>
       </c>
-      <c r="F160" s="21" t="s">
+      <c r="F160" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G160" s="22" t="s">
+      <c r="G160" s="51" t="s">
         <v>55</v>
       </c>
       <c r="H160" s="47">
@@ -9680,14 +9689,308 @@
         <v>43</v>
       </c>
       <c r="N160" s="45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A161" s="19">
+        <v>10160010</v>
+      </c>
+      <c r="B161" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C161" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D161" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E161" s="20">
+        <v>11</v>
+      </c>
+      <c r="F161" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G161" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H161" s="47">
+        <v>0</v>
+      </c>
+      <c r="I161" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J161" s="43">
+        <v>0</v>
+      </c>
+      <c r="K161" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L161" s="48">
+        <v>0</v>
+      </c>
+      <c r="M161" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N161" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O161" s="21"/>
+      <c r="P161" s="21"/>
+      <c r="Q161" s="21"/>
+      <c r="R161" s="21"/>
+      <c r="S161" s="23"/>
+      <c r="T161" s="23"/>
+    </row>
+    <row r="162" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A162" s="19">
+        <v>10160011</v>
+      </c>
+      <c r="B162" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C162" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E162" s="20">
+        <v>12</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G162" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H162" s="47">
+        <v>0</v>
+      </c>
+      <c r="I162" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J162" s="43">
+        <v>0</v>
+      </c>
+      <c r="K162" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L162" s="48">
+        <v>0</v>
+      </c>
+      <c r="M162" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N162" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="O160" s="21"/>
-      <c r="P160" s="21"/>
-      <c r="Q160" s="21"/>
-      <c r="R160" s="21"/>
-      <c r="S160" s="23"/>
-      <c r="T160" s="23"/>
+      <c r="O162" s="21"/>
+      <c r="P162" s="21"/>
+      <c r="Q162" s="21"/>
+      <c r="R162" s="21"/>
+      <c r="S162" s="23"/>
+      <c r="T162" s="23"/>
+    </row>
+    <row r="163" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A163" s="19">
+        <v>10160012</v>
+      </c>
+      <c r="B163" s="19">
+        <v>101600</v>
+      </c>
+      <c r="C163" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D163" s="24">
+        <v>101600001</v>
+      </c>
+      <c r="E163" s="20">
+        <v>13</v>
+      </c>
+      <c r="F163" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G163" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H163" s="47">
+        <v>0</v>
+      </c>
+      <c r="I163" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J163" s="43">
+        <v>0</v>
+      </c>
+      <c r="K163" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L163" s="48">
+        <v>0</v>
+      </c>
+      <c r="M163" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N163" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="O163" s="21"/>
+      <c r="P163" s="21"/>
+      <c r="Q163" s="21"/>
+      <c r="R163" s="21"/>
+      <c r="S163" s="23"/>
+      <c r="T163" s="23"/>
+    </row>
+    <row r="164" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A164" s="19">
+        <v>10150010</v>
+      </c>
+      <c r="B164" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C164" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D164" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E164" s="20">
+        <v>11</v>
+      </c>
+      <c r="F164" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G164" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H164" s="47">
+        <v>0</v>
+      </c>
+      <c r="I164" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J164" s="43">
+        <v>0</v>
+      </c>
+      <c r="K164" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L164" s="48">
+        <v>0</v>
+      </c>
+      <c r="M164" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N164" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="O164" s="21"/>
+      <c r="P164" s="21"/>
+      <c r="Q164" s="21"/>
+      <c r="R164" s="21"/>
+      <c r="S164" s="23"/>
+      <c r="T164" s="23"/>
+    </row>
+    <row r="165" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A165" s="19">
+        <v>10150011</v>
+      </c>
+      <c r="B165" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C165" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D165" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E165" s="20">
+        <v>12</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G165" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="47">
+        <v>0</v>
+      </c>
+      <c r="I165" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J165" s="43">
+        <v>0</v>
+      </c>
+      <c r="K165" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L165" s="48">
+        <v>0</v>
+      </c>
+      <c r="M165" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N165" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="O165" s="21"/>
+      <c r="P165" s="21"/>
+      <c r="Q165" s="21"/>
+      <c r="R165" s="21"/>
+      <c r="S165" s="23"/>
+      <c r="T165" s="23"/>
+    </row>
+    <row r="166" s="2" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A166" s="19">
+        <v>10150012</v>
+      </c>
+      <c r="B166" s="19">
+        <v>101500</v>
+      </c>
+      <c r="C166" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D166" s="24">
+        <v>101500001</v>
+      </c>
+      <c r="E166" s="20">
+        <v>13</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G166" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H166" s="47">
+        <v>0</v>
+      </c>
+      <c r="I166" s="42">
+        <v>9600</v>
+      </c>
+      <c r="J166" s="43">
+        <v>0</v>
+      </c>
+      <c r="K166" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L166" s="48">
+        <v>0</v>
+      </c>
+      <c r="M166" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N166" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="O166" s="21"/>
+      <c r="P166" s="21"/>
+      <c r="Q166" s="21"/>
+      <c r="R166" s="21"/>
+      <c r="S166" s="23"/>
+      <c r="T166" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoom.xlsx
+++ b/slots/resources/sample/BaseRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoom" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="83">
   <si>
     <t>id</t>
   </si>
@@ -359,6 +359,12 @@
     <t>财神</t>
   </si>
   <si>
+    <t>8_16_40_80_160_400_800</t>
+  </si>
+  <si>
+    <t>8:1</t>
+  </si>
+  <si>
     <t>埃及艳后</t>
   </si>
   <si>
@@ -372,6 +378,12 @@
   </si>
   <si>
     <t>财富银行</t>
+  </si>
+  <si>
+    <t>1_2_5_10_20_50_100</t>
+  </si>
+  <si>
+    <t>1:1</t>
   </si>
   <si>
     <t>篮球巨星</t>
@@ -638,16 +650,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -656,9 +668,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -669,19 +681,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -739,6 +751,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1073,7 +1091,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1097,16 +1115,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1115,92 +1133,92 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1279,6 +1297,15 @@
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2335,17 +2362,17 @@
       <c r="E14" s="20">
         <v>1</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>39</v>
+      <c r="F14" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="H14" s="14">
         <v>10000000</v>
       </c>
-      <c r="I14" s="25">
-        <v>9500</v>
+      <c r="I14" s="31">
+        <v>9700</v>
       </c>
       <c r="J14" s="23">
         <v>5000000</v>
@@ -2477,7 +2504,7 @@
         <v>101400</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="24">
         <v>100100026</v>
@@ -2527,7 +2554,7 @@
         <v>101400</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="24">
         <v>100100026</v>
@@ -2577,7 +2604,7 @@
         <v>101400</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" s="24">
         <v>100100026</v>
@@ -2627,7 +2654,7 @@
         <v>101700</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="24">
         <v>101700001</v>
@@ -2677,7 +2704,7 @@
         <v>101700</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="24">
         <v>101700001</v>
@@ -2727,7 +2754,7 @@
         <v>101700</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="24">
         <v>101700001</v>
@@ -2777,7 +2804,7 @@
         <v>102100</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D23" s="24">
         <v>102100001</v>
@@ -2827,7 +2854,7 @@
         <v>102100</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="24">
         <v>102100001</v>
@@ -2877,7 +2904,7 @@
         <v>102100</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="24">
         <v>102100001</v>
@@ -2927,7 +2954,7 @@
         <v>102200</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D26" s="24">
         <v>102200001</v>
@@ -2977,7 +3004,7 @@
         <v>102200</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27" s="24">
         <v>102200001</v>
@@ -3027,7 +3054,7 @@
         <v>102200</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D28" s="24">
         <v>102200001</v>
@@ -3077,7 +3104,7 @@
         <v>102400</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" s="24">
         <v>102400026</v>
@@ -3085,17 +3112,17 @@
       <c r="E29" s="20">
         <v>1</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>35</v>
+      <c r="F29" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="H29" s="14">
         <v>10000000</v>
       </c>
-      <c r="I29" s="25">
-        <v>9500</v>
+      <c r="I29" s="31">
+        <v>9700</v>
       </c>
       <c r="J29" s="23">
         <v>5000000</v>
@@ -3127,7 +3154,7 @@
         <v>102400</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" s="24">
         <v>102400026</v>
@@ -3177,7 +3204,7 @@
         <v>102400</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D31" s="24">
         <v>102400026</v>
@@ -3227,7 +3254,7 @@
         <v>101800</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D32" s="24">
         <v>101800001</v>
@@ -3277,7 +3304,7 @@
         <v>101800</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D33" s="24">
         <v>101800001</v>
@@ -3327,7 +3354,7 @@
         <v>101800</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D34" s="24">
         <v>101800001</v>
@@ -3377,7 +3404,7 @@
         <v>102500</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D35" s="24">
         <v>102500001</v>
@@ -3386,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H35" s="14">
         <v>10000000</v>
@@ -3427,7 +3454,7 @@
         <v>102500</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D36" s="24">
         <v>102500001</v>
@@ -3436,10 +3463,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H36" s="14">
         <v>100000000</v>
@@ -3477,7 +3504,7 @@
         <v>102500</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D37" s="24">
         <v>102500001</v>
@@ -3486,10 +3513,10 @@
         <v>3</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H37" s="28">
         <v>1000000000</v>
@@ -3527,7 +3554,7 @@
         <v>102300</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D38" s="24">
         <v>102300001</v>
@@ -3577,7 +3604,7 @@
         <v>102300</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D39" s="24">
         <v>102300001</v>
@@ -3627,7 +3654,7 @@
         <v>102300</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D40" s="24">
         <v>102300001</v>
@@ -3677,7 +3704,7 @@
         <v>103400</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D41" s="24">
         <v>103000001</v>
@@ -3685,17 +3712,17 @@
       <c r="E41" s="20">
         <v>1</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>67</v>
+      <c r="F41" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G41" s="30" t="s">
+        <v>69</v>
       </c>
       <c r="H41" s="14">
         <v>10000000</v>
       </c>
-      <c r="I41" s="25">
-        <v>9600</v>
+      <c r="I41" s="31">
+        <v>9700</v>
       </c>
       <c r="J41" s="23">
         <v>5000000</v>
@@ -3727,7 +3754,7 @@
         <v>103400</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D42" s="24">
         <v>103000001</v>
@@ -3736,16 +3763,16 @@
         <v>2</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H42" s="14">
         <v>100000000</v>
       </c>
       <c r="I42" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J42" s="23">
         <v>50000000</v>
@@ -3777,7 +3804,7 @@
         <v>103400</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D43" s="24">
         <v>103000001</v>
@@ -3786,16 +3813,16 @@
         <v>3</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H43" s="28">
         <v>1000000000</v>
       </c>
       <c r="I43" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J43" s="23">
         <v>500000000</v>
@@ -3820,19 +3847,19 @@
       <c r="T43" s="23"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A44" s="29">
+      <c r="A44" s="32">
         <v>1035001</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="33">
         <v>103500</v>
       </c>
-      <c r="C44" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="32">
+      <c r="C44" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="35">
         <v>102900001</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="34">
         <v>1</v>
       </c>
       <c r="F44" s="21" t="s">
@@ -3845,44 +3872,44 @@
         <v>10000000</v>
       </c>
       <c r="I44" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J44" s="23">
         <v>5000000</v>
       </c>
-      <c r="K44" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" s="33">
+      <c r="K44" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="36">
         <v>100</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N44" s="34">
-        <v>0</v>
-      </c>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
+      <c r="N44" s="37">
+        <v>0</v>
+      </c>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A45" s="29">
+      <c r="A45" s="32">
         <v>1035002</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="33">
         <v>103500</v>
       </c>
-      <c r="C45" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D45" s="32">
+      <c r="C45" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="35">
         <v>102900001</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="34">
         <v>2</v>
       </c>
       <c r="F45" s="21" t="s">
@@ -3895,44 +3922,44 @@
         <v>100000000</v>
       </c>
       <c r="I45" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J45" s="23">
         <v>50000000</v>
       </c>
-      <c r="K45" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L45" s="33">
+      <c r="K45" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="36">
         <v>100</v>
       </c>
       <c r="M45" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N45" s="34">
-        <v>0</v>
-      </c>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
+      <c r="N45" s="37">
+        <v>0</v>
+      </c>
+      <c r="O45" s="37"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="38"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A46" s="29">
+      <c r="A46" s="32">
         <v>1035003</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="33">
         <v>103500</v>
       </c>
-      <c r="C46" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="32">
+      <c r="C46" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="35">
         <v>102900001</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="34">
         <v>3</v>
       </c>
       <c r="F46" s="21" t="s">
@@ -3945,44 +3972,44 @@
         <v>1000000000</v>
       </c>
       <c r="I46" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J46" s="23">
         <v>500000000</v>
       </c>
-      <c r="K46" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L46" s="33">
+      <c r="K46" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="36">
         <v>100</v>
       </c>
       <c r="M46" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N46" s="34">
-        <v>0</v>
-      </c>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="34"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
+      <c r="N46" s="37">
+        <v>0</v>
+      </c>
+      <c r="O46" s="37"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
+      <c r="S46" s="38"/>
+      <c r="T46" s="38"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A47" s="29">
+      <c r="A47" s="32">
         <v>1035011</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="33">
         <v>103501</v>
       </c>
-      <c r="C47" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="32">
+      <c r="C47" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="35">
         <v>103501001</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="34">
         <v>1</v>
       </c>
       <c r="F47" s="21" t="s">
@@ -3995,44 +4022,44 @@
         <v>10000000</v>
       </c>
       <c r="I47" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J47" s="23">
         <v>5000000</v>
       </c>
-      <c r="K47" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L47" s="33">
+      <c r="K47" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="36">
         <v>100</v>
       </c>
       <c r="M47" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N47" s="34">
-        <v>0</v>
-      </c>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
+      <c r="N47" s="37">
+        <v>0</v>
+      </c>
+      <c r="O47" s="37"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A48" s="29">
+      <c r="A48" s="32">
         <v>1035012</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="33">
         <v>103501</v>
       </c>
-      <c r="C48" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="32">
+      <c r="C48" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="35">
         <v>103501001</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="34">
         <v>2</v>
       </c>
       <c r="F48" s="21" t="s">
@@ -4045,44 +4072,44 @@
         <v>100000000</v>
       </c>
       <c r="I48" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J48" s="23">
         <v>50000000</v>
       </c>
-      <c r="K48" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L48" s="33">
+      <c r="K48" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="36">
         <v>100</v>
       </c>
       <c r="M48" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N48" s="34">
-        <v>0</v>
-      </c>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
+      <c r="N48" s="37">
+        <v>0</v>
+      </c>
+      <c r="O48" s="37"/>
+      <c r="P48" s="37"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="37"/>
+      <c r="S48" s="38"/>
+      <c r="T48" s="38"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A49" s="29">
+      <c r="A49" s="32">
         <v>1035013</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="33">
         <v>103501</v>
       </c>
-      <c r="C49" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="32">
+      <c r="C49" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="35">
         <v>103501001</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="34">
         <v>3</v>
       </c>
       <c r="F49" s="21" t="s">
@@ -4095,44 +4122,44 @@
         <v>1000000000</v>
       </c>
       <c r="I49" s="25">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="J49" s="23">
         <v>500000000</v>
       </c>
-      <c r="K49" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L49" s="33">
+      <c r="K49" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="36">
         <v>100</v>
       </c>
       <c r="M49" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N49" s="34">
-        <v>0</v>
-      </c>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="35"/>
-      <c r="T49" s="35"/>
+      <c r="N49" s="37">
+        <v>0</v>
+      </c>
+      <c r="O49" s="37"/>
+      <c r="P49" s="37"/>
+      <c r="Q49" s="37"/>
+      <c r="R49" s="37"/>
+      <c r="S49" s="38"/>
+      <c r="T49" s="38"/>
     </row>
     <row r="50" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="36">
+      <c r="A50" s="39">
         <v>10010010</v>
       </c>
-      <c r="B50" s="37">
+      <c r="B50" s="40">
         <v>100100</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="39">
+      <c r="D50" s="42">
         <v>100100026</v>
       </c>
-      <c r="E50" s="40">
+      <c r="E50" s="43">
         <v>10</v>
       </c>
       <c r="F50" s="21" t="s">
@@ -4141,48 +4168,48 @@
       <c r="G50" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="41">
-        <v>0</v>
-      </c>
-      <c r="I50" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J50" s="43">
-        <v>0</v>
-      </c>
-      <c r="K50" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="44">
-        <v>0</v>
-      </c>
-      <c r="M50" s="42" t="s">
+      <c r="H50" s="44">
+        <v>0</v>
+      </c>
+      <c r="I50" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J50" s="46">
+        <v>0</v>
+      </c>
+      <c r="K50" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="47">
+        <v>0</v>
+      </c>
+      <c r="M50" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="N50" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="42"/>
-      <c r="T50" s="42"/>
+      <c r="N50" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="O50" s="49"/>
+      <c r="P50" s="49"/>
+      <c r="Q50" s="49"/>
+      <c r="R50" s="49"/>
+      <c r="S50" s="45"/>
+      <c r="T50" s="45"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A51" s="36">
+      <c r="A51" s="39">
         <v>10010011</v>
       </c>
-      <c r="B51" s="37">
+      <c r="B51" s="40">
         <v>100100</v>
       </c>
-      <c r="C51" s="38" t="s">
+      <c r="C51" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="42">
         <v>100100026</v>
       </c>
-      <c r="E51" s="40">
+      <c r="E51" s="43">
         <v>11</v>
       </c>
       <c r="F51" s="21" t="s">
@@ -4191,48 +4218,48 @@
       <c r="G51" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H51" s="41">
-        <v>0</v>
-      </c>
-      <c r="I51" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J51" s="43">
-        <v>0</v>
-      </c>
-      <c r="K51" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L51" s="44">
-        <v>0</v>
-      </c>
-      <c r="M51" s="42" t="s">
+      <c r="H51" s="44">
+        <v>0</v>
+      </c>
+      <c r="I51" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J51" s="46">
+        <v>0</v>
+      </c>
+      <c r="K51" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="47">
+        <v>0</v>
+      </c>
+      <c r="M51" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="N51" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-      <c r="S51" s="42"/>
-      <c r="T51" s="42"/>
+      <c r="N51" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="O51" s="49"/>
+      <c r="P51" s="49"/>
+      <c r="Q51" s="49"/>
+      <c r="R51" s="49"/>
+      <c r="S51" s="45"/>
+      <c r="T51" s="45"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A52" s="36">
+      <c r="A52" s="39">
         <v>10010012</v>
       </c>
-      <c r="B52" s="37">
+      <c r="B52" s="40">
         <v>100100</v>
       </c>
-      <c r="C52" s="38" t="s">
+      <c r="C52" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="39">
+      <c r="D52" s="42">
         <v>100100026</v>
       </c>
-      <c r="E52" s="40">
+      <c r="E52" s="43">
         <v>12</v>
       </c>
       <c r="F52" s="21" t="s">
@@ -4241,48 +4268,48 @@
       <c r="G52" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="47">
-        <v>0</v>
-      </c>
-      <c r="I52" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J52" s="43">
-        <v>0</v>
-      </c>
-      <c r="K52" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L52" s="44">
-        <v>0</v>
-      </c>
-      <c r="M52" s="42" t="s">
+      <c r="H52" s="50">
+        <v>0</v>
+      </c>
+      <c r="I52" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J52" s="46">
+        <v>0</v>
+      </c>
+      <c r="K52" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="47">
+        <v>0</v>
+      </c>
+      <c r="M52" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="N52" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="46"/>
-      <c r="S52" s="42"/>
-      <c r="T52" s="42"/>
+      <c r="N52" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="O52" s="49"/>
+      <c r="P52" s="49"/>
+      <c r="Q52" s="49"/>
+      <c r="R52" s="49"/>
+      <c r="S52" s="45"/>
+      <c r="T52" s="45"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A53" s="36">
+      <c r="A53" s="39">
         <v>10030010</v>
       </c>
-      <c r="B53" s="37">
+      <c r="B53" s="40">
         <v>100300</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D53" s="39">
+      <c r="D53" s="42">
         <v>100100026</v>
       </c>
-      <c r="E53" s="40">
+      <c r="E53" s="43">
         <v>10</v>
       </c>
       <c r="F53" s="21" t="s">
@@ -4291,48 +4318,48 @@
       <c r="G53" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="41">
-        <v>0</v>
-      </c>
-      <c r="I53" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J53" s="43">
-        <v>0</v>
-      </c>
-      <c r="K53" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L53" s="48">
-        <v>0</v>
-      </c>
-      <c r="M53" s="42" t="s">
+      <c r="H53" s="44">
+        <v>0</v>
+      </c>
+      <c r="I53" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J53" s="46">
+        <v>0</v>
+      </c>
+      <c r="K53" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="51">
+        <v>0</v>
+      </c>
+      <c r="M53" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="N53" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="O53" s="46"/>
-      <c r="P53" s="46"/>
-      <c r="Q53" s="46"/>
-      <c r="R53" s="46"/>
-      <c r="S53" s="42"/>
-      <c r="T53" s="42"/>
+      <c r="N53" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="O53" s="49"/>
+      <c r="P53" s="49"/>
+      <c r="Q53" s="49"/>
+      <c r="R53" s="49"/>
+      <c r="S53" s="45"/>
+      <c r="T53" s="45"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A54" s="36">
+      <c r="A54" s="39">
         <v>10030011</v>
       </c>
-      <c r="B54" s="37">
+      <c r="B54" s="40">
         <v>100300</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="39">
+      <c r="D54" s="42">
         <v>100100026</v>
       </c>
-      <c r="E54" s="40">
+      <c r="E54" s="43">
         <v>11</v>
       </c>
       <c r="F54" s="21" t="s">
@@ -4341,48 +4368,48 @@
       <c r="G54" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H54" s="41">
-        <v>0</v>
-      </c>
-      <c r="I54" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J54" s="43">
-        <v>0</v>
-      </c>
-      <c r="K54" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L54" s="48">
-        <v>0</v>
-      </c>
-      <c r="M54" s="42" t="s">
+      <c r="H54" s="44">
+        <v>0</v>
+      </c>
+      <c r="I54" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J54" s="46">
+        <v>0</v>
+      </c>
+      <c r="K54" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="51">
+        <v>0</v>
+      </c>
+      <c r="M54" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="N54" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="O54" s="46"/>
-      <c r="P54" s="46"/>
-      <c r="Q54" s="46"/>
-      <c r="R54" s="46"/>
-      <c r="S54" s="42"/>
-      <c r="T54" s="42"/>
+      <c r="N54" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="O54" s="49"/>
+      <c r="P54" s="49"/>
+      <c r="Q54" s="49"/>
+      <c r="R54" s="49"/>
+      <c r="S54" s="45"/>
+      <c r="T54" s="45"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A55" s="36">
+      <c r="A55" s="39">
         <v>10030012</v>
       </c>
-      <c r="B55" s="37">
+      <c r="B55" s="40">
         <v>100300</v>
       </c>
-      <c r="C55" s="38" t="s">
+      <c r="C55" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="39">
+      <c r="D55" s="42">
         <v>100100026</v>
       </c>
-      <c r="E55" s="40">
+      <c r="E55" s="43">
         <v>12</v>
       </c>
       <c r="F55" s="21" t="s">
@@ -4391,48 +4418,48 @@
       <c r="G55" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="H55" s="47">
-        <v>0</v>
-      </c>
-      <c r="I55" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J55" s="43">
-        <v>0</v>
-      </c>
-      <c r="K55" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L55" s="48">
-        <v>0</v>
-      </c>
-      <c r="M55" s="42" t="s">
+      <c r="H55" s="50">
+        <v>0</v>
+      </c>
+      <c r="I55" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J55" s="46">
+        <v>0</v>
+      </c>
+      <c r="K55" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="51">
+        <v>0</v>
+      </c>
+      <c r="M55" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="N55" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O55" s="46"/>
-      <c r="P55" s="46"/>
-      <c r="Q55" s="46"/>
-      <c r="R55" s="46"/>
-      <c r="S55" s="42"/>
-      <c r="T55" s="42"/>
+      <c r="N55" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="O55" s="49"/>
+      <c r="P55" s="49"/>
+      <c r="Q55" s="49"/>
+      <c r="R55" s="49"/>
+      <c r="S55" s="45"/>
+      <c r="T55" s="45"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A56" s="36">
+      <c r="A56" s="39">
         <v>10070010</v>
       </c>
-      <c r="B56" s="37">
+      <c r="B56" s="40">
         <v>100700</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="D56" s="39">
+      <c r="D56" s="42">
         <v>100100026</v>
       </c>
-      <c r="E56" s="40">
+      <c r="E56" s="43">
         <v>10</v>
       </c>
       <c r="F56" s="21" t="s">
@@ -4441,48 +4468,48 @@
       <c r="G56" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H56" s="41">
-        <v>0</v>
-      </c>
-      <c r="I56" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J56" s="43">
-        <v>0</v>
-      </c>
-      <c r="K56" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="44">
-        <v>0</v>
-      </c>
-      <c r="M56" s="42" t="s">
+      <c r="H56" s="44">
+        <v>0</v>
+      </c>
+      <c r="I56" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J56" s="46">
+        <v>0</v>
+      </c>
+      <c r="K56" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="47">
+        <v>0</v>
+      </c>
+      <c r="M56" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="N56" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46"/>
-      <c r="R56" s="46"/>
-      <c r="S56" s="42"/>
-      <c r="T56" s="42"/>
+      <c r="N56" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="O56" s="49"/>
+      <c r="P56" s="49"/>
+      <c r="Q56" s="49"/>
+      <c r="R56" s="49"/>
+      <c r="S56" s="45"/>
+      <c r="T56" s="45"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A57" s="36">
+      <c r="A57" s="39">
         <v>10070011</v>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="40">
         <v>100700</v>
       </c>
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="39">
+      <c r="D57" s="42">
         <v>100100026</v>
       </c>
-      <c r="E57" s="40">
+      <c r="E57" s="43">
         <v>11</v>
       </c>
       <c r="F57" s="21" t="s">
@@ -4491,48 +4518,48 @@
       <c r="G57" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="41">
-        <v>0</v>
-      </c>
-      <c r="I57" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J57" s="43">
-        <v>0</v>
-      </c>
-      <c r="K57" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L57" s="44">
-        <v>0</v>
-      </c>
-      <c r="M57" s="42" t="s">
+      <c r="H57" s="44">
+        <v>0</v>
+      </c>
+      <c r="I57" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J57" s="46">
+        <v>0</v>
+      </c>
+      <c r="K57" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="47">
+        <v>0</v>
+      </c>
+      <c r="M57" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="N57" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="46"/>
-      <c r="R57" s="46"/>
-      <c r="S57" s="42"/>
-      <c r="T57" s="42"/>
+      <c r="N57" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="O57" s="49"/>
+      <c r="P57" s="49"/>
+      <c r="Q57" s="49"/>
+      <c r="R57" s="49"/>
+      <c r="S57" s="45"/>
+      <c r="T57" s="45"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A58" s="36">
+      <c r="A58" s="39">
         <v>10070012</v>
       </c>
-      <c r="B58" s="37">
+      <c r="B58" s="40">
         <v>100700</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="42">
         <v>100100026</v>
       </c>
-      <c r="E58" s="40">
+      <c r="E58" s="43">
         <v>12</v>
       </c>
       <c r="F58" s="21" t="s">
@@ -4541,48 +4568,48 @@
       <c r="G58" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H58" s="47">
-        <v>0</v>
-      </c>
-      <c r="I58" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J58" s="43">
-        <v>0</v>
-      </c>
-      <c r="K58" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L58" s="44">
-        <v>0</v>
-      </c>
-      <c r="M58" s="42" t="s">
+      <c r="H58" s="50">
+        <v>0</v>
+      </c>
+      <c r="I58" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J58" s="46">
+        <v>0</v>
+      </c>
+      <c r="K58" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="47">
+        <v>0</v>
+      </c>
+      <c r="M58" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="N58" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O58" s="46"/>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="46"/>
-      <c r="S58" s="42"/>
-      <c r="T58" s="42"/>
+      <c r="N58" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="O58" s="49"/>
+      <c r="P58" s="49"/>
+      <c r="Q58" s="49"/>
+      <c r="R58" s="49"/>
+      <c r="S58" s="45"/>
+      <c r="T58" s="45"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A59" s="36">
+      <c r="A59" s="39">
         <v>10120010</v>
       </c>
-      <c r="B59" s="49">
+      <c r="B59" s="52">
         <v>101200</v>
       </c>
-      <c r="C59" s="40" t="s">
+      <c r="C59" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="53">
         <v>101200026</v>
       </c>
-      <c r="E59" s="40">
+      <c r="E59" s="43">
         <v>10</v>
       </c>
       <c r="F59" s="21" t="s">
@@ -4591,48 +4618,48 @@
       <c r="G59" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H59" s="41">
-        <v>0</v>
-      </c>
-      <c r="I59" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J59" s="43">
-        <v>0</v>
-      </c>
-      <c r="K59" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L59" s="48">
-        <v>0</v>
-      </c>
-      <c r="M59" s="43" t="s">
+      <c r="H59" s="44">
+        <v>0</v>
+      </c>
+      <c r="I59" s="46">
+        <v>9500</v>
+      </c>
+      <c r="J59" s="46">
+        <v>0</v>
+      </c>
+      <c r="K59" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="51">
+        <v>0</v>
+      </c>
+      <c r="M59" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="N59" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="O59" s="45"/>
-      <c r="P59" s="45"/>
-      <c r="Q59" s="45"/>
-      <c r="R59" s="45"/>
-      <c r="S59" s="43"/>
-      <c r="T59" s="43"/>
+      <c r="N59" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="O59" s="48"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="48"/>
+      <c r="R59" s="48"/>
+      <c r="S59" s="46"/>
+      <c r="T59" s="46"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A60" s="36">
+      <c r="A60" s="39">
         <v>10120011</v>
       </c>
-      <c r="B60" s="49">
+      <c r="B60" s="52">
         <v>101200</v>
       </c>
-      <c r="C60" s="40" t="s">
+      <c r="C60" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="53">
         <v>101200026</v>
       </c>
-      <c r="E60" s="40">
+      <c r="E60" s="43">
         <v>11</v>
       </c>
       <c r="F60" s="21" t="s">
@@ -4641,48 +4668,48 @@
       <c r="G60" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="41">
-        <v>0</v>
-      </c>
-      <c r="I60" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J60" s="43">
-        <v>0</v>
-      </c>
-      <c r="K60" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="48">
-        <v>0</v>
-      </c>
-      <c r="M60" s="43" t="s">
+      <c r="H60" s="44">
+        <v>0</v>
+      </c>
+      <c r="I60" s="46">
+        <v>9500</v>
+      </c>
+      <c r="J60" s="46">
+        <v>0</v>
+      </c>
+      <c r="K60" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="51">
+        <v>0</v>
+      </c>
+      <c r="M60" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="N60" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="O60" s="45"/>
-      <c r="P60" s="45"/>
-      <c r="Q60" s="45"/>
-      <c r="R60" s="45"/>
-      <c r="S60" s="43"/>
-      <c r="T60" s="43"/>
+      <c r="N60" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="O60" s="48"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="48"/>
+      <c r="R60" s="48"/>
+      <c r="S60" s="46"/>
+      <c r="T60" s="46"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A61" s="36">
+      <c r="A61" s="39">
         <v>10120012</v>
       </c>
-      <c r="B61" s="49">
+      <c r="B61" s="52">
         <v>101200</v>
       </c>
-      <c r="C61" s="40" t="s">
+      <c r="C61" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="53">
         <v>101200026</v>
       </c>
-      <c r="E61" s="40">
+      <c r="E61" s="43">
         <v>12</v>
       </c>
       <c r="F61" s="21" t="s">
@@ -4691,48 +4718,48 @@
       <c r="G61" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H61" s="47">
-        <v>0</v>
-      </c>
-      <c r="I61" s="43">
-        <v>9500</v>
-      </c>
-      <c r="J61" s="43">
-        <v>0</v>
-      </c>
-      <c r="K61" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="48">
-        <v>0</v>
-      </c>
-      <c r="M61" s="43" t="s">
+      <c r="H61" s="50">
+        <v>0</v>
+      </c>
+      <c r="I61" s="46">
+        <v>9500</v>
+      </c>
+      <c r="J61" s="46">
+        <v>0</v>
+      </c>
+      <c r="K61" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="51">
+        <v>0</v>
+      </c>
+      <c r="M61" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="N61" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="O61" s="45"/>
-      <c r="P61" s="45"/>
-      <c r="Q61" s="45"/>
-      <c r="R61" s="45"/>
-      <c r="S61" s="43"/>
-      <c r="T61" s="43"/>
+      <c r="N61" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="O61" s="48"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="48"/>
+      <c r="R61" s="48"/>
+      <c r="S61" s="46"/>
+      <c r="T61" s="46"/>
     </row>
     <row r="62" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="36">
+      <c r="A62" s="39">
         <v>10140010</v>
       </c>
-      <c r="B62" s="37">
+      <c r="B62" s="40">
         <v>101400</v>
       </c>
-      <c r="C62" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="39">
+      <c r="C62" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="42">
         <v>100100026</v>
       </c>
-      <c r="E62" s="40">
+      <c r="E62" s="43">
         <v>10</v>
       </c>
       <c r="F62" s="21" t="s">
@@ -4741,48 +4768,48 @@
       <c r="G62" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H62" s="41">
-        <v>0</v>
-      </c>
-      <c r="I62" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J62" s="43">
-        <v>0</v>
-      </c>
-      <c r="K62" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L62" s="44">
-        <v>0</v>
-      </c>
-      <c r="M62" s="42" t="s">
+      <c r="H62" s="44">
+        <v>0</v>
+      </c>
+      <c r="I62" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J62" s="46">
+        <v>0</v>
+      </c>
+      <c r="K62" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="47">
+        <v>0</v>
+      </c>
+      <c r="M62" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="N62" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="O62" s="46"/>
-      <c r="P62" s="46"/>
-      <c r="Q62" s="46"/>
-      <c r="R62" s="46"/>
-      <c r="S62" s="42"/>
-      <c r="T62" s="42"/>
+      <c r="N62" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="O62" s="49"/>
+      <c r="P62" s="49"/>
+      <c r="Q62" s="49"/>
+      <c r="R62" s="49"/>
+      <c r="S62" s="45"/>
+      <c r="T62" s="45"/>
     </row>
     <row r="63" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A63" s="36">
+      <c r="A63" s="39">
         <v>10140011</v>
       </c>
-      <c r="B63" s="37">
+      <c r="B63" s="40">
         <v>101400</v>
       </c>
-      <c r="C63" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="39">
+      <c r="C63" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="42">
         <v>100100026</v>
       </c>
-      <c r="E63" s="40">
+      <c r="E63" s="43">
         <v>11</v>
       </c>
       <c r="F63" s="21" t="s">
@@ -4791,48 +4818,48 @@
       <c r="G63" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="41">
-        <v>0</v>
-      </c>
-      <c r="I63" s="42">
-        <v>9500</v>
-      </c>
-      <c r="J63" s="43">
-        <v>0</v>
-      </c>
-      <c r="K63" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="44">
-        <v>0</v>
-      </c>
-      <c r="M63" s="42" t="s">
+      <c r="H63" s="44">
+        <v>0</v>
+      </c>
+      <c r="I63" s="45">
+        <v>9500</v>
+      </c>
+      <c r="J63" s="46">
+        <v>0</v>
+      </c>
+      <c r="K63" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="47">
+        <v>0</v>
+      </c>
+      <c r="M63" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="N63" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46